--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6612" uniqueCount="2298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="2417">
   <si>
     <t>日期</t>
   </si>
@@ -6790,6 +6790,363 @@
     <t>研究68/技能62/学历100/行业100/企业95</t>
   </si>
   <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>深圳市瑞沃德生命科技股份有限公司</t>
+  </si>
+  <si>
+    <t>2027校招-耗材工程师（金属方向）</t>
+  </si>
+  <si>
+    <t>负责金属类耗材竞品分析、技术趋势跟踪与评估报告输出；制定耗材开发方案、实验验证及全流程落地，与供应商进行技术对接与工艺沟通。要求金属、材料科学与工程等相关专业，硕士及以上，熟悉材料性能与加工工艺，有耗材研发/材料选型经验者优先。深圳，2027届校招。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/FhN8VnaBE9AF9gDXK1ANPi/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配79分【校园招聘】|值得考虑|医疗器械耗材研发校招岗，材料学方向契合，硕士可投</t>
+  </si>
+  <si>
+    <t>研究72/技能66/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>2027届校园招聘，明确材料科学与工程硕士，深圳为优先城市；耗材研发涉及金属/高分子材料选型与工艺，与候选人材料学背景和支架构件开发经验可迁移；瑞沃德为生命科学仪器与耗材领域成长型企业。</t>
+  </si>
+  <si>
+    <t>突出材料学（金属材料、镍钛合金）与材料性能测试经历；将血管支架课题中的材料选型和工艺验证经验转述为'耗材开发方案制定与实验验证'；补充供应商技术对接、竞品分析相关项目描述。</t>
+  </si>
+  <si>
+    <t>2027校招-耗材工程师（高分子方向）</t>
+  </si>
+  <si>
+    <t>负责高分子类耗材竞品分析、技术趋势跟踪与评估报告输出；制定耗材开发方案、实验验证及全流程落地，与供应商进行技术对接与工艺沟通。要求高分子材料、材料科学与工程等相关专业，硕士及以上，熟悉高分子材料性能、加工工艺及应用场景。深圳，2027届校招。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/5EPZNGFrb1aoTRuYBbhpAD/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配79分【校园招聘】|值得考虑|医疗器械高分子耗材研发校招岗，材料学契合，深圳优先城市</t>
+  </si>
+  <si>
+    <t>研究72/技能68/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>2027届校招，高分子材料硕士方向与候选人材料学基础契合；耗材开发、材料选型、供应商技术对接等工作内容与生物医用材料课题高度可迁移；深圳为优先城市。</t>
+  </si>
+  <si>
+    <t>强化高分子/可降解材料知识与加工工艺描述；将支架课题中的材料表征（SEM/DSC等）与工艺开发经验量化呈现；补充团队协作与供应商沟通经历。</t>
+  </si>
+  <si>
+    <t>广东云曌医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>技术研究员/助理（生物材料）</t>
+  </si>
+  <si>
+    <t>从事生物材料或生物工程相关研究，要求化学、材料科学、生物、生物工程、合成化学、合成生物学或医药等相关专业，硕士及以上；具有生物材料研究或工作经历；有水凝胶/纳米材料制备、医用敷料或纳米药物递送研究经历者优先。</t>
+  </si>
+  <si>
+    <t>广东</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/TQoggxTmNbkdf2hSGKkW5F/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配81分【科研岗】|强烈推荐|生物医用材料研究岗，材料学+生物相容性技能重合，硕士可投</t>
+  </si>
+  <si>
+    <t>研究70/技能76/学历100/行业100/企业84</t>
+  </si>
+  <si>
+    <t>生物材料研究方向与候选人材料学、生物相容性评价背景高度契合；硕士学历门槛匹配；广东为候选可接受区域，云曌医疗为生物材料科创企业，成长空间好。</t>
+  </si>
+  <si>
+    <t>突出生物医用材料、生物相容性评价（细胞毒性/血液相容性/ISO 10993）相关实验技能；补充材料制备与表征（水凝胶/纳米材料）项目；列出与医用敷料/植入材料相关的课题成果。</t>
+  </si>
+  <si>
+    <t>安徽通灵仿生科技有限公司</t>
+  </si>
+  <si>
+    <t>介入耗材工艺工程师</t>
+  </si>
+  <si>
+    <t>负责介入导管、球囊等耗材成型工艺开发与优化；研究医用高分子材料特性、无菌工艺及量产制程；参与耗材研发、验证、转产及相关技术文档编写。</t>
+  </si>
+  <si>
+    <t>安徽</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/XkAzpfoNHnsAWFsGyd5ify/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配82分【社招】|强烈推荐|介入导管/球囊工艺研发岗，方向直接相关，材料学契合</t>
+  </si>
+  <si>
+    <t>研究84/技能70/学历90/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位明确面向介入导管、球囊等介入耗材的成型工艺开发，与候选人血管介入器械方向直接对口；涉及医用高分子材料特性与工艺验证，与支架/导管材料学背景高度重合；通灵仿生专注仿生介入器械，方向契合度高。</t>
+  </si>
+  <si>
+    <t>以血管支架/导管课题为主线，突出高分子材料成型工艺、结构设计与验证经验；补充无菌工艺、转产及技术文档编写相关内容；量化工艺参数优化与性能测试结果。</t>
+  </si>
+  <si>
+    <t>深圳市益心达医学新技术有限公司</t>
+  </si>
+  <si>
+    <t>研发工程师（介入医学导管）</t>
+  </si>
+  <si>
+    <t>负责介入医学导管及附件的研发与设计，含结构设计、材料选型、工艺开发与样品试制验证；由留美医学博士后创办，专注介入导管研发生产。要求本科及以上，生物医学工程/材料/机械等相关专业。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/weixin?type=2&amp;query=%E7%9B%8A%E5%BF%83%E8%BE%BE%20%E4%BB%8B%E5%85%A5%E5%8C%BB%E5%AD%A6%E5%AF%BC%E7%AE%A1%20%E7%A0%94%E5%8F%91%E5%B7%A5%E7%A8%8B%E5%B8%88</t>
+  </si>
+  <si>
+    <t>智能匹配80分【社招】|强烈推荐|介入医学导管研发岗，深圳，方向+材料技能相关</t>
+  </si>
+  <si>
+    <t>研究82/技能68/学历90/行业100/企业78</t>
+  </si>
+  <si>
+    <t>岗位聚焦介入医学导管及附件研发，与候选人血管介入器械方向高度相关；深圳为优先城市；涉及结构设计、材料选型与工艺开发，可直接迁移支架/导管研发经验。</t>
+  </si>
+  <si>
+    <t>突出导管/介入器械结构设计与材料选型经验；补充样品试制、测试验证及生物相容性评价内容；强调动手能力与医疗器械开发流程熟悉度。</t>
+  </si>
+  <si>
+    <t>山东威高集团（精准外科诊疗产业集团）</t>
+  </si>
+  <si>
+    <t>可降解材料研发工程师(J15186)</t>
+  </si>
+  <si>
+    <t>负责高分子材料的产品设计和研发，开展新材料开发与应用；利用现有技术手段进行材料分析和性能评估；配合生产部门监控高分子材料生产过程；撰写新产品技术文档和报告。要求高分子材料或相关专业硕士及以上，具备较强分析测试、材料制备、数据处理能力。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/QCUYtTX5Ui1WH5c6p3KoCZ/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|可降解材料研发岗，与可降解支架方向高度相关，硕士可投</t>
+  </si>
+  <si>
+    <t>研究84/技能76/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>可降解材料研发与候选人血管支架（可降解方向）研究高度契合；高分子材料设计、分析测试、材料制备能力与背景匹配；威高为上市公司/细分龙头，平台稳定，硕士学历门槛匹配。</t>
+  </si>
+  <si>
+    <t>突出可降解高分子材料（PLA/PDO等）相关研究，如涉及则详述降解性能、力学性能表征；补充材料分析测试（DSC/GPC/SEM）与数据处理能力；强调支架材料设计经验。</t>
+  </si>
+  <si>
+    <t>长春圣博玛生物材料有限公司</t>
+  </si>
+  <si>
+    <t>医疗器械材料研发项目主管（校园招聘）</t>
+  </si>
+  <si>
+    <t>从事医疗器械用材料研发，涉及高分子物理化学/材料/生物医学工程等方向；负责材料研发项目管理与推进。2025秋季校招，招聘60人，硕士/博士/博士后均可，长春。</t>
+  </si>
+  <si>
+    <t>http://career.cic.tsinghua.edu.cn/xsglxt/f/jyxt/anony/showZwxx?zpxxid=514529468</t>
+  </si>
+  <si>
+    <t>智能匹配83分【校园招聘】|强烈推荐|医疗器械材料研发校招岗，材料学+生物相容性重合，硕士可投</t>
+  </si>
+  <si>
+    <t>研究76/技能76/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>圣博玛为可降解生物材料（医用聚乳酸）细分龙头，与候选人可降解支架材料方向高度契合；校招面向材料/生物医学工程硕士；涉及医疗器械用材料研发，技能重合度高。</t>
+  </si>
+  <si>
+    <t>突出可降解生物材料与生物相容性评价经验；将支架课题包装为'医疗器械用材料研发'项目；补充项目管理与跨团队协作经历，匹配项目主管定位。</t>
+  </si>
+  <si>
+    <t>斯坦德检测集团股份有限公司</t>
+  </si>
+  <si>
+    <t>介入手术专家（临床前介入实验）</t>
+  </si>
+  <si>
+    <t>负责医疗器械临床前介入手术操作：使用DSA完成大动物（猪/犬/羊）冠脉造影、支架植入、球囊扩张、血管封堵等；术中生命体征监护与抢救；DSA影像质量控制；术后解剖取材、支架内皮化与管腔丢失率分析；撰写符合NMPA/FDA申报要求的实验报告。要求本科及以上、相关专业，有心内科介入或介入科临床手术经验、执业医师资格证。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/3inuwLDCmtLAqiHvem43ez/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配79分【社招】|值得考虑|临床前介入动物实验岗，涉及支架植入与血管介入，方向相关</t>
+  </si>
+  <si>
+    <t>研究82/技能60/学历100/行业95/企业82</t>
+  </si>
+  <si>
+    <t>岗位核心为冠脉支架植入、球囊扩张等介入手术操作及支架内皮化评价，与候选人血管支架与动物实验背景高度相关；斯坦德为第三方检测机构，涉及医疗器械注册申报，行业匹配。需注意该岗要求执业医师资格与临床手术经验，投递前需评估资质差距。</t>
+  </si>
+  <si>
+    <t>突出动物实验（猪/兔模型）、植入实验、组织切片与影像学随访经验；补充支架植入/球囊扩张相关操作技能；如无执业医师证，需明确说明动物实验操作能力并主动沟通岗位资质要求。</t>
+  </si>
+  <si>
+    <t>中红普林医疗用品股份有限公司</t>
+  </si>
+  <si>
+    <t>协助输注类医疗器械新产品设计、研发、绘图及技术资料编制校对；配合完成产品结构优化、工艺开发、测试迭代及数据报告整理；协助新产品试制、样品整改，参与检测分析方法搭建与验证；梳理研发创新点，撰写专利等知识产权材料；整理注册资料。要求本科及以上，机械/材料/生物医学工程等相关专业。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/3CoBPgMf2BMjZLTdRRYRdS/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配75分【校园招聘】|值得考虑|医疗器械研发岗，结构设计+材料技能相关，本科及以上硕士可投</t>
+  </si>
+  <si>
+    <t>研究70/技能62/学历90/行业100/企业80</t>
+  </si>
+  <si>
+    <t>医疗器械新产品设计研发岗，涉及结构优化、工艺开发、测试验证与注册资料，与候选人支架设计、材料学背景可迁移；硕士投递有优势。</t>
+  </si>
+  <si>
+    <t>突出结构设计（SolidWorks/有限元）与工艺开发经验；补充专利/技术文档撰写能力；强调医疗器械注册与检测分析相关认知。</t>
+  </si>
+  <si>
+    <t>南京巨鲨显示科技有限公司</t>
+  </si>
+  <si>
+    <t>从事医疗器械产品研发，招聘本科及以上、硕士学历岗位；南京巨鲨为医用显示与影像设备企业，岗位涉及产品设计与开发。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/6XDNB31WjPJm1hQisizssf/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配74分【校园招聘】|值得考虑|医疗器械研发岗，硕士可投，南京，行业匹配</t>
+  </si>
+  <si>
+    <t>研究70/技能55/学历100/行业100/企业80</t>
+  </si>
+  <si>
+    <t>医疗器械研发岗位，行业完全匹配；南京临近苏州/上海，硕士学历门槛匹配；巨鲨为医用显示细分企业，可作为医疗器械研发方向备选。</t>
+  </si>
+  <si>
+    <t>突出医疗器械研发通用技能（结构设计、材料选型、验证测试）；如岗位偏显示/影像电子，需补充相关项目或强调快速学习能力。</t>
+  </si>
+  <si>
+    <t>杭州凯龙医疗器械有限公司</t>
+  </si>
+  <si>
+    <t>研究X射线产生、与物质相互作用及成像应用；热阴极、电子发射稳定性与寿命研究、阴极结构设计，聚焦钨丝及阴极材料性能与工艺优化、仿真及新型材料研发与相变研究。要求掌握CST/OPERA3D/COMSOL等仿真工具。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/CtJZve8i3wGVPUWrCdUfye/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配72分【校园招聘】|值得考虑|医疗器械研发岗，涉及材料与仿真，硕士可投</t>
+  </si>
+  <si>
+    <t>研究68/技能56/学历90/行业100/企业78</t>
+  </si>
+  <si>
+    <t>医疗器械（X射线球管）研发岗，涉及阴极材料与结构设计，与材料学及有限元仿真背景部分契合；杭州区位交通便利，可作为备选。</t>
+  </si>
+  <si>
+    <t>突出材料性能与工艺研究经验；补充COMSOL/有限元仿真项目；弱化血管支架方向、强调材料与仿真通用能力。</t>
+  </si>
+  <si>
+    <t>康璞基石（陕西）健康生命科技有限公司</t>
+  </si>
+  <si>
+    <t>医疗器械研发SD助理</t>
+  </si>
+  <si>
+    <t>协助医疗器械研发相关工作，硕士及以上学历；岗位为医疗器械研发支持/协理类，涉及产品开发相关事务。</t>
+  </si>
+  <si>
+    <t>陕西</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/RrjnDFEudXTrTnKwVRvCpy/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配74分【校园招聘】|值得考虑|医疗器械研发助理岗，硕士可投，行业匹配</t>
+  </si>
+  <si>
+    <t>研究70/技能56/学历100/行业100/企业78</t>
+  </si>
+  <si>
+    <t>医疗器械研发支持岗，硕士学历门槛匹配；可作为医疗器械研发方向的入门备选岗位。</t>
+  </si>
+  <si>
+    <t>突出医疗器械研发流程与文档能力；强调材料学、生物相容性基础；补充项目协调与数据整理经验。</t>
+  </si>
+  <si>
+    <t>默华医疗科技（湖南）有限公司</t>
+  </si>
+  <si>
+    <t>研发项目助理（医疗器械）</t>
+  </si>
+  <si>
+    <t>协助公司引进国外先进电外科技术与产品创意；深入临床调研，进行产品立项可行性分析、定义开发需求；协助管理引进项目，与第三方衔接与全程把控；协助新产品开发项目，制定开发计划并推动执行，驱动项目从概念到样机落地。要求本科及以上。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/VMd1Av4p5c8qWmrh2tHSTv/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配72分【校园招聘】|值得考虑|医疗器械研发项目助理岗，硕士可投，行业匹配</t>
+  </si>
+  <si>
+    <t>医疗器械新产品开发项目岗，涉及产品立项、需求定义与样机落地，与研发方向契合；硕士投递有优势，可作为项目管理方向备选。</t>
+  </si>
+  <si>
+    <t>突出产品开发全流程认知与项目管理能力；补充临床调研、竞品分析、需求定义相关经历；强调跨部门沟通与推动能力。</t>
+  </si>
+  <si>
+    <t>中石油（上海）新材料研究院有限公司</t>
+  </si>
+  <si>
+    <t>前沿材料研发工程师（先进生物材料方向）</t>
+  </si>
+  <si>
+    <t>从事前沿材料研发，含先进生物材料、新能源材料、电子信息材料等方向。要求博士及以上（部分岗位不限），材料科学与工程相关专业。上海。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/7sbWH2VXXgvG7GqTkAPhsg/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配67分【科研岗】|值得考虑|生物材料研发岗，上海，材料学相关，但偏好博士</t>
+  </si>
+  <si>
+    <t>研究70/技能58/学历50/行业80/企业95</t>
+  </si>
+  <si>
+    <t>先进生物材料研发方向与材料学背景相关，上海为优先城市，央企新材料研究院平台优越。但多数岗位要求博士，硕士投递需关注'不限'岗位并评估竞争压力。</t>
+  </si>
+  <si>
+    <t>突出生物材料与材料表征能力；如有论文/专利成果重点展示；明确标注硕士可投岗位，强调研发潜力。</t>
+  </si>
+  <si>
+    <t>深圳市新产业生物医学工程股份有限公司</t>
+  </si>
+  <si>
+    <t>机械研发工程师【2027届】</t>
+  </si>
+  <si>
+    <t>负责新产品整机结构和零部件的详细设计开发；对产品进行CAE仿真分析并输出技术报告；参与产品优化改进；标准零部件选型；新品样机试制、调试及技术/工艺文件编制。要求机械/材料等相关专业硕士及以上。深圳，2027届校招。</t>
+  </si>
+  <si>
+    <t>https://job.ncss.cn/student/jobs/RS17f8NA5bLeyMRFgoUp43/detail.html</t>
+  </si>
+  <si>
+    <t>智能匹配70分【校园招聘】|值得考虑|医疗器械设备研发校招岗，深圳，硕士，结构设计技能可迁移</t>
+  </si>
+  <si>
+    <t>研究55/技能58/学历100/行业90/企业90</t>
+  </si>
+  <si>
+    <t>2027届校招明确硕士，深圳为优先城市；新产业为上市公司（体外诊断龙头），平台稳定；岗位涉及结构设计与CAE仿真，与支架设计技能可迁移，可作为医疗器械研发备选。</t>
+  </si>
+  <si>
+    <t>突出SolidWorks/CAE仿真与结构设计能力；弱化血管支架方向，强调通用机械设计与材料学基础；补充样机试制与工艺文件编制经验。</t>
+  </si>
+  <si>
     <t>投递日期</t>
   </si>
   <si>
@@ -6841,7 +7198,7 @@
     <t>平均匹配度</t>
   </si>
   <si>
-    <t>8.5</t>
+    <t>8.4</t>
   </si>
   <si>
     <t>最高匹配度</t>
@@ -7342,7 +7699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L304"/>
+  <dimension ref="A1:L319"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -18908,6 +19265,576 @@
       </c>
       <c r="L304" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B305" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C305" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D305" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E305" t="s">
+        <v>747</v>
+      </c>
+      <c r="F305" t="s">
+        <v>2262</v>
+      </c>
+      <c r="G305">
+        <v>8</v>
+      </c>
+      <c r="H305" t="s">
+        <v>2263</v>
+      </c>
+      <c r="I305">
+        <v>79</v>
+      </c>
+      <c r="J305" t="s">
+        <v>2264</v>
+      </c>
+      <c r="K305" t="s">
+        <v>2265</v>
+      </c>
+      <c r="L305" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B306" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C306" t="s">
+        <v>2267</v>
+      </c>
+      <c r="D306" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E306" t="s">
+        <v>747</v>
+      </c>
+      <c r="F306" t="s">
+        <v>2269</v>
+      </c>
+      <c r="G306">
+        <v>8</v>
+      </c>
+      <c r="H306" t="s">
+        <v>2270</v>
+      </c>
+      <c r="I306">
+        <v>79</v>
+      </c>
+      <c r="J306" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K306" t="s">
+        <v>2272</v>
+      </c>
+      <c r="L306" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B307" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C307" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D307" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E307" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F307" t="s">
+        <v>2278</v>
+      </c>
+      <c r="G307">
+        <v>8</v>
+      </c>
+      <c r="H307" t="s">
+        <v>2279</v>
+      </c>
+      <c r="I307">
+        <v>81</v>
+      </c>
+      <c r="J307" t="s">
+        <v>2280</v>
+      </c>
+      <c r="K307" t="s">
+        <v>2281</v>
+      </c>
+      <c r="L307" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B308" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C308" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D308" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E308" t="s">
+        <v>2286</v>
+      </c>
+      <c r="F308" t="s">
+        <v>2287</v>
+      </c>
+      <c r="G308">
+        <v>8</v>
+      </c>
+      <c r="H308" t="s">
+        <v>2288</v>
+      </c>
+      <c r="I308">
+        <v>82</v>
+      </c>
+      <c r="J308" t="s">
+        <v>2289</v>
+      </c>
+      <c r="K308" t="s">
+        <v>2290</v>
+      </c>
+      <c r="L308" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B309" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C309" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D309" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E309" t="s">
+        <v>747</v>
+      </c>
+      <c r="F309" t="s">
+        <v>2295</v>
+      </c>
+      <c r="G309">
+        <v>8</v>
+      </c>
+      <c r="H309" t="s">
+        <v>2296</v>
+      </c>
+      <c r="I309">
+        <v>80</v>
+      </c>
+      <c r="J309" t="s">
+        <v>2297</v>
+      </c>
+      <c r="K309" t="s">
+        <v>2298</v>
+      </c>
+      <c r="L309" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B310" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C310" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D310" t="s">
+        <v>2302</v>
+      </c>
+      <c r="E310" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F310" t="s">
+        <v>2303</v>
+      </c>
+      <c r="G310">
+        <v>9</v>
+      </c>
+      <c r="H310" t="s">
+        <v>2304</v>
+      </c>
+      <c r="I310">
+        <v>86</v>
+      </c>
+      <c r="J310" t="s">
+        <v>2305</v>
+      </c>
+      <c r="K310" t="s">
+        <v>2306</v>
+      </c>
+      <c r="L310" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B311" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C311" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D311" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E311" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F311" t="s">
+        <v>2311</v>
+      </c>
+      <c r="G311">
+        <v>8</v>
+      </c>
+      <c r="H311" t="s">
+        <v>2312</v>
+      </c>
+      <c r="I311">
+        <v>83</v>
+      </c>
+      <c r="J311" t="s">
+        <v>2313</v>
+      </c>
+      <c r="K311" t="s">
+        <v>2314</v>
+      </c>
+      <c r="L311" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B312" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C312" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D312" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E312" t="s">
+        <v>138</v>
+      </c>
+      <c r="F312" t="s">
+        <v>2319</v>
+      </c>
+      <c r="G312">
+        <v>8</v>
+      </c>
+      <c r="H312" t="s">
+        <v>2320</v>
+      </c>
+      <c r="I312">
+        <v>79</v>
+      </c>
+      <c r="J312" t="s">
+        <v>2321</v>
+      </c>
+      <c r="K312" t="s">
+        <v>2322</v>
+      </c>
+      <c r="L312" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B313" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C313" t="s">
+        <v>122</v>
+      </c>
+      <c r="D313" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E313" t="s">
+        <v>230</v>
+      </c>
+      <c r="F313" t="s">
+        <v>2326</v>
+      </c>
+      <c r="G313">
+        <v>8</v>
+      </c>
+      <c r="H313" t="s">
+        <v>2327</v>
+      </c>
+      <c r="I313">
+        <v>75</v>
+      </c>
+      <c r="J313" t="s">
+        <v>2328</v>
+      </c>
+      <c r="K313" t="s">
+        <v>2329</v>
+      </c>
+      <c r="L313" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B314" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C314" t="s">
+        <v>122</v>
+      </c>
+      <c r="D314" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E314" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F314" t="s">
+        <v>2333</v>
+      </c>
+      <c r="G314">
+        <v>7</v>
+      </c>
+      <c r="H314" t="s">
+        <v>2334</v>
+      </c>
+      <c r="I314">
+        <v>74</v>
+      </c>
+      <c r="J314" t="s">
+        <v>2335</v>
+      </c>
+      <c r="K314" t="s">
+        <v>2336</v>
+      </c>
+      <c r="L314" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B315" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C315" t="s">
+        <v>89</v>
+      </c>
+      <c r="D315" t="s">
+        <v>2339</v>
+      </c>
+      <c r="E315" t="s">
+        <v>535</v>
+      </c>
+      <c r="F315" t="s">
+        <v>2340</v>
+      </c>
+      <c r="G315">
+        <v>7</v>
+      </c>
+      <c r="H315" t="s">
+        <v>2341</v>
+      </c>
+      <c r="I315">
+        <v>72</v>
+      </c>
+      <c r="J315" t="s">
+        <v>2342</v>
+      </c>
+      <c r="K315" t="s">
+        <v>2343</v>
+      </c>
+      <c r="L315" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B316" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C316" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D316" t="s">
+        <v>2347</v>
+      </c>
+      <c r="E316" t="s">
+        <v>2348</v>
+      </c>
+      <c r="F316" t="s">
+        <v>2349</v>
+      </c>
+      <c r="G316">
+        <v>7</v>
+      </c>
+      <c r="H316" t="s">
+        <v>2350</v>
+      </c>
+      <c r="I316">
+        <v>74</v>
+      </c>
+      <c r="J316" t="s">
+        <v>2351</v>
+      </c>
+      <c r="K316" t="s">
+        <v>2352</v>
+      </c>
+      <c r="L316" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B317" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C317" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D317" t="s">
+        <v>2356</v>
+      </c>
+      <c r="E317" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F317" t="s">
+        <v>2357</v>
+      </c>
+      <c r="G317">
+        <v>7</v>
+      </c>
+      <c r="H317" t="s">
+        <v>2358</v>
+      </c>
+      <c r="I317">
+        <v>72</v>
+      </c>
+      <c r="J317" t="s">
+        <v>2342</v>
+      </c>
+      <c r="K317" t="s">
+        <v>2359</v>
+      </c>
+      <c r="L317" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B318" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C318" t="s">
+        <v>2362</v>
+      </c>
+      <c r="D318" t="s">
+        <v>2363</v>
+      </c>
+      <c r="E318" t="s">
+        <v>16</v>
+      </c>
+      <c r="F318" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G318">
+        <v>7</v>
+      </c>
+      <c r="H318" t="s">
+        <v>2365</v>
+      </c>
+      <c r="I318">
+        <v>67</v>
+      </c>
+      <c r="J318" t="s">
+        <v>2366</v>
+      </c>
+      <c r="K318" t="s">
+        <v>2367</v>
+      </c>
+      <c r="L318" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B319" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C319" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D319" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E319" t="s">
+        <v>747</v>
+      </c>
+      <c r="F319" t="s">
+        <v>2372</v>
+      </c>
+      <c r="G319">
+        <v>7</v>
+      </c>
+      <c r="H319" t="s">
+        <v>2373</v>
+      </c>
+      <c r="I319">
+        <v>70</v>
+      </c>
+      <c r="J319" t="s">
+        <v>2374</v>
+      </c>
+      <c r="K319" t="s">
+        <v>2375</v>
+      </c>
+      <c r="L319" t="s">
+        <v>2376</v>
       </c>
     </row>
   </sheetData>
@@ -18941,7 +19868,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2258</v>
+        <v>2377</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -18950,16 +19877,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2259</v>
+        <v>2378</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2260</v>
+        <v>2379</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2261</v>
+        <v>2380</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2262</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -18973,13 +19900,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2263</v>
+        <v>2382</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2264</v>
+        <v>2383</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>2265</v>
+        <v>2384</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -19022,7 +19949,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>2270</v>
+        <v>2389</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -19032,31 +19959,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>2271</v>
+        <v>2390</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2272</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2273</v>
+        <v>2392</v>
       </c>
       <c r="B4">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2274</v>
+        <v>2393</v>
       </c>
       <c r="B5" t="s">
-        <v>2275</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2276</v>
+        <v>2395</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -19064,7 +19991,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2277</v>
+        <v>2396</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -19072,39 +19999,39 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2278</v>
+        <v>2397</v>
       </c>
       <c r="B8">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2279</v>
+        <v>2398</v>
       </c>
       <c r="B9">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2280</v>
+        <v>2399</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2281</v>
+        <v>2400</v>
       </c>
       <c r="B11" t="s">
-        <v>2098</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>2282</v>
+        <v>2401</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -19114,15 +20041,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>2283</v>
+        <v>2402</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>2284</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2285</v>
+        <v>2404</v>
       </c>
       <c r="B16" s="5">
         <v>8</v>
@@ -19130,31 +20057,31 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2286</v>
+        <v>2405</v>
       </c>
       <c r="B17" s="5">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2287</v>
+        <v>2406</v>
       </c>
       <c r="B18" s="5">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2288</v>
+        <v>2407</v>
       </c>
       <c r="B19" s="5">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2289</v>
+        <v>2408</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -19162,7 +20089,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2290</v>
+        <v>2409</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -19170,7 +20097,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2291</v>
+        <v>2410</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -19178,7 +20105,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2292</v>
+        <v>2411</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -19186,7 +20113,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2293</v>
+        <v>2412</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -19194,7 +20121,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2294</v>
+        <v>2413</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -19202,7 +20129,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>2295</v>
+        <v>2414</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -19214,7 +20141,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>2296</v>
+        <v>2415</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -19232,7 +20159,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>2297</v>
+        <v>2416</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -22909,25 +23836,25 @@
         <v>142</v>
       </c>
       <c r="B171" t="s">
-        <v>1200</v>
+        <v>2258</v>
       </c>
       <c r="C171" t="s">
-        <v>1201</v>
+        <v>2300</v>
       </c>
       <c r="D171" t="s">
-        <v>1202</v>
+        <v>2301</v>
       </c>
       <c r="E171" t="s">
-        <v>1204</v>
+        <v>1644</v>
       </c>
       <c r="F171" t="s">
-        <v>1205</v>
+        <v>2303</v>
       </c>
       <c r="G171">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H171" t="s">
-        <v>1206</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -22935,25 +23862,25 @@
         <v>143</v>
       </c>
       <c r="B172" t="s">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="C172" t="s">
-        <v>72</v>
+        <v>1201</v>
       </c>
       <c r="D172" t="s">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="E172" t="s">
-        <v>75</v>
+        <v>1204</v>
       </c>
       <c r="F172" t="s">
-        <v>76</v>
+        <v>1205</v>
       </c>
       <c r="G172">
         <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>77</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -22964,22 +23891,22 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D173" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E173" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F173" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G173">
         <v>8</v>
       </c>
       <c r="H173" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -22990,22 +23917,22 @@
         <v>12</v>
       </c>
       <c r="C174" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D174" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E174" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F174" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G174">
         <v>8</v>
       </c>
       <c r="H174" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -23016,22 +23943,22 @@
         <v>12</v>
       </c>
       <c r="C175" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D175" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E175" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F175" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G175">
         <v>8</v>
       </c>
       <c r="H175" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -23042,22 +23969,22 @@
         <v>12</v>
       </c>
       <c r="C176" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D176" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E176" t="s">
         <v>16</v>
       </c>
       <c r="F176" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G176">
         <v>8</v>
       </c>
       <c r="H176" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -23068,22 +23995,22 @@
         <v>12</v>
       </c>
       <c r="C177" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D177" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E177" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F177" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G177">
         <v>8</v>
       </c>
       <c r="H177" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -23094,22 +24021,22 @@
         <v>12</v>
       </c>
       <c r="C178" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="D178" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="E178" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="F178" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G178">
         <v>8</v>
       </c>
       <c r="H178" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -23120,22 +24047,22 @@
         <v>12</v>
       </c>
       <c r="C179" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D179" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E179" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="F179" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G179">
         <v>8</v>
       </c>
       <c r="H179" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -23143,25 +24070,25 @@
         <v>151</v>
       </c>
       <c r="B180" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C180" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="D180" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="E180" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F180" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="G180">
         <v>8</v>
       </c>
       <c r="H180" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -23172,22 +24099,22 @@
         <v>159</v>
       </c>
       <c r="C181" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D181" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E181" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="F181" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G181">
         <v>8</v>
       </c>
       <c r="H181" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -23198,22 +24125,22 @@
         <v>159</v>
       </c>
       <c r="C182" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D182" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E182" t="s">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="F182" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="G182">
         <v>8</v>
       </c>
       <c r="H182" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -23224,22 +24151,22 @@
         <v>159</v>
       </c>
       <c r="C183" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D183" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="E183" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F183" t="s">
-        <v>76</v>
+        <v>231</v>
       </c>
       <c r="G183">
         <v>8</v>
       </c>
       <c r="H183" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -23250,22 +24177,22 @@
         <v>159</v>
       </c>
       <c r="C184" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D184" t="s">
-        <v>241</v>
+        <v>73</v>
       </c>
       <c r="E184" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F184" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="G184">
         <v>8</v>
       </c>
       <c r="H184" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -23276,22 +24203,22 @@
         <v>159</v>
       </c>
       <c r="C185" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D185" t="s">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="E185" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F185" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="G185">
         <v>8</v>
       </c>
       <c r="H185" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -23302,22 +24229,22 @@
         <v>159</v>
       </c>
       <c r="C186" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D186" t="s">
-        <v>249</v>
+        <v>154</v>
       </c>
       <c r="E186" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F186" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="G186">
         <v>8</v>
       </c>
       <c r="H186" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -23328,22 +24255,22 @@
         <v>159</v>
       </c>
       <c r="C187" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D187" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E187" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
       <c r="F187" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G187">
         <v>8</v>
       </c>
       <c r="H187" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -23354,22 +24281,22 @@
         <v>159</v>
       </c>
       <c r="C188" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D188" t="s">
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="E188" t="s">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="F188" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G188">
         <v>8</v>
       </c>
       <c r="H188" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -23380,22 +24307,22 @@
         <v>159</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>267</v>
+        <v>122</v>
       </c>
       <c r="E189" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="F189" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
       <c r="G189">
         <v>8</v>
       </c>
       <c r="H189" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -23406,22 +24333,22 @@
         <v>159</v>
       </c>
       <c r="C190" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E190" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="F190" t="s">
-        <v>281</v>
+        <v>58</v>
       </c>
       <c r="G190">
         <v>8</v>
       </c>
       <c r="H190" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -23429,25 +24356,25 @@
         <v>162</v>
       </c>
       <c r="B191" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C191" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="D191" t="s">
-        <v>316</v>
+        <v>278</v>
       </c>
       <c r="E191" t="s">
-        <v>318</v>
+        <v>280</v>
       </c>
       <c r="F191" t="s">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="G191">
         <v>8</v>
       </c>
       <c r="H191" t="s">
-        <v>320</v>
+        <v>282</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -23458,22 +24385,22 @@
         <v>284</v>
       </c>
       <c r="C192" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="D192" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="E192" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="F192" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="G192">
         <v>8</v>
       </c>
       <c r="H192" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -23484,22 +24411,22 @@
         <v>284</v>
       </c>
       <c r="C193" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="D193" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="E193" t="s">
-        <v>98</v>
+        <v>341</v>
       </c>
       <c r="F193" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="G193">
         <v>8</v>
       </c>
       <c r="H193" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -23510,22 +24437,22 @@
         <v>284</v>
       </c>
       <c r="C194" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D194" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="E194" t="s">
-        <v>356</v>
+        <v>98</v>
       </c>
       <c r="F194" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="G194">
         <v>8</v>
       </c>
       <c r="H194" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -23536,22 +24463,22 @@
         <v>284</v>
       </c>
       <c r="C195" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="D195" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="E195" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="F195" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="G195">
         <v>8</v>
       </c>
       <c r="H195" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -23562,22 +24489,22 @@
         <v>284</v>
       </c>
       <c r="C196" t="s">
-        <v>144</v>
+        <v>377</v>
       </c>
       <c r="D196" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="E196" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="F196" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="G196">
         <v>8</v>
       </c>
       <c r="H196" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -23585,25 +24512,25 @@
         <v>168</v>
       </c>
       <c r="B197" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C197" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="D197" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E197" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F197" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="G197">
         <v>8</v>
       </c>
       <c r="H197" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -23614,22 +24541,22 @@
         <v>402</v>
       </c>
       <c r="C198" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D198" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E198" t="s">
         <v>66</v>
       </c>
       <c r="F198" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="G198">
         <v>8</v>
       </c>
       <c r="H198" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -23640,22 +24567,22 @@
         <v>402</v>
       </c>
       <c r="C199" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D199" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E199" t="s">
         <v>66</v>
       </c>
       <c r="F199" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G199">
         <v>8</v>
       </c>
       <c r="H199" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -23666,22 +24593,22 @@
         <v>402</v>
       </c>
       <c r="C200" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D200" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E200" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F200" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="G200">
         <v>8</v>
       </c>
       <c r="H200" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -23689,25 +24616,25 @@
         <v>172</v>
       </c>
       <c r="B201" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C201" t="s">
-        <v>483</v>
+        <v>430</v>
       </c>
       <c r="D201" t="s">
-        <v>122</v>
+        <v>431</v>
       </c>
       <c r="E201" t="s">
-        <v>485</v>
+        <v>16</v>
       </c>
       <c r="F201" t="s">
-        <v>486</v>
+        <v>433</v>
       </c>
       <c r="G201">
         <v>8</v>
       </c>
       <c r="H201" t="s">
-        <v>487</v>
+        <v>434</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -23718,22 +24645,22 @@
         <v>473</v>
       </c>
       <c r="C202" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="D202" t="s">
-        <v>492</v>
+        <v>122</v>
       </c>
       <c r="E202" t="s">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="F202" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="G202">
         <v>8</v>
       </c>
       <c r="H202" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -23744,22 +24671,22 @@
         <v>473</v>
       </c>
       <c r="C203" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="D203" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="E203" t="s">
-        <v>502</v>
+        <v>75</v>
       </c>
       <c r="F203" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="G203">
         <v>8</v>
       </c>
       <c r="H203" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -23770,22 +24697,22 @@
         <v>473</v>
       </c>
       <c r="C204" t="s">
-        <v>532</v>
+        <v>499</v>
       </c>
       <c r="D204" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="E204" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="F204" t="s">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="G204">
         <v>8</v>
       </c>
       <c r="H204" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -23796,22 +24723,22 @@
         <v>473</v>
       </c>
       <c r="C205" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="D205" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="E205" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="F205" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="G205">
         <v>8</v>
       </c>
       <c r="H205" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -23819,25 +24746,25 @@
         <v>177</v>
       </c>
       <c r="B206" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C206" t="s">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="D206" t="s">
-        <v>579</v>
+        <v>551</v>
       </c>
       <c r="E206" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F206" t="s">
-        <v>581</v>
+        <v>553</v>
       </c>
       <c r="G206">
         <v>8</v>
       </c>
       <c r="H206" t="s">
-        <v>582</v>
+        <v>554</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -23848,22 +24775,22 @@
         <v>556</v>
       </c>
       <c r="C207" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D207" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E207" t="s">
-        <v>587</v>
+        <v>66</v>
       </c>
       <c r="F207" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="G207">
         <v>8</v>
       </c>
       <c r="H207" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -23871,25 +24798,25 @@
         <v>179</v>
       </c>
       <c r="B208" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C208" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="D208" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="E208" t="s">
-        <v>75</v>
+        <v>587</v>
       </c>
       <c r="F208" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="G208">
         <v>8</v>
       </c>
       <c r="H208" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -23900,22 +24827,22 @@
         <v>591</v>
       </c>
       <c r="C209" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D209" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="E209" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F209" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="G209">
         <v>8</v>
       </c>
       <c r="H209" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -23926,22 +24853,22 @@
         <v>591</v>
       </c>
       <c r="C210" t="s">
-        <v>557</v>
+        <v>616</v>
       </c>
       <c r="D210" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="E210" t="s">
         <v>16</v>
       </c>
       <c r="F210" t="s">
-        <v>468</v>
+        <v>618</v>
       </c>
       <c r="G210">
         <v>8</v>
       </c>
       <c r="H210" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -23952,22 +24879,22 @@
         <v>591</v>
       </c>
       <c r="C211" t="s">
-        <v>643</v>
+        <v>557</v>
       </c>
       <c r="D211" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="E211" t="s">
         <v>16</v>
       </c>
       <c r="F211" t="s">
-        <v>618</v>
+        <v>468</v>
       </c>
       <c r="G211">
         <v>8</v>
       </c>
       <c r="H211" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -23978,22 +24905,22 @@
         <v>591</v>
       </c>
       <c r="C212" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="D212" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="E212" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F212" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="G212">
         <v>8</v>
       </c>
       <c r="H212" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -24004,22 +24931,22 @@
         <v>591</v>
       </c>
       <c r="C213" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="D213" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="E213" t="s">
-        <v>661</v>
+        <v>66</v>
       </c>
       <c r="F213" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="G213">
         <v>8</v>
       </c>
       <c r="H213" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -24030,22 +24957,22 @@
         <v>591</v>
       </c>
       <c r="C214" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="D214" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="E214" t="s">
-        <v>75</v>
+        <v>661</v>
       </c>
       <c r="F214" t="s">
-        <v>604</v>
+        <v>662</v>
       </c>
       <c r="G214">
         <v>8</v>
       </c>
       <c r="H214" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -24056,22 +24983,22 @@
         <v>591</v>
       </c>
       <c r="C215" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="D215" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="E215" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F215" t="s">
-        <v>676</v>
+        <v>604</v>
       </c>
       <c r="G215">
         <v>8</v>
       </c>
       <c r="H215" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -24079,25 +25006,25 @@
         <v>187</v>
       </c>
       <c r="B216" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C216" t="s">
-        <v>714</v>
+        <v>673</v>
       </c>
       <c r="D216" t="s">
-        <v>715</v>
+        <v>674</v>
       </c>
       <c r="E216" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F216" t="s">
-        <v>604</v>
+        <v>676</v>
       </c>
       <c r="G216">
         <v>8</v>
       </c>
       <c r="H216" t="s">
-        <v>717</v>
+        <v>677</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -24108,22 +25035,22 @@
         <v>697</v>
       </c>
       <c r="C217" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="D217" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="E217" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F217" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="G217">
         <v>8</v>
       </c>
       <c r="H217" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -24134,22 +25061,22 @@
         <v>697</v>
       </c>
       <c r="C218" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="D218" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="E218" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="F218" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="G218">
         <v>8</v>
       </c>
       <c r="H218" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -24160,22 +25087,22 @@
         <v>697</v>
       </c>
       <c r="C219" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="D219" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="E219" t="s">
-        <v>739</v>
+        <v>535</v>
       </c>
       <c r="F219" t="s">
-        <v>604</v>
+        <v>732</v>
       </c>
       <c r="G219">
         <v>8</v>
       </c>
       <c r="H219" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
@@ -24186,22 +25113,22 @@
         <v>697</v>
       </c>
       <c r="C220" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="D220" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="E220" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="F220" t="s">
-        <v>748</v>
+        <v>604</v>
       </c>
       <c r="G220">
         <v>8</v>
       </c>
       <c r="H220" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -24212,22 +25139,22 @@
         <v>697</v>
       </c>
       <c r="C221" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="D221" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="E221" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="F221" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="G221">
         <v>8</v>
       </c>
       <c r="H221" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -24238,22 +25165,22 @@
         <v>697</v>
       </c>
       <c r="C222" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="D222" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="E222" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="F222" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="G222">
         <v>8</v>
       </c>
       <c r="H222" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -24261,25 +25188,25 @@
         <v>194</v>
       </c>
       <c r="B223" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C223" t="s">
-        <v>791</v>
+        <v>760</v>
       </c>
       <c r="D223" t="s">
-        <v>610</v>
+        <v>761</v>
       </c>
       <c r="E223" t="s">
-        <v>793</v>
+        <v>763</v>
       </c>
       <c r="F223" t="s">
-        <v>794</v>
+        <v>764</v>
       </c>
       <c r="G223">
         <v>8</v>
       </c>
       <c r="H223" t="s">
-        <v>795</v>
+        <v>765</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
@@ -24290,22 +25217,22 @@
         <v>773</v>
       </c>
       <c r="C224" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="D224" t="s">
-        <v>808</v>
+        <v>610</v>
       </c>
       <c r="E224" t="s">
-        <v>810</v>
+        <v>793</v>
       </c>
       <c r="F224" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="G224">
         <v>8</v>
       </c>
       <c r="H224" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
@@ -24316,22 +25243,22 @@
         <v>773</v>
       </c>
       <c r="C225" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="D225" t="s">
-        <v>110</v>
+        <v>808</v>
       </c>
       <c r="E225" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="F225" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="G225">
         <v>8</v>
       </c>
       <c r="H225" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -24339,25 +25266,25 @@
         <v>197</v>
       </c>
       <c r="B226" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C226" t="s">
-        <v>888</v>
+        <v>816</v>
       </c>
       <c r="D226" t="s">
-        <v>889</v>
+        <v>110</v>
       </c>
       <c r="E226" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F226" t="s">
-        <v>891</v>
+        <v>818</v>
       </c>
       <c r="G226">
         <v>8</v>
       </c>
       <c r="H226" t="s">
-        <v>892</v>
+        <v>819</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
@@ -24368,22 +25295,22 @@
         <v>845</v>
       </c>
       <c r="C227" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="D227" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="E227" t="s">
         <v>25</v>
       </c>
       <c r="F227" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G227">
         <v>8</v>
       </c>
       <c r="H227" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -24394,22 +25321,22 @@
         <v>845</v>
       </c>
       <c r="C228" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="D228" t="s">
-        <v>585</v>
+        <v>897</v>
       </c>
       <c r="E228" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F228" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="G228">
         <v>8</v>
       </c>
       <c r="H228" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -24420,22 +25347,22 @@
         <v>845</v>
       </c>
       <c r="C229" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="D229" t="s">
         <v>585</v>
       </c>
       <c r="E229" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F229" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="G229">
         <v>8</v>
       </c>
       <c r="H229" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>
@@ -24451,7 +25378,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K232"/>
+  <dimension ref="A1:K237"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -24468,10 +25395,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>2266</v>
+        <v>2385</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2267</v>
+        <v>2386</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -24498,12 +25425,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>2268</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -24538,7 +25465,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -24573,7 +25500,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -24608,7 +25535,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -24643,7 +25570,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -24678,7 +25605,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -24713,7 +25640,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B8">
         <v>95</v>
@@ -24748,7 +25675,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B9">
         <v>95</v>
@@ -24783,7 +25710,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B10">
         <v>94</v>
@@ -24818,7 +25745,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B11">
         <v>94</v>
@@ -24853,7 +25780,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B12">
         <v>93</v>
@@ -24888,7 +25815,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B13">
         <v>93</v>
@@ -24923,7 +25850,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B14">
         <v>93</v>
@@ -24958,7 +25885,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B15">
         <v>93</v>
@@ -24993,7 +25920,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B16">
         <v>92</v>
@@ -25028,7 +25955,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B17">
         <v>92</v>
@@ -25063,7 +25990,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B18">
         <v>92</v>
@@ -25098,7 +26025,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B19">
         <v>92</v>
@@ -25133,7 +26060,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B20">
         <v>91</v>
@@ -25168,7 +26095,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B21">
         <v>91</v>
@@ -25203,7 +26130,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B22">
         <v>91</v>
@@ -25238,7 +26165,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B23">
         <v>91</v>
@@ -25273,7 +26200,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B24">
         <v>91</v>
@@ -25308,7 +26235,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B25">
         <v>91</v>
@@ -25343,7 +26270,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B26">
         <v>91</v>
@@ -25378,7 +26305,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B27">
         <v>91</v>
@@ -25413,7 +26340,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B28">
         <v>90</v>
@@ -25448,7 +26375,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B29">
         <v>90</v>
@@ -25483,7 +26410,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B30">
         <v>90</v>
@@ -25518,7 +26445,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B31">
         <v>90</v>
@@ -25553,7 +26480,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B32">
         <v>90</v>
@@ -25588,7 +26515,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B33">
         <v>90</v>
@@ -25623,7 +26550,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B34">
         <v>90</v>
@@ -25658,7 +26585,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B35">
         <v>90</v>
@@ -25693,7 +26620,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B36">
         <v>90</v>
@@ -25728,7 +26655,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B37">
         <v>90</v>
@@ -25763,7 +26690,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B38">
         <v>90</v>
@@ -25798,7 +26725,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B39">
         <v>90</v>
@@ -25833,7 +26760,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B40">
         <v>90</v>
@@ -25868,7 +26795,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B41">
         <v>89</v>
@@ -25903,7 +26830,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B42">
         <v>89</v>
@@ -25938,7 +26865,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B43">
         <v>89</v>
@@ -25973,7 +26900,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B44">
         <v>89</v>
@@ -26008,7 +26935,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B45">
         <v>89</v>
@@ -26043,7 +26970,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B46">
         <v>89</v>
@@ -26078,7 +27005,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B47">
         <v>89</v>
@@ -26113,7 +27040,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B48">
         <v>89</v>
@@ -26148,7 +27075,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B49">
         <v>89</v>
@@ -26183,7 +27110,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B50">
         <v>89</v>
@@ -26218,7 +27145,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B51">
         <v>89</v>
@@ -26253,7 +27180,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B52">
         <v>89</v>
@@ -26288,7 +27215,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B53">
         <v>89</v>
@@ -26323,7 +27250,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B54">
         <v>89</v>
@@ -26358,7 +27285,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B55">
         <v>89</v>
@@ -26393,7 +27320,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B56">
         <v>89</v>
@@ -26428,7 +27355,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B57">
         <v>89</v>
@@ -26463,7 +27390,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B58">
         <v>89</v>
@@ -26498,7 +27425,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B59">
         <v>89</v>
@@ -26533,7 +27460,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B60">
         <v>89</v>
@@ -26568,7 +27495,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B61">
         <v>89</v>
@@ -26603,7 +27530,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B62">
         <v>89</v>
@@ -26638,7 +27565,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B63">
         <v>89</v>
@@ -26673,7 +27600,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B64">
         <v>88</v>
@@ -26708,7 +27635,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B65">
         <v>88</v>
@@ -26743,7 +27670,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B66">
         <v>88</v>
@@ -26778,7 +27705,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B67">
         <v>88</v>
@@ -26813,7 +27740,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B68">
         <v>88</v>
@@ -26848,7 +27775,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B69">
         <v>88</v>
@@ -26883,7 +27810,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B70">
         <v>88</v>
@@ -26918,7 +27845,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B71">
         <v>88</v>
@@ -26953,7 +27880,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B72">
         <v>88</v>
@@ -26988,7 +27915,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B73">
         <v>88</v>
@@ -27023,7 +27950,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B74">
         <v>88</v>
@@ -27058,7 +27985,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B75">
         <v>88</v>
@@ -27093,7 +28020,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B76">
         <v>88</v>
@@ -27128,7 +28055,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B77">
         <v>88</v>
@@ -27163,7 +28090,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B78">
         <v>88</v>
@@ -27198,7 +28125,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B79">
         <v>88</v>
@@ -27233,7 +28160,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B80">
         <v>88</v>
@@ -27268,7 +28195,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B81">
         <v>87</v>
@@ -27303,7 +28230,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B82">
         <v>87</v>
@@ -27338,7 +28265,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B83">
         <v>87</v>
@@ -27373,7 +28300,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B84">
         <v>87</v>
@@ -27408,7 +28335,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B85">
         <v>87</v>
@@ -27443,7 +28370,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B86">
         <v>87</v>
@@ -27478,7 +28405,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B87">
         <v>87</v>
@@ -27513,7 +28440,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B88">
         <v>87</v>
@@ -27548,7 +28475,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B89">
         <v>87</v>
@@ -27583,7 +28510,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B90">
         <v>87</v>
@@ -27618,7 +28545,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B91">
         <v>87</v>
@@ -27653,7 +28580,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B92">
         <v>87</v>
@@ -27688,7 +28615,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B93">
         <v>87</v>
@@ -27723,7 +28650,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B94">
         <v>87</v>
@@ -27758,7 +28685,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B95">
         <v>87</v>
@@ -27793,7 +28720,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B96">
         <v>87</v>
@@ -27828,7 +28755,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B97">
         <v>87</v>
@@ -27863,7 +28790,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B98">
         <v>86</v>
@@ -27898,7 +28825,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B99">
         <v>86</v>
@@ -27933,7 +28860,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B100">
         <v>86</v>
@@ -27968,7 +28895,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B101">
         <v>86</v>
@@ -28003,7 +28930,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B102">
         <v>86</v>
@@ -28038,7 +28965,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B103">
         <v>86</v>
@@ -28073,7 +29000,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B104">
         <v>86</v>
@@ -28108,7 +29035,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B105">
         <v>86</v>
@@ -28143,7 +29070,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B106">
         <v>86</v>
@@ -28178,7 +29105,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B107">
         <v>86</v>
@@ -28213,7 +29140,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B108">
         <v>86</v>
@@ -28248,7 +29175,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B109">
         <v>86</v>
@@ -28283,7 +29210,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B110">
         <v>86</v>
@@ -28318,7 +29245,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B111">
         <v>86</v>
@@ -28353,7 +29280,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B112">
         <v>86</v>
@@ -28388,7 +29315,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B113">
         <v>86</v>
@@ -28423,7 +29350,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B114">
         <v>86</v>
@@ -28458,7 +29385,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B115">
         <v>86</v>
@@ -28493,7 +29420,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B116">
         <v>86</v>
@@ -28528,7 +29455,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B117">
         <v>86</v>
@@ -28563,7 +29490,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B118">
         <v>86</v>
@@ -28598,7 +29525,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B119">
         <v>86</v>
@@ -28633,7 +29560,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B120">
         <v>86</v>
@@ -28668,7 +29595,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B121">
         <v>86</v>
@@ -28703,42 +29630,42 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B122">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C122" t="s">
-        <v>12</v>
+        <v>2258</v>
       </c>
       <c r="D122" t="s">
-        <v>55</v>
+        <v>2300</v>
       </c>
       <c r="E122" t="s">
-        <v>56</v>
+        <v>2301</v>
       </c>
       <c r="F122" t="s">
-        <v>16</v>
+        <v>1644</v>
       </c>
       <c r="G122" t="s">
-        <v>58</v>
+        <v>2303</v>
       </c>
       <c r="H122" t="s">
-        <v>60</v>
+        <v>2305</v>
       </c>
       <c r="I122" t="s">
-        <v>61</v>
+        <v>2306</v>
       </c>
       <c r="J122" t="s">
-        <v>62</v>
+        <v>2307</v>
       </c>
       <c r="K122" t="s">
-        <v>57</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B123">
         <v>85</v>
@@ -28747,173 +29674,173 @@
         <v>12</v>
       </c>
       <c r="D123" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="E123" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F123" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G123" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H123" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="I123" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="J123" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="K123" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B124">
         <v>85</v>
       </c>
       <c r="C124" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D124" t="s">
-        <v>300</v>
+        <v>128</v>
       </c>
       <c r="E124" t="s">
-        <v>308</v>
+        <v>89</v>
       </c>
       <c r="F124" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G124" t="s">
-        <v>310</v>
+        <v>131</v>
       </c>
       <c r="H124" t="s">
-        <v>312</v>
+        <v>133</v>
       </c>
       <c r="I124" t="s">
-        <v>313</v>
+        <v>134</v>
       </c>
       <c r="J124" t="s">
-        <v>314</v>
+        <v>135</v>
       </c>
       <c r="K124" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B125">
         <v>85</v>
       </c>
       <c r="C125" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D125" t="s">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="E125" t="s">
-        <v>403</v>
+        <v>308</v>
       </c>
       <c r="F125" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G125" t="s">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="H125" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="I125" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="J125" t="s">
-        <v>409</v>
+        <v>314</v>
       </c>
       <c r="K125" t="s">
-        <v>404</v>
+        <v>309</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B126">
         <v>85</v>
       </c>
       <c r="C126" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D126" t="s">
-        <v>474</v>
+        <v>55</v>
       </c>
       <c r="E126" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="F126" t="s">
-        <v>477</v>
+        <v>16</v>
       </c>
       <c r="G126" t="s">
-        <v>478</v>
+        <v>405</v>
       </c>
       <c r="H126" t="s">
-        <v>480</v>
+        <v>407</v>
       </c>
       <c r="I126" t="s">
-        <v>481</v>
+        <v>408</v>
       </c>
       <c r="J126" t="s">
-        <v>482</v>
+        <v>409</v>
       </c>
       <c r="K126" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B127">
         <v>85</v>
       </c>
       <c r="C127" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D127" t="s">
-        <v>774</v>
+        <v>474</v>
       </c>
       <c r="E127" t="s">
-        <v>783</v>
+        <v>475</v>
       </c>
       <c r="F127" t="s">
-        <v>785</v>
+        <v>477</v>
       </c>
       <c r="G127" t="s">
-        <v>786</v>
+        <v>478</v>
       </c>
       <c r="H127" t="s">
-        <v>788</v>
+        <v>480</v>
       </c>
       <c r="I127" t="s">
-        <v>789</v>
+        <v>481</v>
       </c>
       <c r="J127" t="s">
-        <v>790</v>
+        <v>482</v>
       </c>
       <c r="K127" t="s">
-        <v>784</v>
+        <v>476</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B128">
         <v>85</v>
@@ -28922,33 +29849,33 @@
         <v>773</v>
       </c>
       <c r="D128" t="s">
-        <v>799</v>
+        <v>774</v>
       </c>
       <c r="E128" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="F128" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="G128" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="H128" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="I128" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="J128" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="K128" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B129">
         <v>85</v>
@@ -28957,68 +29884,68 @@
         <v>773</v>
       </c>
       <c r="D129" t="s">
-        <v>821</v>
+        <v>799</v>
       </c>
       <c r="E129" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="F129" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="G129" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
       <c r="H129" t="s">
-        <v>826</v>
+        <v>804</v>
       </c>
       <c r="I129" t="s">
-        <v>827</v>
+        <v>805</v>
       </c>
       <c r="J129" t="s">
-        <v>828</v>
+        <v>806</v>
       </c>
       <c r="K129" t="s">
-        <v>823</v>
+        <v>801</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B130">
         <v>85</v>
       </c>
       <c r="C130" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D130" t="s">
-        <v>989</v>
+        <v>821</v>
       </c>
       <c r="E130" t="s">
-        <v>990</v>
+        <v>822</v>
       </c>
       <c r="F130" t="s">
-        <v>75</v>
+        <v>777</v>
       </c>
       <c r="G130" t="s">
-        <v>959</v>
+        <v>824</v>
       </c>
       <c r="H130" t="s">
-        <v>993</v>
+        <v>826</v>
       </c>
       <c r="I130" t="s">
-        <v>994</v>
+        <v>827</v>
       </c>
       <c r="J130" t="s">
-        <v>995</v>
+        <v>828</v>
       </c>
       <c r="K130" t="s">
-        <v>991</v>
+        <v>823</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B131">
         <v>85</v>
@@ -29027,208 +29954,208 @@
         <v>934</v>
       </c>
       <c r="D131" t="s">
-        <v>1065</v>
+        <v>989</v>
       </c>
       <c r="E131" t="s">
-        <v>1066</v>
+        <v>990</v>
       </c>
       <c r="F131" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="G131" t="s">
-        <v>1068</v>
+        <v>959</v>
       </c>
       <c r="H131" t="s">
-        <v>1070</v>
+        <v>993</v>
       </c>
       <c r="I131" t="s">
-        <v>1071</v>
+        <v>994</v>
       </c>
       <c r="J131" t="s">
-        <v>1072</v>
+        <v>995</v>
       </c>
       <c r="K131" t="s">
-        <v>1067</v>
+        <v>991</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B132">
         <v>85</v>
       </c>
       <c r="C132" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D132" t="s">
-        <v>1242</v>
+        <v>1065</v>
       </c>
       <c r="E132" t="s">
-        <v>610</v>
+        <v>1066</v>
       </c>
       <c r="F132" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G132" t="s">
-        <v>604</v>
+        <v>1068</v>
       </c>
       <c r="H132" t="s">
-        <v>312</v>
+        <v>1070</v>
       </c>
       <c r="I132" t="s">
-        <v>1245</v>
+        <v>1071</v>
       </c>
       <c r="J132" t="s">
-        <v>1246</v>
+        <v>1072</v>
       </c>
       <c r="K132" t="s">
-        <v>1243</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B133">
         <v>85</v>
       </c>
       <c r="C133" t="s">
-        <v>1300</v>
+        <v>1227</v>
       </c>
       <c r="D133" t="s">
-        <v>1345</v>
+        <v>1242</v>
       </c>
       <c r="E133" t="s">
-        <v>1346</v>
+        <v>610</v>
       </c>
       <c r="F133" t="s">
         <v>16</v>
       </c>
       <c r="G133" t="s">
-        <v>1348</v>
+        <v>604</v>
       </c>
       <c r="H133" t="s">
         <v>312</v>
       </c>
       <c r="I133" t="s">
-        <v>1350</v>
+        <v>1245</v>
       </c>
       <c r="J133" t="s">
-        <v>1351</v>
+        <v>1246</v>
       </c>
       <c r="K133" t="s">
-        <v>1347</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B134">
         <v>85</v>
       </c>
       <c r="C134" t="s">
-        <v>1394</v>
+        <v>1300</v>
       </c>
       <c r="D134" t="s">
-        <v>1459</v>
+        <v>1345</v>
       </c>
       <c r="E134" t="s">
-        <v>1460</v>
+        <v>1346</v>
       </c>
       <c r="F134" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G134" t="s">
-        <v>1462</v>
+        <v>1348</v>
       </c>
       <c r="H134" t="s">
-        <v>1464</v>
+        <v>312</v>
       </c>
       <c r="I134" t="s">
-        <v>1465</v>
+        <v>1350</v>
       </c>
       <c r="J134" t="s">
-        <v>1466</v>
+        <v>1351</v>
       </c>
       <c r="K134" t="s">
-        <v>1461</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B135">
         <v>85</v>
       </c>
       <c r="C135" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D135" t="s">
-        <v>1535</v>
+        <v>1459</v>
       </c>
       <c r="E135" t="s">
-        <v>1543</v>
+        <v>1460</v>
       </c>
       <c r="F135" t="s">
-        <v>318</v>
+        <v>66</v>
       </c>
       <c r="G135" t="s">
-        <v>1538</v>
+        <v>1462</v>
       </c>
       <c r="H135" t="s">
-        <v>1546</v>
+        <v>1464</v>
       </c>
       <c r="I135" t="s">
-        <v>1547</v>
+        <v>1465</v>
       </c>
       <c r="J135" t="s">
-        <v>1548</v>
+        <v>1466</v>
       </c>
       <c r="K135" t="s">
-        <v>1544</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B136">
         <v>85</v>
       </c>
       <c r="C136" t="s">
-        <v>1625</v>
+        <v>1534</v>
       </c>
       <c r="D136" t="s">
-        <v>1626</v>
+        <v>1535</v>
       </c>
       <c r="E136" t="s">
-        <v>1627</v>
+        <v>1543</v>
       </c>
       <c r="F136" t="s">
-        <v>1629</v>
+        <v>318</v>
       </c>
       <c r="G136" t="s">
-        <v>1630</v>
+        <v>1538</v>
       </c>
       <c r="H136" t="s">
-        <v>1632</v>
+        <v>1546</v>
       </c>
       <c r="I136" t="s">
-        <v>1633</v>
+        <v>1547</v>
       </c>
       <c r="J136" t="s">
-        <v>1634</v>
+        <v>1548</v>
       </c>
       <c r="K136" t="s">
-        <v>1628</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B137">
         <v>85</v>
@@ -29237,68 +30164,68 @@
         <v>1625</v>
       </c>
       <c r="D137" t="s">
-        <v>1635</v>
+        <v>1626</v>
       </c>
       <c r="E137" t="s">
-        <v>110</v>
+        <v>1627</v>
       </c>
       <c r="F137" t="s">
-        <v>16</v>
+        <v>1629</v>
       </c>
       <c r="G137" t="s">
-        <v>1637</v>
+        <v>1630</v>
       </c>
       <c r="H137" t="s">
-        <v>1639</v>
+        <v>1632</v>
       </c>
       <c r="I137" t="s">
-        <v>1640</v>
+        <v>1633</v>
       </c>
       <c r="J137" t="s">
-        <v>1641</v>
+        <v>1634</v>
       </c>
       <c r="K137" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B138">
         <v>85</v>
       </c>
       <c r="C138" t="s">
-        <v>1727</v>
+        <v>1625</v>
       </c>
       <c r="D138" t="s">
-        <v>1795</v>
+        <v>1635</v>
       </c>
       <c r="E138" t="s">
-        <v>1796</v>
+        <v>110</v>
       </c>
       <c r="F138" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G138" t="s">
-        <v>1798</v>
+        <v>1637</v>
       </c>
       <c r="H138" t="s">
-        <v>1800</v>
+        <v>1639</v>
       </c>
       <c r="I138" t="s">
-        <v>1801</v>
+        <v>1640</v>
       </c>
       <c r="J138" t="s">
-        <v>1802</v>
+        <v>1641</v>
       </c>
       <c r="K138" t="s">
-        <v>1797</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B139">
         <v>85</v>
@@ -29307,33 +30234,33 @@
         <v>1727</v>
       </c>
       <c r="D139" t="s">
-        <v>1201</v>
+        <v>1795</v>
       </c>
       <c r="E139" t="s">
-        <v>1845</v>
+        <v>1796</v>
       </c>
       <c r="F139" t="s">
-        <v>1847</v>
+        <v>25</v>
       </c>
       <c r="G139" t="s">
-        <v>1848</v>
+        <v>1798</v>
       </c>
       <c r="H139" t="s">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="I139" t="s">
-        <v>79</v>
+        <v>1801</v>
       </c>
       <c r="J139" t="s">
-        <v>79</v>
+        <v>1802</v>
       </c>
       <c r="K139" t="s">
-        <v>1846</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B140">
         <v>85</v>
@@ -29342,19 +30269,19 @@
         <v>1727</v>
       </c>
       <c r="D140" t="s">
-        <v>1873</v>
+        <v>1201</v>
       </c>
       <c r="E140" t="s">
-        <v>1874</v>
+        <v>1845</v>
       </c>
       <c r="F140" t="s">
-        <v>1876</v>
+        <v>1847</v>
       </c>
       <c r="G140" t="s">
-        <v>1754</v>
+        <v>1848</v>
       </c>
       <c r="H140" t="s">
-        <v>1878</v>
+        <v>1850</v>
       </c>
       <c r="I140" t="s">
         <v>79</v>
@@ -29363,47 +30290,47 @@
         <v>79</v>
       </c>
       <c r="K140" t="s">
-        <v>1875</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B141">
         <v>85</v>
       </c>
       <c r="C141" t="s">
-        <v>1994</v>
+        <v>1727</v>
       </c>
       <c r="D141" t="s">
-        <v>2039</v>
+        <v>1873</v>
       </c>
       <c r="E141" t="s">
-        <v>2040</v>
+        <v>1874</v>
       </c>
       <c r="F141" t="s">
-        <v>2042</v>
+        <v>1876</v>
       </c>
       <c r="G141" t="s">
-        <v>2043</v>
+        <v>1754</v>
       </c>
       <c r="H141" t="s">
-        <v>2045</v>
+        <v>1878</v>
       </c>
       <c r="I141" t="s">
-        <v>2046</v>
+        <v>79</v>
       </c>
       <c r="J141" t="s">
-        <v>2047</v>
+        <v>79</v>
       </c>
       <c r="K141" t="s">
-        <v>2041</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B142">
         <v>85</v>
@@ -29412,208 +30339,208 @@
         <v>1994</v>
       </c>
       <c r="D142" t="s">
-        <v>2090</v>
+        <v>2039</v>
       </c>
       <c r="E142" t="s">
-        <v>2091</v>
+        <v>2040</v>
       </c>
       <c r="F142" t="s">
-        <v>25</v>
+        <v>2042</v>
       </c>
       <c r="G142" t="s">
-        <v>2093</v>
+        <v>2043</v>
       </c>
       <c r="H142" t="s">
-        <v>2095</v>
+        <v>2045</v>
       </c>
       <c r="I142" t="s">
-        <v>2096</v>
+        <v>2046</v>
       </c>
       <c r="J142" t="s">
-        <v>2097</v>
+        <v>2047</v>
       </c>
       <c r="K142" t="s">
-        <v>2092</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B143">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C143" t="s">
-        <v>12</v>
+        <v>1994</v>
       </c>
       <c r="D143" t="s">
-        <v>144</v>
+        <v>2090</v>
       </c>
       <c r="E143" t="s">
-        <v>145</v>
+        <v>2091</v>
       </c>
       <c r="F143" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="G143" t="s">
-        <v>148</v>
+        <v>2093</v>
       </c>
       <c r="H143" t="s">
-        <v>150</v>
+        <v>2095</v>
       </c>
       <c r="I143" t="s">
-        <v>151</v>
+        <v>2096</v>
       </c>
       <c r="J143" t="s">
-        <v>152</v>
+        <v>2097</v>
       </c>
       <c r="K143" t="s">
-        <v>146</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B144">
         <v>84</v>
       </c>
       <c r="C144" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D144" t="s">
         <v>144</v>
       </c>
       <c r="E144" t="s">
-        <v>394</v>
+        <v>145</v>
       </c>
       <c r="F144" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G144" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
       <c r="H144" t="s">
-        <v>399</v>
+        <v>150</v>
       </c>
       <c r="I144" t="s">
-        <v>400</v>
+        <v>151</v>
       </c>
       <c r="J144" t="s">
-        <v>401</v>
+        <v>152</v>
       </c>
       <c r="K144" t="s">
-        <v>395</v>
+        <v>146</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B145">
         <v>84</v>
       </c>
       <c r="C145" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D145" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E145" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="F145" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="G145" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="H145" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="I145" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="J145" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="K145" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B146">
         <v>84</v>
       </c>
       <c r="C146" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D146" t="s">
-        <v>483</v>
+        <v>410</v>
       </c>
       <c r="E146" t="s">
-        <v>122</v>
+        <v>411</v>
       </c>
       <c r="F146" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="G146" t="s">
-        <v>486</v>
+        <v>413</v>
       </c>
       <c r="H146" t="s">
-        <v>488</v>
+        <v>415</v>
       </c>
       <c r="I146" t="s">
-        <v>489</v>
+        <v>416</v>
       </c>
       <c r="J146" t="s">
-        <v>490</v>
+        <v>417</v>
       </c>
       <c r="K146" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B147">
         <v>84</v>
       </c>
       <c r="C147" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D147" t="s">
-        <v>714</v>
+        <v>483</v>
       </c>
       <c r="E147" t="s">
-        <v>715</v>
+        <v>122</v>
       </c>
       <c r="F147" t="s">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="G147" t="s">
-        <v>604</v>
+        <v>486</v>
       </c>
       <c r="H147" t="s">
-        <v>718</v>
+        <v>488</v>
       </c>
       <c r="I147" t="s">
-        <v>719</v>
+        <v>489</v>
       </c>
       <c r="J147" t="s">
-        <v>720</v>
+        <v>490</v>
       </c>
       <c r="K147" t="s">
-        <v>716</v>
+        <v>484</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B148">
         <v>84</v>
@@ -29622,33 +30549,33 @@
         <v>697</v>
       </c>
       <c r="D148" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E148" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="F148" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G148" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="H148" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="I148" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="J148" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="K148" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B149">
         <v>84</v>
@@ -29657,138 +30584,138 @@
         <v>697</v>
       </c>
       <c r="D149" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="E149" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="F149" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="G149" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="H149" t="s">
         <v>726</v>
       </c>
       <c r="I149" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="J149" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="K149" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B150">
         <v>84</v>
       </c>
       <c r="C150" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D150" t="s">
-        <v>791</v>
+        <v>729</v>
       </c>
       <c r="E150" t="s">
-        <v>610</v>
+        <v>730</v>
       </c>
       <c r="F150" t="s">
-        <v>793</v>
+        <v>535</v>
       </c>
       <c r="G150" t="s">
-        <v>794</v>
+        <v>732</v>
       </c>
       <c r="H150" t="s">
-        <v>796</v>
+        <v>726</v>
       </c>
       <c r="I150" t="s">
-        <v>797</v>
+        <v>734</v>
       </c>
       <c r="J150" t="s">
-        <v>798</v>
+        <v>735</v>
       </c>
       <c r="K150" t="s">
-        <v>792</v>
+        <v>731</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B151">
         <v>84</v>
       </c>
       <c r="C151" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D151" t="s">
-        <v>896</v>
+        <v>791</v>
       </c>
       <c r="E151" t="s">
-        <v>897</v>
+        <v>610</v>
       </c>
       <c r="F151" t="s">
-        <v>25</v>
+        <v>793</v>
       </c>
       <c r="G151" t="s">
-        <v>899</v>
+        <v>794</v>
       </c>
       <c r="H151" t="s">
-        <v>901</v>
+        <v>796</v>
       </c>
       <c r="I151" t="s">
-        <v>902</v>
+        <v>797</v>
       </c>
       <c r="J151" t="s">
-        <v>903</v>
+        <v>798</v>
       </c>
       <c r="K151" t="s">
-        <v>898</v>
+        <v>792</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B152">
         <v>84</v>
       </c>
       <c r="C152" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D152" t="s">
-        <v>964</v>
+        <v>896</v>
       </c>
       <c r="E152" t="s">
-        <v>965</v>
+        <v>897</v>
       </c>
       <c r="F152" t="s">
-        <v>967</v>
+        <v>25</v>
       </c>
       <c r="G152" t="s">
-        <v>968</v>
+        <v>899</v>
       </c>
       <c r="H152" t="s">
-        <v>970</v>
+        <v>901</v>
       </c>
       <c r="I152" t="s">
-        <v>971</v>
+        <v>902</v>
       </c>
       <c r="J152" t="s">
-        <v>972</v>
+        <v>903</v>
       </c>
       <c r="K152" t="s">
-        <v>966</v>
+        <v>898</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B153">
         <v>84</v>
@@ -29797,33 +30724,33 @@
         <v>934</v>
       </c>
       <c r="D153" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="E153" t="s">
-        <v>1002</v>
+        <v>965</v>
       </c>
       <c r="F153" t="s">
-        <v>1004</v>
+        <v>967</v>
       </c>
       <c r="G153" t="s">
-        <v>438</v>
+        <v>968</v>
       </c>
       <c r="H153" t="s">
-        <v>1006</v>
+        <v>970</v>
       </c>
       <c r="I153" t="s">
-        <v>1007</v>
+        <v>971</v>
       </c>
       <c r="J153" t="s">
-        <v>1008</v>
+        <v>972</v>
       </c>
       <c r="K153" t="s">
-        <v>1003</v>
+        <v>966</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B154">
         <v>84</v>
@@ -29832,33 +30759,33 @@
         <v>934</v>
       </c>
       <c r="D154" t="s">
-        <v>213</v>
+        <v>950</v>
       </c>
       <c r="E154" t="s">
-        <v>1032</v>
+        <v>1002</v>
       </c>
       <c r="F154" t="s">
-        <v>106</v>
+        <v>1004</v>
       </c>
       <c r="G154" t="s">
-        <v>1034</v>
+        <v>438</v>
       </c>
       <c r="H154" t="s">
-        <v>1036</v>
+        <v>1006</v>
       </c>
       <c r="I154" t="s">
-        <v>1037</v>
+        <v>1007</v>
       </c>
       <c r="J154" t="s">
-        <v>1038</v>
+        <v>1008</v>
       </c>
       <c r="K154" t="s">
-        <v>1033</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B155">
         <v>84</v>
@@ -29867,173 +30794,173 @@
         <v>934</v>
       </c>
       <c r="D155" t="s">
-        <v>1057</v>
+        <v>213</v>
       </c>
       <c r="E155" t="s">
-        <v>1058</v>
+        <v>1032</v>
       </c>
       <c r="F155" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G155" t="s">
-        <v>1060</v>
+        <v>1034</v>
       </c>
       <c r="H155" t="s">
-        <v>1062</v>
+        <v>1036</v>
       </c>
       <c r="I155" t="s">
-        <v>1063</v>
+        <v>1037</v>
       </c>
       <c r="J155" t="s">
-        <v>1064</v>
+        <v>1038</v>
       </c>
       <c r="K155" t="s">
-        <v>1059</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B156">
         <v>84</v>
       </c>
       <c r="C156" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D156" t="s">
-        <v>271</v>
+        <v>1057</v>
       </c>
       <c r="E156" t="s">
-        <v>1104</v>
+        <v>1058</v>
       </c>
       <c r="F156" t="s">
-        <v>1106</v>
+        <v>16</v>
       </c>
       <c r="G156" t="s">
-        <v>1107</v>
+        <v>1060</v>
       </c>
       <c r="H156" t="s">
-        <v>1109</v>
+        <v>1062</v>
       </c>
       <c r="I156" t="s">
-        <v>1110</v>
+        <v>1063</v>
       </c>
       <c r="J156" t="s">
-        <v>1111</v>
+        <v>1064</v>
       </c>
       <c r="K156" t="s">
-        <v>1105</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B157">
         <v>84</v>
       </c>
       <c r="C157" t="s">
-        <v>1271</v>
+        <v>1087</v>
       </c>
       <c r="D157" t="s">
-        <v>950</v>
+        <v>271</v>
       </c>
       <c r="E157" t="s">
-        <v>463</v>
+        <v>1104</v>
       </c>
       <c r="F157" t="s">
-        <v>66</v>
+        <v>1106</v>
       </c>
       <c r="G157" t="s">
-        <v>438</v>
+        <v>1107</v>
       </c>
       <c r="H157" t="s">
-        <v>1274</v>
+        <v>1109</v>
       </c>
       <c r="I157" t="s">
-        <v>1275</v>
+        <v>1110</v>
       </c>
       <c r="J157" t="s">
-        <v>1276</v>
+        <v>1111</v>
       </c>
       <c r="K157" t="s">
-        <v>1272</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B158">
         <v>84</v>
       </c>
       <c r="C158" t="s">
-        <v>1300</v>
+        <v>1271</v>
       </c>
       <c r="D158" t="s">
-        <v>1338</v>
+        <v>950</v>
       </c>
       <c r="E158" t="s">
-        <v>122</v>
+        <v>463</v>
       </c>
       <c r="F158" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G158" t="s">
-        <v>1340</v>
+        <v>438</v>
       </c>
       <c r="H158" t="s">
-        <v>1342</v>
+        <v>1274</v>
       </c>
       <c r="I158" t="s">
-        <v>1343</v>
+        <v>1275</v>
       </c>
       <c r="J158" t="s">
-        <v>1344</v>
+        <v>1276</v>
       </c>
       <c r="K158" t="s">
-        <v>1339</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B159">
         <v>84</v>
       </c>
       <c r="C159" t="s">
-        <v>1394</v>
+        <v>1300</v>
       </c>
       <c r="D159" t="s">
-        <v>1443</v>
+        <v>1338</v>
       </c>
       <c r="E159" t="s">
-        <v>1444</v>
+        <v>122</v>
       </c>
       <c r="F159" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G159" t="s">
-        <v>1446</v>
+        <v>1340</v>
       </c>
       <c r="H159" t="s">
-        <v>1448</v>
+        <v>1342</v>
       </c>
       <c r="I159" t="s">
-        <v>1449</v>
+        <v>1343</v>
       </c>
       <c r="J159" t="s">
-        <v>1450</v>
+        <v>1344</v>
       </c>
       <c r="K159" t="s">
-        <v>1445</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B160">
         <v>84</v>
@@ -30042,138 +30969,138 @@
         <v>1394</v>
       </c>
       <c r="D160" t="s">
-        <v>1475</v>
+        <v>1443</v>
       </c>
       <c r="E160" t="s">
-        <v>1476</v>
+        <v>1444</v>
       </c>
       <c r="F160" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G160" t="s">
-        <v>1478</v>
+        <v>1446</v>
       </c>
       <c r="H160" t="s">
-        <v>1480</v>
+        <v>1448</v>
       </c>
       <c r="I160" t="s">
-        <v>1481</v>
+        <v>1449</v>
       </c>
       <c r="J160" t="s">
-        <v>1482</v>
+        <v>1450</v>
       </c>
       <c r="K160" t="s">
-        <v>1477</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B161">
         <v>84</v>
       </c>
       <c r="C161" t="s">
-        <v>1625</v>
+        <v>1394</v>
       </c>
       <c r="D161" t="s">
-        <v>1635</v>
+        <v>1475</v>
       </c>
       <c r="E161" t="s">
-        <v>1642</v>
+        <v>1476</v>
       </c>
       <c r="F161" t="s">
-        <v>1644</v>
+        <v>25</v>
       </c>
       <c r="G161" t="s">
-        <v>1637</v>
+        <v>1478</v>
       </c>
       <c r="H161" t="s">
-        <v>1646</v>
+        <v>1480</v>
       </c>
       <c r="I161" t="s">
-        <v>1647</v>
+        <v>1481</v>
       </c>
       <c r="J161" t="s">
-        <v>1648</v>
+        <v>1482</v>
       </c>
       <c r="K161" t="s">
-        <v>1643</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B162">
         <v>84</v>
       </c>
       <c r="C162" t="s">
-        <v>1664</v>
+        <v>1625</v>
       </c>
       <c r="D162" t="s">
-        <v>1665</v>
+        <v>1635</v>
       </c>
       <c r="E162" t="s">
-        <v>1666</v>
+        <v>1642</v>
       </c>
       <c r="F162" t="s">
-        <v>747</v>
+        <v>1644</v>
       </c>
       <c r="G162" t="s">
-        <v>1668</v>
+        <v>1637</v>
       </c>
       <c r="H162" t="s">
-        <v>1670</v>
+        <v>1646</v>
       </c>
       <c r="I162" t="s">
-        <v>1671</v>
+        <v>1647</v>
       </c>
       <c r="J162" t="s">
-        <v>1672</v>
+        <v>1648</v>
       </c>
       <c r="K162" t="s">
-        <v>1667</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B163">
         <v>84</v>
       </c>
       <c r="C163" t="s">
-        <v>1727</v>
+        <v>1664</v>
       </c>
       <c r="D163" t="s">
-        <v>1744</v>
+        <v>1665</v>
       </c>
       <c r="E163" t="s">
-        <v>1536</v>
+        <v>1666</v>
       </c>
       <c r="F163" t="s">
-        <v>25</v>
+        <v>747</v>
       </c>
       <c r="G163" t="s">
-        <v>1746</v>
+        <v>1668</v>
       </c>
       <c r="H163" t="s">
-        <v>1748</v>
+        <v>1670</v>
       </c>
       <c r="I163" t="s">
-        <v>1749</v>
+        <v>1671</v>
       </c>
       <c r="J163" t="s">
-        <v>1750</v>
+        <v>1672</v>
       </c>
       <c r="K163" t="s">
-        <v>1745</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B164">
         <v>84</v>
@@ -30182,33 +31109,33 @@
         <v>1727</v>
       </c>
       <c r="D164" t="s">
-        <v>1751</v>
+        <v>1744</v>
       </c>
       <c r="E164" t="s">
-        <v>1752</v>
+        <v>1536</v>
       </c>
       <c r="F164" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="G164" t="s">
-        <v>1754</v>
+        <v>1746</v>
       </c>
       <c r="H164" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
       <c r="I164" t="s">
-        <v>1757</v>
+        <v>1749</v>
       </c>
       <c r="J164" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
       <c r="K164" t="s">
-        <v>1753</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B165">
         <v>84</v>
@@ -30217,68 +31144,68 @@
         <v>1727</v>
       </c>
       <c r="D165" t="s">
-        <v>1879</v>
+        <v>1751</v>
       </c>
       <c r="E165" t="s">
-        <v>1880</v>
+        <v>1752</v>
       </c>
       <c r="F165" t="s">
-        <v>25</v>
+        <v>535</v>
       </c>
       <c r="G165" t="s">
-        <v>1770</v>
+        <v>1754</v>
       </c>
       <c r="H165" t="s">
-        <v>1883</v>
+        <v>1756</v>
       </c>
       <c r="I165" t="s">
-        <v>79</v>
+        <v>1757</v>
       </c>
       <c r="J165" t="s">
-        <v>79</v>
+        <v>1758</v>
       </c>
       <c r="K165" t="s">
-        <v>1881</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B166">
         <v>84</v>
       </c>
       <c r="C166" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D166" t="s">
-        <v>1899</v>
+        <v>1879</v>
       </c>
       <c r="E166" t="s">
-        <v>1900</v>
+        <v>1880</v>
       </c>
       <c r="F166" t="s">
-        <v>747</v>
+        <v>25</v>
       </c>
       <c r="G166" t="s">
-        <v>1902</v>
+        <v>1770</v>
       </c>
       <c r="H166" t="s">
-        <v>1904</v>
+        <v>1883</v>
       </c>
       <c r="I166" t="s">
-        <v>1905</v>
+        <v>79</v>
       </c>
       <c r="J166" t="s">
-        <v>1906</v>
+        <v>79</v>
       </c>
       <c r="K166" t="s">
-        <v>1901</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B167">
         <v>84</v>
@@ -30287,68 +31214,68 @@
         <v>1884</v>
       </c>
       <c r="D167" t="s">
-        <v>1955</v>
+        <v>1899</v>
       </c>
       <c r="E167" t="s">
-        <v>1956</v>
+        <v>1900</v>
       </c>
       <c r="F167" t="s">
-        <v>1958</v>
+        <v>747</v>
       </c>
       <c r="G167" t="s">
-        <v>959</v>
+        <v>1902</v>
       </c>
       <c r="H167" t="s">
-        <v>1960</v>
+        <v>1904</v>
       </c>
       <c r="I167" t="s">
-        <v>1961</v>
+        <v>1905</v>
       </c>
       <c r="J167" t="s">
-        <v>1962</v>
+        <v>1906</v>
       </c>
       <c r="K167" t="s">
-        <v>1957</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B168">
         <v>84</v>
       </c>
       <c r="C168" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D168" t="s">
-        <v>2176</v>
+        <v>1955</v>
       </c>
       <c r="E168" t="s">
-        <v>2177</v>
+        <v>1956</v>
       </c>
       <c r="F168" t="s">
-        <v>16</v>
+        <v>1958</v>
       </c>
       <c r="G168" t="s">
-        <v>2179</v>
+        <v>959</v>
       </c>
       <c r="H168" t="s">
-        <v>2181</v>
+        <v>1960</v>
       </c>
       <c r="I168" t="s">
-        <v>2182</v>
+        <v>1961</v>
       </c>
       <c r="J168" t="s">
-        <v>2183</v>
+        <v>1962</v>
       </c>
       <c r="K168" t="s">
-        <v>2178</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B169">
         <v>84</v>
@@ -30357,138 +31284,138 @@
         <v>2098</v>
       </c>
       <c r="D169" t="s">
-        <v>2211</v>
+        <v>2176</v>
       </c>
       <c r="E169" t="s">
-        <v>2212</v>
+        <v>2177</v>
       </c>
       <c r="F169" t="s">
         <v>16</v>
       </c>
       <c r="G169" t="s">
-        <v>2214</v>
+        <v>2179</v>
       </c>
       <c r="H169" t="s">
-        <v>2216</v>
+        <v>2181</v>
       </c>
       <c r="I169" t="s">
-        <v>2217</v>
+        <v>2182</v>
       </c>
       <c r="J169" t="s">
-        <v>2218</v>
+        <v>2183</v>
       </c>
       <c r="K169" t="s">
-        <v>2213</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B170">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C170" t="s">
-        <v>1200</v>
+        <v>2098</v>
       </c>
       <c r="D170" t="s">
-        <v>1201</v>
+        <v>2211</v>
       </c>
       <c r="E170" t="s">
-        <v>1202</v>
+        <v>2212</v>
       </c>
       <c r="F170" t="s">
-        <v>1204</v>
+        <v>16</v>
       </c>
       <c r="G170" t="s">
-        <v>1205</v>
+        <v>2214</v>
       </c>
       <c r="H170" t="s">
-        <v>1207</v>
+        <v>2216</v>
       </c>
       <c r="I170" t="s">
-        <v>1208</v>
+        <v>2217</v>
       </c>
       <c r="J170" t="s">
-        <v>1209</v>
+        <v>2218</v>
       </c>
       <c r="K170" t="s">
-        <v>1203</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B171">
         <v>83</v>
       </c>
       <c r="C171" t="s">
-        <v>284</v>
+        <v>1200</v>
       </c>
       <c r="D171" t="s">
-        <v>353</v>
+        <v>1201</v>
       </c>
       <c r="E171" t="s">
-        <v>362</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="s">
-        <v>356</v>
+        <v>1204</v>
       </c>
       <c r="G171" t="s">
-        <v>364</v>
+        <v>1205</v>
       </c>
       <c r="H171" t="s">
-        <v>366</v>
+        <v>1207</v>
       </c>
       <c r="I171" t="s">
-        <v>367</v>
+        <v>1208</v>
       </c>
       <c r="J171" t="s">
-        <v>368</v>
+        <v>1209</v>
       </c>
       <c r="K171" t="s">
-        <v>363</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B172">
         <v>83</v>
       </c>
       <c r="C172" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D172" t="s">
-        <v>491</v>
+        <v>353</v>
       </c>
       <c r="E172" t="s">
-        <v>492</v>
+        <v>362</v>
       </c>
       <c r="F172" t="s">
-        <v>75</v>
+        <v>356</v>
       </c>
       <c r="G172" t="s">
-        <v>494</v>
+        <v>364</v>
       </c>
       <c r="H172" t="s">
-        <v>496</v>
+        <v>366</v>
       </c>
       <c r="I172" t="s">
-        <v>497</v>
+        <v>367</v>
       </c>
       <c r="J172" t="s">
-        <v>498</v>
+        <v>368</v>
       </c>
       <c r="K172" t="s">
-        <v>493</v>
+        <v>363</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B173">
         <v>83</v>
@@ -30497,173 +31424,173 @@
         <v>473</v>
       </c>
       <c r="D173" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="E173" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="F173" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="G173" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="H173" t="s">
-        <v>538</v>
+        <v>496</v>
       </c>
       <c r="I173" t="s">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="J173" t="s">
-        <v>540</v>
+        <v>498</v>
       </c>
       <c r="K173" t="s">
-        <v>534</v>
+        <v>493</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B174">
         <v>83</v>
       </c>
       <c r="C174" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D174" t="s">
-        <v>643</v>
+        <v>532</v>
       </c>
       <c r="E174" t="s">
-        <v>644</v>
+        <v>533</v>
       </c>
       <c r="F174" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="G174" t="s">
-        <v>618</v>
+        <v>536</v>
       </c>
       <c r="H174" t="s">
-        <v>647</v>
+        <v>538</v>
       </c>
       <c r="I174" t="s">
-        <v>648</v>
+        <v>539</v>
       </c>
       <c r="J174" t="s">
-        <v>649</v>
+        <v>540</v>
       </c>
       <c r="K174" t="s">
-        <v>645</v>
+        <v>534</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B175">
         <v>83</v>
       </c>
       <c r="C175" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="D175" t="s">
-        <v>736</v>
+        <v>643</v>
       </c>
       <c r="E175" t="s">
-        <v>737</v>
+        <v>644</v>
       </c>
       <c r="F175" t="s">
-        <v>739</v>
+        <v>16</v>
       </c>
       <c r="G175" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="H175" t="s">
-        <v>741</v>
+        <v>647</v>
       </c>
       <c r="I175" t="s">
-        <v>742</v>
+        <v>648</v>
       </c>
       <c r="J175" t="s">
-        <v>743</v>
+        <v>649</v>
       </c>
       <c r="K175" t="s">
-        <v>738</v>
+        <v>645</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B176">
         <v>83</v>
       </c>
       <c r="C176" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D176" t="s">
-        <v>807</v>
+        <v>736</v>
       </c>
       <c r="E176" t="s">
-        <v>808</v>
+        <v>737</v>
       </c>
       <c r="F176" t="s">
-        <v>810</v>
+        <v>739</v>
       </c>
       <c r="G176" t="s">
-        <v>811</v>
+        <v>604</v>
       </c>
       <c r="H176" t="s">
-        <v>813</v>
+        <v>741</v>
       </c>
       <c r="I176" t="s">
-        <v>814</v>
+        <v>742</v>
       </c>
       <c r="J176" t="s">
-        <v>815</v>
+        <v>743</v>
       </c>
       <c r="K176" t="s">
-        <v>809</v>
+        <v>738</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B177">
         <v>83</v>
       </c>
       <c r="C177" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D177" t="s">
-        <v>650</v>
+        <v>807</v>
       </c>
       <c r="E177" t="s">
-        <v>1016</v>
+        <v>808</v>
       </c>
       <c r="F177" t="s">
-        <v>66</v>
+        <v>810</v>
       </c>
       <c r="G177" t="s">
-        <v>1018</v>
+        <v>811</v>
       </c>
       <c r="H177" t="s">
-        <v>1020</v>
+        <v>813</v>
       </c>
       <c r="I177" t="s">
-        <v>1021</v>
+        <v>814</v>
       </c>
       <c r="J177" t="s">
-        <v>1022</v>
+        <v>815</v>
       </c>
       <c r="K177" t="s">
-        <v>1017</v>
+        <v>809</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B178">
         <v>83</v>
@@ -30672,103 +31599,103 @@
         <v>934</v>
       </c>
       <c r="D178" t="s">
-        <v>1048</v>
+        <v>650</v>
       </c>
       <c r="E178" t="s">
-        <v>1049</v>
+        <v>1016</v>
       </c>
       <c r="F178" t="s">
-        <v>1051</v>
+        <v>66</v>
       </c>
       <c r="G178" t="s">
-        <v>1052</v>
+        <v>1018</v>
       </c>
       <c r="H178" t="s">
-        <v>1054</v>
+        <v>1020</v>
       </c>
       <c r="I178" t="s">
-        <v>1055</v>
+        <v>1021</v>
       </c>
       <c r="J178" t="s">
-        <v>1056</v>
+        <v>1022</v>
       </c>
       <c r="K178" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B179">
         <v>83</v>
       </c>
       <c r="C179" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D179" t="s">
-        <v>1247</v>
+        <v>1048</v>
       </c>
       <c r="E179" t="s">
-        <v>1248</v>
+        <v>1049</v>
       </c>
       <c r="F179" t="s">
-        <v>66</v>
+        <v>1051</v>
       </c>
       <c r="G179" t="s">
-        <v>604</v>
+        <v>1052</v>
       </c>
       <c r="H179" t="s">
-        <v>1251</v>
+        <v>1054</v>
       </c>
       <c r="I179" t="s">
-        <v>1252</v>
+        <v>1055</v>
       </c>
       <c r="J179" t="s">
-        <v>1253</v>
+        <v>1056</v>
       </c>
       <c r="K179" t="s">
-        <v>1249</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B180">
         <v>83</v>
       </c>
       <c r="C180" t="s">
-        <v>1271</v>
+        <v>1227</v>
       </c>
       <c r="D180" t="s">
-        <v>219</v>
+        <v>1247</v>
       </c>
       <c r="E180" t="s">
-        <v>1285</v>
+        <v>1248</v>
       </c>
       <c r="F180" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="G180" t="s">
-        <v>1287</v>
+        <v>604</v>
       </c>
       <c r="H180" t="s">
-        <v>1289</v>
+        <v>1251</v>
       </c>
       <c r="I180" t="s">
-        <v>1290</v>
+        <v>1252</v>
       </c>
       <c r="J180" t="s">
-        <v>1291</v>
+        <v>1253</v>
       </c>
       <c r="K180" t="s">
-        <v>1286</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B181">
         <v>83</v>
@@ -30777,68 +31704,68 @@
         <v>1271</v>
       </c>
       <c r="D181" t="s">
-        <v>1292</v>
+        <v>219</v>
       </c>
       <c r="E181" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="F181" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="G181" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="H181" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
       <c r="I181" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
       <c r="J181" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
       <c r="K181" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B182">
         <v>83</v>
       </c>
       <c r="C182" t="s">
-        <v>1300</v>
+        <v>1271</v>
       </c>
       <c r="D182" t="s">
-        <v>1309</v>
+        <v>1292</v>
       </c>
       <c r="E182" t="s">
-        <v>830</v>
+        <v>1293</v>
       </c>
       <c r="F182" t="s">
-        <v>1311</v>
+        <v>66</v>
       </c>
       <c r="G182" t="s">
-        <v>1318</v>
+        <v>1295</v>
       </c>
       <c r="H182" t="s">
-        <v>1320</v>
+        <v>1297</v>
       </c>
       <c r="I182" t="s">
-        <v>1321</v>
+        <v>1298</v>
       </c>
       <c r="J182" t="s">
-        <v>1322</v>
+        <v>1299</v>
       </c>
       <c r="K182" t="s">
-        <v>1317</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B183">
         <v>83</v>
@@ -30847,68 +31774,68 @@
         <v>1300</v>
       </c>
       <c r="D183" t="s">
-        <v>1352</v>
+        <v>1309</v>
       </c>
       <c r="E183" t="s">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="F183" t="s">
-        <v>16</v>
+        <v>1311</v>
       </c>
       <c r="G183" t="s">
-        <v>1354</v>
+        <v>1318</v>
       </c>
       <c r="H183" t="s">
-        <v>1356</v>
+        <v>1320</v>
       </c>
       <c r="I183" t="s">
-        <v>1357</v>
+        <v>1321</v>
       </c>
       <c r="J183" t="s">
-        <v>1358</v>
+        <v>1322</v>
       </c>
       <c r="K183" t="s">
-        <v>1353</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B184">
         <v>83</v>
       </c>
       <c r="C184" t="s">
-        <v>1394</v>
+        <v>1300</v>
       </c>
       <c r="D184" t="s">
-        <v>491</v>
+        <v>1352</v>
       </c>
       <c r="E184" t="s">
-        <v>1404</v>
+        <v>110</v>
       </c>
       <c r="F184" t="s">
-        <v>1406</v>
+        <v>16</v>
       </c>
       <c r="G184" t="s">
-        <v>1407</v>
+        <v>1354</v>
       </c>
       <c r="H184" t="s">
-        <v>1409</v>
+        <v>1356</v>
       </c>
       <c r="I184" t="s">
-        <v>1410</v>
+        <v>1357</v>
       </c>
       <c r="J184" t="s">
-        <v>1411</v>
+        <v>1358</v>
       </c>
       <c r="K184" t="s">
-        <v>1405</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B185">
         <v>83</v>
@@ -30917,68 +31844,68 @@
         <v>1394</v>
       </c>
       <c r="D185" t="s">
-        <v>1451</v>
+        <v>491</v>
       </c>
       <c r="E185" t="s">
-        <v>1452</v>
+        <v>1404</v>
       </c>
       <c r="F185" t="s">
-        <v>1454</v>
+        <v>1406</v>
       </c>
       <c r="G185" t="s">
-        <v>802</v>
+        <v>1407</v>
       </c>
       <c r="H185" t="s">
-        <v>1456</v>
+        <v>1409</v>
       </c>
       <c r="I185" t="s">
-        <v>1457</v>
+        <v>1410</v>
       </c>
       <c r="J185" t="s">
-        <v>1458</v>
+        <v>1411</v>
       </c>
       <c r="K185" t="s">
-        <v>1453</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B186">
         <v>83</v>
       </c>
       <c r="C186" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D186" t="s">
-        <v>1579</v>
+        <v>1451</v>
       </c>
       <c r="E186" t="s">
-        <v>957</v>
+        <v>1452</v>
       </c>
       <c r="F186" t="s">
-        <v>75</v>
+        <v>1454</v>
       </c>
       <c r="G186" t="s">
-        <v>1581</v>
+        <v>802</v>
       </c>
       <c r="H186" t="s">
-        <v>1583</v>
+        <v>1456</v>
       </c>
       <c r="I186" t="s">
-        <v>1584</v>
+        <v>1457</v>
       </c>
       <c r="J186" t="s">
-        <v>1585</v>
+        <v>1458</v>
       </c>
       <c r="K186" t="s">
-        <v>1580</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B187">
         <v>83</v>
@@ -30987,33 +31914,33 @@
         <v>1534</v>
       </c>
       <c r="D187" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="E187" t="s">
-        <v>1587</v>
+        <v>957</v>
       </c>
       <c r="F187" t="s">
         <v>75</v>
       </c>
       <c r="G187" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="H187" t="s">
         <v>1583</v>
       </c>
       <c r="I187" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="J187" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="K187" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B188">
         <v>83</v>
@@ -31022,68 +31949,68 @@
         <v>1534</v>
       </c>
       <c r="D188" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="E188" t="s">
-        <v>610</v>
+        <v>1587</v>
       </c>
       <c r="F188" t="s">
-        <v>1595</v>
+        <v>75</v>
       </c>
       <c r="G188" t="s">
-        <v>1166</v>
+        <v>1589</v>
       </c>
       <c r="H188" t="s">
-        <v>1597</v>
+        <v>1583</v>
       </c>
       <c r="I188" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="J188" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="K188" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B189">
         <v>83</v>
       </c>
       <c r="C189" t="s">
-        <v>2098</v>
+        <v>1534</v>
       </c>
       <c r="D189" t="s">
-        <v>2099</v>
+        <v>1593</v>
       </c>
       <c r="E189" t="s">
-        <v>830</v>
+        <v>610</v>
       </c>
       <c r="F189" t="s">
-        <v>2101</v>
+        <v>1595</v>
       </c>
       <c r="G189" t="s">
-        <v>2102</v>
+        <v>1166</v>
       </c>
       <c r="H189" t="s">
-        <v>2104</v>
+        <v>1597</v>
       </c>
       <c r="I189" t="s">
-        <v>2105</v>
+        <v>1598</v>
       </c>
       <c r="J189" t="s">
-        <v>2106</v>
+        <v>1599</v>
       </c>
       <c r="K189" t="s">
-        <v>2100</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B190">
         <v>83</v>
@@ -31092,1083 +32019,1083 @@
         <v>2098</v>
       </c>
       <c r="D190" t="s">
-        <v>2162</v>
+        <v>2099</v>
       </c>
       <c r="E190" t="s">
-        <v>2163</v>
+        <v>830</v>
       </c>
       <c r="F190" t="s">
-        <v>16</v>
+        <v>2101</v>
       </c>
       <c r="G190" t="s">
-        <v>2165</v>
+        <v>2102</v>
       </c>
       <c r="H190" t="s">
-        <v>2167</v>
+        <v>2104</v>
       </c>
       <c r="I190" t="s">
-        <v>2168</v>
+        <v>2105</v>
       </c>
       <c r="J190" t="s">
-        <v>2169</v>
+        <v>2106</v>
       </c>
       <c r="K190" t="s">
-        <v>2164</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B191">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C191" t="s">
-        <v>159</v>
+        <v>2098</v>
       </c>
       <c r="D191" t="s">
-        <v>227</v>
+        <v>2162</v>
       </c>
       <c r="E191" t="s">
-        <v>228</v>
+        <v>2163</v>
       </c>
       <c r="F191" t="s">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c r="G191" t="s">
-        <v>231</v>
+        <v>2165</v>
       </c>
       <c r="H191" t="s">
-        <v>233</v>
+        <v>2167</v>
       </c>
       <c r="I191" t="s">
-        <v>234</v>
+        <v>2168</v>
       </c>
       <c r="J191" t="s">
-        <v>235</v>
+        <v>2169</v>
       </c>
       <c r="K191" t="s">
-        <v>229</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B192">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C192" t="s">
-        <v>159</v>
+        <v>2258</v>
       </c>
       <c r="D192" t="s">
-        <v>266</v>
+        <v>2308</v>
       </c>
       <c r="E192" t="s">
-        <v>267</v>
+        <v>2309</v>
       </c>
       <c r="F192" t="s">
-        <v>16</v>
+        <v>1950</v>
       </c>
       <c r="G192" t="s">
-        <v>58</v>
+        <v>2311</v>
       </c>
       <c r="H192" t="s">
-        <v>270</v>
+        <v>2313</v>
       </c>
       <c r="I192" t="s">
-        <v>79</v>
+        <v>2314</v>
       </c>
       <c r="J192" t="s">
-        <v>79</v>
+        <v>2315</v>
       </c>
       <c r="K192" t="s">
-        <v>268</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B193">
         <v>82</v>
       </c>
       <c r="C193" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D193" t="s">
-        <v>338</v>
+        <v>227</v>
       </c>
       <c r="E193" t="s">
-        <v>339</v>
+        <v>228</v>
       </c>
       <c r="F193" t="s">
-        <v>341</v>
+        <v>230</v>
       </c>
       <c r="G193" t="s">
-        <v>342</v>
+        <v>231</v>
       </c>
       <c r="H193" t="s">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="I193" t="s">
-        <v>345</v>
+        <v>234</v>
       </c>
       <c r="J193" t="s">
-        <v>346</v>
+        <v>235</v>
       </c>
       <c r="K193" t="s">
-        <v>340</v>
+        <v>229</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B194">
         <v>82</v>
       </c>
       <c r="C194" t="s">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="D194" t="s">
-        <v>601</v>
+        <v>266</v>
       </c>
       <c r="E194" t="s">
-        <v>602</v>
+        <v>267</v>
       </c>
       <c r="F194" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G194" t="s">
-        <v>604</v>
+        <v>58</v>
       </c>
       <c r="H194" t="s">
-        <v>606</v>
+        <v>270</v>
       </c>
       <c r="I194" t="s">
-        <v>607</v>
+        <v>79</v>
       </c>
       <c r="J194" t="s">
-        <v>608</v>
+        <v>79</v>
       </c>
       <c r="K194" t="s">
-        <v>603</v>
+        <v>268</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B195">
         <v>82</v>
       </c>
       <c r="C195" t="s">
-        <v>934</v>
+        <v>284</v>
       </c>
       <c r="D195" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="E195" t="s">
-        <v>1009</v>
+        <v>339</v>
       </c>
       <c r="F195" t="s">
-        <v>16</v>
+        <v>341</v>
       </c>
       <c r="G195" t="s">
-        <v>1011</v>
+        <v>342</v>
       </c>
       <c r="H195" t="s">
-        <v>1013</v>
+        <v>344</v>
       </c>
       <c r="I195" t="s">
-        <v>1014</v>
+        <v>345</v>
       </c>
       <c r="J195" t="s">
-        <v>1015</v>
+        <v>346</v>
       </c>
       <c r="K195" t="s">
-        <v>1010</v>
+        <v>340</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B196">
         <v>82</v>
       </c>
       <c r="C196" t="s">
-        <v>934</v>
+        <v>591</v>
       </c>
       <c r="D196" t="s">
-        <v>1023</v>
+        <v>601</v>
       </c>
       <c r="E196" t="s">
-        <v>1024</v>
+        <v>602</v>
       </c>
       <c r="F196" t="s">
-        <v>1026</v>
+        <v>75</v>
       </c>
       <c r="G196" t="s">
-        <v>1027</v>
+        <v>604</v>
       </c>
       <c r="H196" t="s">
-        <v>1029</v>
+        <v>606</v>
       </c>
       <c r="I196" t="s">
-        <v>1030</v>
+        <v>607</v>
       </c>
       <c r="J196" t="s">
-        <v>1031</v>
+        <v>608</v>
       </c>
       <c r="K196" t="s">
-        <v>1025</v>
+        <v>603</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B197">
         <v>82</v>
       </c>
       <c r="C197" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D197" t="s">
-        <v>1112</v>
+        <v>13</v>
       </c>
       <c r="E197" t="s">
-        <v>1113</v>
+        <v>1009</v>
       </c>
       <c r="F197" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G197" t="s">
-        <v>1115</v>
+        <v>1011</v>
       </c>
       <c r="H197" t="s">
-        <v>1117</v>
+        <v>1013</v>
       </c>
       <c r="I197" t="s">
-        <v>1118</v>
+        <v>1014</v>
       </c>
       <c r="J197" t="s">
-        <v>1119</v>
+        <v>1015</v>
       </c>
       <c r="K197" t="s">
-        <v>1114</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B198">
         <v>82</v>
       </c>
       <c r="C198" t="s">
-        <v>1210</v>
+        <v>934</v>
       </c>
       <c r="D198" t="s">
-        <v>1211</v>
+        <v>1023</v>
       </c>
       <c r="E198" t="s">
-        <v>89</v>
+        <v>1024</v>
       </c>
       <c r="F198" t="s">
-        <v>1213</v>
+        <v>1026</v>
       </c>
       <c r="G198" t="s">
-        <v>1214</v>
+        <v>1027</v>
       </c>
       <c r="H198" t="s">
-        <v>1216</v>
+        <v>1029</v>
       </c>
       <c r="I198" t="s">
-        <v>1217</v>
+        <v>1030</v>
       </c>
       <c r="J198" t="s">
-        <v>1218</v>
+        <v>1031</v>
       </c>
       <c r="K198" t="s">
-        <v>1212</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B199">
         <v>82</v>
       </c>
       <c r="C199" t="s">
-        <v>1368</v>
+        <v>1087</v>
       </c>
       <c r="D199" t="s">
-        <v>1369</v>
+        <v>1112</v>
       </c>
       <c r="E199" t="s">
-        <v>1370</v>
+        <v>1113</v>
       </c>
       <c r="F199" t="s">
-        <v>1372</v>
+        <v>25</v>
       </c>
       <c r="G199" t="s">
-        <v>1373</v>
+        <v>1115</v>
       </c>
       <c r="H199" t="s">
-        <v>1375</v>
+        <v>1117</v>
       </c>
       <c r="I199" t="s">
-        <v>1376</v>
+        <v>1118</v>
       </c>
       <c r="J199" t="s">
-        <v>1377</v>
+        <v>1119</v>
       </c>
       <c r="K199" t="s">
-        <v>1371</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B200">
         <v>82</v>
       </c>
       <c r="C200" t="s">
-        <v>1534</v>
+        <v>1210</v>
       </c>
       <c r="D200" t="s">
-        <v>1608</v>
+        <v>1211</v>
       </c>
       <c r="E200" t="s">
-        <v>1609</v>
+        <v>89</v>
       </c>
       <c r="F200" t="s">
-        <v>1559</v>
+        <v>1213</v>
       </c>
       <c r="G200" t="s">
-        <v>1611</v>
+        <v>1214</v>
       </c>
       <c r="H200" t="s">
-        <v>1613</v>
+        <v>1216</v>
       </c>
       <c r="I200" t="s">
-        <v>1614</v>
+        <v>1217</v>
       </c>
       <c r="J200" t="s">
-        <v>1615</v>
+        <v>1218</v>
       </c>
       <c r="K200" t="s">
-        <v>1610</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B201">
         <v>82</v>
       </c>
       <c r="C201" t="s">
-        <v>1534</v>
+        <v>1368</v>
       </c>
       <c r="D201" t="s">
-        <v>1616</v>
+        <v>1369</v>
       </c>
       <c r="E201" t="s">
-        <v>1617</v>
+        <v>1370</v>
       </c>
       <c r="F201" t="s">
-        <v>1619</v>
+        <v>1372</v>
       </c>
       <c r="G201" t="s">
-        <v>1620</v>
+        <v>1373</v>
       </c>
       <c r="H201" t="s">
-        <v>1622</v>
+        <v>1375</v>
       </c>
       <c r="I201" t="s">
-        <v>1623</v>
+        <v>1376</v>
       </c>
       <c r="J201" t="s">
-        <v>1624</v>
+        <v>1377</v>
       </c>
       <c r="K201" t="s">
-        <v>1618</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B202">
         <v>82</v>
       </c>
       <c r="C202" t="s">
-        <v>1884</v>
+        <v>1534</v>
       </c>
       <c r="D202" t="s">
-        <v>1979</v>
+        <v>1608</v>
       </c>
       <c r="E202" t="s">
-        <v>1980</v>
+        <v>1609</v>
       </c>
       <c r="F202" t="s">
-        <v>1982</v>
+        <v>1559</v>
       </c>
       <c r="G202" t="s">
-        <v>1983</v>
+        <v>1611</v>
       </c>
       <c r="H202" t="s">
-        <v>1985</v>
+        <v>1613</v>
       </c>
       <c r="I202" t="s">
-        <v>1986</v>
+        <v>1614</v>
       </c>
       <c r="J202" t="s">
-        <v>1987</v>
+        <v>1615</v>
       </c>
       <c r="K202" t="s">
-        <v>1981</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B203">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C203" t="s">
-        <v>12</v>
+        <v>1534</v>
       </c>
       <c r="D203" t="s">
-        <v>80</v>
+        <v>1616</v>
       </c>
       <c r="E203" t="s">
-        <v>81</v>
+        <v>1617</v>
       </c>
       <c r="F203" t="s">
-        <v>25</v>
+        <v>1619</v>
       </c>
       <c r="G203" t="s">
-        <v>83</v>
+        <v>1620</v>
       </c>
       <c r="H203" t="s">
-        <v>85</v>
+        <v>1622</v>
       </c>
       <c r="I203" t="s">
-        <v>86</v>
+        <v>1623</v>
       </c>
       <c r="J203" t="s">
-        <v>87</v>
+        <v>1624</v>
       </c>
       <c r="K203" t="s">
-        <v>82</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B204">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C204" t="s">
-        <v>284</v>
+        <v>1884</v>
       </c>
       <c r="D204" t="s">
-        <v>377</v>
+        <v>1979</v>
       </c>
       <c r="E204" t="s">
-        <v>378</v>
+        <v>1980</v>
       </c>
       <c r="F204" t="s">
-        <v>380</v>
+        <v>1982</v>
       </c>
       <c r="G204" t="s">
-        <v>381</v>
+        <v>1983</v>
       </c>
       <c r="H204" t="s">
-        <v>383</v>
+        <v>1985</v>
       </c>
       <c r="I204" t="s">
-        <v>384</v>
+        <v>1986</v>
       </c>
       <c r="J204" t="s">
-        <v>385</v>
+        <v>1987</v>
       </c>
       <c r="K204" t="s">
-        <v>379</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B205">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C205" t="s">
-        <v>473</v>
+        <v>2258</v>
       </c>
       <c r="D205" t="s">
-        <v>499</v>
+        <v>2283</v>
       </c>
       <c r="E205" t="s">
-        <v>500</v>
+        <v>2284</v>
       </c>
       <c r="F205" t="s">
-        <v>502</v>
+        <v>2286</v>
       </c>
       <c r="G205" t="s">
-        <v>503</v>
+        <v>2287</v>
       </c>
       <c r="H205" t="s">
-        <v>505</v>
+        <v>2289</v>
       </c>
       <c r="I205" t="s">
-        <v>506</v>
+        <v>2290</v>
       </c>
       <c r="J205" t="s">
-        <v>507</v>
+        <v>2291</v>
       </c>
       <c r="K205" t="s">
-        <v>501</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B206">
         <v>81</v>
       </c>
       <c r="C206" t="s">
-        <v>591</v>
+        <v>12</v>
       </c>
       <c r="D206" t="s">
-        <v>616</v>
+        <v>80</v>
       </c>
       <c r="E206" t="s">
-        <v>610</v>
+        <v>81</v>
       </c>
       <c r="F206" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G206" t="s">
-        <v>618</v>
+        <v>83</v>
       </c>
       <c r="H206" t="s">
-        <v>620</v>
+        <v>85</v>
       </c>
       <c r="I206" t="s">
-        <v>621</v>
+        <v>86</v>
       </c>
       <c r="J206" t="s">
-        <v>622</v>
+        <v>87</v>
       </c>
       <c r="K206" t="s">
-        <v>617</v>
+        <v>82</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B207">
         <v>81</v>
       </c>
       <c r="C207" t="s">
-        <v>845</v>
+        <v>284</v>
       </c>
       <c r="D207" t="s">
-        <v>888</v>
+        <v>377</v>
       </c>
       <c r="E207" t="s">
-        <v>889</v>
+        <v>378</v>
       </c>
       <c r="F207" t="s">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="G207" t="s">
-        <v>891</v>
+        <v>381</v>
       </c>
       <c r="H207" t="s">
-        <v>893</v>
+        <v>383</v>
       </c>
       <c r="I207" t="s">
-        <v>894</v>
+        <v>384</v>
       </c>
       <c r="J207" t="s">
-        <v>895</v>
+        <v>385</v>
       </c>
       <c r="K207" t="s">
-        <v>890</v>
+        <v>379</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B208">
         <v>81</v>
       </c>
       <c r="C208" t="s">
-        <v>1087</v>
+        <v>473</v>
       </c>
       <c r="D208" t="s">
-        <v>1120</v>
+        <v>499</v>
       </c>
       <c r="E208" t="s">
-        <v>1121</v>
+        <v>500</v>
       </c>
       <c r="F208" t="s">
-        <v>1123</v>
+        <v>502</v>
       </c>
       <c r="G208" t="s">
-        <v>1124</v>
+        <v>503</v>
       </c>
       <c r="H208" t="s">
-        <v>1126</v>
+        <v>505</v>
       </c>
       <c r="I208" t="s">
-        <v>1127</v>
+        <v>506</v>
       </c>
       <c r="J208" t="s">
-        <v>1128</v>
+        <v>507</v>
       </c>
       <c r="K208" t="s">
-        <v>1122</v>
+        <v>501</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B209">
         <v>81</v>
       </c>
       <c r="C209" t="s">
-        <v>1394</v>
+        <v>591</v>
       </c>
       <c r="D209" t="s">
-        <v>1412</v>
+        <v>616</v>
       </c>
       <c r="E209" t="s">
-        <v>1413</v>
+        <v>610</v>
       </c>
       <c r="F209" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G209" t="s">
-        <v>1415</v>
+        <v>618</v>
       </c>
       <c r="H209" t="s">
-        <v>1417</v>
+        <v>620</v>
       </c>
       <c r="I209" t="s">
-        <v>1418</v>
+        <v>621</v>
       </c>
       <c r="J209" t="s">
-        <v>1419</v>
+        <v>622</v>
       </c>
       <c r="K209" t="s">
-        <v>1414</v>
+        <v>617</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B210">
         <v>81</v>
       </c>
       <c r="C210" t="s">
-        <v>1394</v>
+        <v>845</v>
       </c>
       <c r="D210" t="s">
-        <v>1420</v>
+        <v>888</v>
       </c>
       <c r="E210" t="s">
-        <v>1421</v>
+        <v>889</v>
       </c>
       <c r="F210" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G210" t="s">
-        <v>1423</v>
+        <v>891</v>
       </c>
       <c r="H210" t="s">
-        <v>1425</v>
+        <v>893</v>
       </c>
       <c r="I210" t="s">
-        <v>1426</v>
+        <v>894</v>
       </c>
       <c r="J210" t="s">
-        <v>1427</v>
+        <v>895</v>
       </c>
       <c r="K210" t="s">
-        <v>1422</v>
+        <v>890</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B211">
         <v>81</v>
       </c>
       <c r="C211" t="s">
-        <v>1394</v>
+        <v>1087</v>
       </c>
       <c r="D211" t="s">
-        <v>1467</v>
+        <v>1120</v>
       </c>
       <c r="E211" t="s">
-        <v>1468</v>
+        <v>1121</v>
       </c>
       <c r="F211" t="s">
-        <v>16</v>
+        <v>1123</v>
       </c>
       <c r="G211" t="s">
-        <v>1470</v>
+        <v>1124</v>
       </c>
       <c r="H211" t="s">
-        <v>1472</v>
+        <v>1126</v>
       </c>
       <c r="I211" t="s">
-        <v>1473</v>
+        <v>1127</v>
       </c>
       <c r="J211" t="s">
-        <v>1474</v>
+        <v>1128</v>
       </c>
       <c r="K211" t="s">
-        <v>1469</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B212">
         <v>81</v>
       </c>
       <c r="C212" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D212" t="s">
-        <v>271</v>
+        <v>1412</v>
       </c>
       <c r="E212" t="s">
-        <v>1600</v>
+        <v>1413</v>
       </c>
       <c r="F212" t="s">
-        <v>1602</v>
+        <v>75</v>
       </c>
       <c r="G212" t="s">
-        <v>1603</v>
+        <v>1415</v>
       </c>
       <c r="H212" t="s">
-        <v>1605</v>
+        <v>1417</v>
       </c>
       <c r="I212" t="s">
-        <v>1606</v>
+        <v>1418</v>
       </c>
       <c r="J212" t="s">
-        <v>1607</v>
+        <v>1419</v>
       </c>
       <c r="K212" t="s">
-        <v>1601</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B213">
         <v>81</v>
       </c>
       <c r="C213" t="s">
-        <v>1664</v>
+        <v>1394</v>
       </c>
       <c r="D213" t="s">
-        <v>1708</v>
+        <v>1420</v>
       </c>
       <c r="E213" t="s">
-        <v>1709</v>
+        <v>1421</v>
       </c>
       <c r="F213" t="s">
-        <v>1711</v>
+        <v>16</v>
       </c>
       <c r="G213" t="s">
-        <v>1034</v>
+        <v>1423</v>
       </c>
       <c r="H213" t="s">
-        <v>1713</v>
+        <v>1425</v>
       </c>
       <c r="I213" t="s">
-        <v>1714</v>
+        <v>1426</v>
       </c>
       <c r="J213" t="s">
-        <v>1715</v>
+        <v>1427</v>
       </c>
       <c r="K213" t="s">
-        <v>1710</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B214">
         <v>81</v>
       </c>
       <c r="C214" t="s">
-        <v>1727</v>
+        <v>1394</v>
       </c>
       <c r="D214" t="s">
-        <v>1773</v>
+        <v>1467</v>
       </c>
       <c r="E214" t="s">
-        <v>1774</v>
+        <v>1468</v>
       </c>
       <c r="F214" t="s">
         <v>16</v>
       </c>
       <c r="G214" t="s">
-        <v>1776</v>
+        <v>1470</v>
       </c>
       <c r="H214" t="s">
-        <v>1778</v>
+        <v>1472</v>
       </c>
       <c r="I214" t="s">
-        <v>79</v>
+        <v>1473</v>
       </c>
       <c r="J214" t="s">
-        <v>79</v>
+        <v>1474</v>
       </c>
       <c r="K214" t="s">
-        <v>1775</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B215">
         <v>81</v>
       </c>
       <c r="C215" t="s">
-        <v>1727</v>
+        <v>1534</v>
       </c>
       <c r="D215" t="s">
-        <v>964</v>
+        <v>271</v>
       </c>
       <c r="E215" t="s">
-        <v>362</v>
+        <v>1600</v>
       </c>
       <c r="F215" t="s">
-        <v>356</v>
+        <v>1602</v>
       </c>
       <c r="G215" t="s">
-        <v>1792</v>
+        <v>1603</v>
       </c>
       <c r="H215" t="s">
-        <v>1794</v>
+        <v>1605</v>
       </c>
       <c r="I215" t="s">
-        <v>79</v>
+        <v>1606</v>
       </c>
       <c r="J215" t="s">
-        <v>79</v>
+        <v>1607</v>
       </c>
       <c r="K215" t="s">
-        <v>1791</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B216">
         <v>81</v>
       </c>
       <c r="C216" t="s">
-        <v>1884</v>
+        <v>1664</v>
       </c>
       <c r="D216" t="s">
-        <v>1963</v>
+        <v>1708</v>
       </c>
       <c r="E216" t="s">
-        <v>1964</v>
+        <v>1709</v>
       </c>
       <c r="F216" t="s">
-        <v>25</v>
+        <v>1711</v>
       </c>
       <c r="G216" t="s">
         <v>1034</v>
       </c>
       <c r="H216" t="s">
-        <v>1967</v>
+        <v>1713</v>
       </c>
       <c r="I216" t="s">
-        <v>1968</v>
+        <v>1714</v>
       </c>
       <c r="J216" t="s">
-        <v>1969</v>
+        <v>1715</v>
       </c>
       <c r="K216" t="s">
-        <v>1965</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B217">
         <v>81</v>
       </c>
       <c r="C217" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D217" t="s">
-        <v>1979</v>
+        <v>1773</v>
       </c>
       <c r="E217" t="s">
-        <v>1988</v>
+        <v>1774</v>
       </c>
       <c r="F217" t="s">
-        <v>1982</v>
+        <v>16</v>
       </c>
       <c r="G217" t="s">
-        <v>1983</v>
+        <v>1776</v>
       </c>
       <c r="H217" t="s">
-        <v>1991</v>
+        <v>1778</v>
       </c>
       <c r="I217" t="s">
-        <v>1992</v>
+        <v>79</v>
       </c>
       <c r="J217" t="s">
-        <v>1993</v>
+        <v>79</v>
       </c>
       <c r="K217" t="s">
-        <v>1989</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B218">
         <v>81</v>
       </c>
       <c r="C218" t="s">
-        <v>2098</v>
+        <v>1727</v>
       </c>
       <c r="D218" t="s">
-        <v>2114</v>
+        <v>964</v>
       </c>
       <c r="E218" t="s">
-        <v>830</v>
+        <v>362</v>
       </c>
       <c r="F218" t="s">
-        <v>16</v>
+        <v>356</v>
       </c>
       <c r="G218" t="s">
-        <v>2116</v>
+        <v>1792</v>
       </c>
       <c r="H218" t="s">
-        <v>2118</v>
+        <v>1794</v>
       </c>
       <c r="I218" t="s">
-        <v>2119</v>
+        <v>79</v>
       </c>
       <c r="J218" t="s">
-        <v>2120</v>
+        <v>79</v>
       </c>
       <c r="K218" t="s">
-        <v>2115</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B219">
         <v>81</v>
       </c>
       <c r="C219" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D219" t="s">
-        <v>2126</v>
+        <v>1963</v>
       </c>
       <c r="E219" t="s">
-        <v>2127</v>
+        <v>1964</v>
       </c>
       <c r="F219" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G219" t="s">
-        <v>2129</v>
+        <v>1034</v>
       </c>
       <c r="H219" t="s">
-        <v>2118</v>
+        <v>1967</v>
       </c>
       <c r="I219" t="s">
-        <v>2131</v>
+        <v>1968</v>
       </c>
       <c r="J219" t="s">
-        <v>2132</v>
+        <v>1969</v>
       </c>
       <c r="K219" t="s">
-        <v>2128</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B220">
         <v>81</v>
       </c>
       <c r="C220" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D220" t="s">
-        <v>2148</v>
+        <v>1979</v>
       </c>
       <c r="E220" t="s">
-        <v>110</v>
+        <v>1988</v>
       </c>
       <c r="F220" t="s">
-        <v>25</v>
+        <v>1982</v>
       </c>
       <c r="G220" t="s">
-        <v>2150</v>
+        <v>1983</v>
       </c>
       <c r="H220" t="s">
-        <v>2152</v>
+        <v>1991</v>
       </c>
       <c r="I220" t="s">
-        <v>2153</v>
+        <v>1992</v>
       </c>
       <c r="J220" t="s">
-        <v>2154</v>
+        <v>1993</v>
       </c>
       <c r="K220" t="s">
-        <v>2149</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B221">
         <v>81</v>
@@ -32177,33 +33104,33 @@
         <v>2098</v>
       </c>
       <c r="D221" t="s">
-        <v>2184</v>
+        <v>2114</v>
       </c>
       <c r="E221" t="s">
-        <v>2177</v>
+        <v>830</v>
       </c>
       <c r="F221" t="s">
-        <v>2042</v>
+        <v>16</v>
       </c>
       <c r="G221" t="s">
-        <v>2186</v>
+        <v>2116</v>
       </c>
       <c r="H221" t="s">
-        <v>2188</v>
+        <v>2118</v>
       </c>
       <c r="I221" t="s">
-        <v>2189</v>
+        <v>2119</v>
       </c>
       <c r="J221" t="s">
-        <v>2190</v>
+        <v>2120</v>
       </c>
       <c r="K221" t="s">
-        <v>2185</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B222">
         <v>81</v>
@@ -32212,278 +33139,278 @@
         <v>2098</v>
       </c>
       <c r="D222" t="s">
-        <v>2211</v>
+        <v>2126</v>
       </c>
       <c r="E222" t="s">
-        <v>110</v>
+        <v>2127</v>
       </c>
       <c r="F222" t="s">
         <v>16</v>
       </c>
       <c r="G222" t="s">
-        <v>2220</v>
+        <v>2129</v>
       </c>
       <c r="H222" t="s">
-        <v>2222</v>
+        <v>2118</v>
       </c>
       <c r="I222" t="s">
-        <v>2223</v>
+        <v>2131</v>
       </c>
       <c r="J222" t="s">
-        <v>2224</v>
+        <v>2132</v>
       </c>
       <c r="K222" t="s">
-        <v>2219</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B223">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C223" t="s">
-        <v>934</v>
+        <v>2098</v>
       </c>
       <c r="D223" t="s">
-        <v>1039</v>
+        <v>2148</v>
       </c>
       <c r="E223" t="s">
-        <v>1040</v>
+        <v>110</v>
       </c>
       <c r="F223" t="s">
-        <v>1042</v>
+        <v>25</v>
       </c>
       <c r="G223" t="s">
-        <v>1043</v>
+        <v>2150</v>
       </c>
       <c r="H223" t="s">
-        <v>1045</v>
+        <v>2152</v>
       </c>
       <c r="I223" t="s">
-        <v>1046</v>
+        <v>2153</v>
       </c>
       <c r="J223" t="s">
-        <v>1047</v>
+        <v>2154</v>
       </c>
       <c r="K223" t="s">
-        <v>1041</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B224">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C224" t="s">
-        <v>1884</v>
+        <v>2098</v>
       </c>
       <c r="D224" t="s">
-        <v>1947</v>
+        <v>2184</v>
       </c>
       <c r="E224" t="s">
-        <v>1948</v>
+        <v>2177</v>
       </c>
       <c r="F224" t="s">
-        <v>1950</v>
+        <v>2042</v>
       </c>
       <c r="G224" t="s">
-        <v>1034</v>
+        <v>2186</v>
       </c>
       <c r="H224" t="s">
-        <v>1952</v>
+        <v>2188</v>
       </c>
       <c r="I224" t="s">
-        <v>1953</v>
+        <v>2189</v>
       </c>
       <c r="J224" t="s">
-        <v>1954</v>
+        <v>2190</v>
       </c>
       <c r="K224" t="s">
-        <v>1949</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B225">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C225" t="s">
-        <v>1884</v>
+        <v>2098</v>
       </c>
       <c r="D225" t="s">
-        <v>1970</v>
+        <v>2211</v>
       </c>
       <c r="E225" t="s">
-        <v>1971</v>
+        <v>110</v>
       </c>
       <c r="F225" t="s">
-        <v>1973</v>
+        <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>1974</v>
+        <v>2220</v>
       </c>
       <c r="H225" t="s">
-        <v>1976</v>
+        <v>2222</v>
       </c>
       <c r="I225" t="s">
-        <v>1977</v>
+        <v>2223</v>
       </c>
       <c r="J225" t="s">
-        <v>1978</v>
+        <v>2224</v>
       </c>
       <c r="K225" t="s">
-        <v>1972</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B226">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C226" t="s">
-        <v>2098</v>
+        <v>2258</v>
       </c>
       <c r="D226" t="s">
-        <v>2107</v>
+        <v>2274</v>
       </c>
       <c r="E226" t="s">
-        <v>830</v>
+        <v>2275</v>
       </c>
       <c r="F226" t="s">
-        <v>66</v>
+        <v>2277</v>
       </c>
       <c r="G226" t="s">
-        <v>2109</v>
+        <v>2278</v>
       </c>
       <c r="H226" t="s">
-        <v>2111</v>
+        <v>2280</v>
       </c>
       <c r="I226" t="s">
-        <v>2112</v>
+        <v>2281</v>
       </c>
       <c r="J226" t="s">
-        <v>2113</v>
+        <v>2282</v>
       </c>
       <c r="K226" t="s">
-        <v>2108</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B227">
         <v>80</v>
       </c>
       <c r="C227" t="s">
-        <v>2098</v>
+        <v>934</v>
       </c>
       <c r="D227" t="s">
-        <v>2133</v>
+        <v>1039</v>
       </c>
       <c r="E227" t="s">
-        <v>110</v>
+        <v>1040</v>
       </c>
       <c r="F227" t="s">
-        <v>16</v>
+        <v>1042</v>
       </c>
       <c r="G227" t="s">
-        <v>2135</v>
+        <v>1043</v>
       </c>
       <c r="H227" t="s">
-        <v>2137</v>
+        <v>1045</v>
       </c>
       <c r="I227" t="s">
-        <v>2138</v>
+        <v>1046</v>
       </c>
       <c r="J227" t="s">
-        <v>2139</v>
+        <v>1047</v>
       </c>
       <c r="K227" t="s">
-        <v>2134</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B228">
         <v>80</v>
       </c>
       <c r="C228" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D228" t="s">
-        <v>2140</v>
+        <v>1947</v>
       </c>
       <c r="E228" t="s">
-        <v>2141</v>
+        <v>1948</v>
       </c>
       <c r="F228" t="s">
-        <v>75</v>
+        <v>1950</v>
       </c>
       <c r="G228" t="s">
-        <v>2143</v>
+        <v>1034</v>
       </c>
       <c r="H228" t="s">
-        <v>2145</v>
+        <v>1952</v>
       </c>
       <c r="I228" t="s">
-        <v>2146</v>
+        <v>1953</v>
       </c>
       <c r="J228" t="s">
-        <v>2147</v>
+        <v>1954</v>
       </c>
       <c r="K228" t="s">
-        <v>2142</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B229">
         <v>80</v>
       </c>
       <c r="C229" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D229" t="s">
-        <v>2155</v>
+        <v>1970</v>
       </c>
       <c r="E229" t="s">
-        <v>110</v>
+        <v>1971</v>
       </c>
       <c r="F229" t="s">
-        <v>66</v>
+        <v>1973</v>
       </c>
       <c r="G229" t="s">
-        <v>2157</v>
+        <v>1974</v>
       </c>
       <c r="H229" t="s">
-        <v>2159</v>
+        <v>1976</v>
       </c>
       <c r="I229" t="s">
-        <v>2160</v>
+        <v>1977</v>
       </c>
       <c r="J229" t="s">
-        <v>2161</v>
+        <v>1978</v>
       </c>
       <c r="K229" t="s">
-        <v>2156</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B230">
         <v>80</v>
@@ -32492,33 +33419,33 @@
         <v>2098</v>
       </c>
       <c r="D230" t="s">
-        <v>2162</v>
+        <v>2107</v>
       </c>
       <c r="E230" t="s">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="F230" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G230" t="s">
-        <v>2171</v>
+        <v>2109</v>
       </c>
       <c r="H230" t="s">
-        <v>2173</v>
+        <v>2111</v>
       </c>
       <c r="I230" t="s">
-        <v>2174</v>
+        <v>2112</v>
       </c>
       <c r="J230" t="s">
-        <v>2175</v>
+        <v>2113</v>
       </c>
       <c r="K230" t="s">
-        <v>2170</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B231">
         <v>80</v>
@@ -32527,33 +33454,33 @@
         <v>2098</v>
       </c>
       <c r="D231" t="s">
-        <v>2203</v>
+        <v>2133</v>
       </c>
       <c r="E231" t="s">
-        <v>2204</v>
+        <v>110</v>
       </c>
       <c r="F231" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="G231" t="s">
-        <v>2206</v>
+        <v>2135</v>
       </c>
       <c r="H231" t="s">
-        <v>2208</v>
+        <v>2137</v>
       </c>
       <c r="I231" t="s">
-        <v>2209</v>
+        <v>2138</v>
       </c>
       <c r="J231" t="s">
-        <v>2210</v>
+        <v>2139</v>
       </c>
       <c r="K231" t="s">
-        <v>2205</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>2269</v>
+        <v>2388</v>
       </c>
       <c r="B232">
         <v>80</v>
@@ -32562,28 +33489,203 @@
         <v>2098</v>
       </c>
       <c r="D232" t="s">
+        <v>2140</v>
+      </c>
+      <c r="E232" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F232" t="s">
+        <v>75</v>
+      </c>
+      <c r="G232" t="s">
+        <v>2143</v>
+      </c>
+      <c r="H232" t="s">
+        <v>2145</v>
+      </c>
+      <c r="I232" t="s">
+        <v>2146</v>
+      </c>
+      <c r="J232" t="s">
+        <v>2147</v>
+      </c>
+      <c r="K232" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B233">
+        <v>80</v>
+      </c>
+      <c r="C233" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D233" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E233" t="s">
+        <v>110</v>
+      </c>
+      <c r="F233" t="s">
+        <v>66</v>
+      </c>
+      <c r="G233" t="s">
+        <v>2157</v>
+      </c>
+      <c r="H233" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I233" t="s">
+        <v>2160</v>
+      </c>
+      <c r="J233" t="s">
+        <v>2161</v>
+      </c>
+      <c r="K233" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B234">
+        <v>80</v>
+      </c>
+      <c r="C234" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D234" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E234" t="s">
+        <v>110</v>
+      </c>
+      <c r="F234" t="s">
+        <v>16</v>
+      </c>
+      <c r="G234" t="s">
+        <v>2171</v>
+      </c>
+      <c r="H234" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I234" t="s">
+        <v>2174</v>
+      </c>
+      <c r="J234" t="s">
+        <v>2175</v>
+      </c>
+      <c r="K234" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B235">
+        <v>80</v>
+      </c>
+      <c r="C235" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D235" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E235" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F235" t="s">
+        <v>106</v>
+      </c>
+      <c r="G235" t="s">
+        <v>2206</v>
+      </c>
+      <c r="H235" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I235" t="s">
+        <v>2209</v>
+      </c>
+      <c r="J235" t="s">
+        <v>2210</v>
+      </c>
+      <c r="K235" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B236">
+        <v>80</v>
+      </c>
+      <c r="C236" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D236" t="s">
         <v>2225</v>
       </c>
-      <c r="E232" t="s">
+      <c r="E236" t="s">
         <v>2226</v>
       </c>
-      <c r="F232" t="s">
+      <c r="F236" t="s">
         <v>16</v>
       </c>
-      <c r="G232" t="s">
+      <c r="G236" t="s">
         <v>112</v>
       </c>
-      <c r="H232" t="s">
+      <c r="H236" t="s">
         <v>2229</v>
       </c>
-      <c r="I232" t="s">
+      <c r="I236" t="s">
         <v>2230</v>
       </c>
-      <c r="J232" t="s">
+      <c r="J236" t="s">
         <v>2231</v>
       </c>
-      <c r="K232" t="s">
+      <c r="K236" t="s">
         <v>2227</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B237">
+        <v>80</v>
+      </c>
+      <c r="C237" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D237" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E237" t="s">
+        <v>2293</v>
+      </c>
+      <c r="F237" t="s">
+        <v>747</v>
+      </c>
+      <c r="G237" t="s">
+        <v>2295</v>
+      </c>
+      <c r="H237" t="s">
+        <v>2297</v>
+      </c>
+      <c r="I237" t="s">
+        <v>2298</v>
+      </c>
+      <c r="J237" t="s">
+        <v>2299</v>
+      </c>
+      <c r="K237" t="s">
+        <v>2294</v>
       </c>
     </row>
   </sheetData>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="2417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6952" uniqueCount="2477">
   <si>
     <t>日期</t>
   </si>
@@ -7145,6 +7145,186 @@
   </si>
   <si>
     <t>突出SolidWorks/CAE仿真与结构设计能力；弱化血管支架方向，强调通用机械设计与材料学基础；补充样机试制与工艺文件编制经验。</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（肺栓塞介入器械）</t>
+  </si>
+  <si>
+    <t>国内专注肺栓塞介入治疗器械研发的公司，围绕肺血管及血栓清除介入医疗器械的研发、生产和销售。岗位涉及介入取栓/血栓清除器械的设计开发、工艺与验证，要求生物医学工程/材料/机械相关专业，有植介入器械研发经验优先。</t>
+  </si>
+  <si>
+    <t>https://www.51job.com/</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|肺栓塞介入取栓器械研发，属血管介入方向，与支架/介入能力相关</t>
+  </si>
+  <si>
+    <t>研究85/技能78/学历95/行业100/企业85</t>
+  </si>
+  <si>
+    <t>公司专注肺血管及血栓清除介入器械，属血管介入细分赛道；岗位需要植介入器械设计开发能力，与候选人血管支架研究方向和材料学、生物相容性、动物实验技能高度相关，且上海为优先城市。</t>
+  </si>
+  <si>
+    <t>强调血管介入器械（支架/取栓）结构设计、力学性能测试与动物实验经验；突出对血栓清除/取栓器械的理解与文献调研；补充ISO 10993生物相容性评价相关实验技能；附上项目中从概念到验证的完整开发闭环。</t>
+  </si>
+  <si>
+    <t>湖南华翔医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>负责血管支架产品的工艺开发与优化，参与新产品试制、工艺参数确认与转产；本科以上学历，3-5年相关经验，材料/机械相关专业。公司同时有校园招聘与高学历人才需求（硕士）。</t>
+  </si>
+  <si>
+    <t>https://www.jobui.com/</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|血管支架工艺岗，研究方向高度相关，但偏工艺且需经验</t>
+  </si>
+  <si>
+    <t>研究88/技能78/学历90/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位直接围绕血管支架工艺开发，与候选人研究方向完全一致；公司有校园招聘和高学历人才需求，硕士可争取，能发挥材料学与支架设计技能。</t>
+  </si>
+  <si>
+    <t>重点展示血管支架结构、材料与加工工艺（切割、抛光、热处理等）相关知识；补充工艺参数优化与试制经验；将生物相容性评价与动物实验作为能力佐证；说明对支架转产流程的理解。</t>
+  </si>
+  <si>
+    <t>微至医疗</t>
+  </si>
+  <si>
+    <t>2027届校园招聘（研发工程师）</t>
+  </si>
+  <si>
+    <t>面向2027届毕业生校园招聘，研发岗位要求对医疗器械研发充满热情；技术支持工程师要求本科及以上学历。招聘流程含网申与邮件投递，邮件主题注明应聘岗位。</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/</t>
+  </si>
+  <si>
+    <t>智能匹配80分【校园招聘】|强烈推荐|医疗器械研发校招，行业匹配、应届生优先，方向泛医疗</t>
+  </si>
+  <si>
+    <t>研究75/技能70/学历100/行业100/企业82</t>
+  </si>
+  <si>
+    <t>明确的2027届校园招聘项目，面向应届生；医疗器械研发岗位与候选人行业方向一致，可作为保底校招投递选择，积累面试与流程经验。</t>
+  </si>
+  <si>
+    <t>针对研发岗突出生物医学工程背景与血管支架课题；若投技术支持岗则强调沟通与临床理解；准备一页纸项目成果清单；注意按邮件主题格式规范投递。</t>
+  </si>
+  <si>
+    <t>博动医疗科技</t>
+  </si>
+  <si>
+    <t>研发工程师（泛血管介入精准诊断器械）</t>
+  </si>
+  <si>
+    <t>公司为全球泛血管介入精准诊断领域领跑者，与上海交通大学等合作。岗位围绕泛血管介入精准诊断器械研发，涉及影像/器械结合，招聘研发相关人才，要求生物医学工程/材料/机械等相关专业。</t>
+  </si>
+  <si>
+    <t>智能匹配81分【社招】|强烈推荐|泛血管介入器械研发，方向相关，偏影像诊断交叉</t>
+  </si>
+  <si>
+    <t>研究80/技能68/学历95/行业100/企业88</t>
+  </si>
+  <si>
+    <t>泛血管介入方向创新企业，与血管介入赛道一致；上海为优先城市。岗位对生物医学工程背景友好，可发挥介入器械理解与材料背景，适合作为介入领域拓展投递。</t>
+  </si>
+  <si>
+    <t>突出血管介入器械与血管支架相关研究与技能；补充影像学/介入相关项目或对血管介入诊疗流程的理解；强调医工交叉能力与文献调研能力。</t>
+  </si>
+  <si>
+    <t>弘睿生物</t>
+  </si>
+  <si>
+    <t>高分子材料研发工程师（生物降解材料）</t>
+  </si>
+  <si>
+    <t>负责公司全生物降解材料产品配方的开发工作，对产品开发过程中的疑难点给予解决方案并推进；要求高分子材料、生物材料等相关专业，具备可降解材料开发经验者优先。</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|生物降解材料配方开发，与可降解支架材料技能重合，方向较相关</t>
+  </si>
+  <si>
+    <t>研究78/技能80/学历95/行业95/企业80</t>
+  </si>
+  <si>
+    <t>聚焦生物降解材料配方开发，与候选人材料学、可降解材料技能高度重合；可降解材料是血管支架重要方向，岗位可积累材料开发经验，利于向可降解支架研发迁移。</t>
+  </si>
+  <si>
+    <t>突出高分子/可降解材料配方、聚合与降解性能测试经验；强调材料性能测试与生物相容性评价能力；将血管支架可降解材料课题成果与文献理解写入项目经历。</t>
+  </si>
+  <si>
+    <t>金发科技股份有限公司</t>
+  </si>
+  <si>
+    <t>研发工程师（医疗健康板块）</t>
+  </si>
+  <si>
+    <t>医疗健康板块研发工程师/机械工程师岗位；要求1-5年改性塑料行业产品开发经验，有生物降解材料开发经验优先；思路清晰、善于钻研，具备沟通表达与团队协作能力。另设海外院校研发工程师（医疗健康板块）校招通道。</t>
+  </si>
+  <si>
+    <t>https://www.kingfa.com/</t>
+  </si>
+  <si>
+    <t>智能匹配80分【校园招聘】|强烈推荐|医疗健康板块材料研发，生物降解材料经验优先，技能较重合</t>
+  </si>
+  <si>
+    <t>研究72/技能78/学历95/行业82/企业90</t>
+  </si>
+  <si>
+    <t>上市公司医疗健康板块，材料研发岗位与候选人材料学、生物降解材料技能重合；设有海外院校校招通道，平台稳定、培养体系完善，可作为材料方向职业发展选择。</t>
+  </si>
+  <si>
+    <t>突出高分子材料、生物降解材料相关课题与实验技能；强调材料性能测试与配方开发经验；将生物医用材料方向的动机写进求职意向，弱化纯支架经历以免被判定不匹配。</t>
+  </si>
+  <si>
+    <t>中元汇吉</t>
+  </si>
+  <si>
+    <t>2026届校园招聘（仪器研发类-工程类：系统/硬件/机械/流体/研发质量/验证工程师）</t>
+  </si>
+  <si>
+    <t>2026届校园招聘，专业类别包括生物医学工程、机械类、仪器科学、化学类、自动化；工作地点深圳/重庆。岗位含系统工程师、硬件工程师、机械工程师、流体工程师、整机测试工程师、研发质量工程师、验证工程师。</t>
+  </si>
+  <si>
+    <t>深圳/重庆</t>
+  </si>
+  <si>
+    <t>https://www.zhihu.com/</t>
+  </si>
+  <si>
+    <t>智能匹配78分【校园招聘】|值得考虑|医疗器械2026届校招，应届优先、行业匹配，方向泛器械</t>
+  </si>
+  <si>
+    <t>研究70/技能68/学历100/行业95/企业82</t>
+  </si>
+  <si>
+    <t>明确的2026届校园招聘，专业类别明确包含生物医学工程；深圳为优先城市，医疗器械行业匹配，岗位类型丰富可选择机械/系统/验证方向，适合作为校招批量投递目标。</t>
+  </si>
+  <si>
+    <t>根据岗位方向调整：机械/结构岗突出支架结构设计与有限元；验证岗突出生物相容性与测试经验；系统岗突出生物医学工程综合背景；统一强调医疗器械开发流程认知。</t>
+  </si>
+  <si>
+    <t>永沁泉智能设备</t>
+  </si>
+  <si>
+    <t>生物材料研发工程师，负责生物材料相关产品研发与实验，涉及材料制备、性能表征与评价；要求生物材料、高分子材料、生物医学工程等相关专业，硕士优先。</t>
+  </si>
+  <si>
+    <t>智能匹配78分【社招】|值得考虑|生物材料研发，材料学技能重合，方向属生物医用材料</t>
+  </si>
+  <si>
+    <t>研究72/技能75/学历95/行业90/企业75</t>
+  </si>
+  <si>
+    <t>生物材料研发岗位，与候选人材料学、生物相容性评价技能重合；北京为优先城市，可积累生物医用材料研发经验，作为材料方向备选。</t>
+  </si>
+  <si>
+    <t>突出材料制备、表征与生物相容性评价实验技能；强调细胞毒性、血液相容性等测试经验；将血管支架材料研究作为生物材料研发能力的案例。</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -7699,7 +7879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L319"/>
+  <dimension ref="A1:L327"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -19835,6 +20015,310 @@
       </c>
       <c r="L319" t="s">
         <v>2376</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B320" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C320" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D320" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E320" t="s">
+        <v>16</v>
+      </c>
+      <c r="F320" t="s">
+        <v>2380</v>
+      </c>
+      <c r="G320">
+        <v>9</v>
+      </c>
+      <c r="H320" t="s">
+        <v>2381</v>
+      </c>
+      <c r="I320">
+        <v>86</v>
+      </c>
+      <c r="J320" t="s">
+        <v>2382</v>
+      </c>
+      <c r="K320" t="s">
+        <v>2383</v>
+      </c>
+      <c r="L320" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B321" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C321" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D321" t="s">
+        <v>2386</v>
+      </c>
+      <c r="E321" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F321" t="s">
+        <v>2387</v>
+      </c>
+      <c r="G321">
+        <v>9</v>
+      </c>
+      <c r="H321" t="s">
+        <v>2388</v>
+      </c>
+      <c r="I321">
+        <v>86</v>
+      </c>
+      <c r="J321" t="s">
+        <v>2389</v>
+      </c>
+      <c r="K321" t="s">
+        <v>2390</v>
+      </c>
+      <c r="L321" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B322" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C322" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D322" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E322" t="s">
+        <v>66</v>
+      </c>
+      <c r="F322" t="s">
+        <v>2395</v>
+      </c>
+      <c r="G322">
+        <v>8</v>
+      </c>
+      <c r="H322" t="s">
+        <v>2396</v>
+      </c>
+      <c r="I322">
+        <v>80</v>
+      </c>
+      <c r="J322" t="s">
+        <v>2397</v>
+      </c>
+      <c r="K322" t="s">
+        <v>2398</v>
+      </c>
+      <c r="L322" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B323" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C323" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D323" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E323" t="s">
+        <v>16</v>
+      </c>
+      <c r="F323" t="s">
+        <v>2395</v>
+      </c>
+      <c r="G323">
+        <v>8</v>
+      </c>
+      <c r="H323" t="s">
+        <v>2403</v>
+      </c>
+      <c r="I323">
+        <v>81</v>
+      </c>
+      <c r="J323" t="s">
+        <v>2404</v>
+      </c>
+      <c r="K323" t="s">
+        <v>2405</v>
+      </c>
+      <c r="L323" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B324" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C324" t="s">
+        <v>2408</v>
+      </c>
+      <c r="D324" t="s">
+        <v>2409</v>
+      </c>
+      <c r="E324" t="s">
+        <v>75</v>
+      </c>
+      <c r="F324" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G324">
+        <v>8</v>
+      </c>
+      <c r="H324" t="s">
+        <v>2410</v>
+      </c>
+      <c r="I324">
+        <v>83</v>
+      </c>
+      <c r="J324" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K324" t="s">
+        <v>2412</v>
+      </c>
+      <c r="L324" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B325" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C325" t="s">
+        <v>2415</v>
+      </c>
+      <c r="D325" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E325" t="s">
+        <v>124</v>
+      </c>
+      <c r="F325" t="s">
+        <v>2417</v>
+      </c>
+      <c r="G325">
+        <v>8</v>
+      </c>
+      <c r="H325" t="s">
+        <v>2418</v>
+      </c>
+      <c r="I325">
+        <v>80</v>
+      </c>
+      <c r="J325" t="s">
+        <v>2419</v>
+      </c>
+      <c r="K325" t="s">
+        <v>2420</v>
+      </c>
+      <c r="L325" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B326" t="s">
+        <v>2422</v>
+      </c>
+      <c r="C326" t="s">
+        <v>2423</v>
+      </c>
+      <c r="D326" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E326" t="s">
+        <v>2425</v>
+      </c>
+      <c r="F326" t="s">
+        <v>2426</v>
+      </c>
+      <c r="G326">
+        <v>8</v>
+      </c>
+      <c r="H326" t="s">
+        <v>2427</v>
+      </c>
+      <c r="I326">
+        <v>78</v>
+      </c>
+      <c r="J326" t="s">
+        <v>2428</v>
+      </c>
+      <c r="K326" t="s">
+        <v>2429</v>
+      </c>
+      <c r="L326" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B327" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C327" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D327" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E327" t="s">
+        <v>25</v>
+      </c>
+      <c r="F327" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G327">
+        <v>8</v>
+      </c>
+      <c r="H327" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I327">
+        <v>78</v>
+      </c>
+      <c r="J327" t="s">
+        <v>2434</v>
+      </c>
+      <c r="K327" t="s">
+        <v>2435</v>
+      </c>
+      <c r="L327" t="s">
+        <v>2436</v>
       </c>
     </row>
   </sheetData>
@@ -19868,7 +20352,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2377</v>
+        <v>2437</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -19877,16 +20361,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2378</v>
+        <v>2438</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2379</v>
+        <v>2439</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2380</v>
+        <v>2440</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2381</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -19900,13 +20384,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2382</v>
+        <v>2442</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2383</v>
+        <v>2443</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>2384</v>
+        <v>2444</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -19949,7 +20433,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>2389</v>
+        <v>2449</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -19959,31 +20443,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>2390</v>
+        <v>2450</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2391</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2392</v>
+        <v>2452</v>
       </c>
       <c r="B4">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2393</v>
+        <v>2453</v>
       </c>
       <c r="B5" t="s">
-        <v>2394</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2395</v>
+        <v>2455</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -19991,7 +20475,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2396</v>
+        <v>2456</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -19999,23 +20483,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2397</v>
+        <v>2457</v>
       </c>
       <c r="B8">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2398</v>
+        <v>2458</v>
       </c>
       <c r="B9">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2399</v>
+        <v>2459</v>
       </c>
       <c r="B10">
         <v>16</v>
@@ -20023,15 +20507,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2400</v>
+        <v>2460</v>
       </c>
       <c r="B11" t="s">
-        <v>2258</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>2401</v>
+        <v>2461</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -20041,15 +20525,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>2402</v>
+        <v>2462</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>2403</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2404</v>
+        <v>2464</v>
       </c>
       <c r="B16" s="5">
         <v>8</v>
@@ -20057,23 +20541,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2405</v>
+        <v>2465</v>
       </c>
       <c r="B17" s="5">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2406</v>
+        <v>2466</v>
       </c>
       <c r="B18" s="5">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2407</v>
+        <v>2467</v>
       </c>
       <c r="B19" s="5">
         <v>16</v>
@@ -20081,7 +20565,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2408</v>
+        <v>2468</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -20089,7 +20573,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2409</v>
+        <v>2469</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -20097,7 +20581,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2410</v>
+        <v>2470</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -20105,7 +20589,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2411</v>
+        <v>2471</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -20113,7 +20597,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2412</v>
+        <v>2472</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -20121,7 +20605,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2413</v>
+        <v>2473</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -20129,7 +20613,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>2414</v>
+        <v>2474</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -20141,7 +20625,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>2415</v>
+        <v>2475</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -20159,7 +20643,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>2416</v>
+        <v>2476</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -23862,25 +24346,25 @@
         <v>143</v>
       </c>
       <c r="B172" t="s">
-        <v>1200</v>
+        <v>2377</v>
       </c>
       <c r="C172" t="s">
-        <v>1201</v>
+        <v>1338</v>
       </c>
       <c r="D172" t="s">
-        <v>1202</v>
+        <v>2378</v>
       </c>
       <c r="E172" t="s">
-        <v>1204</v>
+        <v>16</v>
       </c>
       <c r="F172" t="s">
-        <v>1205</v>
+        <v>2380</v>
       </c>
       <c r="G172">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H172" t="s">
-        <v>1206</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -23888,25 +24372,25 @@
         <v>144</v>
       </c>
       <c r="B173" t="s">
-        <v>12</v>
+        <v>2377</v>
       </c>
       <c r="C173" t="s">
-        <v>72</v>
+        <v>2385</v>
       </c>
       <c r="D173" t="s">
-        <v>73</v>
+        <v>1083</v>
       </c>
       <c r="E173" t="s">
-        <v>75</v>
+        <v>2235</v>
       </c>
       <c r="F173" t="s">
-        <v>76</v>
+        <v>2387</v>
       </c>
       <c r="G173">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H173" t="s">
-        <v>77</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -23914,25 +24398,25 @@
         <v>145</v>
       </c>
       <c r="B174" t="s">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="C174" t="s">
-        <v>80</v>
+        <v>1201</v>
       </c>
       <c r="D174" t="s">
-        <v>81</v>
+        <v>1202</v>
       </c>
       <c r="E174" t="s">
-        <v>25</v>
+        <v>1204</v>
       </c>
       <c r="F174" t="s">
-        <v>83</v>
+        <v>1205</v>
       </c>
       <c r="G174">
         <v>8</v>
       </c>
       <c r="H174" t="s">
-        <v>84</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -23943,22 +24427,22 @@
         <v>12</v>
       </c>
       <c r="C175" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D175" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="E175" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F175" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="G175">
         <v>8</v>
       </c>
       <c r="H175" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -23969,22 +24453,22 @@
         <v>12</v>
       </c>
       <c r="C176" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D176" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E176" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F176" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="G176">
         <v>8</v>
       </c>
       <c r="H176" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -23995,22 +24479,22 @@
         <v>12</v>
       </c>
       <c r="C177" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D177" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E177" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F177" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G177">
         <v>8</v>
       </c>
       <c r="H177" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -24021,22 +24505,22 @@
         <v>12</v>
       </c>
       <c r="C178" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D178" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E178" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F178" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G178">
         <v>8</v>
       </c>
       <c r="H178" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -24047,22 +24531,22 @@
         <v>12</v>
       </c>
       <c r="C179" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D179" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="E179" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F179" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="G179">
         <v>8</v>
       </c>
       <c r="H179" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -24073,22 +24557,22 @@
         <v>12</v>
       </c>
       <c r="C180" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="D180" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E180" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F180" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="G180">
         <v>8</v>
       </c>
       <c r="H180" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -24096,25 +24580,25 @@
         <v>152</v>
       </c>
       <c r="B181" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C181" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
       <c r="D181" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E181" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="F181" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="G181">
         <v>8</v>
       </c>
       <c r="H181" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -24122,25 +24606,25 @@
         <v>153</v>
       </c>
       <c r="B182" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C182" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="D182" t="s">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="E182" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F182" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="G182">
         <v>8</v>
       </c>
       <c r="H182" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -24151,22 +24635,22 @@
         <v>159</v>
       </c>
       <c r="C183" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="D183" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="E183" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="F183" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="G183">
         <v>8</v>
       </c>
       <c r="H183" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -24177,22 +24661,22 @@
         <v>159</v>
       </c>
       <c r="C184" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="D184" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="E184" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="F184" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="G184">
         <v>8</v>
       </c>
       <c r="H184" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -24203,22 +24687,22 @@
         <v>159</v>
       </c>
       <c r="C185" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D185" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E185" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="F185" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G185">
         <v>8</v>
       </c>
       <c r="H185" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -24229,22 +24713,22 @@
         <v>159</v>
       </c>
       <c r="C186" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D186" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E186" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F186" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="G186">
         <v>8</v>
       </c>
       <c r="H186" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -24255,22 +24739,22 @@
         <v>159</v>
       </c>
       <c r="C187" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D187" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E187" t="s">
         <v>16</v>
       </c>
       <c r="F187" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G187">
         <v>8</v>
       </c>
       <c r="H187" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -24281,22 +24765,22 @@
         <v>159</v>
       </c>
       <c r="C188" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D188" t="s">
-        <v>255</v>
+        <v>154</v>
       </c>
       <c r="E188" t="s">
-        <v>257</v>
+        <v>25</v>
       </c>
       <c r="F188" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="G188">
         <v>8</v>
       </c>
       <c r="H188" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -24307,22 +24791,22 @@
         <v>159</v>
       </c>
       <c r="C189" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D189" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="E189" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F189" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="G189">
         <v>8</v>
       </c>
       <c r="H189" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -24333,22 +24817,22 @@
         <v>159</v>
       </c>
       <c r="C190" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D190" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E190" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F190" t="s">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="G190">
         <v>8</v>
       </c>
       <c r="H190" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -24359,22 +24843,22 @@
         <v>159</v>
       </c>
       <c r="C191" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="E191" t="s">
-        <v>280</v>
+        <v>147</v>
       </c>
       <c r="F191" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="G191">
         <v>8</v>
       </c>
       <c r="H191" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -24382,25 +24866,25 @@
         <v>163</v>
       </c>
       <c r="B192" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C192" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="D192" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="E192" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="F192" t="s">
-        <v>319</v>
+        <v>58</v>
       </c>
       <c r="G192">
         <v>8</v>
       </c>
       <c r="H192" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -24408,25 +24892,25 @@
         <v>164</v>
       </c>
       <c r="B193" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C193" t="s">
-        <v>338</v>
+        <v>277</v>
       </c>
       <c r="D193" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="E193" t="s">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="F193" t="s">
-        <v>342</v>
+        <v>281</v>
       </c>
       <c r="G193">
         <v>8</v>
       </c>
       <c r="H193" t="s">
-        <v>343</v>
+        <v>282</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -24437,22 +24921,22 @@
         <v>284</v>
       </c>
       <c r="C194" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="D194" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="E194" t="s">
-        <v>98</v>
+        <v>318</v>
       </c>
       <c r="F194" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="G194">
         <v>8</v>
       </c>
       <c r="H194" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -24463,22 +24947,22 @@
         <v>284</v>
       </c>
       <c r="C195" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D195" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="E195" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="F195" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="G195">
         <v>8</v>
       </c>
       <c r="H195" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -24489,22 +24973,22 @@
         <v>284</v>
       </c>
       <c r="C196" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="D196" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="E196" t="s">
-        <v>380</v>
+        <v>98</v>
       </c>
       <c r="F196" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="G196">
         <v>8</v>
       </c>
       <c r="H196" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -24515,22 +24999,22 @@
         <v>284</v>
       </c>
       <c r="C197" t="s">
-        <v>144</v>
+        <v>353</v>
       </c>
       <c r="D197" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E197" t="s">
-        <v>396</v>
+        <v>356</v>
       </c>
       <c r="F197" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="G197">
         <v>8</v>
       </c>
       <c r="H197" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -24538,25 +25022,25 @@
         <v>169</v>
       </c>
       <c r="B198" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C198" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="D198" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="E198" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F198" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="G198">
         <v>8</v>
       </c>
       <c r="H198" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -24564,25 +25048,25 @@
         <v>170</v>
       </c>
       <c r="B199" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C199" t="s">
-        <v>418</v>
+        <v>144</v>
       </c>
       <c r="D199" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="E199" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F199" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="G199">
         <v>8</v>
       </c>
       <c r="H199" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -24593,22 +25077,22 @@
         <v>402</v>
       </c>
       <c r="C200" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D200" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="E200" t="s">
         <v>66</v>
       </c>
       <c r="F200" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="G200">
         <v>8</v>
       </c>
       <c r="H200" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -24619,22 +25103,22 @@
         <v>402</v>
       </c>
       <c r="C201" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D201" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="E201" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F201" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="G201">
         <v>8</v>
       </c>
       <c r="H201" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -24642,25 +25126,25 @@
         <v>173</v>
       </c>
       <c r="B202" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C202" t="s">
-        <v>483</v>
+        <v>424</v>
       </c>
       <c r="D202" t="s">
-        <v>122</v>
+        <v>425</v>
       </c>
       <c r="E202" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F202" t="s">
-        <v>486</v>
+        <v>427</v>
       </c>
       <c r="G202">
         <v>8</v>
       </c>
       <c r="H202" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -24668,25 +25152,25 @@
         <v>174</v>
       </c>
       <c r="B203" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C203" t="s">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="D203" t="s">
-        <v>492</v>
+        <v>431</v>
       </c>
       <c r="E203" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F203" t="s">
-        <v>494</v>
+        <v>433</v>
       </c>
       <c r="G203">
         <v>8</v>
       </c>
       <c r="H203" t="s">
-        <v>495</v>
+        <v>434</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -24697,22 +25181,22 @@
         <v>473</v>
       </c>
       <c r="C204" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="D204" t="s">
-        <v>500</v>
+        <v>122</v>
       </c>
       <c r="E204" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="F204" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="G204">
         <v>8</v>
       </c>
       <c r="H204" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -24723,22 +25207,22 @@
         <v>473</v>
       </c>
       <c r="C205" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="D205" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="E205" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="F205" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="G205">
         <v>8</v>
       </c>
       <c r="H205" t="s">
-        <v>537</v>
+        <v>495</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -24749,22 +25233,22 @@
         <v>473</v>
       </c>
       <c r="C206" t="s">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="D206" t="s">
-        <v>551</v>
+        <v>500</v>
       </c>
       <c r="E206" t="s">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="F206" t="s">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="G206">
         <v>8</v>
       </c>
       <c r="H206" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -24772,25 +25256,25 @@
         <v>178</v>
       </c>
       <c r="B207" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C207" t="s">
-        <v>578</v>
+        <v>532</v>
       </c>
       <c r="D207" t="s">
-        <v>579</v>
+        <v>533</v>
       </c>
       <c r="E207" t="s">
-        <v>66</v>
+        <v>535</v>
       </c>
       <c r="F207" t="s">
-        <v>581</v>
+        <v>536</v>
       </c>
       <c r="G207">
         <v>8</v>
       </c>
       <c r="H207" t="s">
-        <v>582</v>
+        <v>537</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -24798,25 +25282,25 @@
         <v>179</v>
       </c>
       <c r="B208" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C208" t="s">
-        <v>584</v>
+        <v>550</v>
       </c>
       <c r="D208" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="E208" t="s">
-        <v>587</v>
+        <v>16</v>
       </c>
       <c r="F208" t="s">
-        <v>588</v>
+        <v>553</v>
       </c>
       <c r="G208">
         <v>8</v>
       </c>
       <c r="H208" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -24824,25 +25308,25 @@
         <v>180</v>
       </c>
       <c r="B209" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C209" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="D209" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="E209" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F209" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="G209">
         <v>8</v>
       </c>
       <c r="H209" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -24850,25 +25334,25 @@
         <v>181</v>
       </c>
       <c r="B210" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C210" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="D210" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="E210" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F210" t="s">
-        <v>618</v>
+        <v>588</v>
       </c>
       <c r="G210">
         <v>8</v>
       </c>
       <c r="H210" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -24879,22 +25363,22 @@
         <v>591</v>
       </c>
       <c r="C211" t="s">
-        <v>557</v>
+        <v>601</v>
       </c>
       <c r="D211" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="E211" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F211" t="s">
-        <v>468</v>
+        <v>604</v>
       </c>
       <c r="G211">
         <v>8</v>
       </c>
       <c r="H211" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -24905,10 +25389,10 @@
         <v>591</v>
       </c>
       <c r="C212" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="D212" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="E212" t="s">
         <v>16</v>
@@ -24920,7 +25404,7 @@
         <v>8</v>
       </c>
       <c r="H212" t="s">
-        <v>646</v>
+        <v>619</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -24931,22 +25415,22 @@
         <v>591</v>
       </c>
       <c r="C213" t="s">
-        <v>650</v>
+        <v>557</v>
       </c>
       <c r="D213" t="s">
-        <v>651</v>
+        <v>623</v>
       </c>
       <c r="E213" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F213" t="s">
-        <v>653</v>
+        <v>468</v>
       </c>
       <c r="G213">
         <v>8</v>
       </c>
       <c r="H213" t="s">
-        <v>654</v>
+        <v>625</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -24957,22 +25441,22 @@
         <v>591</v>
       </c>
       <c r="C214" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="D214" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="E214" t="s">
-        <v>661</v>
+        <v>16</v>
       </c>
       <c r="F214" t="s">
-        <v>662</v>
+        <v>618</v>
       </c>
       <c r="G214">
         <v>8</v>
       </c>
       <c r="H214" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -24983,22 +25467,22 @@
         <v>591</v>
       </c>
       <c r="C215" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="D215" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="E215" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F215" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="G215">
         <v>8</v>
       </c>
       <c r="H215" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -25009,22 +25493,22 @@
         <v>591</v>
       </c>
       <c r="C216" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="D216" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="E216" t="s">
-        <v>66</v>
+        <v>661</v>
       </c>
       <c r="F216" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="G216">
         <v>8</v>
       </c>
       <c r="H216" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -25032,16 +25516,16 @@
         <v>188</v>
       </c>
       <c r="B217" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C217" t="s">
-        <v>714</v>
+        <v>666</v>
       </c>
       <c r="D217" t="s">
-        <v>715</v>
+        <v>667</v>
       </c>
       <c r="E217" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F217" t="s">
         <v>604</v>
@@ -25050,7 +25534,7 @@
         <v>8</v>
       </c>
       <c r="H217" t="s">
-        <v>717</v>
+        <v>669</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -25058,25 +25542,25 @@
         <v>189</v>
       </c>
       <c r="B218" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C218" t="s">
-        <v>721</v>
+        <v>673</v>
       </c>
       <c r="D218" t="s">
-        <v>722</v>
+        <v>674</v>
       </c>
       <c r="E218" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F218" t="s">
-        <v>724</v>
+        <v>676</v>
       </c>
       <c r="G218">
         <v>8</v>
       </c>
       <c r="H218" t="s">
-        <v>725</v>
+        <v>677</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -25087,22 +25571,22 @@
         <v>697</v>
       </c>
       <c r="C219" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="D219" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="E219" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="F219" t="s">
-        <v>732</v>
+        <v>604</v>
       </c>
       <c r="G219">
         <v>8</v>
       </c>
       <c r="H219" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
@@ -25113,22 +25597,22 @@
         <v>697</v>
       </c>
       <c r="C220" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="D220" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="E220" t="s">
-        <v>739</v>
+        <v>25</v>
       </c>
       <c r="F220" t="s">
-        <v>604</v>
+        <v>724</v>
       </c>
       <c r="G220">
         <v>8</v>
       </c>
       <c r="H220" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -25139,22 +25623,22 @@
         <v>697</v>
       </c>
       <c r="C221" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="D221" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="E221" t="s">
-        <v>747</v>
+        <v>535</v>
       </c>
       <c r="F221" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="G221">
         <v>8</v>
       </c>
       <c r="H221" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -25165,22 +25649,22 @@
         <v>697</v>
       </c>
       <c r="C222" t="s">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="D222" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="E222" t="s">
-        <v>756</v>
+        <v>739</v>
       </c>
       <c r="F222" t="s">
-        <v>757</v>
+        <v>604</v>
       </c>
       <c r="G222">
         <v>8</v>
       </c>
       <c r="H222" t="s">
-        <v>758</v>
+        <v>740</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -25191,22 +25675,22 @@
         <v>697</v>
       </c>
       <c r="C223" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="D223" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="E223" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="F223" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="G223">
         <v>8</v>
       </c>
       <c r="H223" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
@@ -25214,25 +25698,25 @@
         <v>195</v>
       </c>
       <c r="B224" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C224" t="s">
-        <v>791</v>
+        <v>753</v>
       </c>
       <c r="D224" t="s">
-        <v>610</v>
+        <v>754</v>
       </c>
       <c r="E224" t="s">
-        <v>793</v>
+        <v>756</v>
       </c>
       <c r="F224" t="s">
-        <v>794</v>
+        <v>757</v>
       </c>
       <c r="G224">
         <v>8</v>
       </c>
       <c r="H224" t="s">
-        <v>795</v>
+        <v>758</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
@@ -25240,25 +25724,25 @@
         <v>196</v>
       </c>
       <c r="B225" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C225" t="s">
-        <v>807</v>
+        <v>760</v>
       </c>
       <c r="D225" t="s">
-        <v>808</v>
+        <v>761</v>
       </c>
       <c r="E225" t="s">
-        <v>810</v>
+        <v>763</v>
       </c>
       <c r="F225" t="s">
-        <v>811</v>
+        <v>764</v>
       </c>
       <c r="G225">
         <v>8</v>
       </c>
       <c r="H225" t="s">
-        <v>812</v>
+        <v>765</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -25269,22 +25753,22 @@
         <v>773</v>
       </c>
       <c r="C226" t="s">
-        <v>816</v>
+        <v>791</v>
       </c>
       <c r="D226" t="s">
-        <v>110</v>
+        <v>610</v>
       </c>
       <c r="E226" t="s">
-        <v>16</v>
+        <v>793</v>
       </c>
       <c r="F226" t="s">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="G226">
         <v>8</v>
       </c>
       <c r="H226" t="s">
-        <v>819</v>
+        <v>795</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
@@ -25292,25 +25776,25 @@
         <v>198</v>
       </c>
       <c r="B227" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C227" t="s">
-        <v>888</v>
+        <v>807</v>
       </c>
       <c r="D227" t="s">
-        <v>889</v>
+        <v>808</v>
       </c>
       <c r="E227" t="s">
-        <v>25</v>
+        <v>810</v>
       </c>
       <c r="F227" t="s">
-        <v>891</v>
+        <v>811</v>
       </c>
       <c r="G227">
         <v>8</v>
       </c>
       <c r="H227" t="s">
-        <v>892</v>
+        <v>812</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -25318,25 +25802,25 @@
         <v>199</v>
       </c>
       <c r="B228" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C228" t="s">
-        <v>896</v>
+        <v>816</v>
       </c>
       <c r="D228" t="s">
-        <v>897</v>
+        <v>110</v>
       </c>
       <c r="E228" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F228" t="s">
-        <v>899</v>
+        <v>818</v>
       </c>
       <c r="G228">
         <v>8</v>
       </c>
       <c r="H228" t="s">
-        <v>900</v>
+        <v>819</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -25347,22 +25831,22 @@
         <v>845</v>
       </c>
       <c r="C229" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="D229" t="s">
-        <v>585</v>
+        <v>889</v>
       </c>
       <c r="E229" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F229" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="G229">
         <v>8</v>
       </c>
       <c r="H229" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
     </row>
   </sheetData>
@@ -25378,7 +25862,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K237"/>
+  <dimension ref="A1:K243"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -25395,10 +25879,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>2385</v>
+        <v>2445</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2386</v>
+        <v>2446</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -25425,12 +25909,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>2387</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -25465,7 +25949,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -25500,7 +25984,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -25535,7 +26019,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -25570,7 +26054,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -25605,7 +26089,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -25640,7 +26124,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B8">
         <v>95</v>
@@ -25675,7 +26159,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B9">
         <v>95</v>
@@ -25710,7 +26194,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B10">
         <v>94</v>
@@ -25745,7 +26229,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B11">
         <v>94</v>
@@ -25780,7 +26264,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B12">
         <v>93</v>
@@ -25815,7 +26299,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B13">
         <v>93</v>
@@ -25850,7 +26334,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B14">
         <v>93</v>
@@ -25885,7 +26369,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B15">
         <v>93</v>
@@ -25920,7 +26404,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B16">
         <v>92</v>
@@ -25955,7 +26439,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B17">
         <v>92</v>
@@ -25990,7 +26474,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B18">
         <v>92</v>
@@ -26025,7 +26509,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B19">
         <v>92</v>
@@ -26060,7 +26544,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B20">
         <v>91</v>
@@ -26095,7 +26579,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B21">
         <v>91</v>
@@ -26130,7 +26614,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B22">
         <v>91</v>
@@ -26165,7 +26649,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B23">
         <v>91</v>
@@ -26200,7 +26684,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B24">
         <v>91</v>
@@ -26235,7 +26719,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B25">
         <v>91</v>
@@ -26270,7 +26754,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B26">
         <v>91</v>
@@ -26305,7 +26789,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B27">
         <v>91</v>
@@ -26340,7 +26824,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B28">
         <v>90</v>
@@ -26375,7 +26859,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B29">
         <v>90</v>
@@ -26410,7 +26894,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B30">
         <v>90</v>
@@ -26445,7 +26929,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B31">
         <v>90</v>
@@ -26480,7 +26964,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B32">
         <v>90</v>
@@ -26515,7 +26999,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B33">
         <v>90</v>
@@ -26550,7 +27034,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B34">
         <v>90</v>
@@ -26585,7 +27069,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B35">
         <v>90</v>
@@ -26620,7 +27104,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B36">
         <v>90</v>
@@ -26655,7 +27139,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B37">
         <v>90</v>
@@ -26690,7 +27174,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B38">
         <v>90</v>
@@ -26725,7 +27209,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B39">
         <v>90</v>
@@ -26760,7 +27244,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B40">
         <v>90</v>
@@ -26795,7 +27279,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B41">
         <v>89</v>
@@ -26830,7 +27314,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B42">
         <v>89</v>
@@ -26865,7 +27349,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B43">
         <v>89</v>
@@ -26900,7 +27384,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B44">
         <v>89</v>
@@ -26935,7 +27419,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B45">
         <v>89</v>
@@ -26970,7 +27454,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B46">
         <v>89</v>
@@ -27005,7 +27489,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B47">
         <v>89</v>
@@ -27040,7 +27524,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B48">
         <v>89</v>
@@ -27075,7 +27559,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B49">
         <v>89</v>
@@ -27110,7 +27594,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B50">
         <v>89</v>
@@ -27145,7 +27629,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B51">
         <v>89</v>
@@ -27180,7 +27664,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B52">
         <v>89</v>
@@ -27215,7 +27699,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B53">
         <v>89</v>
@@ -27250,7 +27734,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B54">
         <v>89</v>
@@ -27285,7 +27769,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B55">
         <v>89</v>
@@ -27320,7 +27804,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B56">
         <v>89</v>
@@ -27355,7 +27839,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B57">
         <v>89</v>
@@ -27390,7 +27874,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B58">
         <v>89</v>
@@ -27425,7 +27909,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B59">
         <v>89</v>
@@ -27460,7 +27944,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B60">
         <v>89</v>
@@ -27495,7 +27979,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B61">
         <v>89</v>
@@ -27530,7 +28014,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B62">
         <v>89</v>
@@ -27565,7 +28049,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B63">
         <v>89</v>
@@ -27600,7 +28084,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B64">
         <v>88</v>
@@ -27635,7 +28119,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B65">
         <v>88</v>
@@ -27670,7 +28154,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B66">
         <v>88</v>
@@ -27705,7 +28189,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B67">
         <v>88</v>
@@ -27740,7 +28224,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B68">
         <v>88</v>
@@ -27775,7 +28259,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B69">
         <v>88</v>
@@ -27810,7 +28294,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B70">
         <v>88</v>
@@ -27845,7 +28329,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B71">
         <v>88</v>
@@ -27880,7 +28364,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B72">
         <v>88</v>
@@ -27915,7 +28399,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B73">
         <v>88</v>
@@ -27950,7 +28434,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B74">
         <v>88</v>
@@ -27985,7 +28469,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B75">
         <v>88</v>
@@ -28020,7 +28504,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B76">
         <v>88</v>
@@ -28055,7 +28539,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B77">
         <v>88</v>
@@ -28090,7 +28574,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B78">
         <v>88</v>
@@ -28125,7 +28609,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B79">
         <v>88</v>
@@ -28160,7 +28644,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B80">
         <v>88</v>
@@ -28195,7 +28679,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B81">
         <v>87</v>
@@ -28230,7 +28714,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B82">
         <v>87</v>
@@ -28265,7 +28749,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B83">
         <v>87</v>
@@ -28300,7 +28784,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B84">
         <v>87</v>
@@ -28335,7 +28819,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B85">
         <v>87</v>
@@ -28370,7 +28854,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B86">
         <v>87</v>
@@ -28405,7 +28889,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B87">
         <v>87</v>
@@ -28440,7 +28924,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B88">
         <v>87</v>
@@ -28475,7 +28959,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B89">
         <v>87</v>
@@ -28510,7 +28994,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B90">
         <v>87</v>
@@ -28545,7 +29029,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B91">
         <v>87</v>
@@ -28580,7 +29064,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B92">
         <v>87</v>
@@ -28615,7 +29099,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B93">
         <v>87</v>
@@ -28650,7 +29134,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B94">
         <v>87</v>
@@ -28685,7 +29169,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B95">
         <v>87</v>
@@ -28720,7 +29204,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B96">
         <v>87</v>
@@ -28755,7 +29239,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B97">
         <v>87</v>
@@ -28790,7 +29274,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B98">
         <v>86</v>
@@ -28825,7 +29309,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B99">
         <v>86</v>
@@ -28860,7 +29344,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B100">
         <v>86</v>
@@ -28895,7 +29379,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B101">
         <v>86</v>
@@ -28930,7 +29414,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B102">
         <v>86</v>
@@ -28965,7 +29449,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B103">
         <v>86</v>
@@ -29000,7 +29484,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B104">
         <v>86</v>
@@ -29035,7 +29519,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B105">
         <v>86</v>
@@ -29070,7 +29554,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B106">
         <v>86</v>
@@ -29105,7 +29589,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B107">
         <v>86</v>
@@ -29140,7 +29624,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B108">
         <v>86</v>
@@ -29175,7 +29659,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B109">
         <v>86</v>
@@ -29210,7 +29694,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B110">
         <v>86</v>
@@ -29245,7 +29729,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B111">
         <v>86</v>
@@ -29280,7 +29764,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B112">
         <v>86</v>
@@ -29315,7 +29799,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B113">
         <v>86</v>
@@ -29350,7 +29834,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B114">
         <v>86</v>
@@ -29385,7 +29869,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B115">
         <v>86</v>
@@ -29420,7 +29904,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B116">
         <v>86</v>
@@ -29455,7 +29939,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B117">
         <v>86</v>
@@ -29490,7 +29974,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B118">
         <v>86</v>
@@ -29525,7 +30009,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B119">
         <v>86</v>
@@ -29560,7 +30044,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B120">
         <v>86</v>
@@ -29595,7 +30079,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B121">
         <v>86</v>
@@ -29630,7 +30114,7 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B122">
         <v>86</v>
@@ -29665,252 +30149,252 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B123">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C123" t="s">
-        <v>12</v>
+        <v>2377</v>
       </c>
       <c r="D123" t="s">
-        <v>55</v>
+        <v>1338</v>
       </c>
       <c r="E123" t="s">
-        <v>56</v>
+        <v>2378</v>
       </c>
       <c r="F123" t="s">
         <v>16</v>
       </c>
       <c r="G123" t="s">
-        <v>58</v>
+        <v>2380</v>
       </c>
       <c r="H123" t="s">
-        <v>60</v>
+        <v>2382</v>
       </c>
       <c r="I123" t="s">
-        <v>61</v>
+        <v>2383</v>
       </c>
       <c r="J123" t="s">
-        <v>62</v>
+        <v>2384</v>
       </c>
       <c r="K123" t="s">
-        <v>57</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B124">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C124" t="s">
-        <v>12</v>
+        <v>2377</v>
       </c>
       <c r="D124" t="s">
-        <v>128</v>
+        <v>2385</v>
       </c>
       <c r="E124" t="s">
-        <v>89</v>
+        <v>1083</v>
       </c>
       <c r="F124" t="s">
-        <v>130</v>
+        <v>2235</v>
       </c>
       <c r="G124" t="s">
-        <v>131</v>
+        <v>2387</v>
       </c>
       <c r="H124" t="s">
-        <v>133</v>
+        <v>2389</v>
       </c>
       <c r="I124" t="s">
-        <v>134</v>
+        <v>2390</v>
       </c>
       <c r="J124" t="s">
-        <v>135</v>
+        <v>2391</v>
       </c>
       <c r="K124" t="s">
-        <v>129</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B125">
         <v>85</v>
       </c>
       <c r="C125" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D125" t="s">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="E125" t="s">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="F125" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G125" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="H125" t="s">
-        <v>312</v>
+        <v>60</v>
       </c>
       <c r="I125" t="s">
-        <v>313</v>
+        <v>61</v>
       </c>
       <c r="J125" t="s">
-        <v>314</v>
+        <v>62</v>
       </c>
       <c r="K125" t="s">
-        <v>309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B126">
         <v>85</v>
       </c>
       <c r="C126" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D126" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E126" t="s">
-        <v>403</v>
+        <v>89</v>
       </c>
       <c r="F126" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G126" t="s">
-        <v>405</v>
+        <v>131</v>
       </c>
       <c r="H126" t="s">
-        <v>407</v>
+        <v>133</v>
       </c>
       <c r="I126" t="s">
-        <v>408</v>
+        <v>134</v>
       </c>
       <c r="J126" t="s">
-        <v>409</v>
+        <v>135</v>
       </c>
       <c r="K126" t="s">
-        <v>404</v>
+        <v>129</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B127">
         <v>85</v>
       </c>
       <c r="C127" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D127" t="s">
-        <v>474</v>
+        <v>300</v>
       </c>
       <c r="E127" t="s">
-        <v>475</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
-        <v>477</v>
+        <v>147</v>
       </c>
       <c r="G127" t="s">
-        <v>478</v>
+        <v>310</v>
       </c>
       <c r="H127" t="s">
-        <v>480</v>
+        <v>312</v>
       </c>
       <c r="I127" t="s">
-        <v>481</v>
+        <v>313</v>
       </c>
       <c r="J127" t="s">
-        <v>482</v>
+        <v>314</v>
       </c>
       <c r="K127" t="s">
-        <v>476</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B128">
         <v>85</v>
       </c>
       <c r="C128" t="s">
-        <v>773</v>
+        <v>402</v>
       </c>
       <c r="D128" t="s">
-        <v>774</v>
+        <v>55</v>
       </c>
       <c r="E128" t="s">
-        <v>783</v>
+        <v>403</v>
       </c>
       <c r="F128" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G128" t="s">
-        <v>786</v>
+        <v>405</v>
       </c>
       <c r="H128" t="s">
-        <v>788</v>
+        <v>407</v>
       </c>
       <c r="I128" t="s">
-        <v>789</v>
+        <v>408</v>
       </c>
       <c r="J128" t="s">
-        <v>790</v>
+        <v>409</v>
       </c>
       <c r="K128" t="s">
-        <v>784</v>
+        <v>404</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B129">
         <v>85</v>
       </c>
       <c r="C129" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D129" t="s">
-        <v>799</v>
+        <v>474</v>
       </c>
       <c r="E129" t="s">
-        <v>800</v>
+        <v>475</v>
       </c>
       <c r="F129" t="s">
-        <v>793</v>
+        <v>477</v>
       </c>
       <c r="G129" t="s">
-        <v>802</v>
+        <v>478</v>
       </c>
       <c r="H129" t="s">
-        <v>804</v>
+        <v>480</v>
       </c>
       <c r="I129" t="s">
-        <v>805</v>
+        <v>481</v>
       </c>
       <c r="J129" t="s">
-        <v>806</v>
+        <v>482</v>
       </c>
       <c r="K129" t="s">
-        <v>801</v>
+        <v>476</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B130">
         <v>85</v>
@@ -29919,383 +30403,383 @@
         <v>773</v>
       </c>
       <c r="D130" t="s">
-        <v>821</v>
+        <v>774</v>
       </c>
       <c r="E130" t="s">
-        <v>822</v>
+        <v>783</v>
       </c>
       <c r="F130" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="G130" t="s">
-        <v>824</v>
+        <v>786</v>
       </c>
       <c r="H130" t="s">
-        <v>826</v>
+        <v>788</v>
       </c>
       <c r="I130" t="s">
-        <v>827</v>
+        <v>789</v>
       </c>
       <c r="J130" t="s">
-        <v>828</v>
+        <v>790</v>
       </c>
       <c r="K130" t="s">
-        <v>823</v>
+        <v>784</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B131">
         <v>85</v>
       </c>
       <c r="C131" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D131" t="s">
-        <v>989</v>
+        <v>799</v>
       </c>
       <c r="E131" t="s">
-        <v>990</v>
+        <v>800</v>
       </c>
       <c r="F131" t="s">
-        <v>75</v>
+        <v>793</v>
       </c>
       <c r="G131" t="s">
-        <v>959</v>
+        <v>802</v>
       </c>
       <c r="H131" t="s">
-        <v>993</v>
+        <v>804</v>
       </c>
       <c r="I131" t="s">
-        <v>994</v>
+        <v>805</v>
       </c>
       <c r="J131" t="s">
-        <v>995</v>
+        <v>806</v>
       </c>
       <c r="K131" t="s">
-        <v>991</v>
+        <v>801</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B132">
         <v>85</v>
       </c>
       <c r="C132" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D132" t="s">
-        <v>1065</v>
+        <v>821</v>
       </c>
       <c r="E132" t="s">
-        <v>1066</v>
+        <v>822</v>
       </c>
       <c r="F132" t="s">
-        <v>147</v>
+        <v>777</v>
       </c>
       <c r="G132" t="s">
-        <v>1068</v>
+        <v>824</v>
       </c>
       <c r="H132" t="s">
-        <v>1070</v>
+        <v>826</v>
       </c>
       <c r="I132" t="s">
-        <v>1071</v>
+        <v>827</v>
       </c>
       <c r="J132" t="s">
-        <v>1072</v>
+        <v>828</v>
       </c>
       <c r="K132" t="s">
-        <v>1067</v>
+        <v>823</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B133">
         <v>85</v>
       </c>
       <c r="C133" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D133" t="s">
-        <v>1242</v>
+        <v>989</v>
       </c>
       <c r="E133" t="s">
-        <v>610</v>
+        <v>990</v>
       </c>
       <c r="F133" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G133" t="s">
-        <v>604</v>
+        <v>959</v>
       </c>
       <c r="H133" t="s">
-        <v>312</v>
+        <v>993</v>
       </c>
       <c r="I133" t="s">
-        <v>1245</v>
+        <v>994</v>
       </c>
       <c r="J133" t="s">
-        <v>1246</v>
+        <v>995</v>
       </c>
       <c r="K133" t="s">
-        <v>1243</v>
+        <v>991</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B134">
         <v>85</v>
       </c>
       <c r="C134" t="s">
-        <v>1300</v>
+        <v>934</v>
       </c>
       <c r="D134" t="s">
-        <v>1345</v>
+        <v>1065</v>
       </c>
       <c r="E134" t="s">
-        <v>1346</v>
+        <v>1066</v>
       </c>
       <c r="F134" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G134" t="s">
-        <v>1348</v>
+        <v>1068</v>
       </c>
       <c r="H134" t="s">
-        <v>312</v>
+        <v>1070</v>
       </c>
       <c r="I134" t="s">
-        <v>1350</v>
+        <v>1071</v>
       </c>
       <c r="J134" t="s">
-        <v>1351</v>
+        <v>1072</v>
       </c>
       <c r="K134" t="s">
-        <v>1347</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B135">
         <v>85</v>
       </c>
       <c r="C135" t="s">
-        <v>1394</v>
+        <v>1227</v>
       </c>
       <c r="D135" t="s">
-        <v>1459</v>
+        <v>1242</v>
       </c>
       <c r="E135" t="s">
-        <v>1460</v>
+        <v>610</v>
       </c>
       <c r="F135" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G135" t="s">
-        <v>1462</v>
+        <v>604</v>
       </c>
       <c r="H135" t="s">
-        <v>1464</v>
+        <v>312</v>
       </c>
       <c r="I135" t="s">
-        <v>1465</v>
+        <v>1245</v>
       </c>
       <c r="J135" t="s">
-        <v>1466</v>
+        <v>1246</v>
       </c>
       <c r="K135" t="s">
-        <v>1461</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B136">
         <v>85</v>
       </c>
       <c r="C136" t="s">
-        <v>1534</v>
+        <v>1300</v>
       </c>
       <c r="D136" t="s">
-        <v>1535</v>
+        <v>1345</v>
       </c>
       <c r="E136" t="s">
-        <v>1543</v>
+        <v>1346</v>
       </c>
       <c r="F136" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="G136" t="s">
-        <v>1538</v>
+        <v>1348</v>
       </c>
       <c r="H136" t="s">
-        <v>1546</v>
+        <v>312</v>
       </c>
       <c r="I136" t="s">
-        <v>1547</v>
+        <v>1350</v>
       </c>
       <c r="J136" t="s">
-        <v>1548</v>
+        <v>1351</v>
       </c>
       <c r="K136" t="s">
-        <v>1544</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B137">
         <v>85</v>
       </c>
       <c r="C137" t="s">
-        <v>1625</v>
+        <v>1394</v>
       </c>
       <c r="D137" t="s">
-        <v>1626</v>
+        <v>1459</v>
       </c>
       <c r="E137" t="s">
-        <v>1627</v>
+        <v>1460</v>
       </c>
       <c r="F137" t="s">
-        <v>1629</v>
+        <v>66</v>
       </c>
       <c r="G137" t="s">
-        <v>1630</v>
+        <v>1462</v>
       </c>
       <c r="H137" t="s">
-        <v>1632</v>
+        <v>1464</v>
       </c>
       <c r="I137" t="s">
-        <v>1633</v>
+        <v>1465</v>
       </c>
       <c r="J137" t="s">
-        <v>1634</v>
+        <v>1466</v>
       </c>
       <c r="K137" t="s">
-        <v>1628</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B138">
         <v>85</v>
       </c>
       <c r="C138" t="s">
-        <v>1625</v>
+        <v>1534</v>
       </c>
       <c r="D138" t="s">
-        <v>1635</v>
+        <v>1535</v>
       </c>
       <c r="E138" t="s">
-        <v>110</v>
+        <v>1543</v>
       </c>
       <c r="F138" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="G138" t="s">
-        <v>1637</v>
+        <v>1538</v>
       </c>
       <c r="H138" t="s">
-        <v>1639</v>
+        <v>1546</v>
       </c>
       <c r="I138" t="s">
-        <v>1640</v>
+        <v>1547</v>
       </c>
       <c r="J138" t="s">
-        <v>1641</v>
+        <v>1548</v>
       </c>
       <c r="K138" t="s">
-        <v>1636</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B139">
         <v>85</v>
       </c>
       <c r="C139" t="s">
-        <v>1727</v>
+        <v>1625</v>
       </c>
       <c r="D139" t="s">
-        <v>1795</v>
+        <v>1626</v>
       </c>
       <c r="E139" t="s">
-        <v>1796</v>
+        <v>1627</v>
       </c>
       <c r="F139" t="s">
-        <v>25</v>
+        <v>1629</v>
       </c>
       <c r="G139" t="s">
-        <v>1798</v>
+        <v>1630</v>
       </c>
       <c r="H139" t="s">
-        <v>1800</v>
+        <v>1632</v>
       </c>
       <c r="I139" t="s">
-        <v>1801</v>
+        <v>1633</v>
       </c>
       <c r="J139" t="s">
-        <v>1802</v>
+        <v>1634</v>
       </c>
       <c r="K139" t="s">
-        <v>1797</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B140">
         <v>85</v>
       </c>
       <c r="C140" t="s">
-        <v>1727</v>
+        <v>1625</v>
       </c>
       <c r="D140" t="s">
-        <v>1201</v>
+        <v>1635</v>
       </c>
       <c r="E140" t="s">
-        <v>1845</v>
+        <v>110</v>
       </c>
       <c r="F140" t="s">
-        <v>1847</v>
+        <v>16</v>
       </c>
       <c r="G140" t="s">
-        <v>1848</v>
+        <v>1637</v>
       </c>
       <c r="H140" t="s">
-        <v>1850</v>
+        <v>1639</v>
       </c>
       <c r="I140" t="s">
-        <v>79</v>
+        <v>1640</v>
       </c>
       <c r="J140" t="s">
-        <v>79</v>
+        <v>1641</v>
       </c>
       <c r="K140" t="s">
-        <v>1846</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B141">
         <v>85</v>
@@ -30304,313 +30788,313 @@
         <v>1727</v>
       </c>
       <c r="D141" t="s">
-        <v>1873</v>
+        <v>1795</v>
       </c>
       <c r="E141" t="s">
-        <v>1874</v>
+        <v>1796</v>
       </c>
       <c r="F141" t="s">
-        <v>1876</v>
+        <v>25</v>
       </c>
       <c r="G141" t="s">
-        <v>1754</v>
+        <v>1798</v>
       </c>
       <c r="H141" t="s">
-        <v>1878</v>
+        <v>1800</v>
       </c>
       <c r="I141" t="s">
-        <v>79</v>
+        <v>1801</v>
       </c>
       <c r="J141" t="s">
-        <v>79</v>
+        <v>1802</v>
       </c>
       <c r="K141" t="s">
-        <v>1875</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B142">
         <v>85</v>
       </c>
       <c r="C142" t="s">
-        <v>1994</v>
+        <v>1727</v>
       </c>
       <c r="D142" t="s">
-        <v>2039</v>
+        <v>1201</v>
       </c>
       <c r="E142" t="s">
-        <v>2040</v>
+        <v>1845</v>
       </c>
       <c r="F142" t="s">
-        <v>2042</v>
+        <v>1847</v>
       </c>
       <c r="G142" t="s">
-        <v>2043</v>
+        <v>1848</v>
       </c>
       <c r="H142" t="s">
-        <v>2045</v>
+        <v>1850</v>
       </c>
       <c r="I142" t="s">
-        <v>2046</v>
+        <v>79</v>
       </c>
       <c r="J142" t="s">
-        <v>2047</v>
+        <v>79</v>
       </c>
       <c r="K142" t="s">
-        <v>2041</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B143">
         <v>85</v>
       </c>
       <c r="C143" t="s">
-        <v>1994</v>
+        <v>1727</v>
       </c>
       <c r="D143" t="s">
-        <v>2090</v>
+        <v>1873</v>
       </c>
       <c r="E143" t="s">
-        <v>2091</v>
+        <v>1874</v>
       </c>
       <c r="F143" t="s">
-        <v>25</v>
+        <v>1876</v>
       </c>
       <c r="G143" t="s">
-        <v>2093</v>
+        <v>1754</v>
       </c>
       <c r="H143" t="s">
-        <v>2095</v>
+        <v>1878</v>
       </c>
       <c r="I143" t="s">
-        <v>2096</v>
+        <v>79</v>
       </c>
       <c r="J143" t="s">
-        <v>2097</v>
+        <v>79</v>
       </c>
       <c r="K143" t="s">
-        <v>2092</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B144">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C144" t="s">
-        <v>12</v>
+        <v>1994</v>
       </c>
       <c r="D144" t="s">
-        <v>144</v>
+        <v>2039</v>
       </c>
       <c r="E144" t="s">
-        <v>145</v>
+        <v>2040</v>
       </c>
       <c r="F144" t="s">
-        <v>147</v>
+        <v>2042</v>
       </c>
       <c r="G144" t="s">
-        <v>148</v>
+        <v>2043</v>
       </c>
       <c r="H144" t="s">
-        <v>150</v>
+        <v>2045</v>
       </c>
       <c r="I144" t="s">
-        <v>151</v>
+        <v>2046</v>
       </c>
       <c r="J144" t="s">
-        <v>152</v>
+        <v>2047</v>
       </c>
       <c r="K144" t="s">
-        <v>146</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B145">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C145" t="s">
-        <v>284</v>
+        <v>1994</v>
       </c>
       <c r="D145" t="s">
-        <v>144</v>
+        <v>2090</v>
       </c>
       <c r="E145" t="s">
-        <v>394</v>
+        <v>2091</v>
       </c>
       <c r="F145" t="s">
-        <v>396</v>
+        <v>25</v>
       </c>
       <c r="G145" t="s">
-        <v>397</v>
+        <v>2093</v>
       </c>
       <c r="H145" t="s">
-        <v>399</v>
+        <v>2095</v>
       </c>
       <c r="I145" t="s">
-        <v>400</v>
+        <v>2096</v>
       </c>
       <c r="J145" t="s">
-        <v>401</v>
+        <v>2097</v>
       </c>
       <c r="K145" t="s">
-        <v>395</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B146">
         <v>84</v>
       </c>
       <c r="C146" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E146" t="s">
-        <v>411</v>
+        <v>145</v>
       </c>
       <c r="F146" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="G146" t="s">
-        <v>413</v>
+        <v>148</v>
       </c>
       <c r="H146" t="s">
-        <v>415</v>
+        <v>150</v>
       </c>
       <c r="I146" t="s">
-        <v>416</v>
+        <v>151</v>
       </c>
       <c r="J146" t="s">
-        <v>417</v>
+        <v>152</v>
       </c>
       <c r="K146" t="s">
-        <v>412</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B147">
         <v>84</v>
       </c>
       <c r="C147" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D147" t="s">
-        <v>483</v>
+        <v>144</v>
       </c>
       <c r="E147" t="s">
-        <v>122</v>
+        <v>394</v>
       </c>
       <c r="F147" t="s">
-        <v>485</v>
+        <v>396</v>
       </c>
       <c r="G147" t="s">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="H147" t="s">
-        <v>488</v>
+        <v>399</v>
       </c>
       <c r="I147" t="s">
-        <v>489</v>
+        <v>400</v>
       </c>
       <c r="J147" t="s">
-        <v>490</v>
+        <v>401</v>
       </c>
       <c r="K147" t="s">
-        <v>484</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B148">
         <v>84</v>
       </c>
       <c r="C148" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D148" t="s">
-        <v>714</v>
+        <v>410</v>
       </c>
       <c r="E148" t="s">
-        <v>715</v>
+        <v>411</v>
       </c>
       <c r="F148" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G148" t="s">
-        <v>604</v>
+        <v>413</v>
       </c>
       <c r="H148" t="s">
-        <v>718</v>
+        <v>415</v>
       </c>
       <c r="I148" t="s">
-        <v>719</v>
+        <v>416</v>
       </c>
       <c r="J148" t="s">
-        <v>720</v>
+        <v>417</v>
       </c>
       <c r="K148" t="s">
-        <v>716</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B149">
         <v>84</v>
       </c>
       <c r="C149" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D149" t="s">
-        <v>721</v>
+        <v>483</v>
       </c>
       <c r="E149" t="s">
-        <v>722</v>
+        <v>122</v>
       </c>
       <c r="F149" t="s">
-        <v>25</v>
+        <v>485</v>
       </c>
       <c r="G149" t="s">
-        <v>724</v>
+        <v>486</v>
       </c>
       <c r="H149" t="s">
-        <v>726</v>
+        <v>488</v>
       </c>
       <c r="I149" t="s">
-        <v>727</v>
+        <v>489</v>
       </c>
       <c r="J149" t="s">
-        <v>728</v>
+        <v>490</v>
       </c>
       <c r="K149" t="s">
-        <v>723</v>
+        <v>484</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B150">
         <v>84</v>
@@ -30619,173 +31103,173 @@
         <v>697</v>
       </c>
       <c r="D150" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="E150" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="F150" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="G150" t="s">
-        <v>732</v>
+        <v>604</v>
       </c>
       <c r="H150" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="I150" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="J150" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="K150" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B151">
         <v>84</v>
       </c>
       <c r="C151" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D151" t="s">
-        <v>791</v>
+        <v>721</v>
       </c>
       <c r="E151" t="s">
-        <v>610</v>
+        <v>722</v>
       </c>
       <c r="F151" t="s">
-        <v>793</v>
+        <v>25</v>
       </c>
       <c r="G151" t="s">
-        <v>794</v>
+        <v>724</v>
       </c>
       <c r="H151" t="s">
-        <v>796</v>
+        <v>726</v>
       </c>
       <c r="I151" t="s">
-        <v>797</v>
+        <v>727</v>
       </c>
       <c r="J151" t="s">
-        <v>798</v>
+        <v>728</v>
       </c>
       <c r="K151" t="s">
-        <v>792</v>
+        <v>723</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B152">
         <v>84</v>
       </c>
       <c r="C152" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="D152" t="s">
-        <v>896</v>
+        <v>729</v>
       </c>
       <c r="E152" t="s">
-        <v>897</v>
+        <v>730</v>
       </c>
       <c r="F152" t="s">
-        <v>25</v>
+        <v>535</v>
       </c>
       <c r="G152" t="s">
-        <v>899</v>
+        <v>732</v>
       </c>
       <c r="H152" t="s">
-        <v>901</v>
+        <v>726</v>
       </c>
       <c r="I152" t="s">
-        <v>902</v>
+        <v>734</v>
       </c>
       <c r="J152" t="s">
-        <v>903</v>
+        <v>735</v>
       </c>
       <c r="K152" t="s">
-        <v>898</v>
+        <v>731</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B153">
         <v>84</v>
       </c>
       <c r="C153" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D153" t="s">
-        <v>964</v>
+        <v>791</v>
       </c>
       <c r="E153" t="s">
-        <v>965</v>
+        <v>610</v>
       </c>
       <c r="F153" t="s">
-        <v>967</v>
+        <v>793</v>
       </c>
       <c r="G153" t="s">
-        <v>968</v>
+        <v>794</v>
       </c>
       <c r="H153" t="s">
-        <v>970</v>
+        <v>796</v>
       </c>
       <c r="I153" t="s">
-        <v>971</v>
+        <v>797</v>
       </c>
       <c r="J153" t="s">
-        <v>972</v>
+        <v>798</v>
       </c>
       <c r="K153" t="s">
-        <v>966</v>
+        <v>792</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B154">
         <v>84</v>
       </c>
       <c r="C154" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D154" t="s">
-        <v>950</v>
+        <v>896</v>
       </c>
       <c r="E154" t="s">
-        <v>1002</v>
+        <v>897</v>
       </c>
       <c r="F154" t="s">
-        <v>1004</v>
+        <v>25</v>
       </c>
       <c r="G154" t="s">
-        <v>438</v>
+        <v>899</v>
       </c>
       <c r="H154" t="s">
-        <v>1006</v>
+        <v>901</v>
       </c>
       <c r="I154" t="s">
-        <v>1007</v>
+        <v>902</v>
       </c>
       <c r="J154" t="s">
-        <v>1008</v>
+        <v>903</v>
       </c>
       <c r="K154" t="s">
-        <v>1003</v>
+        <v>898</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B155">
         <v>84</v>
@@ -30794,33 +31278,33 @@
         <v>934</v>
       </c>
       <c r="D155" t="s">
-        <v>213</v>
+        <v>964</v>
       </c>
       <c r="E155" t="s">
-        <v>1032</v>
+        <v>965</v>
       </c>
       <c r="F155" t="s">
-        <v>106</v>
+        <v>967</v>
       </c>
       <c r="G155" t="s">
-        <v>1034</v>
+        <v>968</v>
       </c>
       <c r="H155" t="s">
-        <v>1036</v>
+        <v>970</v>
       </c>
       <c r="I155" t="s">
-        <v>1037</v>
+        <v>971</v>
       </c>
       <c r="J155" t="s">
-        <v>1038</v>
+        <v>972</v>
       </c>
       <c r="K155" t="s">
-        <v>1033</v>
+        <v>966</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B156">
         <v>84</v>
@@ -30829,348 +31313,348 @@
         <v>934</v>
       </c>
       <c r="D156" t="s">
-        <v>1057</v>
+        <v>950</v>
       </c>
       <c r="E156" t="s">
-        <v>1058</v>
+        <v>1002</v>
       </c>
       <c r="F156" t="s">
-        <v>16</v>
+        <v>1004</v>
       </c>
       <c r="G156" t="s">
-        <v>1060</v>
+        <v>438</v>
       </c>
       <c r="H156" t="s">
-        <v>1062</v>
+        <v>1006</v>
       </c>
       <c r="I156" t="s">
-        <v>1063</v>
+        <v>1007</v>
       </c>
       <c r="J156" t="s">
-        <v>1064</v>
+        <v>1008</v>
       </c>
       <c r="K156" t="s">
-        <v>1059</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B157">
         <v>84</v>
       </c>
       <c r="C157" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D157" t="s">
-        <v>271</v>
+        <v>213</v>
       </c>
       <c r="E157" t="s">
-        <v>1104</v>
+        <v>1032</v>
       </c>
       <c r="F157" t="s">
-        <v>1106</v>
+        <v>106</v>
       </c>
       <c r="G157" t="s">
-        <v>1107</v>
+        <v>1034</v>
       </c>
       <c r="H157" t="s">
-        <v>1109</v>
+        <v>1036</v>
       </c>
       <c r="I157" t="s">
-        <v>1110</v>
+        <v>1037</v>
       </c>
       <c r="J157" t="s">
-        <v>1111</v>
+        <v>1038</v>
       </c>
       <c r="K157" t="s">
-        <v>1105</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B158">
         <v>84</v>
       </c>
       <c r="C158" t="s">
-        <v>1271</v>
+        <v>934</v>
       </c>
       <c r="D158" t="s">
-        <v>950</v>
+        <v>1057</v>
       </c>
       <c r="E158" t="s">
-        <v>463</v>
+        <v>1058</v>
       </c>
       <c r="F158" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G158" t="s">
-        <v>438</v>
+        <v>1060</v>
       </c>
       <c r="H158" t="s">
-        <v>1274</v>
+        <v>1062</v>
       </c>
       <c r="I158" t="s">
-        <v>1275</v>
+        <v>1063</v>
       </c>
       <c r="J158" t="s">
-        <v>1276</v>
+        <v>1064</v>
       </c>
       <c r="K158" t="s">
-        <v>1272</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B159">
         <v>84</v>
       </c>
       <c r="C159" t="s">
-        <v>1300</v>
+        <v>1087</v>
       </c>
       <c r="D159" t="s">
-        <v>1338</v>
+        <v>271</v>
       </c>
       <c r="E159" t="s">
-        <v>122</v>
+        <v>1104</v>
       </c>
       <c r="F159" t="s">
-        <v>16</v>
+        <v>1106</v>
       </c>
       <c r="G159" t="s">
-        <v>1340</v>
+        <v>1107</v>
       </c>
       <c r="H159" t="s">
-        <v>1342</v>
+        <v>1109</v>
       </c>
       <c r="I159" t="s">
-        <v>1343</v>
+        <v>1110</v>
       </c>
       <c r="J159" t="s">
-        <v>1344</v>
+        <v>1111</v>
       </c>
       <c r="K159" t="s">
-        <v>1339</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B160">
         <v>84</v>
       </c>
       <c r="C160" t="s">
-        <v>1394</v>
+        <v>1271</v>
       </c>
       <c r="D160" t="s">
-        <v>1443</v>
+        <v>950</v>
       </c>
       <c r="E160" t="s">
-        <v>1444</v>
+        <v>463</v>
       </c>
       <c r="F160" t="s">
         <v>66</v>
       </c>
       <c r="G160" t="s">
-        <v>1446</v>
+        <v>438</v>
       </c>
       <c r="H160" t="s">
-        <v>1448</v>
+        <v>1274</v>
       </c>
       <c r="I160" t="s">
-        <v>1449</v>
+        <v>1275</v>
       </c>
       <c r="J160" t="s">
-        <v>1450</v>
+        <v>1276</v>
       </c>
       <c r="K160" t="s">
-        <v>1445</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B161">
         <v>84</v>
       </c>
       <c r="C161" t="s">
-        <v>1394</v>
+        <v>1300</v>
       </c>
       <c r="D161" t="s">
-        <v>1475</v>
+        <v>1338</v>
       </c>
       <c r="E161" t="s">
-        <v>1476</v>
+        <v>122</v>
       </c>
       <c r="F161" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G161" t="s">
-        <v>1478</v>
+        <v>1340</v>
       </c>
       <c r="H161" t="s">
-        <v>1480</v>
+        <v>1342</v>
       </c>
       <c r="I161" t="s">
-        <v>1481</v>
+        <v>1343</v>
       </c>
       <c r="J161" t="s">
-        <v>1482</v>
+        <v>1344</v>
       </c>
       <c r="K161" t="s">
-        <v>1477</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B162">
         <v>84</v>
       </c>
       <c r="C162" t="s">
-        <v>1625</v>
+        <v>1394</v>
       </c>
       <c r="D162" t="s">
-        <v>1635</v>
+        <v>1443</v>
       </c>
       <c r="E162" t="s">
-        <v>1642</v>
+        <v>1444</v>
       </c>
       <c r="F162" t="s">
-        <v>1644</v>
+        <v>66</v>
       </c>
       <c r="G162" t="s">
-        <v>1637</v>
+        <v>1446</v>
       </c>
       <c r="H162" t="s">
-        <v>1646</v>
+        <v>1448</v>
       </c>
       <c r="I162" t="s">
-        <v>1647</v>
+        <v>1449</v>
       </c>
       <c r="J162" t="s">
-        <v>1648</v>
+        <v>1450</v>
       </c>
       <c r="K162" t="s">
-        <v>1643</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B163">
         <v>84</v>
       </c>
       <c r="C163" t="s">
-        <v>1664</v>
+        <v>1394</v>
       </c>
       <c r="D163" t="s">
-        <v>1665</v>
+        <v>1475</v>
       </c>
       <c r="E163" t="s">
-        <v>1666</v>
+        <v>1476</v>
       </c>
       <c r="F163" t="s">
-        <v>747</v>
+        <v>25</v>
       </c>
       <c r="G163" t="s">
-        <v>1668</v>
+        <v>1478</v>
       </c>
       <c r="H163" t="s">
-        <v>1670</v>
+        <v>1480</v>
       </c>
       <c r="I163" t="s">
-        <v>1671</v>
+        <v>1481</v>
       </c>
       <c r="J163" t="s">
-        <v>1672</v>
+        <v>1482</v>
       </c>
       <c r="K163" t="s">
-        <v>1667</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B164">
         <v>84</v>
       </c>
       <c r="C164" t="s">
-        <v>1727</v>
+        <v>1625</v>
       </c>
       <c r="D164" t="s">
-        <v>1744</v>
+        <v>1635</v>
       </c>
       <c r="E164" t="s">
-        <v>1536</v>
+        <v>1642</v>
       </c>
       <c r="F164" t="s">
-        <v>25</v>
+        <v>1644</v>
       </c>
       <c r="G164" t="s">
-        <v>1746</v>
+        <v>1637</v>
       </c>
       <c r="H164" t="s">
-        <v>1748</v>
+        <v>1646</v>
       </c>
       <c r="I164" t="s">
-        <v>1749</v>
+        <v>1647</v>
       </c>
       <c r="J164" t="s">
-        <v>1750</v>
+        <v>1648</v>
       </c>
       <c r="K164" t="s">
-        <v>1745</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B165">
         <v>84</v>
       </c>
       <c r="C165" t="s">
-        <v>1727</v>
+        <v>1664</v>
       </c>
       <c r="D165" t="s">
-        <v>1751</v>
+        <v>1665</v>
       </c>
       <c r="E165" t="s">
-        <v>1752</v>
+        <v>1666</v>
       </c>
       <c r="F165" t="s">
-        <v>535</v>
+        <v>747</v>
       </c>
       <c r="G165" t="s">
-        <v>1754</v>
+        <v>1668</v>
       </c>
       <c r="H165" t="s">
-        <v>1756</v>
+        <v>1670</v>
       </c>
       <c r="I165" t="s">
-        <v>1757</v>
+        <v>1671</v>
       </c>
       <c r="J165" t="s">
-        <v>1758</v>
+        <v>1672</v>
       </c>
       <c r="K165" t="s">
-        <v>1753</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B166">
         <v>84</v>
@@ -31179,803 +31663,803 @@
         <v>1727</v>
       </c>
       <c r="D166" t="s">
-        <v>1879</v>
+        <v>1744</v>
       </c>
       <c r="E166" t="s">
-        <v>1880</v>
+        <v>1536</v>
       </c>
       <c r="F166" t="s">
         <v>25</v>
       </c>
       <c r="G166" t="s">
-        <v>1770</v>
+        <v>1746</v>
       </c>
       <c r="H166" t="s">
-        <v>1883</v>
+        <v>1748</v>
       </c>
       <c r="I166" t="s">
-        <v>79</v>
+        <v>1749</v>
       </c>
       <c r="J166" t="s">
-        <v>79</v>
+        <v>1750</v>
       </c>
       <c r="K166" t="s">
-        <v>1881</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B167">
         <v>84</v>
       </c>
       <c r="C167" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D167" t="s">
-        <v>1899</v>
+        <v>1751</v>
       </c>
       <c r="E167" t="s">
-        <v>1900</v>
+        <v>1752</v>
       </c>
       <c r="F167" t="s">
-        <v>747</v>
+        <v>535</v>
       </c>
       <c r="G167" t="s">
-        <v>1902</v>
+        <v>1754</v>
       </c>
       <c r="H167" t="s">
-        <v>1904</v>
+        <v>1756</v>
       </c>
       <c r="I167" t="s">
-        <v>1905</v>
+        <v>1757</v>
       </c>
       <c r="J167" t="s">
-        <v>1906</v>
+        <v>1758</v>
       </c>
       <c r="K167" t="s">
-        <v>1901</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B168">
         <v>84</v>
       </c>
       <c r="C168" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D168" t="s">
-        <v>1955</v>
+        <v>1879</v>
       </c>
       <c r="E168" t="s">
-        <v>1956</v>
+        <v>1880</v>
       </c>
       <c r="F168" t="s">
-        <v>1958</v>
+        <v>25</v>
       </c>
       <c r="G168" t="s">
-        <v>959</v>
+        <v>1770</v>
       </c>
       <c r="H168" t="s">
-        <v>1960</v>
+        <v>1883</v>
       </c>
       <c r="I168" t="s">
-        <v>1961</v>
+        <v>79</v>
       </c>
       <c r="J168" t="s">
-        <v>1962</v>
+        <v>79</v>
       </c>
       <c r="K168" t="s">
-        <v>1957</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B169">
         <v>84</v>
       </c>
       <c r="C169" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D169" t="s">
-        <v>2176</v>
+        <v>1899</v>
       </c>
       <c r="E169" t="s">
-        <v>2177</v>
+        <v>1900</v>
       </c>
       <c r="F169" t="s">
-        <v>16</v>
+        <v>747</v>
       </c>
       <c r="G169" t="s">
-        <v>2179</v>
+        <v>1902</v>
       </c>
       <c r="H169" t="s">
-        <v>2181</v>
+        <v>1904</v>
       </c>
       <c r="I169" t="s">
-        <v>2182</v>
+        <v>1905</v>
       </c>
       <c r="J169" t="s">
-        <v>2183</v>
+        <v>1906</v>
       </c>
       <c r="K169" t="s">
-        <v>2178</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B170">
         <v>84</v>
       </c>
       <c r="C170" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D170" t="s">
-        <v>2211</v>
+        <v>1955</v>
       </c>
       <c r="E170" t="s">
-        <v>2212</v>
+        <v>1956</v>
       </c>
       <c r="F170" t="s">
-        <v>16</v>
+        <v>1958</v>
       </c>
       <c r="G170" t="s">
-        <v>2214</v>
+        <v>959</v>
       </c>
       <c r="H170" t="s">
-        <v>2216</v>
+        <v>1960</v>
       </c>
       <c r="I170" t="s">
-        <v>2217</v>
+        <v>1961</v>
       </c>
       <c r="J170" t="s">
-        <v>2218</v>
+        <v>1962</v>
       </c>
       <c r="K170" t="s">
-        <v>2213</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B171">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C171" t="s">
-        <v>1200</v>
+        <v>2098</v>
       </c>
       <c r="D171" t="s">
-        <v>1201</v>
+        <v>2176</v>
       </c>
       <c r="E171" t="s">
-        <v>1202</v>
+        <v>2177</v>
       </c>
       <c r="F171" t="s">
-        <v>1204</v>
+        <v>16</v>
       </c>
       <c r="G171" t="s">
-        <v>1205</v>
+        <v>2179</v>
       </c>
       <c r="H171" t="s">
-        <v>1207</v>
+        <v>2181</v>
       </c>
       <c r="I171" t="s">
-        <v>1208</v>
+        <v>2182</v>
       </c>
       <c r="J171" t="s">
-        <v>1209</v>
+        <v>2183</v>
       </c>
       <c r="K171" t="s">
-        <v>1203</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B172">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C172" t="s">
-        <v>284</v>
+        <v>2098</v>
       </c>
       <c r="D172" t="s">
-        <v>353</v>
+        <v>2211</v>
       </c>
       <c r="E172" t="s">
-        <v>362</v>
+        <v>2212</v>
       </c>
       <c r="F172" t="s">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c r="G172" t="s">
-        <v>364</v>
+        <v>2214</v>
       </c>
       <c r="H172" t="s">
-        <v>366</v>
+        <v>2216</v>
       </c>
       <c r="I172" t="s">
-        <v>367</v>
+        <v>2217</v>
       </c>
       <c r="J172" t="s">
-        <v>368</v>
+        <v>2218</v>
       </c>
       <c r="K172" t="s">
-        <v>363</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B173">
         <v>83</v>
       </c>
       <c r="C173" t="s">
-        <v>473</v>
+        <v>1200</v>
       </c>
       <c r="D173" t="s">
-        <v>491</v>
+        <v>1201</v>
       </c>
       <c r="E173" t="s">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="s">
-        <v>75</v>
+        <v>1204</v>
       </c>
       <c r="G173" t="s">
-        <v>494</v>
+        <v>1205</v>
       </c>
       <c r="H173" t="s">
-        <v>496</v>
+        <v>1207</v>
       </c>
       <c r="I173" t="s">
-        <v>497</v>
+        <v>1208</v>
       </c>
       <c r="J173" t="s">
-        <v>498</v>
+        <v>1209</v>
       </c>
       <c r="K173" t="s">
-        <v>493</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B174">
         <v>83</v>
       </c>
       <c r="C174" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D174" t="s">
-        <v>532</v>
+        <v>353</v>
       </c>
       <c r="E174" t="s">
-        <v>533</v>
+        <v>362</v>
       </c>
       <c r="F174" t="s">
-        <v>535</v>
+        <v>356</v>
       </c>
       <c r="G174" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="H174" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="I174" t="s">
-        <v>539</v>
+        <v>367</v>
       </c>
       <c r="J174" t="s">
-        <v>540</v>
+        <v>368</v>
       </c>
       <c r="K174" t="s">
-        <v>534</v>
+        <v>363</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B175">
         <v>83</v>
       </c>
       <c r="C175" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D175" t="s">
-        <v>643</v>
+        <v>491</v>
       </c>
       <c r="E175" t="s">
-        <v>644</v>
+        <v>492</v>
       </c>
       <c r="F175" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G175" t="s">
-        <v>618</v>
+        <v>494</v>
       </c>
       <c r="H175" t="s">
-        <v>647</v>
+        <v>496</v>
       </c>
       <c r="I175" t="s">
-        <v>648</v>
+        <v>497</v>
       </c>
       <c r="J175" t="s">
-        <v>649</v>
+        <v>498</v>
       </c>
       <c r="K175" t="s">
-        <v>645</v>
+        <v>493</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B176">
         <v>83</v>
       </c>
       <c r="C176" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D176" t="s">
-        <v>736</v>
+        <v>532</v>
       </c>
       <c r="E176" t="s">
-        <v>737</v>
+        <v>533</v>
       </c>
       <c r="F176" t="s">
-        <v>739</v>
+        <v>535</v>
       </c>
       <c r="G176" t="s">
-        <v>604</v>
+        <v>536</v>
       </c>
       <c r="H176" t="s">
-        <v>741</v>
+        <v>538</v>
       </c>
       <c r="I176" t="s">
-        <v>742</v>
+        <v>539</v>
       </c>
       <c r="J176" t="s">
-        <v>743</v>
+        <v>540</v>
       </c>
       <c r="K176" t="s">
-        <v>738</v>
+        <v>534</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B177">
         <v>83</v>
       </c>
       <c r="C177" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D177" t="s">
-        <v>807</v>
+        <v>643</v>
       </c>
       <c r="E177" t="s">
-        <v>808</v>
+        <v>644</v>
       </c>
       <c r="F177" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="G177" t="s">
-        <v>811</v>
+        <v>618</v>
       </c>
       <c r="H177" t="s">
-        <v>813</v>
+        <v>647</v>
       </c>
       <c r="I177" t="s">
-        <v>814</v>
+        <v>648</v>
       </c>
       <c r="J177" t="s">
-        <v>815</v>
+        <v>649</v>
       </c>
       <c r="K177" t="s">
-        <v>809</v>
+        <v>645</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B178">
         <v>83</v>
       </c>
       <c r="C178" t="s">
-        <v>934</v>
+        <v>697</v>
       </c>
       <c r="D178" t="s">
-        <v>650</v>
+        <v>736</v>
       </c>
       <c r="E178" t="s">
-        <v>1016</v>
+        <v>737</v>
       </c>
       <c r="F178" t="s">
-        <v>66</v>
+        <v>739</v>
       </c>
       <c r="G178" t="s">
-        <v>1018</v>
+        <v>604</v>
       </c>
       <c r="H178" t="s">
-        <v>1020</v>
+        <v>741</v>
       </c>
       <c r="I178" t="s">
-        <v>1021</v>
+        <v>742</v>
       </c>
       <c r="J178" t="s">
-        <v>1022</v>
+        <v>743</v>
       </c>
       <c r="K178" t="s">
-        <v>1017</v>
+        <v>738</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B179">
         <v>83</v>
       </c>
       <c r="C179" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D179" t="s">
-        <v>1048</v>
+        <v>807</v>
       </c>
       <c r="E179" t="s">
-        <v>1049</v>
+        <v>808</v>
       </c>
       <c r="F179" t="s">
-        <v>1051</v>
+        <v>810</v>
       </c>
       <c r="G179" t="s">
-        <v>1052</v>
+        <v>811</v>
       </c>
       <c r="H179" t="s">
-        <v>1054</v>
+        <v>813</v>
       </c>
       <c r="I179" t="s">
-        <v>1055</v>
+        <v>814</v>
       </c>
       <c r="J179" t="s">
-        <v>1056</v>
+        <v>815</v>
       </c>
       <c r="K179" t="s">
-        <v>1050</v>
+        <v>809</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B180">
         <v>83</v>
       </c>
       <c r="C180" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D180" t="s">
-        <v>1247</v>
+        <v>650</v>
       </c>
       <c r="E180" t="s">
-        <v>1248</v>
+        <v>1016</v>
       </c>
       <c r="F180" t="s">
         <v>66</v>
       </c>
       <c r="G180" t="s">
-        <v>604</v>
+        <v>1018</v>
       </c>
       <c r="H180" t="s">
-        <v>1251</v>
+        <v>1020</v>
       </c>
       <c r="I180" t="s">
-        <v>1252</v>
+        <v>1021</v>
       </c>
       <c r="J180" t="s">
-        <v>1253</v>
+        <v>1022</v>
       </c>
       <c r="K180" t="s">
-        <v>1249</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B181">
         <v>83</v>
       </c>
       <c r="C181" t="s">
-        <v>1271</v>
+        <v>934</v>
       </c>
       <c r="D181" t="s">
-        <v>219</v>
+        <v>1048</v>
       </c>
       <c r="E181" t="s">
-        <v>1285</v>
+        <v>1049</v>
       </c>
       <c r="F181" t="s">
-        <v>98</v>
+        <v>1051</v>
       </c>
       <c r="G181" t="s">
-        <v>1287</v>
+        <v>1052</v>
       </c>
       <c r="H181" t="s">
-        <v>1289</v>
+        <v>1054</v>
       </c>
       <c r="I181" t="s">
-        <v>1290</v>
+        <v>1055</v>
       </c>
       <c r="J181" t="s">
-        <v>1291</v>
+        <v>1056</v>
       </c>
       <c r="K181" t="s">
-        <v>1286</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B182">
         <v>83</v>
       </c>
       <c r="C182" t="s">
-        <v>1271</v>
+        <v>1227</v>
       </c>
       <c r="D182" t="s">
-        <v>1292</v>
+        <v>1247</v>
       </c>
       <c r="E182" t="s">
-        <v>1293</v>
+        <v>1248</v>
       </c>
       <c r="F182" t="s">
         <v>66</v>
       </c>
       <c r="G182" t="s">
-        <v>1295</v>
+        <v>604</v>
       </c>
       <c r="H182" t="s">
-        <v>1297</v>
+        <v>1251</v>
       </c>
       <c r="I182" t="s">
-        <v>1298</v>
+        <v>1252</v>
       </c>
       <c r="J182" t="s">
-        <v>1299</v>
+        <v>1253</v>
       </c>
       <c r="K182" t="s">
-        <v>1294</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B183">
         <v>83</v>
       </c>
       <c r="C183" t="s">
-        <v>1300</v>
+        <v>1271</v>
       </c>
       <c r="D183" t="s">
-        <v>1309</v>
+        <v>219</v>
       </c>
       <c r="E183" t="s">
-        <v>830</v>
+        <v>1285</v>
       </c>
       <c r="F183" t="s">
-        <v>1311</v>
+        <v>98</v>
       </c>
       <c r="G183" t="s">
-        <v>1318</v>
+        <v>1287</v>
       </c>
       <c r="H183" t="s">
-        <v>1320</v>
+        <v>1289</v>
       </c>
       <c r="I183" t="s">
-        <v>1321</v>
+        <v>1290</v>
       </c>
       <c r="J183" t="s">
-        <v>1322</v>
+        <v>1291</v>
       </c>
       <c r="K183" t="s">
-        <v>1317</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B184">
         <v>83</v>
       </c>
       <c r="C184" t="s">
-        <v>1300</v>
+        <v>1271</v>
       </c>
       <c r="D184" t="s">
-        <v>1352</v>
+        <v>1292</v>
       </c>
       <c r="E184" t="s">
-        <v>110</v>
+        <v>1293</v>
       </c>
       <c r="F184" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G184" t="s">
-        <v>1354</v>
+        <v>1295</v>
       </c>
       <c r="H184" t="s">
-        <v>1356</v>
+        <v>1297</v>
       </c>
       <c r="I184" t="s">
-        <v>1357</v>
+        <v>1298</v>
       </c>
       <c r="J184" t="s">
-        <v>1358</v>
+        <v>1299</v>
       </c>
       <c r="K184" t="s">
-        <v>1353</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B185">
         <v>83</v>
       </c>
       <c r="C185" t="s">
-        <v>1394</v>
+        <v>1300</v>
       </c>
       <c r="D185" t="s">
-        <v>491</v>
+        <v>1309</v>
       </c>
       <c r="E185" t="s">
-        <v>1404</v>
+        <v>830</v>
       </c>
       <c r="F185" t="s">
-        <v>1406</v>
+        <v>1311</v>
       </c>
       <c r="G185" t="s">
-        <v>1407</v>
+        <v>1318</v>
       </c>
       <c r="H185" t="s">
-        <v>1409</v>
+        <v>1320</v>
       </c>
       <c r="I185" t="s">
-        <v>1410</v>
+        <v>1321</v>
       </c>
       <c r="J185" t="s">
-        <v>1411</v>
+        <v>1322</v>
       </c>
       <c r="K185" t="s">
-        <v>1405</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B186">
         <v>83</v>
       </c>
       <c r="C186" t="s">
-        <v>1394</v>
+        <v>1300</v>
       </c>
       <c r="D186" t="s">
-        <v>1451</v>
+        <v>1352</v>
       </c>
       <c r="E186" t="s">
-        <v>1452</v>
+        <v>110</v>
       </c>
       <c r="F186" t="s">
-        <v>1454</v>
+        <v>16</v>
       </c>
       <c r="G186" t="s">
-        <v>802</v>
+        <v>1354</v>
       </c>
       <c r="H186" t="s">
-        <v>1456</v>
+        <v>1356</v>
       </c>
       <c r="I186" t="s">
-        <v>1457</v>
+        <v>1357</v>
       </c>
       <c r="J186" t="s">
-        <v>1458</v>
+        <v>1358</v>
       </c>
       <c r="K186" t="s">
-        <v>1453</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B187">
         <v>83</v>
       </c>
       <c r="C187" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D187" t="s">
-        <v>1579</v>
+        <v>491</v>
       </c>
       <c r="E187" t="s">
-        <v>957</v>
+        <v>1404</v>
       </c>
       <c r="F187" t="s">
-        <v>75</v>
+        <v>1406</v>
       </c>
       <c r="G187" t="s">
-        <v>1581</v>
+        <v>1407</v>
       </c>
       <c r="H187" t="s">
-        <v>1583</v>
+        <v>1409</v>
       </c>
       <c r="I187" t="s">
-        <v>1584</v>
+        <v>1410</v>
       </c>
       <c r="J187" t="s">
-        <v>1585</v>
+        <v>1411</v>
       </c>
       <c r="K187" t="s">
-        <v>1580</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B188">
         <v>83</v>
       </c>
       <c r="C188" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D188" t="s">
-        <v>1586</v>
+        <v>1451</v>
       </c>
       <c r="E188" t="s">
-        <v>1587</v>
+        <v>1452</v>
       </c>
       <c r="F188" t="s">
-        <v>75</v>
+        <v>1454</v>
       </c>
       <c r="G188" t="s">
-        <v>1589</v>
+        <v>802</v>
       </c>
       <c r="H188" t="s">
-        <v>1583</v>
+        <v>1456</v>
       </c>
       <c r="I188" t="s">
-        <v>1591</v>
+        <v>1457</v>
       </c>
       <c r="J188" t="s">
-        <v>1592</v>
+        <v>1458</v>
       </c>
       <c r="K188" t="s">
-        <v>1588</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B189">
         <v>83</v>
@@ -31984,1223 +32468,1223 @@
         <v>1534</v>
       </c>
       <c r="D189" t="s">
-        <v>1593</v>
+        <v>1579</v>
       </c>
       <c r="E189" t="s">
-        <v>610</v>
+        <v>957</v>
       </c>
       <c r="F189" t="s">
-        <v>1595</v>
+        <v>75</v>
       </c>
       <c r="G189" t="s">
-        <v>1166</v>
+        <v>1581</v>
       </c>
       <c r="H189" t="s">
-        <v>1597</v>
+        <v>1583</v>
       </c>
       <c r="I189" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="J189" t="s">
-        <v>1599</v>
+        <v>1585</v>
       </c>
       <c r="K189" t="s">
-        <v>1594</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B190">
         <v>83</v>
       </c>
       <c r="C190" t="s">
-        <v>2098</v>
+        <v>1534</v>
       </c>
       <c r="D190" t="s">
-        <v>2099</v>
+        <v>1586</v>
       </c>
       <c r="E190" t="s">
-        <v>830</v>
+        <v>1587</v>
       </c>
       <c r="F190" t="s">
-        <v>2101</v>
+        <v>75</v>
       </c>
       <c r="G190" t="s">
-        <v>2102</v>
+        <v>1589</v>
       </c>
       <c r="H190" t="s">
-        <v>2104</v>
+        <v>1583</v>
       </c>
       <c r="I190" t="s">
-        <v>2105</v>
+        <v>1591</v>
       </c>
       <c r="J190" t="s">
-        <v>2106</v>
+        <v>1592</v>
       </c>
       <c r="K190" t="s">
-        <v>2100</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B191">
         <v>83</v>
       </c>
       <c r="C191" t="s">
-        <v>2098</v>
+        <v>1534</v>
       </c>
       <c r="D191" t="s">
-        <v>2162</v>
+        <v>1593</v>
       </c>
       <c r="E191" t="s">
-        <v>2163</v>
+        <v>610</v>
       </c>
       <c r="F191" t="s">
-        <v>16</v>
+        <v>1595</v>
       </c>
       <c r="G191" t="s">
-        <v>2165</v>
+        <v>1166</v>
       </c>
       <c r="H191" t="s">
-        <v>2167</v>
+        <v>1597</v>
       </c>
       <c r="I191" t="s">
-        <v>2168</v>
+        <v>1598</v>
       </c>
       <c r="J191" t="s">
-        <v>2169</v>
+        <v>1599</v>
       </c>
       <c r="K191" t="s">
-        <v>2164</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B192">
         <v>83</v>
       </c>
       <c r="C192" t="s">
-        <v>2258</v>
+        <v>2098</v>
       </c>
       <c r="D192" t="s">
-        <v>2308</v>
+        <v>2099</v>
       </c>
       <c r="E192" t="s">
-        <v>2309</v>
+        <v>830</v>
       </c>
       <c r="F192" t="s">
-        <v>1950</v>
+        <v>2101</v>
       </c>
       <c r="G192" t="s">
-        <v>2311</v>
+        <v>2102</v>
       </c>
       <c r="H192" t="s">
-        <v>2313</v>
+        <v>2104</v>
       </c>
       <c r="I192" t="s">
-        <v>2314</v>
+        <v>2105</v>
       </c>
       <c r="J192" t="s">
-        <v>2315</v>
+        <v>2106</v>
       </c>
       <c r="K192" t="s">
-        <v>2310</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B193">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C193" t="s">
-        <v>159</v>
+        <v>2098</v>
       </c>
       <c r="D193" t="s">
-        <v>227</v>
+        <v>2162</v>
       </c>
       <c r="E193" t="s">
-        <v>228</v>
+        <v>2163</v>
       </c>
       <c r="F193" t="s">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c r="G193" t="s">
-        <v>231</v>
+        <v>2165</v>
       </c>
       <c r="H193" t="s">
-        <v>233</v>
+        <v>2167</v>
       </c>
       <c r="I193" t="s">
-        <v>234</v>
+        <v>2168</v>
       </c>
       <c r="J193" t="s">
-        <v>235</v>
+        <v>2169</v>
       </c>
       <c r="K193" t="s">
-        <v>229</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B194">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C194" t="s">
-        <v>159</v>
+        <v>2258</v>
       </c>
       <c r="D194" t="s">
-        <v>266</v>
+        <v>2308</v>
       </c>
       <c r="E194" t="s">
-        <v>267</v>
+        <v>2309</v>
       </c>
       <c r="F194" t="s">
-        <v>16</v>
+        <v>1950</v>
       </c>
       <c r="G194" t="s">
-        <v>58</v>
+        <v>2311</v>
       </c>
       <c r="H194" t="s">
-        <v>270</v>
+        <v>2313</v>
       </c>
       <c r="I194" t="s">
-        <v>79</v>
+        <v>2314</v>
       </c>
       <c r="J194" t="s">
-        <v>79</v>
+        <v>2315</v>
       </c>
       <c r="K194" t="s">
-        <v>268</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B195">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C195" t="s">
-        <v>284</v>
+        <v>2377</v>
       </c>
       <c r="D195" t="s">
-        <v>338</v>
+        <v>2407</v>
       </c>
       <c r="E195" t="s">
-        <v>339</v>
+        <v>2408</v>
       </c>
       <c r="F195" t="s">
-        <v>341</v>
+        <v>75</v>
       </c>
       <c r="G195" t="s">
-        <v>342</v>
+        <v>1034</v>
       </c>
       <c r="H195" t="s">
-        <v>344</v>
+        <v>2411</v>
       </c>
       <c r="I195" t="s">
-        <v>345</v>
+        <v>2412</v>
       </c>
       <c r="J195" t="s">
-        <v>346</v>
+        <v>2413</v>
       </c>
       <c r="K195" t="s">
-        <v>340</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B196">
         <v>82</v>
       </c>
       <c r="C196" t="s">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="D196" t="s">
-        <v>601</v>
+        <v>227</v>
       </c>
       <c r="E196" t="s">
-        <v>602</v>
+        <v>228</v>
       </c>
       <c r="F196" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="G196" t="s">
-        <v>604</v>
+        <v>231</v>
       </c>
       <c r="H196" t="s">
-        <v>606</v>
+        <v>233</v>
       </c>
       <c r="I196" t="s">
-        <v>607</v>
+        <v>234</v>
       </c>
       <c r="J196" t="s">
-        <v>608</v>
+        <v>235</v>
       </c>
       <c r="K196" t="s">
-        <v>603</v>
+        <v>229</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B197">
         <v>82</v>
       </c>
       <c r="C197" t="s">
-        <v>934</v>
+        <v>159</v>
       </c>
       <c r="D197" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="E197" t="s">
-        <v>1009</v>
+        <v>267</v>
       </c>
       <c r="F197" t="s">
         <v>16</v>
       </c>
       <c r="G197" t="s">
-        <v>1011</v>
+        <v>58</v>
       </c>
       <c r="H197" t="s">
-        <v>1013</v>
+        <v>270</v>
       </c>
       <c r="I197" t="s">
-        <v>1014</v>
+        <v>79</v>
       </c>
       <c r="J197" t="s">
-        <v>1015</v>
+        <v>79</v>
       </c>
       <c r="K197" t="s">
-        <v>1010</v>
+        <v>268</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B198">
         <v>82</v>
       </c>
       <c r="C198" t="s">
-        <v>934</v>
+        <v>284</v>
       </c>
       <c r="D198" t="s">
-        <v>1023</v>
+        <v>338</v>
       </c>
       <c r="E198" t="s">
-        <v>1024</v>
+        <v>339</v>
       </c>
       <c r="F198" t="s">
-        <v>1026</v>
+        <v>341</v>
       </c>
       <c r="G198" t="s">
-        <v>1027</v>
+        <v>342</v>
       </c>
       <c r="H198" t="s">
-        <v>1029</v>
+        <v>344</v>
       </c>
       <c r="I198" t="s">
-        <v>1030</v>
+        <v>345</v>
       </c>
       <c r="J198" t="s">
-        <v>1031</v>
+        <v>346</v>
       </c>
       <c r="K198" t="s">
-        <v>1025</v>
+        <v>340</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B199">
         <v>82</v>
       </c>
       <c r="C199" t="s">
-        <v>1087</v>
+        <v>591</v>
       </c>
       <c r="D199" t="s">
-        <v>1112</v>
+        <v>601</v>
       </c>
       <c r="E199" t="s">
-        <v>1113</v>
+        <v>602</v>
       </c>
       <c r="F199" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G199" t="s">
-        <v>1115</v>
+        <v>604</v>
       </c>
       <c r="H199" t="s">
-        <v>1117</v>
+        <v>606</v>
       </c>
       <c r="I199" t="s">
-        <v>1118</v>
+        <v>607</v>
       </c>
       <c r="J199" t="s">
-        <v>1119</v>
+        <v>608</v>
       </c>
       <c r="K199" t="s">
-        <v>1114</v>
+        <v>603</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B200">
         <v>82</v>
       </c>
       <c r="C200" t="s">
-        <v>1210</v>
+        <v>934</v>
       </c>
       <c r="D200" t="s">
-        <v>1211</v>
+        <v>13</v>
       </c>
       <c r="E200" t="s">
-        <v>89</v>
+        <v>1009</v>
       </c>
       <c r="F200" t="s">
-        <v>1213</v>
+        <v>16</v>
       </c>
       <c r="G200" t="s">
-        <v>1214</v>
+        <v>1011</v>
       </c>
       <c r="H200" t="s">
-        <v>1216</v>
+        <v>1013</v>
       </c>
       <c r="I200" t="s">
-        <v>1217</v>
+        <v>1014</v>
       </c>
       <c r="J200" t="s">
-        <v>1218</v>
+        <v>1015</v>
       </c>
       <c r="K200" t="s">
-        <v>1212</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B201">
         <v>82</v>
       </c>
       <c r="C201" t="s">
-        <v>1368</v>
+        <v>934</v>
       </c>
       <c r="D201" t="s">
-        <v>1369</v>
+        <v>1023</v>
       </c>
       <c r="E201" t="s">
-        <v>1370</v>
+        <v>1024</v>
       </c>
       <c r="F201" t="s">
-        <v>1372</v>
+        <v>1026</v>
       </c>
       <c r="G201" t="s">
-        <v>1373</v>
+        <v>1027</v>
       </c>
       <c r="H201" t="s">
-        <v>1375</v>
+        <v>1029</v>
       </c>
       <c r="I201" t="s">
-        <v>1376</v>
+        <v>1030</v>
       </c>
       <c r="J201" t="s">
-        <v>1377</v>
+        <v>1031</v>
       </c>
       <c r="K201" t="s">
-        <v>1371</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B202">
         <v>82</v>
       </c>
       <c r="C202" t="s">
-        <v>1534</v>
+        <v>1087</v>
       </c>
       <c r="D202" t="s">
-        <v>1608</v>
+        <v>1112</v>
       </c>
       <c r="E202" t="s">
-        <v>1609</v>
+        <v>1113</v>
       </c>
       <c r="F202" t="s">
-        <v>1559</v>
+        <v>25</v>
       </c>
       <c r="G202" t="s">
-        <v>1611</v>
+        <v>1115</v>
       </c>
       <c r="H202" t="s">
-        <v>1613</v>
+        <v>1117</v>
       </c>
       <c r="I202" t="s">
-        <v>1614</v>
+        <v>1118</v>
       </c>
       <c r="J202" t="s">
-        <v>1615</v>
+        <v>1119</v>
       </c>
       <c r="K202" t="s">
-        <v>1610</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B203">
         <v>82</v>
       </c>
       <c r="C203" t="s">
-        <v>1534</v>
+        <v>1210</v>
       </c>
       <c r="D203" t="s">
-        <v>1616</v>
+        <v>1211</v>
       </c>
       <c r="E203" t="s">
-        <v>1617</v>
+        <v>89</v>
       </c>
       <c r="F203" t="s">
-        <v>1619</v>
+        <v>1213</v>
       </c>
       <c r="G203" t="s">
-        <v>1620</v>
+        <v>1214</v>
       </c>
       <c r="H203" t="s">
-        <v>1622</v>
+        <v>1216</v>
       </c>
       <c r="I203" t="s">
-        <v>1623</v>
+        <v>1217</v>
       </c>
       <c r="J203" t="s">
-        <v>1624</v>
+        <v>1218</v>
       </c>
       <c r="K203" t="s">
-        <v>1618</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B204">
         <v>82</v>
       </c>
       <c r="C204" t="s">
-        <v>1884</v>
+        <v>1368</v>
       </c>
       <c r="D204" t="s">
-        <v>1979</v>
+        <v>1369</v>
       </c>
       <c r="E204" t="s">
-        <v>1980</v>
+        <v>1370</v>
       </c>
       <c r="F204" t="s">
-        <v>1982</v>
+        <v>1372</v>
       </c>
       <c r="G204" t="s">
-        <v>1983</v>
+        <v>1373</v>
       </c>
       <c r="H204" t="s">
-        <v>1985</v>
+        <v>1375</v>
       </c>
       <c r="I204" t="s">
-        <v>1986</v>
+        <v>1376</v>
       </c>
       <c r="J204" t="s">
-        <v>1987</v>
+        <v>1377</v>
       </c>
       <c r="K204" t="s">
-        <v>1981</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B205">
         <v>82</v>
       </c>
       <c r="C205" t="s">
-        <v>2258</v>
+        <v>1534</v>
       </c>
       <c r="D205" t="s">
-        <v>2283</v>
+        <v>1608</v>
       </c>
       <c r="E205" t="s">
-        <v>2284</v>
+        <v>1609</v>
       </c>
       <c r="F205" t="s">
-        <v>2286</v>
+        <v>1559</v>
       </c>
       <c r="G205" t="s">
-        <v>2287</v>
+        <v>1611</v>
       </c>
       <c r="H205" t="s">
-        <v>2289</v>
+        <v>1613</v>
       </c>
       <c r="I205" t="s">
-        <v>2290</v>
+        <v>1614</v>
       </c>
       <c r="J205" t="s">
-        <v>2291</v>
+        <v>1615</v>
       </c>
       <c r="K205" t="s">
-        <v>2285</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B206">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C206" t="s">
-        <v>12</v>
+        <v>1534</v>
       </c>
       <c r="D206" t="s">
-        <v>80</v>
+        <v>1616</v>
       </c>
       <c r="E206" t="s">
-        <v>81</v>
+        <v>1617</v>
       </c>
       <c r="F206" t="s">
-        <v>25</v>
+        <v>1619</v>
       </c>
       <c r="G206" t="s">
-        <v>83</v>
+        <v>1620</v>
       </c>
       <c r="H206" t="s">
-        <v>85</v>
+        <v>1622</v>
       </c>
       <c r="I206" t="s">
-        <v>86</v>
+        <v>1623</v>
       </c>
       <c r="J206" t="s">
-        <v>87</v>
+        <v>1624</v>
       </c>
       <c r="K206" t="s">
-        <v>82</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B207">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C207" t="s">
-        <v>284</v>
+        <v>1884</v>
       </c>
       <c r="D207" t="s">
-        <v>377</v>
+        <v>1979</v>
       </c>
       <c r="E207" t="s">
-        <v>378</v>
+        <v>1980</v>
       </c>
       <c r="F207" t="s">
-        <v>380</v>
+        <v>1982</v>
       </c>
       <c r="G207" t="s">
-        <v>381</v>
+        <v>1983</v>
       </c>
       <c r="H207" t="s">
-        <v>383</v>
+        <v>1985</v>
       </c>
       <c r="I207" t="s">
-        <v>384</v>
+        <v>1986</v>
       </c>
       <c r="J207" t="s">
-        <v>385</v>
+        <v>1987</v>
       </c>
       <c r="K207" t="s">
-        <v>379</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B208">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C208" t="s">
-        <v>473</v>
+        <v>2258</v>
       </c>
       <c r="D208" t="s">
-        <v>499</v>
+        <v>2283</v>
       </c>
       <c r="E208" t="s">
-        <v>500</v>
+        <v>2284</v>
       </c>
       <c r="F208" t="s">
-        <v>502</v>
+        <v>2286</v>
       </c>
       <c r="G208" t="s">
-        <v>503</v>
+        <v>2287</v>
       </c>
       <c r="H208" t="s">
-        <v>505</v>
+        <v>2289</v>
       </c>
       <c r="I208" t="s">
-        <v>506</v>
+        <v>2290</v>
       </c>
       <c r="J208" t="s">
-        <v>507</v>
+        <v>2291</v>
       </c>
       <c r="K208" t="s">
-        <v>501</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B209">
         <v>81</v>
       </c>
       <c r="C209" t="s">
-        <v>591</v>
+        <v>12</v>
       </c>
       <c r="D209" t="s">
-        <v>616</v>
+        <v>80</v>
       </c>
       <c r="E209" t="s">
-        <v>610</v>
+        <v>81</v>
       </c>
       <c r="F209" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G209" t="s">
-        <v>618</v>
+        <v>83</v>
       </c>
       <c r="H209" t="s">
-        <v>620</v>
+        <v>85</v>
       </c>
       <c r="I209" t="s">
-        <v>621</v>
+        <v>86</v>
       </c>
       <c r="J209" t="s">
-        <v>622</v>
+        <v>87</v>
       </c>
       <c r="K209" t="s">
-        <v>617</v>
+        <v>82</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B210">
         <v>81</v>
       </c>
       <c r="C210" t="s">
-        <v>845</v>
+        <v>284</v>
       </c>
       <c r="D210" t="s">
-        <v>888</v>
+        <v>377</v>
       </c>
       <c r="E210" t="s">
-        <v>889</v>
+        <v>378</v>
       </c>
       <c r="F210" t="s">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="G210" t="s">
-        <v>891</v>
+        <v>381</v>
       </c>
       <c r="H210" t="s">
-        <v>893</v>
+        <v>383</v>
       </c>
       <c r="I210" t="s">
-        <v>894</v>
+        <v>384</v>
       </c>
       <c r="J210" t="s">
-        <v>895</v>
+        <v>385</v>
       </c>
       <c r="K210" t="s">
-        <v>890</v>
+        <v>379</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B211">
         <v>81</v>
       </c>
       <c r="C211" t="s">
-        <v>1087</v>
+        <v>473</v>
       </c>
       <c r="D211" t="s">
-        <v>1120</v>
+        <v>499</v>
       </c>
       <c r="E211" t="s">
-        <v>1121</v>
+        <v>500</v>
       </c>
       <c r="F211" t="s">
-        <v>1123</v>
+        <v>502</v>
       </c>
       <c r="G211" t="s">
-        <v>1124</v>
+        <v>503</v>
       </c>
       <c r="H211" t="s">
-        <v>1126</v>
+        <v>505</v>
       </c>
       <c r="I211" t="s">
-        <v>1127</v>
+        <v>506</v>
       </c>
       <c r="J211" t="s">
-        <v>1128</v>
+        <v>507</v>
       </c>
       <c r="K211" t="s">
-        <v>1122</v>
+        <v>501</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B212">
         <v>81</v>
       </c>
       <c r="C212" t="s">
-        <v>1394</v>
+        <v>591</v>
       </c>
       <c r="D212" t="s">
-        <v>1412</v>
+        <v>616</v>
       </c>
       <c r="E212" t="s">
-        <v>1413</v>
+        <v>610</v>
       </c>
       <c r="F212" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G212" t="s">
-        <v>1415</v>
+        <v>618</v>
       </c>
       <c r="H212" t="s">
-        <v>1417</v>
+        <v>620</v>
       </c>
       <c r="I212" t="s">
-        <v>1418</v>
+        <v>621</v>
       </c>
       <c r="J212" t="s">
-        <v>1419</v>
+        <v>622</v>
       </c>
       <c r="K212" t="s">
-        <v>1414</v>
+        <v>617</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B213">
         <v>81</v>
       </c>
       <c r="C213" t="s">
-        <v>1394</v>
+        <v>845</v>
       </c>
       <c r="D213" t="s">
-        <v>1420</v>
+        <v>888</v>
       </c>
       <c r="E213" t="s">
-        <v>1421</v>
+        <v>889</v>
       </c>
       <c r="F213" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G213" t="s">
-        <v>1423</v>
+        <v>891</v>
       </c>
       <c r="H213" t="s">
-        <v>1425</v>
+        <v>893</v>
       </c>
       <c r="I213" t="s">
-        <v>1426</v>
+        <v>894</v>
       </c>
       <c r="J213" t="s">
-        <v>1427</v>
+        <v>895</v>
       </c>
       <c r="K213" t="s">
-        <v>1422</v>
+        <v>890</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B214">
         <v>81</v>
       </c>
       <c r="C214" t="s">
-        <v>1394</v>
+        <v>1087</v>
       </c>
       <c r="D214" t="s">
-        <v>1467</v>
+        <v>1120</v>
       </c>
       <c r="E214" t="s">
-        <v>1468</v>
+        <v>1121</v>
       </c>
       <c r="F214" t="s">
-        <v>16</v>
+        <v>1123</v>
       </c>
       <c r="G214" t="s">
-        <v>1470</v>
+        <v>1124</v>
       </c>
       <c r="H214" t="s">
-        <v>1472</v>
+        <v>1126</v>
       </c>
       <c r="I214" t="s">
-        <v>1473</v>
+        <v>1127</v>
       </c>
       <c r="J214" t="s">
-        <v>1474</v>
+        <v>1128</v>
       </c>
       <c r="K214" t="s">
-        <v>1469</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B215">
         <v>81</v>
       </c>
       <c r="C215" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D215" t="s">
-        <v>271</v>
+        <v>1412</v>
       </c>
       <c r="E215" t="s">
-        <v>1600</v>
+        <v>1413</v>
       </c>
       <c r="F215" t="s">
-        <v>1602</v>
+        <v>75</v>
       </c>
       <c r="G215" t="s">
-        <v>1603</v>
+        <v>1415</v>
       </c>
       <c r="H215" t="s">
-        <v>1605</v>
+        <v>1417</v>
       </c>
       <c r="I215" t="s">
-        <v>1606</v>
+        <v>1418</v>
       </c>
       <c r="J215" t="s">
-        <v>1607</v>
+        <v>1419</v>
       </c>
       <c r="K215" t="s">
-        <v>1601</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B216">
         <v>81</v>
       </c>
       <c r="C216" t="s">
-        <v>1664</v>
+        <v>1394</v>
       </c>
       <c r="D216" t="s">
-        <v>1708</v>
+        <v>1420</v>
       </c>
       <c r="E216" t="s">
-        <v>1709</v>
+        <v>1421</v>
       </c>
       <c r="F216" t="s">
-        <v>1711</v>
+        <v>16</v>
       </c>
       <c r="G216" t="s">
-        <v>1034</v>
+        <v>1423</v>
       </c>
       <c r="H216" t="s">
-        <v>1713</v>
+        <v>1425</v>
       </c>
       <c r="I216" t="s">
-        <v>1714</v>
+        <v>1426</v>
       </c>
       <c r="J216" t="s">
-        <v>1715</v>
+        <v>1427</v>
       </c>
       <c r="K216" t="s">
-        <v>1710</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B217">
         <v>81</v>
       </c>
       <c r="C217" t="s">
-        <v>1727</v>
+        <v>1394</v>
       </c>
       <c r="D217" t="s">
-        <v>1773</v>
+        <v>1467</v>
       </c>
       <c r="E217" t="s">
-        <v>1774</v>
+        <v>1468</v>
       </c>
       <c r="F217" t="s">
         <v>16</v>
       </c>
       <c r="G217" t="s">
-        <v>1776</v>
+        <v>1470</v>
       </c>
       <c r="H217" t="s">
-        <v>1778</v>
+        <v>1472</v>
       </c>
       <c r="I217" t="s">
-        <v>79</v>
+        <v>1473</v>
       </c>
       <c r="J217" t="s">
-        <v>79</v>
+        <v>1474</v>
       </c>
       <c r="K217" t="s">
-        <v>1775</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B218">
         <v>81</v>
       </c>
       <c r="C218" t="s">
-        <v>1727</v>
+        <v>1534</v>
       </c>
       <c r="D218" t="s">
-        <v>964</v>
+        <v>271</v>
       </c>
       <c r="E218" t="s">
-        <v>362</v>
+        <v>1600</v>
       </c>
       <c r="F218" t="s">
-        <v>356</v>
+        <v>1602</v>
       </c>
       <c r="G218" t="s">
-        <v>1792</v>
+        <v>1603</v>
       </c>
       <c r="H218" t="s">
-        <v>1794</v>
+        <v>1605</v>
       </c>
       <c r="I218" t="s">
-        <v>79</v>
+        <v>1606</v>
       </c>
       <c r="J218" t="s">
-        <v>79</v>
+        <v>1607</v>
       </c>
       <c r="K218" t="s">
-        <v>1791</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B219">
         <v>81</v>
       </c>
       <c r="C219" t="s">
-        <v>1884</v>
+        <v>1664</v>
       </c>
       <c r="D219" t="s">
-        <v>1963</v>
+        <v>1708</v>
       </c>
       <c r="E219" t="s">
-        <v>1964</v>
+        <v>1709</v>
       </c>
       <c r="F219" t="s">
-        <v>25</v>
+        <v>1711</v>
       </c>
       <c r="G219" t="s">
         <v>1034</v>
       </c>
       <c r="H219" t="s">
-        <v>1967</v>
+        <v>1713</v>
       </c>
       <c r="I219" t="s">
-        <v>1968</v>
+        <v>1714</v>
       </c>
       <c r="J219" t="s">
-        <v>1969</v>
+        <v>1715</v>
       </c>
       <c r="K219" t="s">
-        <v>1965</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B220">
         <v>81</v>
       </c>
       <c r="C220" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D220" t="s">
-        <v>1979</v>
+        <v>1773</v>
       </c>
       <c r="E220" t="s">
-        <v>1988</v>
+        <v>1774</v>
       </c>
       <c r="F220" t="s">
-        <v>1982</v>
+        <v>16</v>
       </c>
       <c r="G220" t="s">
-        <v>1983</v>
+        <v>1776</v>
       </c>
       <c r="H220" t="s">
-        <v>1991</v>
+        <v>1778</v>
       </c>
       <c r="I220" t="s">
-        <v>1992</v>
+        <v>79</v>
       </c>
       <c r="J220" t="s">
-        <v>1993</v>
+        <v>79</v>
       </c>
       <c r="K220" t="s">
-        <v>1989</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B221">
         <v>81</v>
       </c>
       <c r="C221" t="s">
-        <v>2098</v>
+        <v>1727</v>
       </c>
       <c r="D221" t="s">
-        <v>2114</v>
+        <v>964</v>
       </c>
       <c r="E221" t="s">
-        <v>830</v>
+        <v>362</v>
       </c>
       <c r="F221" t="s">
-        <v>16</v>
+        <v>356</v>
       </c>
       <c r="G221" t="s">
-        <v>2116</v>
+        <v>1792</v>
       </c>
       <c r="H221" t="s">
-        <v>2118</v>
+        <v>1794</v>
       </c>
       <c r="I221" t="s">
-        <v>2119</v>
+        <v>79</v>
       </c>
       <c r="J221" t="s">
-        <v>2120</v>
+        <v>79</v>
       </c>
       <c r="K221" t="s">
-        <v>2115</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B222">
         <v>81</v>
       </c>
       <c r="C222" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D222" t="s">
-        <v>2126</v>
+        <v>1963</v>
       </c>
       <c r="E222" t="s">
-        <v>2127</v>
+        <v>1964</v>
       </c>
       <c r="F222" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G222" t="s">
-        <v>2129</v>
+        <v>1034</v>
       </c>
       <c r="H222" t="s">
-        <v>2118</v>
+        <v>1967</v>
       </c>
       <c r="I222" t="s">
-        <v>2131</v>
+        <v>1968</v>
       </c>
       <c r="J222" t="s">
-        <v>2132</v>
+        <v>1969</v>
       </c>
       <c r="K222" t="s">
-        <v>2128</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B223">
         <v>81</v>
       </c>
       <c r="C223" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D223" t="s">
-        <v>2148</v>
+        <v>1979</v>
       </c>
       <c r="E223" t="s">
-        <v>110</v>
+        <v>1988</v>
       </c>
       <c r="F223" t="s">
-        <v>25</v>
+        <v>1982</v>
       </c>
       <c r="G223" t="s">
-        <v>2150</v>
+        <v>1983</v>
       </c>
       <c r="H223" t="s">
-        <v>2152</v>
+        <v>1991</v>
       </c>
       <c r="I223" t="s">
-        <v>2153</v>
+        <v>1992</v>
       </c>
       <c r="J223" t="s">
-        <v>2154</v>
+        <v>1993</v>
       </c>
       <c r="K223" t="s">
-        <v>2149</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B224">
         <v>81</v>
@@ -33209,33 +33693,33 @@
         <v>2098</v>
       </c>
       <c r="D224" t="s">
-        <v>2184</v>
+        <v>2114</v>
       </c>
       <c r="E224" t="s">
-        <v>2177</v>
+        <v>830</v>
       </c>
       <c r="F224" t="s">
-        <v>2042</v>
+        <v>16</v>
       </c>
       <c r="G224" t="s">
-        <v>2186</v>
+        <v>2116</v>
       </c>
       <c r="H224" t="s">
-        <v>2188</v>
+        <v>2118</v>
       </c>
       <c r="I224" t="s">
-        <v>2189</v>
+        <v>2119</v>
       </c>
       <c r="J224" t="s">
-        <v>2190</v>
+        <v>2120</v>
       </c>
       <c r="K224" t="s">
-        <v>2185</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B225">
         <v>81</v>
@@ -33244,313 +33728,313 @@
         <v>2098</v>
       </c>
       <c r="D225" t="s">
-        <v>2211</v>
+        <v>2126</v>
       </c>
       <c r="E225" t="s">
-        <v>110</v>
+        <v>2127</v>
       </c>
       <c r="F225" t="s">
         <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>2220</v>
+        <v>2129</v>
       </c>
       <c r="H225" t="s">
-        <v>2222</v>
+        <v>2118</v>
       </c>
       <c r="I225" t="s">
-        <v>2223</v>
+        <v>2131</v>
       </c>
       <c r="J225" t="s">
-        <v>2224</v>
+        <v>2132</v>
       </c>
       <c r="K225" t="s">
-        <v>2219</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B226">
         <v>81</v>
       </c>
       <c r="C226" t="s">
-        <v>2258</v>
+        <v>2098</v>
       </c>
       <c r="D226" t="s">
-        <v>2274</v>
+        <v>2148</v>
       </c>
       <c r="E226" t="s">
-        <v>2275</v>
+        <v>110</v>
       </c>
       <c r="F226" t="s">
-        <v>2277</v>
+        <v>25</v>
       </c>
       <c r="G226" t="s">
-        <v>2278</v>
+        <v>2150</v>
       </c>
       <c r="H226" t="s">
-        <v>2280</v>
+        <v>2152</v>
       </c>
       <c r="I226" t="s">
-        <v>2281</v>
+        <v>2153</v>
       </c>
       <c r="J226" t="s">
-        <v>2282</v>
+        <v>2154</v>
       </c>
       <c r="K226" t="s">
-        <v>2276</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B227">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C227" t="s">
-        <v>934</v>
+        <v>2098</v>
       </c>
       <c r="D227" t="s">
-        <v>1039</v>
+        <v>2184</v>
       </c>
       <c r="E227" t="s">
-        <v>1040</v>
+        <v>2177</v>
       </c>
       <c r="F227" t="s">
-        <v>1042</v>
+        <v>2042</v>
       </c>
       <c r="G227" t="s">
-        <v>1043</v>
+        <v>2186</v>
       </c>
       <c r="H227" t="s">
-        <v>1045</v>
+        <v>2188</v>
       </c>
       <c r="I227" t="s">
-        <v>1046</v>
+        <v>2189</v>
       </c>
       <c r="J227" t="s">
-        <v>1047</v>
+        <v>2190</v>
       </c>
       <c r="K227" t="s">
-        <v>1041</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B228">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C228" t="s">
-        <v>1884</v>
+        <v>2098</v>
       </c>
       <c r="D228" t="s">
-        <v>1947</v>
+        <v>2211</v>
       </c>
       <c r="E228" t="s">
-        <v>1948</v>
+        <v>110</v>
       </c>
       <c r="F228" t="s">
-        <v>1950</v>
+        <v>16</v>
       </c>
       <c r="G228" t="s">
-        <v>1034</v>
+        <v>2220</v>
       </c>
       <c r="H228" t="s">
-        <v>1952</v>
+        <v>2222</v>
       </c>
       <c r="I228" t="s">
-        <v>1953</v>
+        <v>2223</v>
       </c>
       <c r="J228" t="s">
-        <v>1954</v>
+        <v>2224</v>
       </c>
       <c r="K228" t="s">
-        <v>1949</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B229">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C229" t="s">
-        <v>1884</v>
+        <v>2258</v>
       </c>
       <c r="D229" t="s">
-        <v>1970</v>
+        <v>2274</v>
       </c>
       <c r="E229" t="s">
-        <v>1971</v>
+        <v>2275</v>
       </c>
       <c r="F229" t="s">
-        <v>1973</v>
+        <v>2277</v>
       </c>
       <c r="G229" t="s">
-        <v>1974</v>
+        <v>2278</v>
       </c>
       <c r="H229" t="s">
-        <v>1976</v>
+        <v>2280</v>
       </c>
       <c r="I229" t="s">
-        <v>1977</v>
+        <v>2281</v>
       </c>
       <c r="J229" t="s">
-        <v>1978</v>
+        <v>2282</v>
       </c>
       <c r="K229" t="s">
-        <v>1972</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B230">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C230" t="s">
-        <v>2098</v>
+        <v>2377</v>
       </c>
       <c r="D230" t="s">
-        <v>2107</v>
+        <v>2400</v>
       </c>
       <c r="E230" t="s">
-        <v>830</v>
+        <v>2401</v>
       </c>
       <c r="F230" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G230" t="s">
-        <v>2109</v>
+        <v>2395</v>
       </c>
       <c r="H230" t="s">
-        <v>2111</v>
+        <v>2404</v>
       </c>
       <c r="I230" t="s">
-        <v>2112</v>
+        <v>2405</v>
       </c>
       <c r="J230" t="s">
-        <v>2113</v>
+        <v>2406</v>
       </c>
       <c r="K230" t="s">
-        <v>2108</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B231">
         <v>80</v>
       </c>
       <c r="C231" t="s">
-        <v>2098</v>
+        <v>934</v>
       </c>
       <c r="D231" t="s">
-        <v>2133</v>
+        <v>1039</v>
       </c>
       <c r="E231" t="s">
-        <v>110</v>
+        <v>1040</v>
       </c>
       <c r="F231" t="s">
-        <v>16</v>
+        <v>1042</v>
       </c>
       <c r="G231" t="s">
-        <v>2135</v>
+        <v>1043</v>
       </c>
       <c r="H231" t="s">
-        <v>2137</v>
+        <v>1045</v>
       </c>
       <c r="I231" t="s">
-        <v>2138</v>
+        <v>1046</v>
       </c>
       <c r="J231" t="s">
-        <v>2139</v>
+        <v>1047</v>
       </c>
       <c r="K231" t="s">
-        <v>2134</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B232">
         <v>80</v>
       </c>
       <c r="C232" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D232" t="s">
-        <v>2140</v>
+        <v>1947</v>
       </c>
       <c r="E232" t="s">
-        <v>2141</v>
+        <v>1948</v>
       </c>
       <c r="F232" t="s">
-        <v>75</v>
+        <v>1950</v>
       </c>
       <c r="G232" t="s">
-        <v>2143</v>
+        <v>1034</v>
       </c>
       <c r="H232" t="s">
-        <v>2145</v>
+        <v>1952</v>
       </c>
       <c r="I232" t="s">
-        <v>2146</v>
+        <v>1953</v>
       </c>
       <c r="J232" t="s">
-        <v>2147</v>
+        <v>1954</v>
       </c>
       <c r="K232" t="s">
-        <v>2142</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B233">
         <v>80</v>
       </c>
       <c r="C233" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D233" t="s">
-        <v>2155</v>
+        <v>1970</v>
       </c>
       <c r="E233" t="s">
-        <v>110</v>
+        <v>1971</v>
       </c>
       <c r="F233" t="s">
-        <v>66</v>
+        <v>1973</v>
       </c>
       <c r="G233" t="s">
-        <v>2157</v>
+        <v>1974</v>
       </c>
       <c r="H233" t="s">
-        <v>2159</v>
+        <v>1976</v>
       </c>
       <c r="I233" t="s">
-        <v>2160</v>
+        <v>1977</v>
       </c>
       <c r="J233" t="s">
-        <v>2161</v>
+        <v>1978</v>
       </c>
       <c r="K233" t="s">
-        <v>2156</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B234">
         <v>80</v>
@@ -33559,33 +34043,33 @@
         <v>2098</v>
       </c>
       <c r="D234" t="s">
-        <v>2162</v>
+        <v>2107</v>
       </c>
       <c r="E234" t="s">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="F234" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G234" t="s">
-        <v>2171</v>
+        <v>2109</v>
       </c>
       <c r="H234" t="s">
-        <v>2173</v>
+        <v>2111</v>
       </c>
       <c r="I234" t="s">
-        <v>2174</v>
+        <v>2112</v>
       </c>
       <c r="J234" t="s">
-        <v>2175</v>
+        <v>2113</v>
       </c>
       <c r="K234" t="s">
-        <v>2170</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B235">
         <v>80</v>
@@ -33594,33 +34078,33 @@
         <v>2098</v>
       </c>
       <c r="D235" t="s">
-        <v>2203</v>
+        <v>2133</v>
       </c>
       <c r="E235" t="s">
-        <v>2204</v>
+        <v>110</v>
       </c>
       <c r="F235" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="G235" t="s">
-        <v>2206</v>
+        <v>2135</v>
       </c>
       <c r="H235" t="s">
-        <v>2208</v>
+        <v>2137</v>
       </c>
       <c r="I235" t="s">
-        <v>2209</v>
+        <v>2138</v>
       </c>
       <c r="J235" t="s">
-        <v>2210</v>
+        <v>2139</v>
       </c>
       <c r="K235" t="s">
-        <v>2205</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B236">
         <v>80</v>
@@ -33629,63 +34113,273 @@
         <v>2098</v>
       </c>
       <c r="D236" t="s">
-        <v>2225</v>
+        <v>2140</v>
       </c>
       <c r="E236" t="s">
-        <v>2226</v>
+        <v>2141</v>
       </c>
       <c r="F236" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G236" t="s">
-        <v>112</v>
+        <v>2143</v>
       </c>
       <c r="H236" t="s">
-        <v>2229</v>
+        <v>2145</v>
       </c>
       <c r="I236" t="s">
-        <v>2230</v>
+        <v>2146</v>
       </c>
       <c r="J236" t="s">
-        <v>2231</v>
+        <v>2147</v>
       </c>
       <c r="K236" t="s">
-        <v>2227</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>2388</v>
+        <v>2448</v>
       </c>
       <c r="B237">
         <v>80</v>
       </c>
       <c r="C237" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D237" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E237" t="s">
+        <v>110</v>
+      </c>
+      <c r="F237" t="s">
+        <v>66</v>
+      </c>
+      <c r="G237" t="s">
+        <v>2157</v>
+      </c>
+      <c r="H237" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I237" t="s">
+        <v>2160</v>
+      </c>
+      <c r="J237" t="s">
+        <v>2161</v>
+      </c>
+      <c r="K237" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B238">
+        <v>80</v>
+      </c>
+      <c r="C238" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D238" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E238" t="s">
+        <v>110</v>
+      </c>
+      <c r="F238" t="s">
+        <v>16</v>
+      </c>
+      <c r="G238" t="s">
+        <v>2171</v>
+      </c>
+      <c r="H238" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I238" t="s">
+        <v>2174</v>
+      </c>
+      <c r="J238" t="s">
+        <v>2175</v>
+      </c>
+      <c r="K238" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B239">
+        <v>80</v>
+      </c>
+      <c r="C239" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D239" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E239" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F239" t="s">
+        <v>106</v>
+      </c>
+      <c r="G239" t="s">
+        <v>2206</v>
+      </c>
+      <c r="H239" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I239" t="s">
+        <v>2209</v>
+      </c>
+      <c r="J239" t="s">
+        <v>2210</v>
+      </c>
+      <c r="K239" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B240">
+        <v>80</v>
+      </c>
+      <c r="C240" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D240" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E240" t="s">
+        <v>2226</v>
+      </c>
+      <c r="F240" t="s">
+        <v>16</v>
+      </c>
+      <c r="G240" t="s">
+        <v>112</v>
+      </c>
+      <c r="H240" t="s">
+        <v>2229</v>
+      </c>
+      <c r="I240" t="s">
+        <v>2230</v>
+      </c>
+      <c r="J240" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K240" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B241">
+        <v>80</v>
+      </c>
+      <c r="C241" t="s">
         <v>2258</v>
       </c>
-      <c r="D237" t="s">
+      <c r="D241" t="s">
         <v>2292</v>
       </c>
-      <c r="E237" t="s">
+      <c r="E241" t="s">
         <v>2293</v>
       </c>
-      <c r="F237" t="s">
+      <c r="F241" t="s">
         <v>747</v>
       </c>
-      <c r="G237" t="s">
+      <c r="G241" t="s">
         <v>2295</v>
       </c>
-      <c r="H237" t="s">
+      <c r="H241" t="s">
         <v>2297</v>
       </c>
-      <c r="I237" t="s">
+      <c r="I241" t="s">
         <v>2298</v>
       </c>
-      <c r="J237" t="s">
+      <c r="J241" t="s">
         <v>2299</v>
       </c>
-      <c r="K237" t="s">
+      <c r="K241" t="s">
         <v>2294</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B242">
+        <v>80</v>
+      </c>
+      <c r="C242" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D242" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E242" t="s">
+        <v>2393</v>
+      </c>
+      <c r="F242" t="s">
+        <v>66</v>
+      </c>
+      <c r="G242" t="s">
+        <v>2395</v>
+      </c>
+      <c r="H242" t="s">
+        <v>2397</v>
+      </c>
+      <c r="I242" t="s">
+        <v>2398</v>
+      </c>
+      <c r="J242" t="s">
+        <v>2399</v>
+      </c>
+      <c r="K242" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B243">
+        <v>80</v>
+      </c>
+      <c r="C243" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D243" t="s">
+        <v>2414</v>
+      </c>
+      <c r="E243" t="s">
+        <v>2415</v>
+      </c>
+      <c r="F243" t="s">
+        <v>124</v>
+      </c>
+      <c r="G243" t="s">
+        <v>2417</v>
+      </c>
+      <c r="H243" t="s">
+        <v>2419</v>
+      </c>
+      <c r="I243" t="s">
+        <v>2420</v>
+      </c>
+      <c r="J243" t="s">
+        <v>2421</v>
+      </c>
+      <c r="K243" t="s">
+        <v>2416</v>
       </c>
     </row>
   </sheetData>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7612" uniqueCount="2715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7652" uniqueCount="2732">
   <si>
     <t>日期</t>
   </si>
@@ -8039,6 +8039,57 @@
   </si>
   <si>
     <t>突出微导管/导管工艺开发与样品试制经历；补充工艺数据统计分析与工艺文件编制；强调材料学与实验能力。</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>深圳兰度生物材料有限公司</t>
+  </si>
+  <si>
+    <t>研发工程师（医用高分子方向）</t>
+  </si>
+  <si>
+    <t>清华大学数名博士创办的高端生物医用材料企业，招聘研发工程师（医用高分子方向）10名、研发工程师（生物学评价）等。从事创面、口腔、消化道、神经肌腱等高端生物医用材料的研发。要求化学、生物化学、分析化学、有机化学、材料化学工程、高分子材料等相关专业，研究生及以上学历（优秀本科亦可），薪资12k-20k。工作地点深圳。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/weixin?type=2&amp;query=深圳兰度生物材料+研发工程师</t>
+  </si>
+  <si>
+    <t>智能匹配82分【校园招聘】|强烈推荐|生物医用材料研发岗位，材料学+生物相容性/生物学评价技能重合，硕士可投的校招岗，位于深圳</t>
+  </si>
+  <si>
+    <t>研究72/技能78/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>兰度生物是清华博士团队创办的高端生物医用材料企业，属专精特新方向，行业赛道与候选人生物医学工程背景高度契合。岗位面向研究生招聘（校招性质），硕士可投，地点在目标城市深圳。岗位涉及医用高分子材料研发与生物学评价，与候选人材料学、生物相容性评价两项核心技能直接对应，是从生物医用材料切入医疗器械行业的优质校招机会，且企业有正规研发体系，利于应届生成长。</t>
+  </si>
+  <si>
+    <t>突出生物医学工程硕士背景与高分子/生物医用材料相关课程及科研经历；将硕士课题中涉及的材料选型、性能测试、降解/生物学评价内容量化呈现；强调生物相容性评价（细胞毒性、溶血、ISO 10993）相关实验技能；补充高分子材料表征（DSC、SEM、力学测试）等实验技能关键词；如有动物实验或植入材料研究经历务必单列，契合其创面/组织修复产品线。</t>
+  </si>
+  <si>
+    <t>产品研发工程师</t>
+  </si>
+  <si>
+    <t>业聚医疗为心血管介入治疗领域港股上市公司，招聘产品研发工程师。主要职责：参与心血管介入器械（球囊导管、支架输送系统等）的新产品开发，协助项目负责人完成产品设计、工艺开发、样品测试与设计验证；要求生物医学工程、材料、机械等相关专业，本科及以上，应届生可投。工作地点深圳/苏州。</t>
+  </si>
+  <si>
+    <t>深圳/苏州</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/weixin?type=2&amp;query=业聚医疗+研发工程师+招聘</t>
+  </si>
+  <si>
+    <t>智能匹配87分【校园招聘】|强烈推荐|心血管介入器械研发岗（球囊/导管/支架输送系统），方向直接相关，港股上市公司，应届生可投</t>
+  </si>
+  <si>
+    <t>研究85/技能76/学历100/行业100/企业92</t>
+  </si>
+  <si>
+    <t>业聚医疗是心血管介入治疗领域的港股上市公司（HK6996），产品覆盖冠脉球囊、导管等介入器械，属血管介入核心赛道，与候选人血管支架/介入器械研究方向高度匹配。岗位为产品研发工程师，明确接收应届生，位于深圳、苏州两个目标城市，职业起点好且平台规范。企业研发体系成熟，能提供从产品设计到工艺开发、设计验证的完整研发训练，非常契合硕士应届生的职业发展需求。</t>
+  </si>
+  <si>
+    <t>重点突出血管介入器械（球囊/导管/支架）相关科研或项目经历，明确写出所涉及的产品类型；强化结构设计与三维建模软件技能（SolidWorks/ProE/CAD），并用具体案例说明；将支架/导管设计中涉及的力学分析、有限元仿真、样品测试与设计验证内容量化；补充材料选型与性能测试经验（镍钛、高分子）；如参与过动物实验或产品注册，单列以体现全流程研发能力。</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -8593,7 +8644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L360"/>
+  <dimension ref="A1:L362"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -22287,6 +22338,82 @@
       </c>
       <c r="L360" t="s">
         <v>2674</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>2675</v>
+      </c>
+      <c r="B361" t="s">
+        <v>2676</v>
+      </c>
+      <c r="C361" t="s">
+        <v>2677</v>
+      </c>
+      <c r="D361" t="s">
+        <v>2678</v>
+      </c>
+      <c r="E361" t="s">
+        <v>66</v>
+      </c>
+      <c r="F361" t="s">
+        <v>2679</v>
+      </c>
+      <c r="G361">
+        <v>8</v>
+      </c>
+      <c r="H361" t="s">
+        <v>2680</v>
+      </c>
+      <c r="I361">
+        <v>82</v>
+      </c>
+      <c r="J361" t="s">
+        <v>2681</v>
+      </c>
+      <c r="K361" t="s">
+        <v>2682</v>
+      </c>
+      <c r="L361" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>2675</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C362" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D362" t="s">
+        <v>2685</v>
+      </c>
+      <c r="E362" t="s">
+        <v>2686</v>
+      </c>
+      <c r="F362" t="s">
+        <v>2687</v>
+      </c>
+      <c r="G362">
+        <v>9</v>
+      </c>
+      <c r="H362" t="s">
+        <v>2688</v>
+      </c>
+      <c r="I362">
+        <v>87</v>
+      </c>
+      <c r="J362" t="s">
+        <v>2689</v>
+      </c>
+      <c r="K362" t="s">
+        <v>2690</v>
+      </c>
+      <c r="L362" t="s">
+        <v>2691</v>
       </c>
     </row>
   </sheetData>
@@ -22320,7 +22447,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2675</v>
+        <v>2692</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -22329,16 +22456,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2676</v>
+        <v>2693</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2677</v>
+        <v>2694</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2678</v>
+        <v>2695</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2679</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -22352,13 +22479,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2680</v>
+        <v>2697</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2681</v>
+        <v>2698</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>2682</v>
+        <v>2699</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -22401,7 +22528,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>2687</v>
+        <v>2704</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -22411,31 +22538,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>2688</v>
+        <v>2705</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2689</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2690</v>
+        <v>2707</v>
       </c>
       <c r="B4">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2691</v>
+        <v>2708</v>
       </c>
       <c r="B5" t="s">
-        <v>2692</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2693</v>
+        <v>2710</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -22443,7 +22570,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2694</v>
+        <v>2711</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -22451,23 +22578,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2695</v>
+        <v>2712</v>
       </c>
       <c r="B8">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2696</v>
+        <v>2713</v>
       </c>
       <c r="B9">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2697</v>
+        <v>2714</v>
       </c>
       <c r="B10">
         <v>16</v>
@@ -22475,15 +22602,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2698</v>
+        <v>2715</v>
       </c>
       <c r="B11" t="s">
-        <v>2437</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>2699</v>
+        <v>2716</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -22493,15 +22620,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>2700</v>
+        <v>2717</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>2701</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2702</v>
+        <v>2719</v>
       </c>
       <c r="B16" s="5">
         <v>8</v>
@@ -22509,23 +22636,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2703</v>
+        <v>2720</v>
       </c>
       <c r="B17" s="5">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2704</v>
+        <v>2721</v>
       </c>
       <c r="B18" s="5">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2705</v>
+        <v>2722</v>
       </c>
       <c r="B19" s="5">
         <v>16</v>
@@ -22533,7 +22660,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2706</v>
+        <v>2723</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -22541,7 +22668,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2707</v>
+        <v>2724</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -22549,7 +22676,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2708</v>
+        <v>2725</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -22557,7 +22684,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2709</v>
+        <v>2726</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -22565,7 +22692,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2710</v>
+        <v>2727</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -22573,7 +22700,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2711</v>
+        <v>2728</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -22581,7 +22708,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>2712</v>
+        <v>2729</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -22593,7 +22720,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>2713</v>
+        <v>2730</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -22611,7 +22738,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>2714</v>
+        <v>2731</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -27224,25 +27351,25 @@
         <v>178</v>
       </c>
       <c r="B207" t="s">
-        <v>1200</v>
+        <v>2675</v>
       </c>
       <c r="C207" t="s">
-        <v>1201</v>
+        <v>1899</v>
       </c>
       <c r="D207" t="s">
-        <v>1202</v>
+        <v>2684</v>
       </c>
       <c r="E207" t="s">
-        <v>1204</v>
+        <v>2686</v>
       </c>
       <c r="F207" t="s">
-        <v>1205</v>
+        <v>2687</v>
       </c>
       <c r="G207">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H207" t="s">
-        <v>1206</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -27250,25 +27377,25 @@
         <v>179</v>
       </c>
       <c r="B208" t="s">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="C208" t="s">
-        <v>72</v>
+        <v>1201</v>
       </c>
       <c r="D208" t="s">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="E208" t="s">
-        <v>75</v>
+        <v>1204</v>
       </c>
       <c r="F208" t="s">
-        <v>76</v>
+        <v>1205</v>
       </c>
       <c r="G208">
         <v>8</v>
       </c>
       <c r="H208" t="s">
-        <v>77</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -27279,22 +27406,22 @@
         <v>12</v>
       </c>
       <c r="C209" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D209" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E209" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F209" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G209">
         <v>8</v>
       </c>
       <c r="H209" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -27305,22 +27432,22 @@
         <v>12</v>
       </c>
       <c r="C210" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D210" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E210" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F210" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G210">
         <v>8</v>
       </c>
       <c r="H210" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -27331,22 +27458,22 @@
         <v>12</v>
       </c>
       <c r="C211" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D211" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E211" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F211" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G211">
         <v>8</v>
       </c>
       <c r="H211" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -27357,22 +27484,22 @@
         <v>12</v>
       </c>
       <c r="C212" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D212" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E212" t="s">
         <v>16</v>
       </c>
       <c r="F212" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G212">
         <v>8</v>
       </c>
       <c r="H212" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -27383,22 +27510,22 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D213" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E213" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F213" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G213">
         <v>8</v>
       </c>
       <c r="H213" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -27409,22 +27536,22 @@
         <v>12</v>
       </c>
       <c r="C214" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="D214" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="E214" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="F214" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G214">
         <v>8</v>
       </c>
       <c r="H214" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -27435,22 +27562,22 @@
         <v>12</v>
       </c>
       <c r="C215" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D215" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E215" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="F215" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G215">
         <v>8</v>
       </c>
       <c r="H215" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -27458,25 +27585,25 @@
         <v>187</v>
       </c>
       <c r="B216" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C216" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="D216" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="E216" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F216" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="G216">
         <v>8</v>
       </c>
       <c r="H216" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -27487,22 +27614,22 @@
         <v>159</v>
       </c>
       <c r="C217" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D217" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E217" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="F217" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G217">
         <v>8</v>
       </c>
       <c r="H217" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -27513,22 +27640,22 @@
         <v>159</v>
       </c>
       <c r="C218" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D218" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E218" t="s">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="F218" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="G218">
         <v>8</v>
       </c>
       <c r="H218" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -27539,22 +27666,22 @@
         <v>159</v>
       </c>
       <c r="C219" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D219" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="E219" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F219" t="s">
-        <v>76</v>
+        <v>231</v>
       </c>
       <c r="G219">
         <v>8</v>
       </c>
       <c r="H219" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
@@ -27565,22 +27692,22 @@
         <v>159</v>
       </c>
       <c r="C220" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D220" t="s">
-        <v>241</v>
+        <v>73</v>
       </c>
       <c r="E220" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F220" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="G220">
         <v>8</v>
       </c>
       <c r="H220" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -27591,22 +27718,22 @@
         <v>159</v>
       </c>
       <c r="C221" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D221" t="s">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="E221" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F221" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="G221">
         <v>8</v>
       </c>
       <c r="H221" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -27617,22 +27744,22 @@
         <v>159</v>
       </c>
       <c r="C222" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D222" t="s">
-        <v>249</v>
+        <v>154</v>
       </c>
       <c r="E222" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F222" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="G222">
         <v>8</v>
       </c>
       <c r="H222" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -27643,22 +27770,22 @@
         <v>159</v>
       </c>
       <c r="C223" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D223" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E223" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
       <c r="F223" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G223">
         <v>8</v>
       </c>
       <c r="H223" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
@@ -27669,22 +27796,22 @@
         <v>159</v>
       </c>
       <c r="C224" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D224" t="s">
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="E224" t="s">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="F224" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G224">
         <v>8</v>
       </c>
       <c r="H224" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
@@ -27695,22 +27822,22 @@
         <v>159</v>
       </c>
       <c r="C225" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>267</v>
+        <v>122</v>
       </c>
       <c r="E225" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="F225" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
       <c r="G225">
         <v>8</v>
       </c>
       <c r="H225" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -27721,22 +27848,22 @@
         <v>159</v>
       </c>
       <c r="C226" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E226" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="F226" t="s">
-        <v>281</v>
+        <v>58</v>
       </c>
       <c r="G226">
         <v>8</v>
       </c>
       <c r="H226" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
@@ -27744,25 +27871,25 @@
         <v>198</v>
       </c>
       <c r="B227" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C227" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="D227" t="s">
-        <v>316</v>
+        <v>278</v>
       </c>
       <c r="E227" t="s">
-        <v>318</v>
+        <v>280</v>
       </c>
       <c r="F227" t="s">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="G227">
         <v>8</v>
       </c>
       <c r="H227" t="s">
-        <v>320</v>
+        <v>282</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -27773,22 +27900,22 @@
         <v>284</v>
       </c>
       <c r="C228" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="D228" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="E228" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="F228" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="G228">
         <v>8</v>
       </c>
       <c r="H228" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -27799,22 +27926,22 @@
         <v>284</v>
       </c>
       <c r="C229" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="D229" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="E229" t="s">
-        <v>98</v>
+        <v>341</v>
       </c>
       <c r="F229" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="G229">
         <v>8</v>
       </c>
       <c r="H229" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -27830,7 +27957,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K276"/>
+  <dimension ref="A1:K278"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -27847,10 +27974,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>2683</v>
+        <v>2700</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2684</v>
+        <v>2701</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -27877,12 +28004,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>2685</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -27917,7 +28044,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -27952,7 +28079,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -27987,7 +28114,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -28022,7 +28149,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -28057,7 +28184,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -28092,7 +28219,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B8">
         <v>95</v>
@@ -28127,7 +28254,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B9">
         <v>95</v>
@@ -28162,7 +28289,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B10">
         <v>94</v>
@@ -28197,7 +28324,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B11">
         <v>94</v>
@@ -28232,7 +28359,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B12">
         <v>93</v>
@@ -28267,7 +28394,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B13">
         <v>93</v>
@@ -28302,7 +28429,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B14">
         <v>93</v>
@@ -28337,7 +28464,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B15">
         <v>93</v>
@@ -28372,7 +28499,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B16">
         <v>93</v>
@@ -28407,7 +28534,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B17">
         <v>92</v>
@@ -28442,7 +28569,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B18">
         <v>92</v>
@@ -28477,7 +28604,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B19">
         <v>92</v>
@@ -28512,7 +28639,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B20">
         <v>92</v>
@@ -28547,7 +28674,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B21">
         <v>92</v>
@@ -28582,7 +28709,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B22">
         <v>92</v>
@@ -28617,7 +28744,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B23">
         <v>91</v>
@@ -28652,7 +28779,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B24">
         <v>91</v>
@@ -28687,7 +28814,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B25">
         <v>91</v>
@@ -28722,7 +28849,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B26">
         <v>91</v>
@@ -28757,7 +28884,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B27">
         <v>91</v>
@@ -28792,7 +28919,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B28">
         <v>91</v>
@@ -28827,7 +28954,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B29">
         <v>91</v>
@@ -28862,7 +28989,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B30">
         <v>91</v>
@@ -28897,7 +29024,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B31">
         <v>91</v>
@@ -28932,7 +29059,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B32">
         <v>91</v>
@@ -28967,7 +29094,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B33">
         <v>90</v>
@@ -29002,7 +29129,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B34">
         <v>90</v>
@@ -29037,7 +29164,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B35">
         <v>90</v>
@@ -29072,7 +29199,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B36">
         <v>90</v>
@@ -29107,7 +29234,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B37">
         <v>90</v>
@@ -29142,7 +29269,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B38">
         <v>90</v>
@@ -29177,7 +29304,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B39">
         <v>90</v>
@@ -29212,7 +29339,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B40">
         <v>90</v>
@@ -29247,7 +29374,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B41">
         <v>90</v>
@@ -29282,7 +29409,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B42">
         <v>90</v>
@@ -29317,7 +29444,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B43">
         <v>90</v>
@@ -29352,7 +29479,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B44">
         <v>90</v>
@@ -29387,7 +29514,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B45">
         <v>90</v>
@@ -29422,7 +29549,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B46">
         <v>90</v>
@@ -29457,7 +29584,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B47">
         <v>90</v>
@@ -29492,7 +29619,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B48">
         <v>90</v>
@@ -29527,7 +29654,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B49">
         <v>89</v>
@@ -29562,7 +29689,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B50">
         <v>89</v>
@@ -29597,7 +29724,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B51">
         <v>89</v>
@@ -29632,7 +29759,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B52">
         <v>89</v>
@@ -29667,7 +29794,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B53">
         <v>89</v>
@@ -29702,7 +29829,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B54">
         <v>89</v>
@@ -29737,7 +29864,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B55">
         <v>89</v>
@@ -29772,7 +29899,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B56">
         <v>89</v>
@@ -29807,7 +29934,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B57">
         <v>89</v>
@@ -29842,7 +29969,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B58">
         <v>89</v>
@@ -29877,7 +30004,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B59">
         <v>89</v>
@@ -29912,7 +30039,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B60">
         <v>89</v>
@@ -29947,7 +30074,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B61">
         <v>89</v>
@@ -29982,7 +30109,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B62">
         <v>89</v>
@@ -30017,7 +30144,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B63">
         <v>89</v>
@@ -30052,7 +30179,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B64">
         <v>89</v>
@@ -30087,7 +30214,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B65">
         <v>89</v>
@@ -30122,7 +30249,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B66">
         <v>89</v>
@@ -30157,7 +30284,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B67">
         <v>89</v>
@@ -30192,7 +30319,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B68">
         <v>89</v>
@@ -30227,7 +30354,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B69">
         <v>89</v>
@@ -30262,7 +30389,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B70">
         <v>89</v>
@@ -30297,7 +30424,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B71">
         <v>89</v>
@@ -30332,7 +30459,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B72">
         <v>89</v>
@@ -30367,7 +30494,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B73">
         <v>89</v>
@@ -30402,7 +30529,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B74">
         <v>89</v>
@@ -30437,7 +30564,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B75">
         <v>89</v>
@@ -30472,7 +30599,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B76">
         <v>88</v>
@@ -30507,7 +30634,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B77">
         <v>88</v>
@@ -30542,7 +30669,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B78">
         <v>88</v>
@@ -30577,7 +30704,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B79">
         <v>88</v>
@@ -30612,7 +30739,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B80">
         <v>88</v>
@@ -30647,7 +30774,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B81">
         <v>88</v>
@@ -30682,7 +30809,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B82">
         <v>88</v>
@@ -30717,7 +30844,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B83">
         <v>88</v>
@@ -30752,7 +30879,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B84">
         <v>88</v>
@@ -30787,7 +30914,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B85">
         <v>88</v>
@@ -30822,7 +30949,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B86">
         <v>88</v>
@@ -30857,7 +30984,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B87">
         <v>88</v>
@@ -30892,7 +31019,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B88">
         <v>88</v>
@@ -30927,7 +31054,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B89">
         <v>88</v>
@@ -30962,7 +31089,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B90">
         <v>88</v>
@@ -30997,7 +31124,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B91">
         <v>88</v>
@@ -31032,7 +31159,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B92">
         <v>88</v>
@@ -31067,7 +31194,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B93">
         <v>88</v>
@@ -31102,7 +31229,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B94">
         <v>88</v>
@@ -31137,7 +31264,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B95">
         <v>88</v>
@@ -31172,7 +31299,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B96">
         <v>88</v>
@@ -31207,7 +31334,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B97">
         <v>88</v>
@@ -31242,7 +31369,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B98">
         <v>88</v>
@@ -31277,7 +31404,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B99">
         <v>88</v>
@@ -31312,7 +31439,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B100">
         <v>88</v>
@@ -31347,7 +31474,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B101">
         <v>88</v>
@@ -31382,7 +31509,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B102">
         <v>88</v>
@@ -31417,7 +31544,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B103">
         <v>87</v>
@@ -31452,7 +31579,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B104">
         <v>87</v>
@@ -31487,7 +31614,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B105">
         <v>87</v>
@@ -31522,7 +31649,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B106">
         <v>87</v>
@@ -31557,7 +31684,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B107">
         <v>87</v>
@@ -31592,7 +31719,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B108">
         <v>87</v>
@@ -31627,7 +31754,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B109">
         <v>87</v>
@@ -31662,7 +31789,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B110">
         <v>87</v>
@@ -31697,7 +31824,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B111">
         <v>87</v>
@@ -31732,7 +31859,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B112">
         <v>87</v>
@@ -31767,7 +31894,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B113">
         <v>87</v>
@@ -31802,7 +31929,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B114">
         <v>87</v>
@@ -31837,7 +31964,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B115">
         <v>87</v>
@@ -31872,7 +31999,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B116">
         <v>87</v>
@@ -31907,7 +32034,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B117">
         <v>87</v>
@@ -31942,7 +32069,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B118">
         <v>87</v>
@@ -31977,7 +32104,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B119">
         <v>87</v>
@@ -32012,7 +32139,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B120">
         <v>87</v>
@@ -32047,7 +32174,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B121">
         <v>87</v>
@@ -32082,7 +32209,7 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B122">
         <v>87</v>
@@ -32117,7 +32244,7 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B123">
         <v>87</v>
@@ -32152,7 +32279,7 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B124">
         <v>87</v>
@@ -32187,7 +32314,7 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B125">
         <v>87</v>
@@ -32222,7 +32349,7 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B126">
         <v>87</v>
@@ -32257,7 +32384,7 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B127">
         <v>87</v>
@@ -32292,77 +32419,77 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B128">
+        <v>87</v>
+      </c>
+      <c r="C128" t="s">
+        <v>2675</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1899</v>
+      </c>
+      <c r="E128" t="s">
+        <v>2684</v>
+      </c>
+      <c r="F128" t="s">
         <v>2686</v>
       </c>
-      <c r="B128">
-        <v>86</v>
-      </c>
-      <c r="C128" t="s">
-        <v>284</v>
-      </c>
-      <c r="D128" t="s">
-        <v>369</v>
-      </c>
-      <c r="E128" t="s">
-        <v>370</v>
-      </c>
-      <c r="F128" t="s">
-        <v>16</v>
-      </c>
       <c r="G128" t="s">
-        <v>372</v>
+        <v>2687</v>
       </c>
       <c r="H128" t="s">
-        <v>374</v>
+        <v>2689</v>
       </c>
       <c r="I128" t="s">
-        <v>375</v>
+        <v>2690</v>
       </c>
       <c r="J128" t="s">
-        <v>376</v>
+        <v>2691</v>
       </c>
       <c r="K128" t="s">
-        <v>371</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B129">
         <v>86</v>
       </c>
       <c r="C129" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D129" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="E129" t="s">
-        <v>457</v>
+        <v>370</v>
       </c>
       <c r="F129" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G129" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="H129" t="s">
-        <v>460</v>
+        <v>374</v>
       </c>
       <c r="I129" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="J129" t="s">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="K129" t="s">
-        <v>458</v>
+        <v>371</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B130">
         <v>86</v>
@@ -32371,138 +32498,138 @@
         <v>402</v>
       </c>
       <c r="D130" t="s">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="E130" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F130" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G130" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H130" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="I130" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J130" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="K130" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B131">
         <v>86</v>
       </c>
       <c r="C131" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D131" t="s">
-        <v>541</v>
+        <v>322</v>
       </c>
       <c r="E131" t="s">
-        <v>542</v>
+        <v>466</v>
       </c>
       <c r="F131" t="s">
-        <v>544</v>
+        <v>16</v>
       </c>
       <c r="G131" t="s">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="H131" t="s">
-        <v>547</v>
+        <v>470</v>
       </c>
       <c r="I131" t="s">
-        <v>548</v>
+        <v>471</v>
       </c>
       <c r="J131" t="s">
-        <v>549</v>
+        <v>472</v>
       </c>
       <c r="K131" t="s">
-        <v>543</v>
+        <v>467</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B132">
         <v>86</v>
       </c>
       <c r="C132" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D132" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E132" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="F132" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G132" t="s">
-        <v>468</v>
+        <v>545</v>
       </c>
       <c r="H132" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="I132" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="J132" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="K132" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B133">
         <v>86</v>
       </c>
       <c r="C133" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D133" t="s">
-        <v>609</v>
+        <v>557</v>
       </c>
       <c r="E133" t="s">
-        <v>610</v>
+        <v>558</v>
       </c>
       <c r="F133" t="s">
         <v>16</v>
       </c>
       <c r="G133" t="s">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="H133" t="s">
-        <v>613</v>
+        <v>561</v>
       </c>
       <c r="I133" t="s">
-        <v>614</v>
+        <v>562</v>
       </c>
       <c r="J133" t="s">
-        <v>615</v>
+        <v>563</v>
       </c>
       <c r="K133" t="s">
-        <v>611</v>
+        <v>559</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B134">
         <v>86</v>
@@ -32511,33 +32638,33 @@
         <v>591</v>
       </c>
       <c r="D134" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="E134" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="F134" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G134" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="H134" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="I134" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="J134" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="K134" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B135">
         <v>86</v>
@@ -32546,103 +32673,103 @@
         <v>591</v>
       </c>
       <c r="D135" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="E135" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F135" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G135" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="H135" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="I135" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="J135" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="K135" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B136">
         <v>86</v>
       </c>
       <c r="C136" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D136" t="s">
-        <v>829</v>
+        <v>635</v>
       </c>
       <c r="E136" t="s">
-        <v>830</v>
+        <v>636</v>
       </c>
       <c r="F136" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G136" t="s">
-        <v>832</v>
+        <v>638</v>
       </c>
       <c r="H136" t="s">
-        <v>834</v>
+        <v>640</v>
       </c>
       <c r="I136" t="s">
-        <v>835</v>
+        <v>641</v>
       </c>
       <c r="J136" t="s">
-        <v>836</v>
+        <v>642</v>
       </c>
       <c r="K136" t="s">
-        <v>831</v>
+        <v>637</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B137">
         <v>86</v>
       </c>
       <c r="C137" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D137" t="s">
-        <v>872</v>
+        <v>829</v>
       </c>
       <c r="E137" t="s">
-        <v>873</v>
+        <v>830</v>
       </c>
       <c r="F137" t="s">
-        <v>380</v>
+        <v>785</v>
       </c>
       <c r="G137" t="s">
-        <v>875</v>
+        <v>832</v>
       </c>
       <c r="H137" t="s">
-        <v>877</v>
+        <v>834</v>
       </c>
       <c r="I137" t="s">
-        <v>878</v>
+        <v>835</v>
       </c>
       <c r="J137" t="s">
-        <v>879</v>
+        <v>836</v>
       </c>
       <c r="K137" t="s">
-        <v>874</v>
+        <v>831</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B138">
         <v>86</v>
@@ -32651,68 +32778,68 @@
         <v>845</v>
       </c>
       <c r="D138" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="E138" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="F138" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G138" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="H138" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="I138" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J138" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="K138" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B139">
         <v>86</v>
       </c>
       <c r="C139" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D139" t="s">
-        <v>973</v>
+        <v>880</v>
       </c>
       <c r="E139" t="s">
-        <v>974</v>
+        <v>881</v>
       </c>
       <c r="F139" t="s">
         <v>16</v>
       </c>
       <c r="G139" t="s">
-        <v>468</v>
+        <v>883</v>
       </c>
       <c r="H139" t="s">
-        <v>977</v>
+        <v>885</v>
       </c>
       <c r="I139" t="s">
-        <v>978</v>
+        <v>886</v>
       </c>
       <c r="J139" t="s">
-        <v>979</v>
+        <v>887</v>
       </c>
       <c r="K139" t="s">
-        <v>975</v>
+        <v>882</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B140">
         <v>86</v>
@@ -32721,33 +32848,33 @@
         <v>934</v>
       </c>
       <c r="D140" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="E140" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="F140" t="s">
-        <v>983</v>
+        <v>16</v>
       </c>
       <c r="G140" t="s">
-        <v>984</v>
+        <v>468</v>
       </c>
       <c r="H140" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="I140" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="J140" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="K140" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B141">
         <v>86</v>
@@ -32756,68 +32883,68 @@
         <v>934</v>
       </c>
       <c r="D141" t="s">
-        <v>1073</v>
+        <v>980</v>
       </c>
       <c r="E141" t="s">
-        <v>1074</v>
+        <v>981</v>
       </c>
       <c r="F141" t="s">
-        <v>1076</v>
+        <v>983</v>
       </c>
       <c r="G141" t="s">
-        <v>1077</v>
+        <v>984</v>
       </c>
       <c r="H141" t="s">
-        <v>1079</v>
+        <v>986</v>
       </c>
       <c r="I141" t="s">
-        <v>1080</v>
+        <v>987</v>
       </c>
       <c r="J141" t="s">
-        <v>1081</v>
+        <v>988</v>
       </c>
       <c r="K141" t="s">
-        <v>1075</v>
+        <v>982</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B142">
         <v>86</v>
       </c>
       <c r="C142" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D142" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="E142" t="s">
-        <v>1089</v>
+        <v>1074</v>
       </c>
       <c r="F142" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
       <c r="G142" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="H142" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
       <c r="I142" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="J142" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="K142" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B143">
         <v>86</v>
@@ -32826,103 +32953,103 @@
         <v>1087</v>
       </c>
       <c r="D143" t="s">
-        <v>1146</v>
+        <v>1088</v>
       </c>
       <c r="E143" t="s">
-        <v>1147</v>
+        <v>1089</v>
       </c>
       <c r="F143" t="s">
-        <v>1149</v>
+        <v>1091</v>
       </c>
       <c r="G143" t="s">
-        <v>1150</v>
+        <v>1092</v>
       </c>
       <c r="H143" t="s">
-        <v>1152</v>
+        <v>1094</v>
       </c>
       <c r="I143" t="s">
-        <v>1153</v>
+        <v>1095</v>
       </c>
       <c r="J143" t="s">
-        <v>1154</v>
+        <v>1096</v>
       </c>
       <c r="K143" t="s">
-        <v>1148</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B144">
         <v>86</v>
       </c>
       <c r="C144" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="D144" t="s">
-        <v>1164</v>
+        <v>1146</v>
       </c>
       <c r="E144" t="s">
-        <v>610</v>
+        <v>1147</v>
       </c>
       <c r="F144" t="s">
-        <v>16</v>
+        <v>1149</v>
       </c>
       <c r="G144" t="s">
-        <v>1166</v>
+        <v>1150</v>
       </c>
       <c r="H144" t="s">
-        <v>1168</v>
+        <v>1152</v>
       </c>
       <c r="I144" t="s">
-        <v>1169</v>
+        <v>1153</v>
       </c>
       <c r="J144" t="s">
-        <v>1170</v>
+        <v>1154</v>
       </c>
       <c r="K144" t="s">
-        <v>1165</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B145">
         <v>86</v>
       </c>
       <c r="C145" t="s">
-        <v>1300</v>
+        <v>1155</v>
       </c>
       <c r="D145" t="s">
-        <v>1309</v>
+        <v>1164</v>
       </c>
       <c r="E145" t="s">
         <v>610</v>
       </c>
       <c r="F145" t="s">
-        <v>1311</v>
+        <v>16</v>
       </c>
       <c r="G145" t="s">
-        <v>1312</v>
+        <v>1166</v>
       </c>
       <c r="H145" t="s">
-        <v>1314</v>
+        <v>1168</v>
       </c>
       <c r="I145" t="s">
-        <v>1315</v>
+        <v>1169</v>
       </c>
       <c r="J145" t="s">
-        <v>1316</v>
+        <v>1170</v>
       </c>
       <c r="K145" t="s">
-        <v>1310</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B146">
         <v>86</v>
@@ -32931,278 +33058,278 @@
         <v>1300</v>
       </c>
       <c r="D146" t="s">
-        <v>1323</v>
+        <v>1309</v>
       </c>
       <c r="E146" t="s">
-        <v>89</v>
+        <v>610</v>
       </c>
       <c r="F146" t="s">
-        <v>25</v>
+        <v>1311</v>
       </c>
       <c r="G146" t="s">
-        <v>1325</v>
+        <v>1312</v>
       </c>
       <c r="H146" t="s">
-        <v>1327</v>
+        <v>1314</v>
       </c>
       <c r="I146" t="s">
-        <v>1328</v>
+        <v>1315</v>
       </c>
       <c r="J146" t="s">
-        <v>1329</v>
+        <v>1316</v>
       </c>
       <c r="K146" t="s">
-        <v>1324</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B147">
         <v>86</v>
       </c>
       <c r="C147" t="s">
-        <v>1534</v>
+        <v>1300</v>
       </c>
       <c r="D147" t="s">
-        <v>1191</v>
+        <v>1323</v>
       </c>
       <c r="E147" t="s">
-        <v>1549</v>
+        <v>89</v>
       </c>
       <c r="F147" t="s">
-        <v>1551</v>
+        <v>25</v>
       </c>
       <c r="G147" t="s">
-        <v>1552</v>
+        <v>1325</v>
       </c>
       <c r="H147" t="s">
-        <v>1554</v>
+        <v>1327</v>
       </c>
       <c r="I147" t="s">
-        <v>1555</v>
+        <v>1328</v>
       </c>
       <c r="J147" t="s">
-        <v>1556</v>
+        <v>1329</v>
       </c>
       <c r="K147" t="s">
-        <v>1550</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B148">
         <v>86</v>
       </c>
       <c r="C148" t="s">
-        <v>1649</v>
+        <v>1534</v>
       </c>
       <c r="D148" t="s">
-        <v>1650</v>
+        <v>1191</v>
       </c>
       <c r="E148" t="s">
-        <v>1651</v>
+        <v>1549</v>
       </c>
       <c r="F148" t="s">
-        <v>510</v>
+        <v>1551</v>
       </c>
       <c r="G148" t="s">
-        <v>1653</v>
+        <v>1552</v>
       </c>
       <c r="H148" t="s">
-        <v>1327</v>
+        <v>1554</v>
       </c>
       <c r="I148" t="s">
-        <v>1655</v>
+        <v>1555</v>
       </c>
       <c r="J148" t="s">
-        <v>1656</v>
+        <v>1556</v>
       </c>
       <c r="K148" t="s">
-        <v>1652</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B149">
         <v>86</v>
       </c>
       <c r="C149" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="D149" t="s">
-        <v>1673</v>
+        <v>1650</v>
       </c>
       <c r="E149" t="s">
-        <v>1674</v>
+        <v>1651</v>
       </c>
       <c r="F149" t="s">
-        <v>747</v>
+        <v>510</v>
       </c>
       <c r="G149" t="s">
-        <v>1676</v>
+        <v>1653</v>
       </c>
       <c r="H149" t="s">
-        <v>1678</v>
+        <v>1327</v>
       </c>
       <c r="I149" t="s">
-        <v>1679</v>
+        <v>1655</v>
       </c>
       <c r="J149" t="s">
-        <v>1680</v>
+        <v>1656</v>
       </c>
       <c r="K149" t="s">
-        <v>1675</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B150">
         <v>86</v>
       </c>
       <c r="C150" t="s">
-        <v>1727</v>
+        <v>1664</v>
       </c>
       <c r="D150" t="s">
-        <v>791</v>
+        <v>1673</v>
       </c>
       <c r="E150" t="s">
-        <v>1767</v>
+        <v>1674</v>
       </c>
       <c r="F150" t="s">
-        <v>1769</v>
+        <v>747</v>
       </c>
       <c r="G150" t="s">
-        <v>1770</v>
+        <v>1676</v>
       </c>
       <c r="H150" t="s">
-        <v>1772</v>
+        <v>1678</v>
       </c>
       <c r="I150" t="s">
-        <v>79</v>
+        <v>1679</v>
       </c>
       <c r="J150" t="s">
-        <v>79</v>
+        <v>1680</v>
       </c>
       <c r="K150" t="s">
-        <v>1768</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B151">
         <v>86</v>
       </c>
       <c r="C151" t="s">
-        <v>1994</v>
+        <v>1727</v>
       </c>
       <c r="D151" t="s">
-        <v>2076</v>
+        <v>791</v>
       </c>
       <c r="E151" t="s">
-        <v>2077</v>
+        <v>1767</v>
       </c>
       <c r="F151" t="s">
-        <v>16</v>
+        <v>1769</v>
       </c>
       <c r="G151" t="s">
-        <v>2079</v>
+        <v>1770</v>
       </c>
       <c r="H151" t="s">
-        <v>2081</v>
+        <v>1772</v>
       </c>
       <c r="I151" t="s">
-        <v>2082</v>
+        <v>79</v>
       </c>
       <c r="J151" t="s">
-        <v>2083</v>
+        <v>79</v>
       </c>
       <c r="K151" t="s">
-        <v>2078</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B152">
         <v>86</v>
       </c>
       <c r="C152" t="s">
-        <v>2258</v>
+        <v>1994</v>
       </c>
       <c r="D152" t="s">
-        <v>2300</v>
+        <v>2076</v>
       </c>
       <c r="E152" t="s">
-        <v>2301</v>
+        <v>2077</v>
       </c>
       <c r="F152" t="s">
-        <v>1644</v>
+        <v>16</v>
       </c>
       <c r="G152" t="s">
-        <v>2303</v>
+        <v>2079</v>
       </c>
       <c r="H152" t="s">
-        <v>2305</v>
+        <v>2081</v>
       </c>
       <c r="I152" t="s">
-        <v>2306</v>
+        <v>2082</v>
       </c>
       <c r="J152" t="s">
-        <v>2307</v>
+        <v>2083</v>
       </c>
       <c r="K152" t="s">
-        <v>2302</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B153">
         <v>86</v>
       </c>
       <c r="C153" t="s">
-        <v>2377</v>
+        <v>2258</v>
       </c>
       <c r="D153" t="s">
-        <v>1338</v>
+        <v>2300</v>
       </c>
       <c r="E153" t="s">
-        <v>2378</v>
+        <v>2301</v>
       </c>
       <c r="F153" t="s">
-        <v>16</v>
+        <v>1644</v>
       </c>
       <c r="G153" t="s">
-        <v>2380</v>
+        <v>2303</v>
       </c>
       <c r="H153" t="s">
-        <v>2382</v>
+        <v>2305</v>
       </c>
       <c r="I153" t="s">
-        <v>2383</v>
+        <v>2306</v>
       </c>
       <c r="J153" t="s">
-        <v>2384</v>
+        <v>2307</v>
       </c>
       <c r="K153" t="s">
-        <v>2379</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B154">
         <v>86</v>
@@ -33211,68 +33338,68 @@
         <v>2377</v>
       </c>
       <c r="D154" t="s">
-        <v>2385</v>
+        <v>1338</v>
       </c>
       <c r="E154" t="s">
-        <v>1083</v>
+        <v>2378</v>
       </c>
       <c r="F154" t="s">
-        <v>2235</v>
+        <v>16</v>
       </c>
       <c r="G154" t="s">
-        <v>2387</v>
+        <v>2380</v>
       </c>
       <c r="H154" t="s">
-        <v>2389</v>
+        <v>2382</v>
       </c>
       <c r="I154" t="s">
-        <v>2390</v>
+        <v>2383</v>
       </c>
       <c r="J154" t="s">
-        <v>2391</v>
+        <v>2384</v>
       </c>
       <c r="K154" t="s">
-        <v>2386</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B155">
         <v>86</v>
       </c>
       <c r="C155" t="s">
-        <v>2437</v>
+        <v>2377</v>
       </c>
       <c r="D155" t="s">
-        <v>2126</v>
+        <v>2385</v>
       </c>
       <c r="E155" t="s">
-        <v>2550</v>
+        <v>1083</v>
       </c>
       <c r="F155" t="s">
-        <v>2538</v>
+        <v>2235</v>
       </c>
       <c r="G155" t="s">
-        <v>2552</v>
+        <v>2387</v>
       </c>
       <c r="H155" t="s">
-        <v>2554</v>
+        <v>2389</v>
       </c>
       <c r="I155" t="s">
-        <v>2555</v>
+        <v>2390</v>
       </c>
       <c r="J155" t="s">
-        <v>2556</v>
+        <v>2391</v>
       </c>
       <c r="K155" t="s">
-        <v>2551</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B156">
         <v>86</v>
@@ -33281,68 +33408,68 @@
         <v>2437</v>
       </c>
       <c r="D156" t="s">
-        <v>2600</v>
+        <v>2126</v>
       </c>
       <c r="E156" t="s">
-        <v>110</v>
+        <v>2550</v>
       </c>
       <c r="F156" t="s">
-        <v>2461</v>
+        <v>2538</v>
       </c>
       <c r="G156" t="s">
-        <v>2602</v>
+        <v>2552</v>
       </c>
       <c r="H156" t="s">
-        <v>2604</v>
+        <v>2554</v>
       </c>
       <c r="I156" t="s">
-        <v>2605</v>
+        <v>2555</v>
       </c>
       <c r="J156" t="s">
-        <v>2606</v>
+        <v>2556</v>
       </c>
       <c r="K156" t="s">
-        <v>2601</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B157">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C157" t="s">
-        <v>12</v>
+        <v>2437</v>
       </c>
       <c r="D157" t="s">
-        <v>55</v>
+        <v>2600</v>
       </c>
       <c r="E157" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="F157" t="s">
-        <v>16</v>
+        <v>2461</v>
       </c>
       <c r="G157" t="s">
-        <v>58</v>
+        <v>2602</v>
       </c>
       <c r="H157" t="s">
-        <v>60</v>
+        <v>2604</v>
       </c>
       <c r="I157" t="s">
-        <v>61</v>
+        <v>2605</v>
       </c>
       <c r="J157" t="s">
-        <v>62</v>
+        <v>2606</v>
       </c>
       <c r="K157" t="s">
-        <v>57</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B158">
         <v>85</v>
@@ -33351,173 +33478,173 @@
         <v>12</v>
       </c>
       <c r="D158" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="E158" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F158" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G158" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H158" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="I158" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="J158" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="K158" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B159">
         <v>85</v>
       </c>
       <c r="C159" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D159" t="s">
-        <v>300</v>
+        <v>128</v>
       </c>
       <c r="E159" t="s">
-        <v>308</v>
+        <v>89</v>
       </c>
       <c r="F159" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G159" t="s">
-        <v>310</v>
+        <v>131</v>
       </c>
       <c r="H159" t="s">
-        <v>312</v>
+        <v>133</v>
       </c>
       <c r="I159" t="s">
-        <v>313</v>
+        <v>134</v>
       </c>
       <c r="J159" t="s">
-        <v>314</v>
+        <v>135</v>
       </c>
       <c r="K159" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B160">
         <v>85</v>
       </c>
       <c r="C160" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D160" t="s">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="E160" t="s">
-        <v>403</v>
+        <v>308</v>
       </c>
       <c r="F160" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G160" t="s">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="H160" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="I160" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="J160" t="s">
-        <v>409</v>
+        <v>314</v>
       </c>
       <c r="K160" t="s">
-        <v>404</v>
+        <v>309</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B161">
         <v>85</v>
       </c>
       <c r="C161" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D161" t="s">
-        <v>474</v>
+        <v>55</v>
       </c>
       <c r="E161" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="F161" t="s">
-        <v>477</v>
+        <v>16</v>
       </c>
       <c r="G161" t="s">
-        <v>478</v>
+        <v>405</v>
       </c>
       <c r="H161" t="s">
-        <v>480</v>
+        <v>407</v>
       </c>
       <c r="I161" t="s">
-        <v>481</v>
+        <v>408</v>
       </c>
       <c r="J161" t="s">
-        <v>482</v>
+        <v>409</v>
       </c>
       <c r="K161" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B162">
         <v>85</v>
       </c>
       <c r="C162" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D162" t="s">
-        <v>774</v>
+        <v>474</v>
       </c>
       <c r="E162" t="s">
-        <v>783</v>
+        <v>475</v>
       </c>
       <c r="F162" t="s">
-        <v>785</v>
+        <v>477</v>
       </c>
       <c r="G162" t="s">
-        <v>786</v>
+        <v>478</v>
       </c>
       <c r="H162" t="s">
-        <v>788</v>
+        <v>480</v>
       </c>
       <c r="I162" t="s">
-        <v>789</v>
+        <v>481</v>
       </c>
       <c r="J162" t="s">
-        <v>790</v>
+        <v>482</v>
       </c>
       <c r="K162" t="s">
-        <v>784</v>
+        <v>476</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B163">
         <v>85</v>
@@ -33526,33 +33653,33 @@
         <v>773</v>
       </c>
       <c r="D163" t="s">
-        <v>799</v>
+        <v>774</v>
       </c>
       <c r="E163" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="F163" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="G163" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="H163" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="I163" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="J163" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="K163" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B164">
         <v>85</v>
@@ -33561,68 +33688,68 @@
         <v>773</v>
       </c>
       <c r="D164" t="s">
-        <v>821</v>
+        <v>799</v>
       </c>
       <c r="E164" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="F164" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="G164" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
       <c r="H164" t="s">
-        <v>826</v>
+        <v>804</v>
       </c>
       <c r="I164" t="s">
-        <v>827</v>
+        <v>805</v>
       </c>
       <c r="J164" t="s">
-        <v>828</v>
+        <v>806</v>
       </c>
       <c r="K164" t="s">
-        <v>823</v>
+        <v>801</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B165">
         <v>85</v>
       </c>
       <c r="C165" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D165" t="s">
-        <v>989</v>
+        <v>821</v>
       </c>
       <c r="E165" t="s">
-        <v>990</v>
+        <v>822</v>
       </c>
       <c r="F165" t="s">
-        <v>75</v>
+        <v>777</v>
       </c>
       <c r="G165" t="s">
-        <v>959</v>
+        <v>824</v>
       </c>
       <c r="H165" t="s">
-        <v>993</v>
+        <v>826</v>
       </c>
       <c r="I165" t="s">
-        <v>994</v>
+        <v>827</v>
       </c>
       <c r="J165" t="s">
-        <v>995</v>
+        <v>828</v>
       </c>
       <c r="K165" t="s">
-        <v>991</v>
+        <v>823</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B166">
         <v>85</v>
@@ -33631,208 +33758,208 @@
         <v>934</v>
       </c>
       <c r="D166" t="s">
-        <v>1065</v>
+        <v>989</v>
       </c>
       <c r="E166" t="s">
-        <v>1066</v>
+        <v>990</v>
       </c>
       <c r="F166" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="G166" t="s">
-        <v>1068</v>
+        <v>959</v>
       </c>
       <c r="H166" t="s">
-        <v>1070</v>
+        <v>993</v>
       </c>
       <c r="I166" t="s">
-        <v>1071</v>
+        <v>994</v>
       </c>
       <c r="J166" t="s">
-        <v>1072</v>
+        <v>995</v>
       </c>
       <c r="K166" t="s">
-        <v>1067</v>
+        <v>991</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B167">
         <v>85</v>
       </c>
       <c r="C167" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D167" t="s">
-        <v>1242</v>
+        <v>1065</v>
       </c>
       <c r="E167" t="s">
-        <v>610</v>
+        <v>1066</v>
       </c>
       <c r="F167" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G167" t="s">
-        <v>604</v>
+        <v>1068</v>
       </c>
       <c r="H167" t="s">
-        <v>312</v>
+        <v>1070</v>
       </c>
       <c r="I167" t="s">
-        <v>1245</v>
+        <v>1071</v>
       </c>
       <c r="J167" t="s">
-        <v>1246</v>
+        <v>1072</v>
       </c>
       <c r="K167" t="s">
-        <v>1243</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B168">
         <v>85</v>
       </c>
       <c r="C168" t="s">
-        <v>1300</v>
+        <v>1227</v>
       </c>
       <c r="D168" t="s">
-        <v>1345</v>
+        <v>1242</v>
       </c>
       <c r="E168" t="s">
-        <v>1346</v>
+        <v>610</v>
       </c>
       <c r="F168" t="s">
         <v>16</v>
       </c>
       <c r="G168" t="s">
-        <v>1348</v>
+        <v>604</v>
       </c>
       <c r="H168" t="s">
         <v>312</v>
       </c>
       <c r="I168" t="s">
-        <v>1350</v>
+        <v>1245</v>
       </c>
       <c r="J168" t="s">
-        <v>1351</v>
+        <v>1246</v>
       </c>
       <c r="K168" t="s">
-        <v>1347</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B169">
         <v>85</v>
       </c>
       <c r="C169" t="s">
-        <v>1394</v>
+        <v>1300</v>
       </c>
       <c r="D169" t="s">
-        <v>1459</v>
+        <v>1345</v>
       </c>
       <c r="E169" t="s">
-        <v>1460</v>
+        <v>1346</v>
       </c>
       <c r="F169" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G169" t="s">
-        <v>1462</v>
+        <v>1348</v>
       </c>
       <c r="H169" t="s">
-        <v>1464</v>
+        <v>312</v>
       </c>
       <c r="I169" t="s">
-        <v>1465</v>
+        <v>1350</v>
       </c>
       <c r="J169" t="s">
-        <v>1466</v>
+        <v>1351</v>
       </c>
       <c r="K169" t="s">
-        <v>1461</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B170">
         <v>85</v>
       </c>
       <c r="C170" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D170" t="s">
-        <v>1535</v>
+        <v>1459</v>
       </c>
       <c r="E170" t="s">
-        <v>1543</v>
+        <v>1460</v>
       </c>
       <c r="F170" t="s">
-        <v>318</v>
+        <v>66</v>
       </c>
       <c r="G170" t="s">
-        <v>1538</v>
+        <v>1462</v>
       </c>
       <c r="H170" t="s">
-        <v>1546</v>
+        <v>1464</v>
       </c>
       <c r="I170" t="s">
-        <v>1547</v>
+        <v>1465</v>
       </c>
       <c r="J170" t="s">
-        <v>1548</v>
+        <v>1466</v>
       </c>
       <c r="K170" t="s">
-        <v>1544</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B171">
         <v>85</v>
       </c>
       <c r="C171" t="s">
-        <v>1625</v>
+        <v>1534</v>
       </c>
       <c r="D171" t="s">
-        <v>1626</v>
+        <v>1535</v>
       </c>
       <c r="E171" t="s">
-        <v>1627</v>
+        <v>1543</v>
       </c>
       <c r="F171" t="s">
-        <v>1629</v>
+        <v>318</v>
       </c>
       <c r="G171" t="s">
-        <v>1630</v>
+        <v>1538</v>
       </c>
       <c r="H171" t="s">
-        <v>1632</v>
+        <v>1546</v>
       </c>
       <c r="I171" t="s">
-        <v>1633</v>
+        <v>1547</v>
       </c>
       <c r="J171" t="s">
-        <v>1634</v>
+        <v>1548</v>
       </c>
       <c r="K171" t="s">
-        <v>1628</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B172">
         <v>85</v>
@@ -33841,68 +33968,68 @@
         <v>1625</v>
       </c>
       <c r="D172" t="s">
-        <v>1635</v>
+        <v>1626</v>
       </c>
       <c r="E172" t="s">
-        <v>110</v>
+        <v>1627</v>
       </c>
       <c r="F172" t="s">
-        <v>16</v>
+        <v>1629</v>
       </c>
       <c r="G172" t="s">
-        <v>1637</v>
+        <v>1630</v>
       </c>
       <c r="H172" t="s">
-        <v>1639</v>
+        <v>1632</v>
       </c>
       <c r="I172" t="s">
-        <v>1640</v>
+        <v>1633</v>
       </c>
       <c r="J172" t="s">
-        <v>1641</v>
+        <v>1634</v>
       </c>
       <c r="K172" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B173">
         <v>85</v>
       </c>
       <c r="C173" t="s">
-        <v>1727</v>
+        <v>1625</v>
       </c>
       <c r="D173" t="s">
-        <v>1795</v>
+        <v>1635</v>
       </c>
       <c r="E173" t="s">
-        <v>1796</v>
+        <v>110</v>
       </c>
       <c r="F173" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G173" t="s">
-        <v>1798</v>
+        <v>1637</v>
       </c>
       <c r="H173" t="s">
-        <v>1800</v>
+        <v>1639</v>
       </c>
       <c r="I173" t="s">
-        <v>1801</v>
+        <v>1640</v>
       </c>
       <c r="J173" t="s">
-        <v>1802</v>
+        <v>1641</v>
       </c>
       <c r="K173" t="s">
-        <v>1797</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B174">
         <v>85</v>
@@ -33911,33 +34038,33 @@
         <v>1727</v>
       </c>
       <c r="D174" t="s">
-        <v>1201</v>
+        <v>1795</v>
       </c>
       <c r="E174" t="s">
-        <v>1845</v>
+        <v>1796</v>
       </c>
       <c r="F174" t="s">
-        <v>1847</v>
+        <v>25</v>
       </c>
       <c r="G174" t="s">
-        <v>1848</v>
+        <v>1798</v>
       </c>
       <c r="H174" t="s">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="I174" t="s">
-        <v>79</v>
+        <v>1801</v>
       </c>
       <c r="J174" t="s">
-        <v>79</v>
+        <v>1802</v>
       </c>
       <c r="K174" t="s">
-        <v>1846</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B175">
         <v>85</v>
@@ -33946,19 +34073,19 @@
         <v>1727</v>
       </c>
       <c r="D175" t="s">
-        <v>1873</v>
+        <v>1201</v>
       </c>
       <c r="E175" t="s">
-        <v>1874</v>
+        <v>1845</v>
       </c>
       <c r="F175" t="s">
-        <v>1876</v>
+        <v>1847</v>
       </c>
       <c r="G175" t="s">
-        <v>1754</v>
+        <v>1848</v>
       </c>
       <c r="H175" t="s">
-        <v>1878</v>
+        <v>1850</v>
       </c>
       <c r="I175" t="s">
         <v>79</v>
@@ -33967,47 +34094,47 @@
         <v>79</v>
       </c>
       <c r="K175" t="s">
-        <v>1875</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B176">
         <v>85</v>
       </c>
       <c r="C176" t="s">
-        <v>1994</v>
+        <v>1727</v>
       </c>
       <c r="D176" t="s">
-        <v>2039</v>
+        <v>1873</v>
       </c>
       <c r="E176" t="s">
-        <v>2040</v>
+        <v>1874</v>
       </c>
       <c r="F176" t="s">
-        <v>2042</v>
+        <v>1876</v>
       </c>
       <c r="G176" t="s">
-        <v>2043</v>
+        <v>1754</v>
       </c>
       <c r="H176" t="s">
-        <v>2045</v>
+        <v>1878</v>
       </c>
       <c r="I176" t="s">
-        <v>2046</v>
+        <v>79</v>
       </c>
       <c r="J176" t="s">
-        <v>2047</v>
+        <v>79</v>
       </c>
       <c r="K176" t="s">
-        <v>2041</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B177">
         <v>85</v>
@@ -34016,243 +34143,243 @@
         <v>1994</v>
       </c>
       <c r="D177" t="s">
-        <v>2090</v>
+        <v>2039</v>
       </c>
       <c r="E177" t="s">
-        <v>2091</v>
+        <v>2040</v>
       </c>
       <c r="F177" t="s">
-        <v>25</v>
+        <v>2042</v>
       </c>
       <c r="G177" t="s">
-        <v>2093</v>
+        <v>2043</v>
       </c>
       <c r="H177" t="s">
-        <v>2095</v>
+        <v>2045</v>
       </c>
       <c r="I177" t="s">
-        <v>2096</v>
+        <v>2046</v>
       </c>
       <c r="J177" t="s">
-        <v>2097</v>
+        <v>2047</v>
       </c>
       <c r="K177" t="s">
-        <v>2092</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B178">
         <v>85</v>
       </c>
       <c r="C178" t="s">
-        <v>2437</v>
+        <v>1994</v>
       </c>
       <c r="D178" t="s">
-        <v>2659</v>
+        <v>2090</v>
       </c>
       <c r="E178" t="s">
-        <v>2660</v>
+        <v>2091</v>
       </c>
       <c r="F178" t="s">
-        <v>2638</v>
+        <v>25</v>
       </c>
       <c r="G178" t="s">
-        <v>2662</v>
+        <v>2093</v>
       </c>
       <c r="H178" t="s">
-        <v>2664</v>
+        <v>2095</v>
       </c>
       <c r="I178" t="s">
-        <v>2665</v>
+        <v>2096</v>
       </c>
       <c r="J178" t="s">
-        <v>2666</v>
+        <v>2097</v>
       </c>
       <c r="K178" t="s">
-        <v>2661</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B179">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C179" t="s">
-        <v>12</v>
+        <v>2437</v>
       </c>
       <c r="D179" t="s">
-        <v>144</v>
+        <v>2659</v>
       </c>
       <c r="E179" t="s">
-        <v>145</v>
+        <v>2660</v>
       </c>
       <c r="F179" t="s">
-        <v>147</v>
+        <v>2638</v>
       </c>
       <c r="G179" t="s">
-        <v>148</v>
+        <v>2662</v>
       </c>
       <c r="H179" t="s">
-        <v>150</v>
+        <v>2664</v>
       </c>
       <c r="I179" t="s">
-        <v>151</v>
+        <v>2665</v>
       </c>
       <c r="J179" t="s">
-        <v>152</v>
+        <v>2666</v>
       </c>
       <c r="K179" t="s">
-        <v>146</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B180">
         <v>84</v>
       </c>
       <c r="C180" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D180" t="s">
         <v>144</v>
       </c>
       <c r="E180" t="s">
-        <v>394</v>
+        <v>145</v>
       </c>
       <c r="F180" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G180" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
       <c r="H180" t="s">
-        <v>399</v>
+        <v>150</v>
       </c>
       <c r="I180" t="s">
-        <v>400</v>
+        <v>151</v>
       </c>
       <c r="J180" t="s">
-        <v>401</v>
+        <v>152</v>
       </c>
       <c r="K180" t="s">
-        <v>395</v>
+        <v>146</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B181">
         <v>84</v>
       </c>
       <c r="C181" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D181" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E181" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="F181" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="G181" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="H181" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="I181" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="J181" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="K181" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B182">
         <v>84</v>
       </c>
       <c r="C182" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D182" t="s">
-        <v>483</v>
+        <v>410</v>
       </c>
       <c r="E182" t="s">
-        <v>122</v>
+        <v>411</v>
       </c>
       <c r="F182" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="G182" t="s">
-        <v>486</v>
+        <v>413</v>
       </c>
       <c r="H182" t="s">
-        <v>488</v>
+        <v>415</v>
       </c>
       <c r="I182" t="s">
-        <v>489</v>
+        <v>416</v>
       </c>
       <c r="J182" t="s">
-        <v>490</v>
+        <v>417</v>
       </c>
       <c r="K182" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B183">
         <v>84</v>
       </c>
       <c r="C183" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D183" t="s">
-        <v>714</v>
+        <v>483</v>
       </c>
       <c r="E183" t="s">
-        <v>715</v>
+        <v>122</v>
       </c>
       <c r="F183" t="s">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="G183" t="s">
-        <v>604</v>
+        <v>486</v>
       </c>
       <c r="H183" t="s">
-        <v>718</v>
+        <v>488</v>
       </c>
       <c r="I183" t="s">
-        <v>719</v>
+        <v>489</v>
       </c>
       <c r="J183" t="s">
-        <v>720</v>
+        <v>490</v>
       </c>
       <c r="K183" t="s">
-        <v>716</v>
+        <v>484</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B184">
         <v>84</v>
@@ -34261,33 +34388,33 @@
         <v>697</v>
       </c>
       <c r="D184" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E184" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="F184" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G184" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="H184" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="I184" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="J184" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="K184" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B185">
         <v>84</v>
@@ -34296,138 +34423,138 @@
         <v>697</v>
       </c>
       <c r="D185" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="E185" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="F185" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="G185" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="H185" t="s">
         <v>726</v>
       </c>
       <c r="I185" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="J185" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="K185" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B186">
         <v>84</v>
       </c>
       <c r="C186" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D186" t="s">
-        <v>791</v>
+        <v>729</v>
       </c>
       <c r="E186" t="s">
-        <v>610</v>
+        <v>730</v>
       </c>
       <c r="F186" t="s">
-        <v>793</v>
+        <v>535</v>
       </c>
       <c r="G186" t="s">
-        <v>794</v>
+        <v>732</v>
       </c>
       <c r="H186" t="s">
-        <v>796</v>
+        <v>726</v>
       </c>
       <c r="I186" t="s">
-        <v>797</v>
+        <v>734</v>
       </c>
       <c r="J186" t="s">
-        <v>798</v>
+        <v>735</v>
       </c>
       <c r="K186" t="s">
-        <v>792</v>
+        <v>731</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B187">
         <v>84</v>
       </c>
       <c r="C187" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D187" t="s">
-        <v>896</v>
+        <v>791</v>
       </c>
       <c r="E187" t="s">
-        <v>897</v>
+        <v>610</v>
       </c>
       <c r="F187" t="s">
-        <v>25</v>
+        <v>793</v>
       </c>
       <c r="G187" t="s">
-        <v>899</v>
+        <v>794</v>
       </c>
       <c r="H187" t="s">
-        <v>901</v>
+        <v>796</v>
       </c>
       <c r="I187" t="s">
-        <v>902</v>
+        <v>797</v>
       </c>
       <c r="J187" t="s">
-        <v>903</v>
+        <v>798</v>
       </c>
       <c r="K187" t="s">
-        <v>898</v>
+        <v>792</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B188">
         <v>84</v>
       </c>
       <c r="C188" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D188" t="s">
-        <v>964</v>
+        <v>896</v>
       </c>
       <c r="E188" t="s">
-        <v>965</v>
+        <v>897</v>
       </c>
       <c r="F188" t="s">
-        <v>967</v>
+        <v>25</v>
       </c>
       <c r="G188" t="s">
-        <v>968</v>
+        <v>899</v>
       </c>
       <c r="H188" t="s">
-        <v>970</v>
+        <v>901</v>
       </c>
       <c r="I188" t="s">
-        <v>971</v>
+        <v>902</v>
       </c>
       <c r="J188" t="s">
-        <v>972</v>
+        <v>903</v>
       </c>
       <c r="K188" t="s">
-        <v>966</v>
+        <v>898</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B189">
         <v>84</v>
@@ -34436,33 +34563,33 @@
         <v>934</v>
       </c>
       <c r="D189" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="E189" t="s">
-        <v>1002</v>
+        <v>965</v>
       </c>
       <c r="F189" t="s">
-        <v>1004</v>
+        <v>967</v>
       </c>
       <c r="G189" t="s">
-        <v>438</v>
+        <v>968</v>
       </c>
       <c r="H189" t="s">
-        <v>1006</v>
+        <v>970</v>
       </c>
       <c r="I189" t="s">
-        <v>1007</v>
+        <v>971</v>
       </c>
       <c r="J189" t="s">
-        <v>1008</v>
+        <v>972</v>
       </c>
       <c r="K189" t="s">
-        <v>1003</v>
+        <v>966</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B190">
         <v>84</v>
@@ -34471,33 +34598,33 @@
         <v>934</v>
       </c>
       <c r="D190" t="s">
-        <v>213</v>
+        <v>950</v>
       </c>
       <c r="E190" t="s">
-        <v>1032</v>
+        <v>1002</v>
       </c>
       <c r="F190" t="s">
-        <v>106</v>
+        <v>1004</v>
       </c>
       <c r="G190" t="s">
-        <v>1034</v>
+        <v>438</v>
       </c>
       <c r="H190" t="s">
-        <v>1036</v>
+        <v>1006</v>
       </c>
       <c r="I190" t="s">
-        <v>1037</v>
+        <v>1007</v>
       </c>
       <c r="J190" t="s">
-        <v>1038</v>
+        <v>1008</v>
       </c>
       <c r="K190" t="s">
-        <v>1033</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B191">
         <v>84</v>
@@ -34506,173 +34633,173 @@
         <v>934</v>
       </c>
       <c r="D191" t="s">
-        <v>1057</v>
+        <v>213</v>
       </c>
       <c r="E191" t="s">
-        <v>1058</v>
+        <v>1032</v>
       </c>
       <c r="F191" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G191" t="s">
-        <v>1060</v>
+        <v>1034</v>
       </c>
       <c r="H191" t="s">
-        <v>1062</v>
+        <v>1036</v>
       </c>
       <c r="I191" t="s">
-        <v>1063</v>
+        <v>1037</v>
       </c>
       <c r="J191" t="s">
-        <v>1064</v>
+        <v>1038</v>
       </c>
       <c r="K191" t="s">
-        <v>1059</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B192">
         <v>84</v>
       </c>
       <c r="C192" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D192" t="s">
-        <v>271</v>
+        <v>1057</v>
       </c>
       <c r="E192" t="s">
-        <v>1104</v>
+        <v>1058</v>
       </c>
       <c r="F192" t="s">
-        <v>1106</v>
+        <v>16</v>
       </c>
       <c r="G192" t="s">
-        <v>1107</v>
+        <v>1060</v>
       </c>
       <c r="H192" t="s">
-        <v>1109</v>
+        <v>1062</v>
       </c>
       <c r="I192" t="s">
-        <v>1110</v>
+        <v>1063</v>
       </c>
       <c r="J192" t="s">
-        <v>1111</v>
+        <v>1064</v>
       </c>
       <c r="K192" t="s">
-        <v>1105</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B193">
         <v>84</v>
       </c>
       <c r="C193" t="s">
-        <v>1271</v>
+        <v>1087</v>
       </c>
       <c r="D193" t="s">
-        <v>950</v>
+        <v>271</v>
       </c>
       <c r="E193" t="s">
-        <v>463</v>
+        <v>1104</v>
       </c>
       <c r="F193" t="s">
-        <v>66</v>
+        <v>1106</v>
       </c>
       <c r="G193" t="s">
-        <v>438</v>
+        <v>1107</v>
       </c>
       <c r="H193" t="s">
-        <v>1274</v>
+        <v>1109</v>
       </c>
       <c r="I193" t="s">
-        <v>1275</v>
+        <v>1110</v>
       </c>
       <c r="J193" t="s">
-        <v>1276</v>
+        <v>1111</v>
       </c>
       <c r="K193" t="s">
-        <v>1272</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B194">
         <v>84</v>
       </c>
       <c r="C194" t="s">
-        <v>1300</v>
+        <v>1271</v>
       </c>
       <c r="D194" t="s">
-        <v>1338</v>
+        <v>950</v>
       </c>
       <c r="E194" t="s">
-        <v>122</v>
+        <v>463</v>
       </c>
       <c r="F194" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G194" t="s">
-        <v>1340</v>
+        <v>438</v>
       </c>
       <c r="H194" t="s">
-        <v>1342</v>
+        <v>1274</v>
       </c>
       <c r="I194" t="s">
-        <v>1343</v>
+        <v>1275</v>
       </c>
       <c r="J194" t="s">
-        <v>1344</v>
+        <v>1276</v>
       </c>
       <c r="K194" t="s">
-        <v>1339</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B195">
         <v>84</v>
       </c>
       <c r="C195" t="s">
-        <v>1394</v>
+        <v>1300</v>
       </c>
       <c r="D195" t="s">
-        <v>1443</v>
+        <v>1338</v>
       </c>
       <c r="E195" t="s">
-        <v>1444</v>
+        <v>122</v>
       </c>
       <c r="F195" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G195" t="s">
-        <v>1446</v>
+        <v>1340</v>
       </c>
       <c r="H195" t="s">
-        <v>1448</v>
+        <v>1342</v>
       </c>
       <c r="I195" t="s">
-        <v>1449</v>
+        <v>1343</v>
       </c>
       <c r="J195" t="s">
-        <v>1450</v>
+        <v>1344</v>
       </c>
       <c r="K195" t="s">
-        <v>1445</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B196">
         <v>84</v>
@@ -34681,138 +34808,138 @@
         <v>1394</v>
       </c>
       <c r="D196" t="s">
-        <v>1475</v>
+        <v>1443</v>
       </c>
       <c r="E196" t="s">
-        <v>1476</v>
+        <v>1444</v>
       </c>
       <c r="F196" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G196" t="s">
-        <v>1478</v>
+        <v>1446</v>
       </c>
       <c r="H196" t="s">
-        <v>1480</v>
+        <v>1448</v>
       </c>
       <c r="I196" t="s">
-        <v>1481</v>
+        <v>1449</v>
       </c>
       <c r="J196" t="s">
-        <v>1482</v>
+        <v>1450</v>
       </c>
       <c r="K196" t="s">
-        <v>1477</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B197">
         <v>84</v>
       </c>
       <c r="C197" t="s">
-        <v>1625</v>
+        <v>1394</v>
       </c>
       <c r="D197" t="s">
-        <v>1635</v>
+        <v>1475</v>
       </c>
       <c r="E197" t="s">
-        <v>1642</v>
+        <v>1476</v>
       </c>
       <c r="F197" t="s">
-        <v>1644</v>
+        <v>25</v>
       </c>
       <c r="G197" t="s">
-        <v>1637</v>
+        <v>1478</v>
       </c>
       <c r="H197" t="s">
-        <v>1646</v>
+        <v>1480</v>
       </c>
       <c r="I197" t="s">
-        <v>1647</v>
+        <v>1481</v>
       </c>
       <c r="J197" t="s">
-        <v>1648</v>
+        <v>1482</v>
       </c>
       <c r="K197" t="s">
-        <v>1643</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B198">
         <v>84</v>
       </c>
       <c r="C198" t="s">
-        <v>1664</v>
+        <v>1625</v>
       </c>
       <c r="D198" t="s">
-        <v>1665</v>
+        <v>1635</v>
       </c>
       <c r="E198" t="s">
-        <v>1666</v>
+        <v>1642</v>
       </c>
       <c r="F198" t="s">
-        <v>747</v>
+        <v>1644</v>
       </c>
       <c r="G198" t="s">
-        <v>1668</v>
+        <v>1637</v>
       </c>
       <c r="H198" t="s">
-        <v>1670</v>
+        <v>1646</v>
       </c>
       <c r="I198" t="s">
-        <v>1671</v>
+        <v>1647</v>
       </c>
       <c r="J198" t="s">
-        <v>1672</v>
+        <v>1648</v>
       </c>
       <c r="K198" t="s">
-        <v>1667</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B199">
         <v>84</v>
       </c>
       <c r="C199" t="s">
-        <v>1727</v>
+        <v>1664</v>
       </c>
       <c r="D199" t="s">
-        <v>1744</v>
+        <v>1665</v>
       </c>
       <c r="E199" t="s">
-        <v>1536</v>
+        <v>1666</v>
       </c>
       <c r="F199" t="s">
-        <v>25</v>
+        <v>747</v>
       </c>
       <c r="G199" t="s">
-        <v>1746</v>
+        <v>1668</v>
       </c>
       <c r="H199" t="s">
-        <v>1748</v>
+        <v>1670</v>
       </c>
       <c r="I199" t="s">
-        <v>1749</v>
+        <v>1671</v>
       </c>
       <c r="J199" t="s">
-        <v>1750</v>
+        <v>1672</v>
       </c>
       <c r="K199" t="s">
-        <v>1745</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B200">
         <v>84</v>
@@ -34821,33 +34948,33 @@
         <v>1727</v>
       </c>
       <c r="D200" t="s">
-        <v>1751</v>
+        <v>1744</v>
       </c>
       <c r="E200" t="s">
-        <v>1752</v>
+        <v>1536</v>
       </c>
       <c r="F200" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="G200" t="s">
-        <v>1754</v>
+        <v>1746</v>
       </c>
       <c r="H200" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
       <c r="I200" t="s">
-        <v>1757</v>
+        <v>1749</v>
       </c>
       <c r="J200" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
       <c r="K200" t="s">
-        <v>1753</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B201">
         <v>84</v>
@@ -34856,68 +34983,68 @@
         <v>1727</v>
       </c>
       <c r="D201" t="s">
-        <v>1879</v>
+        <v>1751</v>
       </c>
       <c r="E201" t="s">
-        <v>1880</v>
+        <v>1752</v>
       </c>
       <c r="F201" t="s">
-        <v>25</v>
+        <v>535</v>
       </c>
       <c r="G201" t="s">
-        <v>1770</v>
+        <v>1754</v>
       </c>
       <c r="H201" t="s">
-        <v>1883</v>
+        <v>1756</v>
       </c>
       <c r="I201" t="s">
-        <v>79</v>
+        <v>1757</v>
       </c>
       <c r="J201" t="s">
-        <v>79</v>
+        <v>1758</v>
       </c>
       <c r="K201" t="s">
-        <v>1881</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B202">
         <v>84</v>
       </c>
       <c r="C202" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D202" t="s">
-        <v>1899</v>
+        <v>1879</v>
       </c>
       <c r="E202" t="s">
-        <v>1900</v>
+        <v>1880</v>
       </c>
       <c r="F202" t="s">
-        <v>747</v>
+        <v>25</v>
       </c>
       <c r="G202" t="s">
-        <v>1902</v>
+        <v>1770</v>
       </c>
       <c r="H202" t="s">
-        <v>1904</v>
+        <v>1883</v>
       </c>
       <c r="I202" t="s">
-        <v>1905</v>
+        <v>79</v>
       </c>
       <c r="J202" t="s">
-        <v>1906</v>
+        <v>79</v>
       </c>
       <c r="K202" t="s">
-        <v>1901</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B203">
         <v>84</v>
@@ -34926,68 +35053,68 @@
         <v>1884</v>
       </c>
       <c r="D203" t="s">
-        <v>1955</v>
+        <v>1899</v>
       </c>
       <c r="E203" t="s">
-        <v>1956</v>
+        <v>1900</v>
       </c>
       <c r="F203" t="s">
-        <v>1958</v>
+        <v>747</v>
       </c>
       <c r="G203" t="s">
-        <v>959</v>
+        <v>1902</v>
       </c>
       <c r="H203" t="s">
-        <v>1960</v>
+        <v>1904</v>
       </c>
       <c r="I203" t="s">
-        <v>1961</v>
+        <v>1905</v>
       </c>
       <c r="J203" t="s">
-        <v>1962</v>
+        <v>1906</v>
       </c>
       <c r="K203" t="s">
-        <v>1957</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B204">
         <v>84</v>
       </c>
       <c r="C204" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D204" t="s">
-        <v>2176</v>
+        <v>1955</v>
       </c>
       <c r="E204" t="s">
-        <v>2177</v>
+        <v>1956</v>
       </c>
       <c r="F204" t="s">
-        <v>16</v>
+        <v>1958</v>
       </c>
       <c r="G204" t="s">
-        <v>2179</v>
+        <v>959</v>
       </c>
       <c r="H204" t="s">
-        <v>2181</v>
+        <v>1960</v>
       </c>
       <c r="I204" t="s">
-        <v>2182</v>
+        <v>1961</v>
       </c>
       <c r="J204" t="s">
-        <v>2183</v>
+        <v>1962</v>
       </c>
       <c r="K204" t="s">
-        <v>2178</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B205">
         <v>84</v>
@@ -34996,138 +35123,138 @@
         <v>2098</v>
       </c>
       <c r="D205" t="s">
-        <v>2211</v>
+        <v>2176</v>
       </c>
       <c r="E205" t="s">
-        <v>2212</v>
+        <v>2177</v>
       </c>
       <c r="F205" t="s">
         <v>16</v>
       </c>
       <c r="G205" t="s">
-        <v>2214</v>
+        <v>2179</v>
       </c>
       <c r="H205" t="s">
-        <v>2216</v>
+        <v>2181</v>
       </c>
       <c r="I205" t="s">
-        <v>2217</v>
+        <v>2182</v>
       </c>
       <c r="J205" t="s">
-        <v>2218</v>
+        <v>2183</v>
       </c>
       <c r="K205" t="s">
-        <v>2213</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B206">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C206" t="s">
-        <v>1200</v>
+        <v>2098</v>
       </c>
       <c r="D206" t="s">
-        <v>1201</v>
+        <v>2211</v>
       </c>
       <c r="E206" t="s">
-        <v>1202</v>
+        <v>2212</v>
       </c>
       <c r="F206" t="s">
-        <v>1204</v>
+        <v>16</v>
       </c>
       <c r="G206" t="s">
-        <v>1205</v>
+        <v>2214</v>
       </c>
       <c r="H206" t="s">
-        <v>1207</v>
+        <v>2216</v>
       </c>
       <c r="I206" t="s">
-        <v>1208</v>
+        <v>2217</v>
       </c>
       <c r="J206" t="s">
-        <v>1209</v>
+        <v>2218</v>
       </c>
       <c r="K206" t="s">
-        <v>1203</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B207">
         <v>83</v>
       </c>
       <c r="C207" t="s">
-        <v>284</v>
+        <v>1200</v>
       </c>
       <c r="D207" t="s">
-        <v>353</v>
+        <v>1201</v>
       </c>
       <c r="E207" t="s">
-        <v>362</v>
+        <v>1202</v>
       </c>
       <c r="F207" t="s">
-        <v>356</v>
+        <v>1204</v>
       </c>
       <c r="G207" t="s">
-        <v>364</v>
+        <v>1205</v>
       </c>
       <c r="H207" t="s">
-        <v>366</v>
+        <v>1207</v>
       </c>
       <c r="I207" t="s">
-        <v>367</v>
+        <v>1208</v>
       </c>
       <c r="J207" t="s">
-        <v>368</v>
+        <v>1209</v>
       </c>
       <c r="K207" t="s">
-        <v>363</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B208">
         <v>83</v>
       </c>
       <c r="C208" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D208" t="s">
-        <v>491</v>
+        <v>353</v>
       </c>
       <c r="E208" t="s">
-        <v>492</v>
+        <v>362</v>
       </c>
       <c r="F208" t="s">
-        <v>75</v>
+        <v>356</v>
       </c>
       <c r="G208" t="s">
-        <v>494</v>
+        <v>364</v>
       </c>
       <c r="H208" t="s">
-        <v>496</v>
+        <v>366</v>
       </c>
       <c r="I208" t="s">
-        <v>497</v>
+        <v>367</v>
       </c>
       <c r="J208" t="s">
-        <v>498</v>
+        <v>368</v>
       </c>
       <c r="K208" t="s">
-        <v>493</v>
+        <v>363</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B209">
         <v>83</v>
@@ -35136,173 +35263,173 @@
         <v>473</v>
       </c>
       <c r="D209" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="E209" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="F209" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="G209" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="H209" t="s">
-        <v>538</v>
+        <v>496</v>
       </c>
       <c r="I209" t="s">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="J209" t="s">
-        <v>540</v>
+        <v>498</v>
       </c>
       <c r="K209" t="s">
-        <v>534</v>
+        <v>493</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B210">
         <v>83</v>
       </c>
       <c r="C210" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D210" t="s">
-        <v>643</v>
+        <v>532</v>
       </c>
       <c r="E210" t="s">
-        <v>644</v>
+        <v>533</v>
       </c>
       <c r="F210" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="G210" t="s">
-        <v>618</v>
+        <v>536</v>
       </c>
       <c r="H210" t="s">
-        <v>647</v>
+        <v>538</v>
       </c>
       <c r="I210" t="s">
-        <v>648</v>
+        <v>539</v>
       </c>
       <c r="J210" t="s">
-        <v>649</v>
+        <v>540</v>
       </c>
       <c r="K210" t="s">
-        <v>645</v>
+        <v>534</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B211">
         <v>83</v>
       </c>
       <c r="C211" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="D211" t="s">
-        <v>736</v>
+        <v>643</v>
       </c>
       <c r="E211" t="s">
-        <v>737</v>
+        <v>644</v>
       </c>
       <c r="F211" t="s">
-        <v>739</v>
+        <v>16</v>
       </c>
       <c r="G211" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="H211" t="s">
-        <v>741</v>
+        <v>647</v>
       </c>
       <c r="I211" t="s">
-        <v>742</v>
+        <v>648</v>
       </c>
       <c r="J211" t="s">
-        <v>743</v>
+        <v>649</v>
       </c>
       <c r="K211" t="s">
-        <v>738</v>
+        <v>645</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B212">
         <v>83</v>
       </c>
       <c r="C212" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D212" t="s">
-        <v>807</v>
+        <v>736</v>
       </c>
       <c r="E212" t="s">
-        <v>808</v>
+        <v>737</v>
       </c>
       <c r="F212" t="s">
-        <v>810</v>
+        <v>739</v>
       </c>
       <c r="G212" t="s">
-        <v>811</v>
+        <v>604</v>
       </c>
       <c r="H212" t="s">
-        <v>813</v>
+        <v>741</v>
       </c>
       <c r="I212" t="s">
-        <v>814</v>
+        <v>742</v>
       </c>
       <c r="J212" t="s">
-        <v>815</v>
+        <v>743</v>
       </c>
       <c r="K212" t="s">
-        <v>809</v>
+        <v>738</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B213">
         <v>83</v>
       </c>
       <c r="C213" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D213" t="s">
-        <v>650</v>
+        <v>807</v>
       </c>
       <c r="E213" t="s">
-        <v>1016</v>
+        <v>808</v>
       </c>
       <c r="F213" t="s">
-        <v>66</v>
+        <v>810</v>
       </c>
       <c r="G213" t="s">
-        <v>1018</v>
+        <v>811</v>
       </c>
       <c r="H213" t="s">
-        <v>1020</v>
+        <v>813</v>
       </c>
       <c r="I213" t="s">
-        <v>1021</v>
+        <v>814</v>
       </c>
       <c r="J213" t="s">
-        <v>1022</v>
+        <v>815</v>
       </c>
       <c r="K213" t="s">
-        <v>1017</v>
+        <v>809</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B214">
         <v>83</v>
@@ -35311,103 +35438,103 @@
         <v>934</v>
       </c>
       <c r="D214" t="s">
-        <v>1048</v>
+        <v>650</v>
       </c>
       <c r="E214" t="s">
-        <v>1049</v>
+        <v>1016</v>
       </c>
       <c r="F214" t="s">
-        <v>1051</v>
+        <v>66</v>
       </c>
       <c r="G214" t="s">
-        <v>1052</v>
+        <v>1018</v>
       </c>
       <c r="H214" t="s">
-        <v>1054</v>
+        <v>1020</v>
       </c>
       <c r="I214" t="s">
-        <v>1055</v>
+        <v>1021</v>
       </c>
       <c r="J214" t="s">
-        <v>1056</v>
+        <v>1022</v>
       </c>
       <c r="K214" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B215">
         <v>83</v>
       </c>
       <c r="C215" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D215" t="s">
-        <v>1247</v>
+        <v>1048</v>
       </c>
       <c r="E215" t="s">
-        <v>1248</v>
+        <v>1049</v>
       </c>
       <c r="F215" t="s">
-        <v>66</v>
+        <v>1051</v>
       </c>
       <c r="G215" t="s">
-        <v>604</v>
+        <v>1052</v>
       </c>
       <c r="H215" t="s">
-        <v>1251</v>
+        <v>1054</v>
       </c>
       <c r="I215" t="s">
-        <v>1252</v>
+        <v>1055</v>
       </c>
       <c r="J215" t="s">
-        <v>1253</v>
+        <v>1056</v>
       </c>
       <c r="K215" t="s">
-        <v>1249</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B216">
         <v>83</v>
       </c>
       <c r="C216" t="s">
-        <v>1271</v>
+        <v>1227</v>
       </c>
       <c r="D216" t="s">
-        <v>219</v>
+        <v>1247</v>
       </c>
       <c r="E216" t="s">
-        <v>1285</v>
+        <v>1248</v>
       </c>
       <c r="F216" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="G216" t="s">
-        <v>1287</v>
+        <v>604</v>
       </c>
       <c r="H216" t="s">
-        <v>1289</v>
+        <v>1251</v>
       </c>
       <c r="I216" t="s">
-        <v>1290</v>
+        <v>1252</v>
       </c>
       <c r="J216" t="s">
-        <v>1291</v>
+        <v>1253</v>
       </c>
       <c r="K216" t="s">
-        <v>1286</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B217">
         <v>83</v>
@@ -35416,68 +35543,68 @@
         <v>1271</v>
       </c>
       <c r="D217" t="s">
-        <v>1292</v>
+        <v>219</v>
       </c>
       <c r="E217" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="F217" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="G217" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="H217" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
       <c r="I217" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
       <c r="J217" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
       <c r="K217" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B218">
         <v>83</v>
       </c>
       <c r="C218" t="s">
-        <v>1300</v>
+        <v>1271</v>
       </c>
       <c r="D218" t="s">
-        <v>1309</v>
+        <v>1292</v>
       </c>
       <c r="E218" t="s">
-        <v>830</v>
+        <v>1293</v>
       </c>
       <c r="F218" t="s">
-        <v>1311</v>
+        <v>66</v>
       </c>
       <c r="G218" t="s">
-        <v>1318</v>
+        <v>1295</v>
       </c>
       <c r="H218" t="s">
-        <v>1320</v>
+        <v>1297</v>
       </c>
       <c r="I218" t="s">
-        <v>1321</v>
+        <v>1298</v>
       </c>
       <c r="J218" t="s">
-        <v>1322</v>
+        <v>1299</v>
       </c>
       <c r="K218" t="s">
-        <v>1317</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B219">
         <v>83</v>
@@ -35486,68 +35613,68 @@
         <v>1300</v>
       </c>
       <c r="D219" t="s">
-        <v>1352</v>
+        <v>1309</v>
       </c>
       <c r="E219" t="s">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="F219" t="s">
-        <v>16</v>
+        <v>1311</v>
       </c>
       <c r="G219" t="s">
-        <v>1354</v>
+        <v>1318</v>
       </c>
       <c r="H219" t="s">
-        <v>1356</v>
+        <v>1320</v>
       </c>
       <c r="I219" t="s">
-        <v>1357</v>
+        <v>1321</v>
       </c>
       <c r="J219" t="s">
-        <v>1358</v>
+        <v>1322</v>
       </c>
       <c r="K219" t="s">
-        <v>1353</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B220">
         <v>83</v>
       </c>
       <c r="C220" t="s">
-        <v>1394</v>
+        <v>1300</v>
       </c>
       <c r="D220" t="s">
-        <v>491</v>
+        <v>1352</v>
       </c>
       <c r="E220" t="s">
-        <v>1404</v>
+        <v>110</v>
       </c>
       <c r="F220" t="s">
-        <v>1406</v>
+        <v>16</v>
       </c>
       <c r="G220" t="s">
-        <v>1407</v>
+        <v>1354</v>
       </c>
       <c r="H220" t="s">
-        <v>1409</v>
+        <v>1356</v>
       </c>
       <c r="I220" t="s">
-        <v>1410</v>
+        <v>1357</v>
       </c>
       <c r="J220" t="s">
-        <v>1411</v>
+        <v>1358</v>
       </c>
       <c r="K220" t="s">
-        <v>1405</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B221">
         <v>83</v>
@@ -35556,68 +35683,68 @@
         <v>1394</v>
       </c>
       <c r="D221" t="s">
-        <v>1451</v>
+        <v>491</v>
       </c>
       <c r="E221" t="s">
-        <v>1452</v>
+        <v>1404</v>
       </c>
       <c r="F221" t="s">
-        <v>1454</v>
+        <v>1406</v>
       </c>
       <c r="G221" t="s">
-        <v>802</v>
+        <v>1407</v>
       </c>
       <c r="H221" t="s">
-        <v>1456</v>
+        <v>1409</v>
       </c>
       <c r="I221" t="s">
-        <v>1457</v>
+        <v>1410</v>
       </c>
       <c r="J221" t="s">
-        <v>1458</v>
+        <v>1411</v>
       </c>
       <c r="K221" t="s">
-        <v>1453</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B222">
         <v>83</v>
       </c>
       <c r="C222" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D222" t="s">
-        <v>1579</v>
+        <v>1451</v>
       </c>
       <c r="E222" t="s">
-        <v>957</v>
+        <v>1452</v>
       </c>
       <c r="F222" t="s">
-        <v>75</v>
+        <v>1454</v>
       </c>
       <c r="G222" t="s">
-        <v>1581</v>
+        <v>802</v>
       </c>
       <c r="H222" t="s">
-        <v>1583</v>
+        <v>1456</v>
       </c>
       <c r="I222" t="s">
-        <v>1584</v>
+        <v>1457</v>
       </c>
       <c r="J222" t="s">
-        <v>1585</v>
+        <v>1458</v>
       </c>
       <c r="K222" t="s">
-        <v>1580</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B223">
         <v>83</v>
@@ -35626,33 +35753,33 @@
         <v>1534</v>
       </c>
       <c r="D223" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="E223" t="s">
-        <v>1587</v>
+        <v>957</v>
       </c>
       <c r="F223" t="s">
         <v>75</v>
       </c>
       <c r="G223" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="H223" t="s">
         <v>1583</v>
       </c>
       <c r="I223" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="J223" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="K223" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B224">
         <v>83</v>
@@ -35661,68 +35788,68 @@
         <v>1534</v>
       </c>
       <c r="D224" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="E224" t="s">
-        <v>610</v>
+        <v>1587</v>
       </c>
       <c r="F224" t="s">
-        <v>1595</v>
+        <v>75</v>
       </c>
       <c r="G224" t="s">
-        <v>1166</v>
+        <v>1589</v>
       </c>
       <c r="H224" t="s">
-        <v>1597</v>
+        <v>1583</v>
       </c>
       <c r="I224" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="J224" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="K224" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B225">
         <v>83</v>
       </c>
       <c r="C225" t="s">
-        <v>2098</v>
+        <v>1534</v>
       </c>
       <c r="D225" t="s">
-        <v>2099</v>
+        <v>1593</v>
       </c>
       <c r="E225" t="s">
-        <v>830</v>
+        <v>610</v>
       </c>
       <c r="F225" t="s">
-        <v>2101</v>
+        <v>1595</v>
       </c>
       <c r="G225" t="s">
-        <v>2102</v>
+        <v>1166</v>
       </c>
       <c r="H225" t="s">
-        <v>2104</v>
+        <v>1597</v>
       </c>
       <c r="I225" t="s">
-        <v>2105</v>
+        <v>1598</v>
       </c>
       <c r="J225" t="s">
-        <v>2106</v>
+        <v>1599</v>
       </c>
       <c r="K225" t="s">
-        <v>2100</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B226">
         <v>83</v>
@@ -35731,138 +35858,138 @@
         <v>2098</v>
       </c>
       <c r="D226" t="s">
-        <v>2162</v>
+        <v>2099</v>
       </c>
       <c r="E226" t="s">
-        <v>2163</v>
+        <v>830</v>
       </c>
       <c r="F226" t="s">
-        <v>16</v>
+        <v>2101</v>
       </c>
       <c r="G226" t="s">
-        <v>2165</v>
+        <v>2102</v>
       </c>
       <c r="H226" t="s">
-        <v>2167</v>
+        <v>2104</v>
       </c>
       <c r="I226" t="s">
-        <v>2168</v>
+        <v>2105</v>
       </c>
       <c r="J226" t="s">
-        <v>2169</v>
+        <v>2106</v>
       </c>
       <c r="K226" t="s">
-        <v>2164</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B227">
         <v>83</v>
       </c>
       <c r="C227" t="s">
-        <v>2258</v>
+        <v>2098</v>
       </c>
       <c r="D227" t="s">
-        <v>2308</v>
+        <v>2162</v>
       </c>
       <c r="E227" t="s">
-        <v>2309</v>
+        <v>2163</v>
       </c>
       <c r="F227" t="s">
-        <v>1950</v>
+        <v>16</v>
       </c>
       <c r="G227" t="s">
-        <v>2311</v>
+        <v>2165</v>
       </c>
       <c r="H227" t="s">
-        <v>2313</v>
+        <v>2167</v>
       </c>
       <c r="I227" t="s">
-        <v>2314</v>
+        <v>2168</v>
       </c>
       <c r="J227" t="s">
-        <v>2315</v>
+        <v>2169</v>
       </c>
       <c r="K227" t="s">
-        <v>2310</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B228">
         <v>83</v>
       </c>
       <c r="C228" t="s">
-        <v>2377</v>
+        <v>2258</v>
       </c>
       <c r="D228" t="s">
-        <v>2407</v>
+        <v>2308</v>
       </c>
       <c r="E228" t="s">
-        <v>2408</v>
+        <v>2309</v>
       </c>
       <c r="F228" t="s">
-        <v>75</v>
+        <v>1950</v>
       </c>
       <c r="G228" t="s">
-        <v>1034</v>
+        <v>2311</v>
       </c>
       <c r="H228" t="s">
-        <v>2411</v>
+        <v>2313</v>
       </c>
       <c r="I228" t="s">
-        <v>2412</v>
+        <v>2314</v>
       </c>
       <c r="J228" t="s">
-        <v>2413</v>
+        <v>2315</v>
       </c>
       <c r="K228" t="s">
-        <v>2409</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B229">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C229" t="s">
-        <v>159</v>
+        <v>2377</v>
       </c>
       <c r="D229" t="s">
-        <v>227</v>
+        <v>2407</v>
       </c>
       <c r="E229" t="s">
-        <v>228</v>
+        <v>2408</v>
       </c>
       <c r="F229" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="G229" t="s">
-        <v>231</v>
+        <v>1034</v>
       </c>
       <c r="H229" t="s">
-        <v>233</v>
+        <v>2411</v>
       </c>
       <c r="I229" t="s">
-        <v>234</v>
+        <v>2412</v>
       </c>
       <c r="J229" t="s">
-        <v>235</v>
+        <v>2413</v>
       </c>
       <c r="K229" t="s">
-        <v>229</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B230">
         <v>82</v>
@@ -35871,138 +35998,138 @@
         <v>159</v>
       </c>
       <c r="D230" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="E230" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="F230" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="G230" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c r="H230" t="s">
-        <v>270</v>
+        <v>233</v>
       </c>
       <c r="I230" t="s">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="J230" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="K230" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B231">
         <v>82</v>
       </c>
       <c r="C231" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D231" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="E231" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="F231" t="s">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="G231" t="s">
-        <v>342</v>
+        <v>58</v>
       </c>
       <c r="H231" t="s">
-        <v>344</v>
+        <v>270</v>
       </c>
       <c r="I231" t="s">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="J231" t="s">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="K231" t="s">
-        <v>340</v>
+        <v>268</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B232">
         <v>82</v>
       </c>
       <c r="C232" t="s">
-        <v>591</v>
+        <v>284</v>
       </c>
       <c r="D232" t="s">
-        <v>601</v>
+        <v>338</v>
       </c>
       <c r="E232" t="s">
-        <v>602</v>
+        <v>339</v>
       </c>
       <c r="F232" t="s">
-        <v>75</v>
+        <v>341</v>
       </c>
       <c r="G232" t="s">
-        <v>604</v>
+        <v>342</v>
       </c>
       <c r="H232" t="s">
-        <v>606</v>
+        <v>344</v>
       </c>
       <c r="I232" t="s">
-        <v>607</v>
+        <v>345</v>
       </c>
       <c r="J232" t="s">
-        <v>608</v>
+        <v>346</v>
       </c>
       <c r="K232" t="s">
-        <v>603</v>
+        <v>340</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B233">
         <v>82</v>
       </c>
       <c r="C233" t="s">
-        <v>934</v>
+        <v>591</v>
       </c>
       <c r="D233" t="s">
-        <v>13</v>
+        <v>601</v>
       </c>
       <c r="E233" t="s">
-        <v>1009</v>
+        <v>602</v>
       </c>
       <c r="F233" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G233" t="s">
-        <v>1011</v>
+        <v>604</v>
       </c>
       <c r="H233" t="s">
-        <v>1013</v>
+        <v>606</v>
       </c>
       <c r="I233" t="s">
-        <v>1014</v>
+        <v>607</v>
       </c>
       <c r="J233" t="s">
-        <v>1015</v>
+        <v>608</v>
       </c>
       <c r="K233" t="s">
-        <v>1010</v>
+        <v>603</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B234">
         <v>82</v>
@@ -36011,173 +36138,173 @@
         <v>934</v>
       </c>
       <c r="D234" t="s">
-        <v>1023</v>
+        <v>13</v>
       </c>
       <c r="E234" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="F234" t="s">
-        <v>1026</v>
+        <v>16</v>
       </c>
       <c r="G234" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="H234" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="I234" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="J234" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="K234" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B235">
         <v>82</v>
       </c>
       <c r="C235" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D235" t="s">
-        <v>1112</v>
+        <v>1023</v>
       </c>
       <c r="E235" t="s">
-        <v>1113</v>
+        <v>1024</v>
       </c>
       <c r="F235" t="s">
-        <v>25</v>
+        <v>1026</v>
       </c>
       <c r="G235" t="s">
-        <v>1115</v>
+        <v>1027</v>
       </c>
       <c r="H235" t="s">
-        <v>1117</v>
+        <v>1029</v>
       </c>
       <c r="I235" t="s">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="J235" t="s">
-        <v>1119</v>
+        <v>1031</v>
       </c>
       <c r="K235" t="s">
-        <v>1114</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B236">
         <v>82</v>
       </c>
       <c r="C236" t="s">
-        <v>1210</v>
+        <v>1087</v>
       </c>
       <c r="D236" t="s">
-        <v>1211</v>
+        <v>1112</v>
       </c>
       <c r="E236" t="s">
-        <v>89</v>
+        <v>1113</v>
       </c>
       <c r="F236" t="s">
-        <v>1213</v>
+        <v>25</v>
       </c>
       <c r="G236" t="s">
-        <v>1214</v>
+        <v>1115</v>
       </c>
       <c r="H236" t="s">
-        <v>1216</v>
+        <v>1117</v>
       </c>
       <c r="I236" t="s">
-        <v>1217</v>
+        <v>1118</v>
       </c>
       <c r="J236" t="s">
-        <v>1218</v>
+        <v>1119</v>
       </c>
       <c r="K236" t="s">
-        <v>1212</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B237">
         <v>82</v>
       </c>
       <c r="C237" t="s">
-        <v>1368</v>
+        <v>1210</v>
       </c>
       <c r="D237" t="s">
-        <v>1369</v>
+        <v>1211</v>
       </c>
       <c r="E237" t="s">
-        <v>1370</v>
+        <v>89</v>
       </c>
       <c r="F237" t="s">
-        <v>1372</v>
+        <v>1213</v>
       </c>
       <c r="G237" t="s">
-        <v>1373</v>
+        <v>1214</v>
       </c>
       <c r="H237" t="s">
-        <v>1375</v>
+        <v>1216</v>
       </c>
       <c r="I237" t="s">
-        <v>1376</v>
+        <v>1217</v>
       </c>
       <c r="J237" t="s">
-        <v>1377</v>
+        <v>1218</v>
       </c>
       <c r="K237" t="s">
-        <v>1371</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B238">
         <v>82</v>
       </c>
       <c r="C238" t="s">
-        <v>1534</v>
+        <v>1368</v>
       </c>
       <c r="D238" t="s">
-        <v>1608</v>
+        <v>1369</v>
       </c>
       <c r="E238" t="s">
-        <v>1609</v>
+        <v>1370</v>
       </c>
       <c r="F238" t="s">
-        <v>1559</v>
+        <v>1372</v>
       </c>
       <c r="G238" t="s">
-        <v>1611</v>
+        <v>1373</v>
       </c>
       <c r="H238" t="s">
-        <v>1613</v>
+        <v>1375</v>
       </c>
       <c r="I238" t="s">
-        <v>1614</v>
+        <v>1376</v>
       </c>
       <c r="J238" t="s">
-        <v>1615</v>
+        <v>1377</v>
       </c>
       <c r="K238" t="s">
-        <v>1610</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B239">
         <v>82</v>
@@ -36186,383 +36313,383 @@
         <v>1534</v>
       </c>
       <c r="D239" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="E239" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="F239" t="s">
-        <v>1619</v>
+        <v>1559</v>
       </c>
       <c r="G239" t="s">
-        <v>1620</v>
+        <v>1611</v>
       </c>
       <c r="H239" t="s">
-        <v>1622</v>
+        <v>1613</v>
       </c>
       <c r="I239" t="s">
-        <v>1623</v>
+        <v>1614</v>
       </c>
       <c r="J239" t="s">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="K239" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B240">
         <v>82</v>
       </c>
       <c r="C240" t="s">
-        <v>1884</v>
+        <v>1534</v>
       </c>
       <c r="D240" t="s">
-        <v>1979</v>
+        <v>1616</v>
       </c>
       <c r="E240" t="s">
-        <v>1980</v>
+        <v>1617</v>
       </c>
       <c r="F240" t="s">
-        <v>1982</v>
+        <v>1619</v>
       </c>
       <c r="G240" t="s">
-        <v>1983</v>
+        <v>1620</v>
       </c>
       <c r="H240" t="s">
-        <v>1985</v>
+        <v>1622</v>
       </c>
       <c r="I240" t="s">
-        <v>1986</v>
+        <v>1623</v>
       </c>
       <c r="J240" t="s">
-        <v>1987</v>
+        <v>1624</v>
       </c>
       <c r="K240" t="s">
-        <v>1981</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B241">
         <v>82</v>
       </c>
       <c r="C241" t="s">
-        <v>2258</v>
+        <v>1884</v>
       </c>
       <c r="D241" t="s">
-        <v>2283</v>
+        <v>1979</v>
       </c>
       <c r="E241" t="s">
-        <v>2284</v>
+        <v>1980</v>
       </c>
       <c r="F241" t="s">
-        <v>2286</v>
+        <v>1982</v>
       </c>
       <c r="G241" t="s">
-        <v>2287</v>
+        <v>1983</v>
       </c>
       <c r="H241" t="s">
-        <v>2289</v>
+        <v>1985</v>
       </c>
       <c r="I241" t="s">
-        <v>2290</v>
+        <v>1986</v>
       </c>
       <c r="J241" t="s">
-        <v>2291</v>
+        <v>1987</v>
       </c>
       <c r="K241" t="s">
-        <v>2285</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B242">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C242" t="s">
-        <v>12</v>
+        <v>2258</v>
       </c>
       <c r="D242" t="s">
-        <v>80</v>
+        <v>2283</v>
       </c>
       <c r="E242" t="s">
-        <v>81</v>
+        <v>2284</v>
       </c>
       <c r="F242" t="s">
-        <v>25</v>
+        <v>2286</v>
       </c>
       <c r="G242" t="s">
-        <v>83</v>
+        <v>2287</v>
       </c>
       <c r="H242" t="s">
-        <v>85</v>
+        <v>2289</v>
       </c>
       <c r="I242" t="s">
-        <v>86</v>
+        <v>2290</v>
       </c>
       <c r="J242" t="s">
-        <v>87</v>
+        <v>2291</v>
       </c>
       <c r="K242" t="s">
-        <v>82</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B243">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C243" t="s">
-        <v>284</v>
+        <v>2675</v>
       </c>
       <c r="D243" t="s">
-        <v>377</v>
+        <v>2676</v>
       </c>
       <c r="E243" t="s">
-        <v>378</v>
+        <v>2677</v>
       </c>
       <c r="F243" t="s">
-        <v>380</v>
+        <v>66</v>
       </c>
       <c r="G243" t="s">
-        <v>381</v>
+        <v>2679</v>
       </c>
       <c r="H243" t="s">
-        <v>383</v>
+        <v>2681</v>
       </c>
       <c r="I243" t="s">
-        <v>384</v>
+        <v>2682</v>
       </c>
       <c r="J243" t="s">
-        <v>385</v>
+        <v>2683</v>
       </c>
       <c r="K243" t="s">
-        <v>379</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B244">
         <v>81</v>
       </c>
       <c r="C244" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D244" t="s">
-        <v>499</v>
+        <v>80</v>
       </c>
       <c r="E244" t="s">
-        <v>500</v>
+        <v>81</v>
       </c>
       <c r="F244" t="s">
-        <v>502</v>
+        <v>25</v>
       </c>
       <c r="G244" t="s">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="H244" t="s">
-        <v>505</v>
+        <v>85</v>
       </c>
       <c r="I244" t="s">
-        <v>506</v>
+        <v>86</v>
       </c>
       <c r="J244" t="s">
-        <v>507</v>
+        <v>87</v>
       </c>
       <c r="K244" t="s">
-        <v>501</v>
+        <v>82</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B245">
         <v>81</v>
       </c>
       <c r="C245" t="s">
-        <v>591</v>
+        <v>284</v>
       </c>
       <c r="D245" t="s">
-        <v>616</v>
+        <v>377</v>
       </c>
       <c r="E245" t="s">
-        <v>610</v>
+        <v>378</v>
       </c>
       <c r="F245" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G245" t="s">
-        <v>618</v>
+        <v>381</v>
       </c>
       <c r="H245" t="s">
-        <v>620</v>
+        <v>383</v>
       </c>
       <c r="I245" t="s">
-        <v>621</v>
+        <v>384</v>
       </c>
       <c r="J245" t="s">
-        <v>622</v>
+        <v>385</v>
       </c>
       <c r="K245" t="s">
-        <v>617</v>
+        <v>379</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B246">
         <v>81</v>
       </c>
       <c r="C246" t="s">
-        <v>845</v>
+        <v>473</v>
       </c>
       <c r="D246" t="s">
-        <v>888</v>
+        <v>499</v>
       </c>
       <c r="E246" t="s">
-        <v>889</v>
+        <v>500</v>
       </c>
       <c r="F246" t="s">
-        <v>25</v>
+        <v>502</v>
       </c>
       <c r="G246" t="s">
-        <v>891</v>
+        <v>503</v>
       </c>
       <c r="H246" t="s">
-        <v>893</v>
+        <v>505</v>
       </c>
       <c r="I246" t="s">
-        <v>894</v>
+        <v>506</v>
       </c>
       <c r="J246" t="s">
-        <v>895</v>
+        <v>507</v>
       </c>
       <c r="K246" t="s">
-        <v>890</v>
+        <v>501</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B247">
         <v>81</v>
       </c>
       <c r="C247" t="s">
-        <v>1087</v>
+        <v>591</v>
       </c>
       <c r="D247" t="s">
-        <v>1120</v>
+        <v>616</v>
       </c>
       <c r="E247" t="s">
-        <v>1121</v>
+        <v>610</v>
       </c>
       <c r="F247" t="s">
-        <v>1123</v>
+        <v>16</v>
       </c>
       <c r="G247" t="s">
-        <v>1124</v>
+        <v>618</v>
       </c>
       <c r="H247" t="s">
-        <v>1126</v>
+        <v>620</v>
       </c>
       <c r="I247" t="s">
-        <v>1127</v>
+        <v>621</v>
       </c>
       <c r="J247" t="s">
-        <v>1128</v>
+        <v>622</v>
       </c>
       <c r="K247" t="s">
-        <v>1122</v>
+        <v>617</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B248">
         <v>81</v>
       </c>
       <c r="C248" t="s">
-        <v>1394</v>
+        <v>845</v>
       </c>
       <c r="D248" t="s">
-        <v>1412</v>
+        <v>888</v>
       </c>
       <c r="E248" t="s">
-        <v>1413</v>
+        <v>889</v>
       </c>
       <c r="F248" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G248" t="s">
-        <v>1415</v>
+        <v>891</v>
       </c>
       <c r="H248" t="s">
-        <v>1417</v>
+        <v>893</v>
       </c>
       <c r="I248" t="s">
-        <v>1418</v>
+        <v>894</v>
       </c>
       <c r="J248" t="s">
-        <v>1419</v>
+        <v>895</v>
       </c>
       <c r="K248" t="s">
-        <v>1414</v>
+        <v>890</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B249">
         <v>81</v>
       </c>
       <c r="C249" t="s">
-        <v>1394</v>
+        <v>1087</v>
       </c>
       <c r="D249" t="s">
-        <v>1420</v>
+        <v>1120</v>
       </c>
       <c r="E249" t="s">
-        <v>1421</v>
+        <v>1121</v>
       </c>
       <c r="F249" t="s">
-        <v>16</v>
+        <v>1123</v>
       </c>
       <c r="G249" t="s">
-        <v>1423</v>
+        <v>1124</v>
       </c>
       <c r="H249" t="s">
-        <v>1425</v>
+        <v>1126</v>
       </c>
       <c r="I249" t="s">
-        <v>1426</v>
+        <v>1127</v>
       </c>
       <c r="J249" t="s">
-        <v>1427</v>
+        <v>1128</v>
       </c>
       <c r="K249" t="s">
-        <v>1422</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B250">
         <v>81</v>
@@ -36571,313 +36698,313 @@
         <v>1394</v>
       </c>
       <c r="D250" t="s">
-        <v>1467</v>
+        <v>1412</v>
       </c>
       <c r="E250" t="s">
-        <v>1468</v>
+        <v>1413</v>
       </c>
       <c r="F250" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G250" t="s">
-        <v>1470</v>
+        <v>1415</v>
       </c>
       <c r="H250" t="s">
-        <v>1472</v>
+        <v>1417</v>
       </c>
       <c r="I250" t="s">
-        <v>1473</v>
+        <v>1418</v>
       </c>
       <c r="J250" t="s">
-        <v>1474</v>
+        <v>1419</v>
       </c>
       <c r="K250" t="s">
-        <v>1469</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B251">
         <v>81</v>
       </c>
       <c r="C251" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D251" t="s">
-        <v>271</v>
+        <v>1420</v>
       </c>
       <c r="E251" t="s">
-        <v>1600</v>
+        <v>1421</v>
       </c>
       <c r="F251" t="s">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="G251" t="s">
-        <v>1603</v>
+        <v>1423</v>
       </c>
       <c r="H251" t="s">
-        <v>1605</v>
+        <v>1425</v>
       </c>
       <c r="I251" t="s">
-        <v>1606</v>
+        <v>1426</v>
       </c>
       <c r="J251" t="s">
-        <v>1607</v>
+        <v>1427</v>
       </c>
       <c r="K251" t="s">
-        <v>1601</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B252">
         <v>81</v>
       </c>
       <c r="C252" t="s">
-        <v>1664</v>
+        <v>1394</v>
       </c>
       <c r="D252" t="s">
-        <v>1708</v>
+        <v>1467</v>
       </c>
       <c r="E252" t="s">
-        <v>1709</v>
+        <v>1468</v>
       </c>
       <c r="F252" t="s">
-        <v>1711</v>
+        <v>16</v>
       </c>
       <c r="G252" t="s">
-        <v>1034</v>
+        <v>1470</v>
       </c>
       <c r="H252" t="s">
-        <v>1713</v>
+        <v>1472</v>
       </c>
       <c r="I252" t="s">
-        <v>1714</v>
+        <v>1473</v>
       </c>
       <c r="J252" t="s">
-        <v>1715</v>
+        <v>1474</v>
       </c>
       <c r="K252" t="s">
-        <v>1710</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B253">
         <v>81</v>
       </c>
       <c r="C253" t="s">
-        <v>1727</v>
+        <v>1534</v>
       </c>
       <c r="D253" t="s">
-        <v>1773</v>
+        <v>271</v>
       </c>
       <c r="E253" t="s">
-        <v>1774</v>
+        <v>1600</v>
       </c>
       <c r="F253" t="s">
-        <v>16</v>
+        <v>1602</v>
       </c>
       <c r="G253" t="s">
-        <v>1776</v>
+        <v>1603</v>
       </c>
       <c r="H253" t="s">
-        <v>1778</v>
+        <v>1605</v>
       </c>
       <c r="I253" t="s">
-        <v>79</v>
+        <v>1606</v>
       </c>
       <c r="J253" t="s">
-        <v>79</v>
+        <v>1607</v>
       </c>
       <c r="K253" t="s">
-        <v>1775</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B254">
         <v>81</v>
       </c>
       <c r="C254" t="s">
-        <v>1727</v>
+        <v>1664</v>
       </c>
       <c r="D254" t="s">
-        <v>964</v>
+        <v>1708</v>
       </c>
       <c r="E254" t="s">
-        <v>362</v>
+        <v>1709</v>
       </c>
       <c r="F254" t="s">
-        <v>356</v>
+        <v>1711</v>
       </c>
       <c r="G254" t="s">
-        <v>1792</v>
+        <v>1034</v>
       </c>
       <c r="H254" t="s">
-        <v>1794</v>
+        <v>1713</v>
       </c>
       <c r="I254" t="s">
-        <v>79</v>
+        <v>1714</v>
       </c>
       <c r="J254" t="s">
-        <v>79</v>
+        <v>1715</v>
       </c>
       <c r="K254" t="s">
-        <v>1791</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B255">
         <v>81</v>
       </c>
       <c r="C255" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D255" t="s">
-        <v>1963</v>
+        <v>1773</v>
       </c>
       <c r="E255" t="s">
-        <v>1964</v>
+        <v>1774</v>
       </c>
       <c r="F255" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G255" t="s">
-        <v>1034</v>
+        <v>1776</v>
       </c>
       <c r="H255" t="s">
-        <v>1967</v>
+        <v>1778</v>
       </c>
       <c r="I255" t="s">
-        <v>1968</v>
+        <v>79</v>
       </c>
       <c r="J255" t="s">
-        <v>1969</v>
+        <v>79</v>
       </c>
       <c r="K255" t="s">
-        <v>1965</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B256">
         <v>81</v>
       </c>
       <c r="C256" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D256" t="s">
-        <v>1979</v>
+        <v>964</v>
       </c>
       <c r="E256" t="s">
-        <v>1988</v>
+        <v>362</v>
       </c>
       <c r="F256" t="s">
-        <v>1982</v>
+        <v>356</v>
       </c>
       <c r="G256" t="s">
-        <v>1983</v>
+        <v>1792</v>
       </c>
       <c r="H256" t="s">
-        <v>1991</v>
+        <v>1794</v>
       </c>
       <c r="I256" t="s">
-        <v>1992</v>
+        <v>79</v>
       </c>
       <c r="J256" t="s">
-        <v>1993</v>
+        <v>79</v>
       </c>
       <c r="K256" t="s">
-        <v>1989</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B257">
         <v>81</v>
       </c>
       <c r="C257" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D257" t="s">
-        <v>2114</v>
+        <v>1963</v>
       </c>
       <c r="E257" t="s">
-        <v>830</v>
+        <v>1964</v>
       </c>
       <c r="F257" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G257" t="s">
-        <v>2116</v>
+        <v>1034</v>
       </c>
       <c r="H257" t="s">
-        <v>2118</v>
+        <v>1967</v>
       </c>
       <c r="I257" t="s">
-        <v>2119</v>
+        <v>1968</v>
       </c>
       <c r="J257" t="s">
-        <v>2120</v>
+        <v>1969</v>
       </c>
       <c r="K257" t="s">
-        <v>2115</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B258">
         <v>81</v>
       </c>
       <c r="C258" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D258" t="s">
-        <v>2126</v>
+        <v>1979</v>
       </c>
       <c r="E258" t="s">
-        <v>2127</v>
+        <v>1988</v>
       </c>
       <c r="F258" t="s">
-        <v>16</v>
+        <v>1982</v>
       </c>
       <c r="G258" t="s">
-        <v>2129</v>
+        <v>1983</v>
       </c>
       <c r="H258" t="s">
-        <v>2118</v>
+        <v>1991</v>
       </c>
       <c r="I258" t="s">
-        <v>2131</v>
+        <v>1992</v>
       </c>
       <c r="J258" t="s">
-        <v>2132</v>
+        <v>1993</v>
       </c>
       <c r="K258" t="s">
-        <v>2128</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B259">
         <v>81</v>
@@ -36886,33 +37013,33 @@
         <v>2098</v>
       </c>
       <c r="D259" t="s">
-        <v>2148</v>
+        <v>2114</v>
       </c>
       <c r="E259" t="s">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="F259" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G259" t="s">
-        <v>2150</v>
+        <v>2116</v>
       </c>
       <c r="H259" t="s">
-        <v>2152</v>
+        <v>2118</v>
       </c>
       <c r="I259" t="s">
-        <v>2153</v>
+        <v>2119</v>
       </c>
       <c r="J259" t="s">
-        <v>2154</v>
+        <v>2120</v>
       </c>
       <c r="K259" t="s">
-        <v>2149</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B260">
         <v>81</v>
@@ -36921,33 +37048,33 @@
         <v>2098</v>
       </c>
       <c r="D260" t="s">
-        <v>2184</v>
+        <v>2126</v>
       </c>
       <c r="E260" t="s">
-        <v>2177</v>
+        <v>2127</v>
       </c>
       <c r="F260" t="s">
-        <v>2042</v>
+        <v>16</v>
       </c>
       <c r="G260" t="s">
-        <v>2186</v>
+        <v>2129</v>
       </c>
       <c r="H260" t="s">
-        <v>2188</v>
+        <v>2118</v>
       </c>
       <c r="I260" t="s">
-        <v>2189</v>
+        <v>2131</v>
       </c>
       <c r="J260" t="s">
-        <v>2190</v>
+        <v>2132</v>
       </c>
       <c r="K260" t="s">
-        <v>2185</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B261">
         <v>81</v>
@@ -36956,278 +37083,278 @@
         <v>2098</v>
       </c>
       <c r="D261" t="s">
-        <v>2211</v>
+        <v>2148</v>
       </c>
       <c r="E261" t="s">
         <v>110</v>
       </c>
       <c r="F261" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G261" t="s">
-        <v>2220</v>
+        <v>2150</v>
       </c>
       <c r="H261" t="s">
-        <v>2222</v>
+        <v>2152</v>
       </c>
       <c r="I261" t="s">
-        <v>2223</v>
+        <v>2153</v>
       </c>
       <c r="J261" t="s">
-        <v>2224</v>
+        <v>2154</v>
       </c>
       <c r="K261" t="s">
-        <v>2219</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B262">
         <v>81</v>
       </c>
       <c r="C262" t="s">
-        <v>2258</v>
+        <v>2098</v>
       </c>
       <c r="D262" t="s">
-        <v>2274</v>
+        <v>2184</v>
       </c>
       <c r="E262" t="s">
-        <v>2275</v>
+        <v>2177</v>
       </c>
       <c r="F262" t="s">
-        <v>2277</v>
+        <v>2042</v>
       </c>
       <c r="G262" t="s">
-        <v>2278</v>
+        <v>2186</v>
       </c>
       <c r="H262" t="s">
-        <v>2280</v>
+        <v>2188</v>
       </c>
       <c r="I262" t="s">
-        <v>2281</v>
+        <v>2189</v>
       </c>
       <c r="J262" t="s">
-        <v>2282</v>
+        <v>2190</v>
       </c>
       <c r="K262" t="s">
-        <v>2276</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B263">
         <v>81</v>
       </c>
       <c r="C263" t="s">
-        <v>2377</v>
+        <v>2098</v>
       </c>
       <c r="D263" t="s">
-        <v>2400</v>
+        <v>2211</v>
       </c>
       <c r="E263" t="s">
-        <v>2401</v>
+        <v>110</v>
       </c>
       <c r="F263" t="s">
         <v>16</v>
       </c>
       <c r="G263" t="s">
-        <v>2395</v>
+        <v>2220</v>
       </c>
       <c r="H263" t="s">
-        <v>2404</v>
+        <v>2222</v>
       </c>
       <c r="I263" t="s">
-        <v>2405</v>
+        <v>2223</v>
       </c>
       <c r="J263" t="s">
-        <v>2406</v>
+        <v>2224</v>
       </c>
       <c r="K263" t="s">
-        <v>2402</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B264">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C264" t="s">
-        <v>934</v>
+        <v>2258</v>
       </c>
       <c r="D264" t="s">
-        <v>1039</v>
+        <v>2274</v>
       </c>
       <c r="E264" t="s">
-        <v>1040</v>
+        <v>2275</v>
       </c>
       <c r="F264" t="s">
-        <v>1042</v>
+        <v>2277</v>
       </c>
       <c r="G264" t="s">
-        <v>1043</v>
+        <v>2278</v>
       </c>
       <c r="H264" t="s">
-        <v>1045</v>
+        <v>2280</v>
       </c>
       <c r="I264" t="s">
-        <v>1046</v>
+        <v>2281</v>
       </c>
       <c r="J264" t="s">
-        <v>1047</v>
+        <v>2282</v>
       </c>
       <c r="K264" t="s">
-        <v>1041</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B265">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C265" t="s">
-        <v>1884</v>
+        <v>2377</v>
       </c>
       <c r="D265" t="s">
-        <v>1947</v>
+        <v>2400</v>
       </c>
       <c r="E265" t="s">
-        <v>1948</v>
+        <v>2401</v>
       </c>
       <c r="F265" t="s">
-        <v>1950</v>
+        <v>16</v>
       </c>
       <c r="G265" t="s">
-        <v>1034</v>
+        <v>2395</v>
       </c>
       <c r="H265" t="s">
-        <v>1952</v>
+        <v>2404</v>
       </c>
       <c r="I265" t="s">
-        <v>1953</v>
+        <v>2405</v>
       </c>
       <c r="J265" t="s">
-        <v>1954</v>
+        <v>2406</v>
       </c>
       <c r="K265" t="s">
-        <v>1949</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B266">
         <v>80</v>
       </c>
       <c r="C266" t="s">
-        <v>1884</v>
+        <v>934</v>
       </c>
       <c r="D266" t="s">
-        <v>1970</v>
+        <v>1039</v>
       </c>
       <c r="E266" t="s">
-        <v>1971</v>
+        <v>1040</v>
       </c>
       <c r="F266" t="s">
-        <v>1973</v>
+        <v>1042</v>
       </c>
       <c r="G266" t="s">
-        <v>1974</v>
+        <v>1043</v>
       </c>
       <c r="H266" t="s">
-        <v>1976</v>
+        <v>1045</v>
       </c>
       <c r="I266" t="s">
-        <v>1977</v>
+        <v>1046</v>
       </c>
       <c r="J266" t="s">
-        <v>1978</v>
+        <v>1047</v>
       </c>
       <c r="K266" t="s">
-        <v>1972</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B267">
         <v>80</v>
       </c>
       <c r="C267" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D267" t="s">
-        <v>2107</v>
+        <v>1947</v>
       </c>
       <c r="E267" t="s">
-        <v>830</v>
+        <v>1948</v>
       </c>
       <c r="F267" t="s">
-        <v>66</v>
+        <v>1950</v>
       </c>
       <c r="G267" t="s">
-        <v>2109</v>
+        <v>1034</v>
       </c>
       <c r="H267" t="s">
-        <v>2111</v>
+        <v>1952</v>
       </c>
       <c r="I267" t="s">
-        <v>2112</v>
+        <v>1953</v>
       </c>
       <c r="J267" t="s">
-        <v>2113</v>
+        <v>1954</v>
       </c>
       <c r="K267" t="s">
-        <v>2108</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B268">
         <v>80</v>
       </c>
       <c r="C268" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D268" t="s">
-        <v>2133</v>
+        <v>1970</v>
       </c>
       <c r="E268" t="s">
-        <v>110</v>
+        <v>1971</v>
       </c>
       <c r="F268" t="s">
-        <v>16</v>
+        <v>1973</v>
       </c>
       <c r="G268" t="s">
-        <v>2135</v>
+        <v>1974</v>
       </c>
       <c r="H268" t="s">
-        <v>2137</v>
+        <v>1976</v>
       </c>
       <c r="I268" t="s">
-        <v>2138</v>
+        <v>1977</v>
       </c>
       <c r="J268" t="s">
-        <v>2139</v>
+        <v>1978</v>
       </c>
       <c r="K268" t="s">
-        <v>2134</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B269">
         <v>80</v>
@@ -37236,33 +37363,33 @@
         <v>2098</v>
       </c>
       <c r="D269" t="s">
-        <v>2140</v>
+        <v>2107</v>
       </c>
       <c r="E269" t="s">
-        <v>2141</v>
+        <v>830</v>
       </c>
       <c r="F269" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G269" t="s">
-        <v>2143</v>
+        <v>2109</v>
       </c>
       <c r="H269" t="s">
-        <v>2145</v>
+        <v>2111</v>
       </c>
       <c r="I269" t="s">
-        <v>2146</v>
+        <v>2112</v>
       </c>
       <c r="J269" t="s">
-        <v>2147</v>
+        <v>2113</v>
       </c>
       <c r="K269" t="s">
-        <v>2142</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B270">
         <v>80</v>
@@ -37271,33 +37398,33 @@
         <v>2098</v>
       </c>
       <c r="D270" t="s">
-        <v>2155</v>
+        <v>2133</v>
       </c>
       <c r="E270" t="s">
         <v>110</v>
       </c>
       <c r="F270" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G270" t="s">
-        <v>2157</v>
+        <v>2135</v>
       </c>
       <c r="H270" t="s">
-        <v>2159</v>
+        <v>2137</v>
       </c>
       <c r="I270" t="s">
-        <v>2160</v>
+        <v>2138</v>
       </c>
       <c r="J270" t="s">
-        <v>2161</v>
+        <v>2139</v>
       </c>
       <c r="K270" t="s">
-        <v>2156</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B271">
         <v>80</v>
@@ -37306,33 +37433,33 @@
         <v>2098</v>
       </c>
       <c r="D271" t="s">
-        <v>2162</v>
+        <v>2140</v>
       </c>
       <c r="E271" t="s">
-        <v>110</v>
+        <v>2141</v>
       </c>
       <c r="F271" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G271" t="s">
-        <v>2171</v>
+        <v>2143</v>
       </c>
       <c r="H271" t="s">
-        <v>2173</v>
+        <v>2145</v>
       </c>
       <c r="I271" t="s">
-        <v>2174</v>
+        <v>2146</v>
       </c>
       <c r="J271" t="s">
-        <v>2175</v>
+        <v>2147</v>
       </c>
       <c r="K271" t="s">
-        <v>2170</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B272">
         <v>80</v>
@@ -37341,33 +37468,33 @@
         <v>2098</v>
       </c>
       <c r="D272" t="s">
-        <v>2203</v>
+        <v>2155</v>
       </c>
       <c r="E272" t="s">
-        <v>2204</v>
+        <v>110</v>
       </c>
       <c r="F272" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="G272" t="s">
-        <v>2206</v>
+        <v>2157</v>
       </c>
       <c r="H272" t="s">
-        <v>2208</v>
+        <v>2159</v>
       </c>
       <c r="I272" t="s">
-        <v>2209</v>
+        <v>2160</v>
       </c>
       <c r="J272" t="s">
-        <v>2210</v>
+        <v>2161</v>
       </c>
       <c r="K272" t="s">
-        <v>2205</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B273">
         <v>80</v>
@@ -37376,132 +37503,202 @@
         <v>2098</v>
       </c>
       <c r="D273" t="s">
-        <v>2225</v>
+        <v>2162</v>
       </c>
       <c r="E273" t="s">
-        <v>2226</v>
+        <v>110</v>
       </c>
       <c r="F273" t="s">
         <v>16</v>
       </c>
       <c r="G273" t="s">
-        <v>112</v>
+        <v>2171</v>
       </c>
       <c r="H273" t="s">
-        <v>2229</v>
+        <v>2173</v>
       </c>
       <c r="I273" t="s">
-        <v>2230</v>
+        <v>2174</v>
       </c>
       <c r="J273" t="s">
-        <v>2231</v>
+        <v>2175</v>
       </c>
       <c r="K273" t="s">
-        <v>2227</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B274">
         <v>80</v>
       </c>
       <c r="C274" t="s">
-        <v>2258</v>
+        <v>2098</v>
       </c>
       <c r="D274" t="s">
-        <v>2292</v>
+        <v>2203</v>
       </c>
       <c r="E274" t="s">
-        <v>2293</v>
+        <v>2204</v>
       </c>
       <c r="F274" t="s">
-        <v>747</v>
+        <v>106</v>
       </c>
       <c r="G274" t="s">
-        <v>2295</v>
+        <v>2206</v>
       </c>
       <c r="H274" t="s">
-        <v>2297</v>
+        <v>2208</v>
       </c>
       <c r="I274" t="s">
-        <v>2298</v>
+        <v>2209</v>
       </c>
       <c r="J274" t="s">
-        <v>2299</v>
+        <v>2210</v>
       </c>
       <c r="K274" t="s">
-        <v>2294</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B275">
         <v>80</v>
       </c>
       <c r="C275" t="s">
-        <v>2377</v>
+        <v>2098</v>
       </c>
       <c r="D275" t="s">
-        <v>2392</v>
+        <v>2225</v>
       </c>
       <c r="E275" t="s">
-        <v>2393</v>
+        <v>2226</v>
       </c>
       <c r="F275" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G275" t="s">
-        <v>2395</v>
+        <v>112</v>
       </c>
       <c r="H275" t="s">
-        <v>2397</v>
+        <v>2229</v>
       </c>
       <c r="I275" t="s">
-        <v>2398</v>
+        <v>2230</v>
       </c>
       <c r="J275" t="s">
-        <v>2399</v>
+        <v>2231</v>
       </c>
       <c r="K275" t="s">
-        <v>2394</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>2686</v>
+        <v>2703</v>
       </c>
       <c r="B276">
         <v>80</v>
       </c>
       <c r="C276" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D276" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E276" t="s">
+        <v>2293</v>
+      </c>
+      <c r="F276" t="s">
+        <v>747</v>
+      </c>
+      <c r="G276" t="s">
+        <v>2295</v>
+      </c>
+      <c r="H276" t="s">
+        <v>2297</v>
+      </c>
+      <c r="I276" t="s">
+        <v>2298</v>
+      </c>
+      <c r="J276" t="s">
+        <v>2299</v>
+      </c>
+      <c r="K276" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B277">
+        <v>80</v>
+      </c>
+      <c r="C277" t="s">
         <v>2377</v>
       </c>
-      <c r="D276" t="s">
+      <c r="D277" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E277" t="s">
+        <v>2393</v>
+      </c>
+      <c r="F277" t="s">
+        <v>66</v>
+      </c>
+      <c r="G277" t="s">
+        <v>2395</v>
+      </c>
+      <c r="H277" t="s">
+        <v>2397</v>
+      </c>
+      <c r="I277" t="s">
+        <v>2398</v>
+      </c>
+      <c r="J277" t="s">
+        <v>2399</v>
+      </c>
+      <c r="K277" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B278">
+        <v>80</v>
+      </c>
+      <c r="C278" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D278" t="s">
         <v>2414</v>
       </c>
-      <c r="E276" t="s">
+      <c r="E278" t="s">
         <v>2415</v>
       </c>
-      <c r="F276" t="s">
+      <c r="F278" t="s">
         <v>124</v>
       </c>
-      <c r="G276" t="s">
+      <c r="G278" t="s">
         <v>2417</v>
       </c>
-      <c r="H276" t="s">
+      <c r="H278" t="s">
         <v>2419</v>
       </c>
-      <c r="I276" t="s">
+      <c r="I278" t="s">
         <v>2420</v>
       </c>
-      <c r="J276" t="s">
+      <c r="J278" t="s">
         <v>2421</v>
       </c>
-      <c r="K276" t="s">
+      <c r="K278" t="s">
         <v>2416</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9292" uniqueCount="3351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9332" uniqueCount="3361">
   <si>
     <t>日期</t>
   </si>
@@ -9947,6 +9947,36 @@
   </si>
   <si>
     <t>如投递需突出介入导管/球囊相关的结构设计、材料与工艺能力；补充对研发全流程合规（DHF/DMR）的认知；以扎实方法学弥补经验年限不足。</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>材料研发工程师（2027届校园招聘·研发创新方向）</t>
+  </si>
+  <si>
+    <t>大博医疗（002901，深交所上市，医疗器械行业龙头）2027届校招，研发创新方向材料研发工程师，面向高分子材料、生物、化学化工专业，本科及以上，应届2027届（毕业时间2026.10-2027.9），工作地点厦门，截止2026-11-19。方向为再生医学、生物材料等。</t>
+  </si>
+  <si>
+    <t>https://www.wondercv.com/xiaozhao/dabo-medical-2027-campus-recruitment-16228-5d5277/</t>
+  </si>
+  <si>
+    <t>智能匹配81分【校园招聘】|强烈推荐|上市龙头医疗器械校招材料研发岗，材料学技能重合，方向为生物材料泛医疗器械而非血管支架</t>
+  </si>
+  <si>
+    <t>研究72/技能72/学历100/行业100/企业95</t>
+  </si>
+  <si>
+    <t>研发管培生（2027届校园招聘·管培生计划）</t>
+  </si>
+  <si>
+    <t>大博医疗2027届校招研发管培生，面向材料类、生物医学、化工化学、机械电子等相关专业，本科及以上，应届2027届，工作地点厦门。管培生计划含项目管理、制造、质量、研发四个方向轮岗，培养期后定岗。</t>
+  </si>
+  <si>
+    <t>智能匹配80分【校园招聘】|强烈推荐|上市医疗器械龙头研发管培生，专业覆盖生物医学/材料，方向为医疗器械泛方向</t>
+  </si>
+  <si>
+    <t>研究70/技能70/学历100/行业100/企业95</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -10501,7 +10531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L449"/>
+  <dimension ref="A1:L451"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -27577,6 +27607,82 @@
       </c>
       <c r="L449" t="s">
         <v>3310</v>
+      </c>
+    </row>
+    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C450" t="s">
+        <v>3312</v>
+      </c>
+      <c r="D450" t="s">
+        <v>3313</v>
+      </c>
+      <c r="E450" t="s">
+        <v>3298</v>
+      </c>
+      <c r="F450" t="s">
+        <v>3314</v>
+      </c>
+      <c r="G450">
+        <v>8</v>
+      </c>
+      <c r="H450" t="s">
+        <v>3315</v>
+      </c>
+      <c r="I450">
+        <v>81</v>
+      </c>
+      <c r="J450" t="s">
+        <v>3316</v>
+      </c>
+      <c r="K450" t="s">
+        <v>79</v>
+      </c>
+      <c r="L450" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C451" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D451" t="s">
+        <v>3318</v>
+      </c>
+      <c r="E451" t="s">
+        <v>3298</v>
+      </c>
+      <c r="F451" t="s">
+        <v>3314</v>
+      </c>
+      <c r="G451">
+        <v>8</v>
+      </c>
+      <c r="H451" t="s">
+        <v>3319</v>
+      </c>
+      <c r="I451">
+        <v>80</v>
+      </c>
+      <c r="J451" t="s">
+        <v>3320</v>
+      </c>
+      <c r="K451" t="s">
+        <v>79</v>
+      </c>
+      <c r="L451" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -27610,7 +27716,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3311</v>
+        <v>3321</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -27619,16 +27725,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3312</v>
+        <v>3322</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3313</v>
+        <v>3323</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3314</v>
+        <v>3324</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3315</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -27642,13 +27748,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3316</v>
+        <v>3326</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>3317</v>
+        <v>3327</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>3318</v>
+        <v>3328</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -27691,7 +27797,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>3323</v>
+        <v>3333</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -27701,31 +27807,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>3324</v>
+        <v>3334</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>3325</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3326</v>
+        <v>3336</v>
       </c>
       <c r="B4">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3327</v>
+        <v>3337</v>
       </c>
       <c r="B5" t="s">
-        <v>3328</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3329</v>
+        <v>3339</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -27733,7 +27839,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3330</v>
+        <v>3340</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -27741,7 +27847,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3331</v>
+        <v>3341</v>
       </c>
       <c r="B8">
         <v>232</v>
@@ -27749,15 +27855,15 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3332</v>
+        <v>3342</v>
       </c>
       <c r="B9">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3333</v>
+        <v>3343</v>
       </c>
       <c r="B10">
         <v>18</v>
@@ -27765,15 +27871,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3334</v>
+        <v>3344</v>
       </c>
       <c r="B11" t="s">
-        <v>3243</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>3335</v>
+        <v>3345</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -27783,15 +27889,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>3336</v>
+        <v>3346</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>3337</v>
+        <v>3347</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3338</v>
+        <v>3348</v>
       </c>
       <c r="B16" s="5">
         <v>8</v>
@@ -27799,7 +27905,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3339</v>
+        <v>3349</v>
       </c>
       <c r="B17" s="5">
         <v>224</v>
@@ -27807,15 +27913,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3340</v>
+        <v>3350</v>
       </c>
       <c r="B18" s="5">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3341</v>
+        <v>3351</v>
       </c>
       <c r="B19" s="5">
         <v>18</v>
@@ -27823,7 +27929,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3342</v>
+        <v>3352</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -27831,7 +27937,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3343</v>
+        <v>3353</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -27839,7 +27945,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3344</v>
+        <v>3354</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -27847,7 +27953,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3345</v>
+        <v>3355</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -27855,7 +27961,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3346</v>
+        <v>3356</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -27863,7 +27969,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3347</v>
+        <v>3357</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -27871,7 +27977,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>3348</v>
+        <v>3358</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -27883,7 +27989,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>3349</v>
+        <v>3359</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -27901,7 +28007,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>3350</v>
+        <v>3360</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -33120,7 +33226,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K355"/>
+  <dimension ref="A1:K357"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -33137,10 +33243,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>3319</v>
+        <v>3329</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>3320</v>
+        <v>3330</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -33167,12 +33273,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>3321</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -33207,7 +33313,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -33242,7 +33348,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -33277,7 +33383,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -33312,7 +33418,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -33347,7 +33453,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -33382,7 +33488,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B8">
         <v>95</v>
@@ -33417,7 +33523,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B9">
         <v>95</v>
@@ -33452,7 +33558,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B10">
         <v>94</v>
@@ -33487,7 +33593,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B11">
         <v>94</v>
@@ -33522,7 +33628,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B12">
         <v>94</v>
@@ -33557,7 +33663,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B13">
         <v>93</v>
@@ -33592,7 +33698,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B14">
         <v>93</v>
@@ -33627,7 +33733,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B15">
         <v>93</v>
@@ -33662,7 +33768,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B16">
         <v>93</v>
@@ -33697,7 +33803,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B17">
         <v>93</v>
@@ -33732,7 +33838,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B18">
         <v>93</v>
@@ -33767,7 +33873,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B19">
         <v>93</v>
@@ -33802,7 +33908,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B20">
         <v>93</v>
@@ -33837,7 +33943,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B21">
         <v>92</v>
@@ -33872,7 +33978,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B22">
         <v>92</v>
@@ -33907,7 +34013,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B23">
         <v>92</v>
@@ -33942,7 +34048,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B24">
         <v>92</v>
@@ -33977,7 +34083,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B25">
         <v>92</v>
@@ -34012,7 +34118,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B26">
         <v>92</v>
@@ -34047,7 +34153,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B27">
         <v>92</v>
@@ -34082,7 +34188,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B28">
         <v>92</v>
@@ -34117,7 +34223,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B29">
         <v>92</v>
@@ -34152,7 +34258,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B30">
         <v>92</v>
@@ -34187,7 +34293,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B31">
         <v>91</v>
@@ -34222,7 +34328,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B32">
         <v>91</v>
@@ -34257,7 +34363,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B33">
         <v>91</v>
@@ -34292,7 +34398,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B34">
         <v>91</v>
@@ -34327,7 +34433,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B35">
         <v>91</v>
@@ -34362,7 +34468,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B36">
         <v>91</v>
@@ -34397,7 +34503,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B37">
         <v>91</v>
@@ -34432,7 +34538,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B38">
         <v>91</v>
@@ -34467,7 +34573,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B39">
         <v>91</v>
@@ -34502,7 +34608,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B40">
         <v>91</v>
@@ -34537,7 +34643,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B41">
         <v>91</v>
@@ -34572,7 +34678,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B42">
         <v>91</v>
@@ -34607,7 +34713,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B43">
         <v>91</v>
@@ -34642,7 +34748,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B44">
         <v>91</v>
@@ -34677,7 +34783,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B45">
         <v>91</v>
@@ -34712,7 +34818,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B46">
         <v>91</v>
@@ -34747,7 +34853,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B47">
         <v>90</v>
@@ -34782,7 +34888,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B48">
         <v>90</v>
@@ -34817,7 +34923,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B49">
         <v>90</v>
@@ -34852,7 +34958,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B50">
         <v>90</v>
@@ -34887,7 +34993,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B51">
         <v>90</v>
@@ -34922,7 +35028,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B52">
         <v>90</v>
@@ -34957,7 +35063,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B53">
         <v>90</v>
@@ -34992,7 +35098,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B54">
         <v>90</v>
@@ -35027,7 +35133,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B55">
         <v>90</v>
@@ -35062,7 +35168,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B56">
         <v>90</v>
@@ -35097,7 +35203,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B57">
         <v>90</v>
@@ -35132,7 +35238,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B58">
         <v>90</v>
@@ -35167,7 +35273,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B59">
         <v>90</v>
@@ -35202,7 +35308,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B60">
         <v>90</v>
@@ -35237,7 +35343,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B61">
         <v>90</v>
@@ -35272,7 +35378,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B62">
         <v>90</v>
@@ -35307,7 +35413,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B63">
         <v>90</v>
@@ -35342,7 +35448,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B64">
         <v>90</v>
@@ -35377,7 +35483,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B65">
         <v>90</v>
@@ -35412,7 +35518,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B66">
         <v>90</v>
@@ -35447,7 +35553,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B67">
         <v>90</v>
@@ -35482,7 +35588,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B68">
         <v>90</v>
@@ -35517,7 +35623,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B69">
         <v>90</v>
@@ -35552,7 +35658,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B70">
         <v>89</v>
@@ -35587,7 +35693,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B71">
         <v>89</v>
@@ -35622,7 +35728,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B72">
         <v>89</v>
@@ -35657,7 +35763,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B73">
         <v>89</v>
@@ -35692,7 +35798,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B74">
         <v>89</v>
@@ -35727,7 +35833,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B75">
         <v>89</v>
@@ -35762,7 +35868,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B76">
         <v>89</v>
@@ -35797,7 +35903,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B77">
         <v>89</v>
@@ -35832,7 +35938,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B78">
         <v>89</v>
@@ -35867,7 +35973,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B79">
         <v>89</v>
@@ -35902,7 +36008,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B80">
         <v>89</v>
@@ -35937,7 +36043,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B81">
         <v>89</v>
@@ -35972,7 +36078,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B82">
         <v>89</v>
@@ -36007,7 +36113,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B83">
         <v>89</v>
@@ -36042,7 +36148,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B84">
         <v>89</v>
@@ -36077,7 +36183,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B85">
         <v>89</v>
@@ -36112,7 +36218,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B86">
         <v>89</v>
@@ -36147,7 +36253,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B87">
         <v>89</v>
@@ -36182,7 +36288,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B88">
         <v>89</v>
@@ -36217,7 +36323,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B89">
         <v>89</v>
@@ -36252,7 +36358,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B90">
         <v>89</v>
@@ -36287,7 +36393,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B91">
         <v>89</v>
@@ -36322,7 +36428,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B92">
         <v>89</v>
@@ -36357,7 +36463,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B93">
         <v>89</v>
@@ -36392,7 +36498,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B94">
         <v>89</v>
@@ -36427,7 +36533,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B95">
         <v>89</v>
@@ -36462,7 +36568,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B96">
         <v>89</v>
@@ -36497,7 +36603,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B97">
         <v>89</v>
@@ -36532,7 +36638,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B98">
         <v>89</v>
@@ -36567,7 +36673,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B99">
         <v>89</v>
@@ -36602,7 +36708,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B100">
         <v>89</v>
@@ -36637,7 +36743,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B101">
         <v>89</v>
@@ -36672,7 +36778,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B102">
         <v>88</v>
@@ -36707,7 +36813,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B103">
         <v>88</v>
@@ -36742,7 +36848,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B104">
         <v>88</v>
@@ -36777,7 +36883,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B105">
         <v>88</v>
@@ -36812,7 +36918,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B106">
         <v>88</v>
@@ -36847,7 +36953,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B107">
         <v>88</v>
@@ -36882,7 +36988,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B108">
         <v>88</v>
@@ -36917,7 +37023,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B109">
         <v>88</v>
@@ -36952,7 +37058,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B110">
         <v>88</v>
@@ -36987,7 +37093,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B111">
         <v>88</v>
@@ -37022,7 +37128,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B112">
         <v>88</v>
@@ -37057,7 +37163,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B113">
         <v>88</v>
@@ -37092,7 +37198,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B114">
         <v>88</v>
@@ -37127,7 +37233,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B115">
         <v>88</v>
@@ -37162,7 +37268,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B116">
         <v>88</v>
@@ -37197,7 +37303,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B117">
         <v>88</v>
@@ -37232,7 +37338,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B118">
         <v>88</v>
@@ -37267,7 +37373,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B119">
         <v>88</v>
@@ -37302,7 +37408,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B120">
         <v>88</v>
@@ -37337,7 +37443,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B121">
         <v>88</v>
@@ -37372,7 +37478,7 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B122">
         <v>88</v>
@@ -37407,7 +37513,7 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B123">
         <v>88</v>
@@ -37442,7 +37548,7 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B124">
         <v>88</v>
@@ -37477,7 +37583,7 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B125">
         <v>88</v>
@@ -37512,7 +37618,7 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B126">
         <v>88</v>
@@ -37547,7 +37653,7 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B127">
         <v>88</v>
@@ -37582,7 +37688,7 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B128">
         <v>88</v>
@@ -37617,7 +37723,7 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B129">
         <v>88</v>
@@ -37652,7 +37758,7 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B130">
         <v>88</v>
@@ -37687,7 +37793,7 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B131">
         <v>88</v>
@@ -37722,7 +37828,7 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B132">
         <v>88</v>
@@ -37757,7 +37863,7 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B133">
         <v>88</v>
@@ -37792,7 +37898,7 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B134">
         <v>88</v>
@@ -37827,7 +37933,7 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B135">
         <v>88</v>
@@ -37862,7 +37968,7 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B136">
         <v>88</v>
@@ -37897,7 +38003,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B137">
         <v>87</v>
@@ -37932,7 +38038,7 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B138">
         <v>87</v>
@@ -37967,7 +38073,7 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B139">
         <v>87</v>
@@ -38002,7 +38108,7 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B140">
         <v>87</v>
@@ -38037,7 +38143,7 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B141">
         <v>87</v>
@@ -38072,7 +38178,7 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B142">
         <v>87</v>
@@ -38107,7 +38213,7 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B143">
         <v>87</v>
@@ -38142,7 +38248,7 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B144">
         <v>87</v>
@@ -38177,7 +38283,7 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B145">
         <v>87</v>
@@ -38212,7 +38318,7 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B146">
         <v>87</v>
@@ -38247,7 +38353,7 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B147">
         <v>87</v>
@@ -38282,7 +38388,7 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B148">
         <v>87</v>
@@ -38317,7 +38423,7 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B149">
         <v>87</v>
@@ -38352,7 +38458,7 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B150">
         <v>87</v>
@@ -38387,7 +38493,7 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B151">
         <v>87</v>
@@ -38422,7 +38528,7 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B152">
         <v>87</v>
@@ -38457,7 +38563,7 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B153">
         <v>87</v>
@@ -38492,7 +38598,7 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B154">
         <v>87</v>
@@ -38527,7 +38633,7 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B155">
         <v>87</v>
@@ -38562,7 +38668,7 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B156">
         <v>87</v>
@@ -38597,7 +38703,7 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B157">
         <v>87</v>
@@ -38632,7 +38738,7 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B158">
         <v>87</v>
@@ -38667,7 +38773,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B159">
         <v>87</v>
@@ -38702,7 +38808,7 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B160">
         <v>87</v>
@@ -38737,7 +38843,7 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B161">
         <v>87</v>
@@ -38772,7 +38878,7 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B162">
         <v>87</v>
@@ -38807,7 +38913,7 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B163">
         <v>87</v>
@@ -38842,7 +38948,7 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B164">
         <v>87</v>
@@ -38877,7 +38983,7 @@
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B165">
         <v>87</v>
@@ -38912,7 +39018,7 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B166">
         <v>86</v>
@@ -38947,7 +39053,7 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B167">
         <v>86</v>
@@ -38982,7 +39088,7 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B168">
         <v>86</v>
@@ -39017,7 +39123,7 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B169">
         <v>86</v>
@@ -39052,7 +39158,7 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B170">
         <v>86</v>
@@ -39087,7 +39193,7 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B171">
         <v>86</v>
@@ -39122,7 +39228,7 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B172">
         <v>86</v>
@@ -39157,7 +39263,7 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B173">
         <v>86</v>
@@ -39192,7 +39298,7 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B174">
         <v>86</v>
@@ -39227,7 +39333,7 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B175">
         <v>86</v>
@@ -39262,7 +39368,7 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B176">
         <v>86</v>
@@ -39297,7 +39403,7 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B177">
         <v>86</v>
@@ -39332,7 +39438,7 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B178">
         <v>86</v>
@@ -39367,7 +39473,7 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B179">
         <v>86</v>
@@ -39402,7 +39508,7 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B180">
         <v>86</v>
@@ -39437,7 +39543,7 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B181">
         <v>86</v>
@@ -39472,7 +39578,7 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B182">
         <v>86</v>
@@ -39507,7 +39613,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B183">
         <v>86</v>
@@ -39542,7 +39648,7 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B184">
         <v>86</v>
@@ -39577,7 +39683,7 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B185">
         <v>86</v>
@@ -39612,7 +39718,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B186">
         <v>86</v>
@@ -39647,7 +39753,7 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B187">
         <v>86</v>
@@ -39682,7 +39788,7 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B188">
         <v>86</v>
@@ -39717,7 +39823,7 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B189">
         <v>86</v>
@@ -39752,7 +39858,7 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B190">
         <v>86</v>
@@ -39787,7 +39893,7 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B191">
         <v>86</v>
@@ -39822,7 +39928,7 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B192">
         <v>86</v>
@@ -39857,7 +39963,7 @@
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B193">
         <v>86</v>
@@ -39892,7 +39998,7 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B194">
         <v>86</v>
@@ -39927,7 +40033,7 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B195">
         <v>86</v>
@@ -39962,7 +40068,7 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B196">
         <v>86</v>
@@ -39997,7 +40103,7 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B197">
         <v>86</v>
@@ -40032,7 +40138,7 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B198">
         <v>86</v>
@@ -40067,7 +40173,7 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B199">
         <v>86</v>
@@ -40102,7 +40208,7 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B200">
         <v>86</v>
@@ -40137,7 +40243,7 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B201">
         <v>86</v>
@@ -40172,7 +40278,7 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B202">
         <v>86</v>
@@ -40207,7 +40313,7 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B203">
         <v>86</v>
@@ -40242,7 +40348,7 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B204">
         <v>86</v>
@@ -40277,7 +40383,7 @@
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B205">
         <v>85</v>
@@ -40312,7 +40418,7 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B206">
         <v>85</v>
@@ -40347,7 +40453,7 @@
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B207">
         <v>85</v>
@@ -40382,7 +40488,7 @@
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B208">
         <v>85</v>
@@ -40417,7 +40523,7 @@
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B209">
         <v>85</v>
@@ -40452,7 +40558,7 @@
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B210">
         <v>85</v>
@@ -40487,7 +40593,7 @@
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B211">
         <v>85</v>
@@ -40522,7 +40628,7 @@
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B212">
         <v>85</v>
@@ -40557,7 +40663,7 @@
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B213">
         <v>85</v>
@@ -40592,7 +40698,7 @@
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B214">
         <v>85</v>
@@ -40627,7 +40733,7 @@
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B215">
         <v>85</v>
@@ -40662,7 +40768,7 @@
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B216">
         <v>85</v>
@@ -40697,7 +40803,7 @@
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B217">
         <v>85</v>
@@ -40732,7 +40838,7 @@
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B218">
         <v>85</v>
@@ -40767,7 +40873,7 @@
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B219">
         <v>85</v>
@@ -40802,7 +40908,7 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B220">
         <v>85</v>
@@ -40837,7 +40943,7 @@
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B221">
         <v>85</v>
@@ -40872,7 +40978,7 @@
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B222">
         <v>85</v>
@@ -40907,7 +41013,7 @@
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B223">
         <v>85</v>
@@ -40942,7 +41048,7 @@
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B224">
         <v>85</v>
@@ -40977,7 +41083,7 @@
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B225">
         <v>85</v>
@@ -41012,7 +41118,7 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B226">
         <v>85</v>
@@ -41047,7 +41153,7 @@
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B227">
         <v>85</v>
@@ -41082,7 +41188,7 @@
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B228">
         <v>85</v>
@@ -41117,7 +41223,7 @@
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B229">
         <v>85</v>
@@ -41152,7 +41258,7 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B230">
         <v>85</v>
@@ -41187,7 +41293,7 @@
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B231">
         <v>85</v>
@@ -41222,7 +41328,7 @@
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B232">
         <v>85</v>
@@ -41257,7 +41363,7 @@
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B233">
         <v>85</v>
@@ -41292,7 +41398,7 @@
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B234">
         <v>84</v>
@@ -41327,7 +41433,7 @@
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B235">
         <v>84</v>
@@ -41362,7 +41468,7 @@
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B236">
         <v>84</v>
@@ -41397,7 +41503,7 @@
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B237">
         <v>84</v>
@@ -41432,7 +41538,7 @@
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B238">
         <v>84</v>
@@ -41467,7 +41573,7 @@
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B239">
         <v>84</v>
@@ -41502,7 +41608,7 @@
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B240">
         <v>84</v>
@@ -41537,7 +41643,7 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B241">
         <v>84</v>
@@ -41572,7 +41678,7 @@
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B242">
         <v>84</v>
@@ -41607,7 +41713,7 @@
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B243">
         <v>84</v>
@@ -41642,7 +41748,7 @@
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B244">
         <v>84</v>
@@ -41677,7 +41783,7 @@
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B245">
         <v>84</v>
@@ -41712,7 +41818,7 @@
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B246">
         <v>84</v>
@@ -41747,7 +41853,7 @@
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B247">
         <v>84</v>
@@ -41782,7 +41888,7 @@
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B248">
         <v>84</v>
@@ -41817,7 +41923,7 @@
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B249">
         <v>84</v>
@@ -41852,7 +41958,7 @@
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B250">
         <v>84</v>
@@ -41887,7 +41993,7 @@
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B251">
         <v>84</v>
@@ -41922,7 +42028,7 @@
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B252">
         <v>84</v>
@@ -41957,7 +42063,7 @@
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B253">
         <v>84</v>
@@ -41992,7 +42098,7 @@
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B254">
         <v>84</v>
@@ -42027,7 +42133,7 @@
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B255">
         <v>84</v>
@@ -42062,7 +42168,7 @@
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B256">
         <v>84</v>
@@ -42097,7 +42203,7 @@
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B257">
         <v>84</v>
@@ -42132,7 +42238,7 @@
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B258">
         <v>84</v>
@@ -42167,7 +42273,7 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B259">
         <v>84</v>
@@ -42202,7 +42308,7 @@
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B260">
         <v>84</v>
@@ -42237,7 +42343,7 @@
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B261">
         <v>84</v>
@@ -42272,7 +42378,7 @@
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B262">
         <v>84</v>
@@ -42307,7 +42413,7 @@
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B263">
         <v>84</v>
@@ -42342,7 +42448,7 @@
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B264">
         <v>84</v>
@@ -42377,7 +42483,7 @@
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B265">
         <v>84</v>
@@ -42412,7 +42518,7 @@
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B266">
         <v>84</v>
@@ -42447,7 +42553,7 @@
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B267">
         <v>84</v>
@@ -42482,7 +42588,7 @@
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B268">
         <v>83</v>
@@ -42517,7 +42623,7 @@
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B269">
         <v>83</v>
@@ -42552,7 +42658,7 @@
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B270">
         <v>83</v>
@@ -42587,7 +42693,7 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B271">
         <v>83</v>
@@ -42622,7 +42728,7 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B272">
         <v>83</v>
@@ -42657,7 +42763,7 @@
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B273">
         <v>83</v>
@@ -42692,7 +42798,7 @@
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B274">
         <v>83</v>
@@ -42727,7 +42833,7 @@
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B275">
         <v>83</v>
@@ -42762,7 +42868,7 @@
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B276">
         <v>83</v>
@@ -42797,7 +42903,7 @@
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B277">
         <v>83</v>
@@ -42832,7 +42938,7 @@
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B278">
         <v>83</v>
@@ -42867,7 +42973,7 @@
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B279">
         <v>83</v>
@@ -42902,7 +43008,7 @@
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B280">
         <v>83</v>
@@ -42937,7 +43043,7 @@
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B281">
         <v>83</v>
@@ -42972,7 +43078,7 @@
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B282">
         <v>83</v>
@@ -43007,7 +43113,7 @@
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B283">
         <v>83</v>
@@ -43042,7 +43148,7 @@
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B284">
         <v>83</v>
@@ -43077,7 +43183,7 @@
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B285">
         <v>83</v>
@@ -43112,7 +43218,7 @@
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B286">
         <v>83</v>
@@ -43147,7 +43253,7 @@
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B287">
         <v>83</v>
@@ -43182,7 +43288,7 @@
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B288">
         <v>83</v>
@@ -43217,7 +43323,7 @@
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B289">
         <v>83</v>
@@ -43252,7 +43358,7 @@
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B290">
         <v>83</v>
@@ -43287,7 +43393,7 @@
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B291">
         <v>83</v>
@@ -43322,7 +43428,7 @@
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B292">
         <v>83</v>
@@ -43357,7 +43463,7 @@
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B293">
         <v>83</v>
@@ -43392,7 +43498,7 @@
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B294">
         <v>83</v>
@@ -43427,7 +43533,7 @@
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B295">
         <v>83</v>
@@ -43462,7 +43568,7 @@
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B296">
         <v>83</v>
@@ -43497,7 +43603,7 @@
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B297">
         <v>83</v>
@@ -43532,7 +43638,7 @@
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B298">
         <v>83</v>
@@ -43567,7 +43673,7 @@
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B299">
         <v>82</v>
@@ -43602,7 +43708,7 @@
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B300">
         <v>82</v>
@@ -43637,7 +43743,7 @@
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B301">
         <v>82</v>
@@ -43672,7 +43778,7 @@
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B302">
         <v>82</v>
@@ -43707,7 +43813,7 @@
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B303">
         <v>82</v>
@@ -43742,7 +43848,7 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B304">
         <v>82</v>
@@ -43777,7 +43883,7 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B305">
         <v>82</v>
@@ -43812,7 +43918,7 @@
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B306">
         <v>82</v>
@@ -43847,7 +43953,7 @@
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B307">
         <v>82</v>
@@ -43882,7 +43988,7 @@
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B308">
         <v>82</v>
@@ -43917,7 +44023,7 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B309">
         <v>82</v>
@@ -43952,7 +44058,7 @@
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B310">
         <v>82</v>
@@ -43987,7 +44093,7 @@
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B311">
         <v>82</v>
@@ -44022,7 +44128,7 @@
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B312">
         <v>82</v>
@@ -44057,7 +44163,7 @@
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B313">
         <v>82</v>
@@ -44092,7 +44198,7 @@
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B314">
         <v>82</v>
@@ -44127,7 +44233,7 @@
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B315">
         <v>81</v>
@@ -44162,7 +44268,7 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B316">
         <v>81</v>
@@ -44197,7 +44303,7 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B317">
         <v>81</v>
@@ -44232,7 +44338,7 @@
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B318">
         <v>81</v>
@@ -44267,7 +44373,7 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B319">
         <v>81</v>
@@ -44302,7 +44408,7 @@
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B320">
         <v>81</v>
@@ -44337,7 +44443,7 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B321">
         <v>81</v>
@@ -44372,7 +44478,7 @@
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B322">
         <v>81</v>
@@ -44407,7 +44513,7 @@
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B323">
         <v>81</v>
@@ -44442,7 +44548,7 @@
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B324">
         <v>81</v>
@@ -44477,7 +44583,7 @@
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B325">
         <v>81</v>
@@ -44512,7 +44618,7 @@
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B326">
         <v>81</v>
@@ -44547,7 +44653,7 @@
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B327">
         <v>81</v>
@@ -44582,7 +44688,7 @@
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B328">
         <v>81</v>
@@ -44617,7 +44723,7 @@
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B329">
         <v>81</v>
@@ -44652,7 +44758,7 @@
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B330">
         <v>81</v>
@@ -44687,7 +44793,7 @@
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B331">
         <v>81</v>
@@ -44722,7 +44828,7 @@
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B332">
         <v>81</v>
@@ -44757,7 +44863,7 @@
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B333">
         <v>81</v>
@@ -44792,7 +44898,7 @@
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B334">
         <v>81</v>
@@ -44827,7 +44933,7 @@
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B335">
         <v>81</v>
@@ -44862,7 +44968,7 @@
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B336">
         <v>81</v>
@@ -44897,7 +45003,7 @@
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B337">
         <v>81</v>
@@ -44932,7 +45038,7 @@
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B338">
         <v>81</v>
@@ -44967,7 +45073,7 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B339">
         <v>81</v>
@@ -45002,7 +45108,7 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B340">
         <v>81</v>
@@ -45037,7 +45143,7 @@
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B341">
         <v>81</v>
@@ -45072,77 +45178,77 @@
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B342">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C342" t="s">
-        <v>934</v>
+        <v>3311</v>
       </c>
       <c r="D342" t="s">
-        <v>1039</v>
+        <v>1048</v>
       </c>
       <c r="E342" t="s">
-        <v>1040</v>
+        <v>3312</v>
       </c>
       <c r="F342" t="s">
-        <v>1042</v>
+        <v>3298</v>
       </c>
       <c r="G342" t="s">
-        <v>1043</v>
+        <v>3314</v>
       </c>
       <c r="H342" t="s">
-        <v>1045</v>
+        <v>3316</v>
       </c>
       <c r="I342" t="s">
-        <v>1046</v>
+        <v>79</v>
       </c>
       <c r="J342" t="s">
-        <v>1047</v>
+        <v>79</v>
       </c>
       <c r="K342" t="s">
-        <v>1041</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B343">
         <v>80</v>
       </c>
       <c r="C343" t="s">
-        <v>1884</v>
+        <v>934</v>
       </c>
       <c r="D343" t="s">
-        <v>1947</v>
+        <v>1039</v>
       </c>
       <c r="E343" t="s">
-        <v>1948</v>
+        <v>1040</v>
       </c>
       <c r="F343" t="s">
-        <v>1950</v>
+        <v>1042</v>
       </c>
       <c r="G343" t="s">
-        <v>1034</v>
+        <v>1043</v>
       </c>
       <c r="H343" t="s">
-        <v>1952</v>
+        <v>1045</v>
       </c>
       <c r="I343" t="s">
-        <v>1953</v>
+        <v>1046</v>
       </c>
       <c r="J343" t="s">
-        <v>1954</v>
+        <v>1047</v>
       </c>
       <c r="K343" t="s">
-        <v>1949</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B344">
         <v>80</v>
@@ -45151,68 +45257,68 @@
         <v>1884</v>
       </c>
       <c r="D344" t="s">
-        <v>1970</v>
+        <v>1947</v>
       </c>
       <c r="E344" t="s">
-        <v>1971</v>
+        <v>1948</v>
       </c>
       <c r="F344" t="s">
-        <v>1973</v>
+        <v>1950</v>
       </c>
       <c r="G344" t="s">
-        <v>1974</v>
+        <v>1034</v>
       </c>
       <c r="H344" t="s">
-        <v>1976</v>
+        <v>1952</v>
       </c>
       <c r="I344" t="s">
-        <v>1977</v>
+        <v>1953</v>
       </c>
       <c r="J344" t="s">
-        <v>1978</v>
+        <v>1954</v>
       </c>
       <c r="K344" t="s">
-        <v>1972</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B345">
         <v>80</v>
       </c>
       <c r="C345" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D345" t="s">
-        <v>2107</v>
+        <v>1970</v>
       </c>
       <c r="E345" t="s">
-        <v>830</v>
+        <v>1971</v>
       </c>
       <c r="F345" t="s">
-        <v>66</v>
+        <v>1973</v>
       </c>
       <c r="G345" t="s">
-        <v>2109</v>
+        <v>1974</v>
       </c>
       <c r="H345" t="s">
-        <v>2111</v>
+        <v>1976</v>
       </c>
       <c r="I345" t="s">
-        <v>2112</v>
+        <v>1977</v>
       </c>
       <c r="J345" t="s">
-        <v>2113</v>
+        <v>1978</v>
       </c>
       <c r="K345" t="s">
-        <v>2108</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B346">
         <v>80</v>
@@ -45221,33 +45327,33 @@
         <v>2098</v>
       </c>
       <c r="D346" t="s">
-        <v>2133</v>
+        <v>2107</v>
       </c>
       <c r="E346" t="s">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="F346" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G346" t="s">
-        <v>2135</v>
+        <v>2109</v>
       </c>
       <c r="H346" t="s">
-        <v>2137</v>
+        <v>2111</v>
       </c>
       <c r="I346" t="s">
-        <v>2138</v>
+        <v>2112</v>
       </c>
       <c r="J346" t="s">
-        <v>2139</v>
+        <v>2113</v>
       </c>
       <c r="K346" t="s">
-        <v>2134</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B347">
         <v>80</v>
@@ -45256,33 +45362,33 @@
         <v>2098</v>
       </c>
       <c r="D347" t="s">
-        <v>2140</v>
+        <v>2133</v>
       </c>
       <c r="E347" t="s">
-        <v>2141</v>
+        <v>110</v>
       </c>
       <c r="F347" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G347" t="s">
-        <v>2143</v>
+        <v>2135</v>
       </c>
       <c r="H347" t="s">
-        <v>2145</v>
+        <v>2137</v>
       </c>
       <c r="I347" t="s">
-        <v>2146</v>
+        <v>2138</v>
       </c>
       <c r="J347" t="s">
-        <v>2147</v>
+        <v>2139</v>
       </c>
       <c r="K347" t="s">
-        <v>2142</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B348">
         <v>80</v>
@@ -45291,33 +45397,33 @@
         <v>2098</v>
       </c>
       <c r="D348" t="s">
-        <v>2155</v>
+        <v>2140</v>
       </c>
       <c r="E348" t="s">
-        <v>110</v>
+        <v>2141</v>
       </c>
       <c r="F348" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G348" t="s">
-        <v>2157</v>
+        <v>2143</v>
       </c>
       <c r="H348" t="s">
-        <v>2159</v>
+        <v>2145</v>
       </c>
       <c r="I348" t="s">
-        <v>2160</v>
+        <v>2146</v>
       </c>
       <c r="J348" t="s">
-        <v>2161</v>
+        <v>2147</v>
       </c>
       <c r="K348" t="s">
-        <v>2156</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B349">
         <v>80</v>
@@ -45326,33 +45432,33 @@
         <v>2098</v>
       </c>
       <c r="D349" t="s">
-        <v>2162</v>
+        <v>2155</v>
       </c>
       <c r="E349" t="s">
         <v>110</v>
       </c>
       <c r="F349" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G349" t="s">
-        <v>2171</v>
+        <v>2157</v>
       </c>
       <c r="H349" t="s">
-        <v>2173</v>
+        <v>2159</v>
       </c>
       <c r="I349" t="s">
-        <v>2174</v>
+        <v>2160</v>
       </c>
       <c r="J349" t="s">
-        <v>2175</v>
+        <v>2161</v>
       </c>
       <c r="K349" t="s">
-        <v>2170</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B350">
         <v>80</v>
@@ -45361,33 +45467,33 @@
         <v>2098</v>
       </c>
       <c r="D350" t="s">
-        <v>2203</v>
+        <v>2162</v>
       </c>
       <c r="E350" t="s">
-        <v>2204</v>
+        <v>110</v>
       </c>
       <c r="F350" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="G350" t="s">
-        <v>2206</v>
+        <v>2171</v>
       </c>
       <c r="H350" t="s">
-        <v>2208</v>
+        <v>2173</v>
       </c>
       <c r="I350" t="s">
-        <v>2209</v>
+        <v>2174</v>
       </c>
       <c r="J350" t="s">
-        <v>2210</v>
+        <v>2175</v>
       </c>
       <c r="K350" t="s">
-        <v>2205</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B351">
         <v>80</v>
@@ -45396,103 +45502,103 @@
         <v>2098</v>
       </c>
       <c r="D351" t="s">
-        <v>2225</v>
+        <v>2203</v>
       </c>
       <c r="E351" t="s">
-        <v>2226</v>
+        <v>2204</v>
       </c>
       <c r="F351" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G351" t="s">
-        <v>112</v>
+        <v>2206</v>
       </c>
       <c r="H351" t="s">
-        <v>2229</v>
+        <v>2208</v>
       </c>
       <c r="I351" t="s">
-        <v>2230</v>
+        <v>2209</v>
       </c>
       <c r="J351" t="s">
-        <v>2231</v>
+        <v>2210</v>
       </c>
       <c r="K351" t="s">
-        <v>2227</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B352">
         <v>80</v>
       </c>
       <c r="C352" t="s">
-        <v>2258</v>
+        <v>2098</v>
       </c>
       <c r="D352" t="s">
-        <v>2292</v>
+        <v>2225</v>
       </c>
       <c r="E352" t="s">
-        <v>2293</v>
+        <v>2226</v>
       </c>
       <c r="F352" t="s">
-        <v>747</v>
+        <v>16</v>
       </c>
       <c r="G352" t="s">
-        <v>2295</v>
+        <v>112</v>
       </c>
       <c r="H352" t="s">
-        <v>2297</v>
+        <v>2229</v>
       </c>
       <c r="I352" t="s">
-        <v>2298</v>
+        <v>2230</v>
       </c>
       <c r="J352" t="s">
-        <v>2299</v>
+        <v>2231</v>
       </c>
       <c r="K352" t="s">
-        <v>2294</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B353">
         <v>80</v>
       </c>
       <c r="C353" t="s">
-        <v>2377</v>
+        <v>2258</v>
       </c>
       <c r="D353" t="s">
-        <v>2392</v>
+        <v>2292</v>
       </c>
       <c r="E353" t="s">
-        <v>2393</v>
+        <v>2293</v>
       </c>
       <c r="F353" t="s">
-        <v>66</v>
+        <v>747</v>
       </c>
       <c r="G353" t="s">
-        <v>2395</v>
+        <v>2295</v>
       </c>
       <c r="H353" t="s">
-        <v>2397</v>
+        <v>2297</v>
       </c>
       <c r="I353" t="s">
-        <v>2398</v>
+        <v>2298</v>
       </c>
       <c r="J353" t="s">
-        <v>2399</v>
+        <v>2299</v>
       </c>
       <c r="K353" t="s">
-        <v>2394</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B354">
         <v>80</v>
@@ -45501,63 +45607,133 @@
         <v>2377</v>
       </c>
       <c r="D354" t="s">
-        <v>2414</v>
+        <v>2392</v>
       </c>
       <c r="E354" t="s">
-        <v>2415</v>
+        <v>2393</v>
       </c>
       <c r="F354" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="G354" t="s">
-        <v>2417</v>
+        <v>2395</v>
       </c>
       <c r="H354" t="s">
-        <v>2419</v>
+        <v>2397</v>
       </c>
       <c r="I354" t="s">
-        <v>2420</v>
+        <v>2398</v>
       </c>
       <c r="J354" t="s">
-        <v>2421</v>
+        <v>2399</v>
       </c>
       <c r="K354" t="s">
-        <v>2416</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="B355">
         <v>80</v>
       </c>
       <c r="C355" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D355" t="s">
+        <v>2414</v>
+      </c>
+      <c r="E355" t="s">
+        <v>2415</v>
+      </c>
+      <c r="F355" t="s">
+        <v>124</v>
+      </c>
+      <c r="G355" t="s">
+        <v>2417</v>
+      </c>
+      <c r="H355" t="s">
+        <v>2419</v>
+      </c>
+      <c r="I355" t="s">
+        <v>2420</v>
+      </c>
+      <c r="J355" t="s">
+        <v>2421</v>
+      </c>
+      <c r="K355" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>3332</v>
+      </c>
+      <c r="B356">
+        <v>80</v>
+      </c>
+      <c r="C356" t="s">
         <v>2760</v>
       </c>
-      <c r="D355" t="s">
+      <c r="D356" t="s">
         <v>1681</v>
       </c>
-      <c r="E355" t="s">
+      <c r="E356" t="s">
         <v>2864</v>
       </c>
-      <c r="F355" t="s">
+      <c r="F356" t="s">
         <v>1684</v>
       </c>
-      <c r="G355" t="s">
+      <c r="G356" t="s">
         <v>2866</v>
       </c>
-      <c r="H355" t="s">
+      <c r="H356" t="s">
         <v>2868</v>
       </c>
-      <c r="I355" t="s">
+      <c r="I356" t="s">
         <v>2869</v>
       </c>
-      <c r="J355" t="s">
+      <c r="J356" t="s">
         <v>2870</v>
       </c>
-      <c r="K355" t="s">
+      <c r="K356" t="s">
         <v>2865</v>
+      </c>
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>3332</v>
+      </c>
+      <c r="B357">
+        <v>80</v>
+      </c>
+      <c r="C357" t="s">
+        <v>3311</v>
+      </c>
+      <c r="D357" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E357" t="s">
+        <v>3317</v>
+      </c>
+      <c r="F357" t="s">
+        <v>3298</v>
+      </c>
+      <c r="G357" t="s">
+        <v>3314</v>
+      </c>
+      <c r="H357" t="s">
+        <v>3320</v>
+      </c>
+      <c r="I357" t="s">
+        <v>79</v>
+      </c>
+      <c r="J357" t="s">
+        <v>79</v>
+      </c>
+      <c r="K357" t="s">
+        <v>3318</v>
       </c>
     </row>
   </sheetData>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9782" uniqueCount="3517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9802" uniqueCount="3526">
   <si>
     <t>日期</t>
   </si>
@@ -10445,6 +10445,33 @@
   </si>
   <si>
     <t>研究80/技能80/学历50/行业100/企业86</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>项目管理工程师（研发管理部）</t>
+  </si>
+  <si>
+    <t>隶属于研发管理部，负责研发项目的计划、进度与资源协调管理，跟进医疗器械（含心血管介入、可吸收支架方向）产品开发流程；要求本科及以上学历，理工科/材料/生物医学工程背景，具备项目管理意识与沟通协调能力，熟悉医疗器械产品开发流程者优先。</t>
+  </si>
+  <si>
+    <t>智能匹配77分【社招】|值得考虑|先健为铁基可吸收支架领军上市企业，研发管理岗可发挥支架研发背景的项目协调能力，方向属医疗器械泛匹配</t>
+  </si>
+  <si>
+    <t>研究72/技能62/学历90/行业100/企业100</t>
+  </si>
+  <si>
+    <t>临床项目经理（营销系统）</t>
+  </si>
+  <si>
+    <t>负责心血管介入/植入类产品临床研究项目的策划与实施管理，对接临床中心与医生，推进临床试验方案落地；要求本科及以上学历，医学、生物医学工程或相关专业，有医疗器械临床试验或项目管理经验者优先。</t>
+  </si>
+  <si>
+    <t>智能匹配73分【社招】|值得考虑|先健介入器械临床项目岗，与心血管介入方向相关，但偏临床注册管理，技能重合度一般</t>
+  </si>
+  <si>
+    <t>研究68/技能55/学历85/行业100/企业100</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -10999,7 +11026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L474"/>
+  <dimension ref="A1:L476"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -29024,6 +29051,82 @@
         <v>79</v>
       </c>
       <c r="L474" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>3477</v>
+      </c>
+      <c r="B475" t="s">
+        <v>207</v>
+      </c>
+      <c r="C475" t="s">
+        <v>3478</v>
+      </c>
+      <c r="D475" t="s">
+        <v>3479</v>
+      </c>
+      <c r="E475" t="s">
+        <v>66</v>
+      </c>
+      <c r="F475" t="s">
+        <v>438</v>
+      </c>
+      <c r="G475">
+        <v>8</v>
+      </c>
+      <c r="H475" t="s">
+        <v>3480</v>
+      </c>
+      <c r="I475">
+        <v>77</v>
+      </c>
+      <c r="J475" t="s">
+        <v>3481</v>
+      </c>
+      <c r="K475" t="s">
+        <v>79</v>
+      </c>
+      <c r="L475" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>3477</v>
+      </c>
+      <c r="B476" t="s">
+        <v>207</v>
+      </c>
+      <c r="C476" t="s">
+        <v>3482</v>
+      </c>
+      <c r="D476" t="s">
+        <v>3483</v>
+      </c>
+      <c r="E476" t="s">
+        <v>66</v>
+      </c>
+      <c r="F476" t="s">
+        <v>438</v>
+      </c>
+      <c r="G476">
+        <v>7</v>
+      </c>
+      <c r="H476" t="s">
+        <v>3484</v>
+      </c>
+      <c r="I476">
+        <v>73</v>
+      </c>
+      <c r="J476" t="s">
+        <v>3485</v>
+      </c>
+      <c r="K476" t="s">
+        <v>79</v>
+      </c>
+      <c r="L476" t="s">
         <v>79</v>
       </c>
     </row>
@@ -29058,7 +29161,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3477</v>
+        <v>3486</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -29067,16 +29170,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3478</v>
+        <v>3487</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3479</v>
+        <v>3488</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3480</v>
+        <v>3489</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3481</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -29090,13 +29193,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3482</v>
+        <v>3491</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>3483</v>
+        <v>3492</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>3484</v>
+        <v>3493</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -29139,7 +29242,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>3489</v>
+        <v>3498</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -29149,31 +29252,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>3490</v>
+        <v>3499</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>3491</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3492</v>
+        <v>3501</v>
       </c>
       <c r="B4">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3493</v>
+        <v>3502</v>
       </c>
       <c r="B5" t="s">
-        <v>3494</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3495</v>
+        <v>3504</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -29181,7 +29284,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3496</v>
+        <v>3505</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -29189,7 +29292,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3497</v>
+        <v>3506</v>
       </c>
       <c r="B8">
         <v>245</v>
@@ -29197,31 +29300,31 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3498</v>
+        <v>3507</v>
       </c>
       <c r="B9">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3499</v>
+        <v>3508</v>
       </c>
       <c r="B10">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3500</v>
+        <v>3509</v>
       </c>
       <c r="B11" t="s">
-        <v>3460</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>3501</v>
+        <v>3510</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -29231,15 +29334,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>3502</v>
+        <v>3511</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>3503</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3504</v>
+        <v>3513</v>
       </c>
       <c r="B16" s="5">
         <v>9</v>
@@ -29247,7 +29350,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3505</v>
+        <v>3514</v>
       </c>
       <c r="B17" s="5">
         <v>236</v>
@@ -29255,23 +29358,23 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3506</v>
+        <v>3515</v>
       </c>
       <c r="B18" s="5">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3507</v>
+        <v>3516</v>
       </c>
       <c r="B19" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3508</v>
+        <v>3517</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -29279,7 +29382,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3509</v>
+        <v>3518</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -29287,7 +29390,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3510</v>
+        <v>3519</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -29295,7 +29398,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3511</v>
+        <v>3520</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -29303,7 +29406,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3512</v>
+        <v>3521</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -29311,7 +29414,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3513</v>
+        <v>3522</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -29319,7 +29422,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>3514</v>
+        <v>3523</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -29331,7 +29434,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>3515</v>
+        <v>3524</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -29349,7 +29452,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>3516</v>
+        <v>3525</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -34585,10 +34688,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>3485</v>
+        <v>3494</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>3486</v>
+        <v>3495</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -34615,12 +34718,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>3487</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -34655,7 +34758,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -34690,7 +34793,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -34725,7 +34828,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -34760,7 +34863,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -34795,7 +34898,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -34830,7 +34933,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B8">
         <v>95</v>
@@ -34865,7 +34968,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B9">
         <v>95</v>
@@ -34900,7 +35003,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B10">
         <v>95</v>
@@ -34935,7 +35038,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B11">
         <v>94</v>
@@ -34970,7 +35073,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B12">
         <v>94</v>
@@ -35005,7 +35108,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B13">
         <v>94</v>
@@ -35040,7 +35143,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B14">
         <v>93</v>
@@ -35075,7 +35178,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B15">
         <v>93</v>
@@ -35110,7 +35213,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B16">
         <v>93</v>
@@ -35145,7 +35248,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B17">
         <v>93</v>
@@ -35180,7 +35283,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B18">
         <v>93</v>
@@ -35215,7 +35318,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B19">
         <v>93</v>
@@ -35250,7 +35353,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B20">
         <v>93</v>
@@ -35285,7 +35388,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B21">
         <v>93</v>
@@ -35320,7 +35423,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B22">
         <v>93</v>
@@ -35355,7 +35458,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B23">
         <v>92</v>
@@ -35390,7 +35493,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B24">
         <v>92</v>
@@ -35425,7 +35528,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B25">
         <v>92</v>
@@ -35460,7 +35563,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B26">
         <v>92</v>
@@ -35495,7 +35598,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B27">
         <v>92</v>
@@ -35530,7 +35633,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B28">
         <v>92</v>
@@ -35565,7 +35668,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B29">
         <v>92</v>
@@ -35600,7 +35703,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B30">
         <v>92</v>
@@ -35635,7 +35738,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B31">
         <v>92</v>
@@ -35670,7 +35773,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B32">
         <v>92</v>
@@ -35705,7 +35808,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B33">
         <v>92</v>
@@ -35740,7 +35843,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B34">
         <v>91</v>
@@ -35775,7 +35878,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B35">
         <v>91</v>
@@ -35810,7 +35913,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B36">
         <v>91</v>
@@ -35845,7 +35948,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B37">
         <v>91</v>
@@ -35880,7 +35983,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B38">
         <v>91</v>
@@ -35915,7 +36018,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B39">
         <v>91</v>
@@ -35950,7 +36053,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B40">
         <v>91</v>
@@ -35985,7 +36088,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B41">
         <v>91</v>
@@ -36020,7 +36123,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B42">
         <v>91</v>
@@ -36055,7 +36158,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B43">
         <v>91</v>
@@ -36090,7 +36193,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B44">
         <v>91</v>
@@ -36125,7 +36228,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B45">
         <v>91</v>
@@ -36160,7 +36263,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B46">
         <v>91</v>
@@ -36195,7 +36298,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B47">
         <v>91</v>
@@ -36230,7 +36333,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B48">
         <v>91</v>
@@ -36265,7 +36368,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B49">
         <v>91</v>
@@ -36300,7 +36403,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B50">
         <v>91</v>
@@ -36335,7 +36438,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B51">
         <v>91</v>
@@ -36370,7 +36473,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B52">
         <v>90</v>
@@ -36405,7 +36508,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B53">
         <v>90</v>
@@ -36440,7 +36543,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B54">
         <v>90</v>
@@ -36475,7 +36578,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B55">
         <v>90</v>
@@ -36510,7 +36613,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B56">
         <v>90</v>
@@ -36545,7 +36648,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B57">
         <v>90</v>
@@ -36580,7 +36683,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B58">
         <v>90</v>
@@ -36615,7 +36718,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B59">
         <v>90</v>
@@ -36650,7 +36753,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B60">
         <v>90</v>
@@ -36685,7 +36788,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B61">
         <v>90</v>
@@ -36720,7 +36823,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B62">
         <v>90</v>
@@ -36755,7 +36858,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B63">
         <v>90</v>
@@ -36790,7 +36893,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B64">
         <v>90</v>
@@ -36825,7 +36928,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B65">
         <v>90</v>
@@ -36860,7 +36963,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B66">
         <v>90</v>
@@ -36895,7 +36998,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B67">
         <v>90</v>
@@ -36930,7 +37033,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B68">
         <v>90</v>
@@ -36965,7 +37068,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B69">
         <v>90</v>
@@ -37000,7 +37103,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B70">
         <v>90</v>
@@ -37035,7 +37138,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B71">
         <v>90</v>
@@ -37070,7 +37173,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B72">
         <v>90</v>
@@ -37105,7 +37208,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B73">
         <v>90</v>
@@ -37140,7 +37243,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B74">
         <v>90</v>
@@ -37175,7 +37278,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B75">
         <v>90</v>
@@ -37210,7 +37313,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B76">
         <v>89</v>
@@ -37245,7 +37348,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B77">
         <v>89</v>
@@ -37280,7 +37383,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B78">
         <v>89</v>
@@ -37315,7 +37418,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B79">
         <v>89</v>
@@ -37350,7 +37453,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B80">
         <v>89</v>
@@ -37385,7 +37488,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B81">
         <v>89</v>
@@ -37420,7 +37523,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B82">
         <v>89</v>
@@ -37455,7 +37558,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B83">
         <v>89</v>
@@ -37490,7 +37593,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B84">
         <v>89</v>
@@ -37525,7 +37628,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B85">
         <v>89</v>
@@ -37560,7 +37663,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B86">
         <v>89</v>
@@ -37595,7 +37698,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B87">
         <v>89</v>
@@ -37630,7 +37733,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B88">
         <v>89</v>
@@ -37665,7 +37768,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B89">
         <v>89</v>
@@ -37700,7 +37803,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B90">
         <v>89</v>
@@ -37735,7 +37838,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B91">
         <v>89</v>
@@ -37770,7 +37873,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B92">
         <v>89</v>
@@ -37805,7 +37908,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B93">
         <v>89</v>
@@ -37840,7 +37943,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B94">
         <v>89</v>
@@ -37875,7 +37978,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B95">
         <v>89</v>
@@ -37910,7 +38013,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B96">
         <v>89</v>
@@ -37945,7 +38048,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B97">
         <v>89</v>
@@ -37980,7 +38083,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B98">
         <v>89</v>
@@ -38015,7 +38118,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B99">
         <v>89</v>
@@ -38050,7 +38153,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B100">
         <v>89</v>
@@ -38085,7 +38188,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B101">
         <v>89</v>
@@ -38120,7 +38223,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B102">
         <v>89</v>
@@ -38155,7 +38258,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B103">
         <v>89</v>
@@ -38190,7 +38293,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B104">
         <v>89</v>
@@ -38225,7 +38328,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B105">
         <v>89</v>
@@ -38260,7 +38363,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B106">
         <v>89</v>
@@ -38295,7 +38398,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B107">
         <v>89</v>
@@ -38330,7 +38433,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B108">
         <v>89</v>
@@ -38365,7 +38468,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B109">
         <v>89</v>
@@ -38400,7 +38503,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B110">
         <v>89</v>
@@ -38435,7 +38538,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B111">
         <v>89</v>
@@ -38470,7 +38573,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B112">
         <v>88</v>
@@ -38505,7 +38608,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B113">
         <v>88</v>
@@ -38540,7 +38643,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B114">
         <v>88</v>
@@ -38575,7 +38678,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B115">
         <v>88</v>
@@ -38610,7 +38713,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B116">
         <v>88</v>
@@ -38645,7 +38748,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B117">
         <v>88</v>
@@ -38680,7 +38783,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B118">
         <v>88</v>
@@ -38715,7 +38818,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B119">
         <v>88</v>
@@ -38750,7 +38853,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B120">
         <v>88</v>
@@ -38785,7 +38888,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B121">
         <v>88</v>
@@ -38820,7 +38923,7 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B122">
         <v>88</v>
@@ -38855,7 +38958,7 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B123">
         <v>88</v>
@@ -38890,7 +38993,7 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B124">
         <v>88</v>
@@ -38925,7 +39028,7 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B125">
         <v>88</v>
@@ -38960,7 +39063,7 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B126">
         <v>88</v>
@@ -38995,7 +39098,7 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B127">
         <v>88</v>
@@ -39030,7 +39133,7 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B128">
         <v>88</v>
@@ -39065,7 +39168,7 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B129">
         <v>88</v>
@@ -39100,7 +39203,7 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B130">
         <v>88</v>
@@ -39135,7 +39238,7 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B131">
         <v>88</v>
@@ -39170,7 +39273,7 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B132">
         <v>88</v>
@@ -39205,7 +39308,7 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B133">
         <v>88</v>
@@ -39240,7 +39343,7 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B134">
         <v>88</v>
@@ -39275,7 +39378,7 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B135">
         <v>88</v>
@@ -39310,7 +39413,7 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B136">
         <v>88</v>
@@ -39345,7 +39448,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B137">
         <v>88</v>
@@ -39380,7 +39483,7 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B138">
         <v>88</v>
@@ -39415,7 +39518,7 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B139">
         <v>88</v>
@@ -39450,7 +39553,7 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B140">
         <v>88</v>
@@ -39485,7 +39588,7 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B141">
         <v>88</v>
@@ -39520,7 +39623,7 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B142">
         <v>88</v>
@@ -39555,7 +39658,7 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B143">
         <v>88</v>
@@ -39590,7 +39693,7 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B144">
         <v>88</v>
@@ -39625,7 +39728,7 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B145">
         <v>88</v>
@@ -39660,7 +39763,7 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B146">
         <v>88</v>
@@ -39695,7 +39798,7 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B147">
         <v>88</v>
@@ -39730,7 +39833,7 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B148">
         <v>87</v>
@@ -39765,7 +39868,7 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B149">
         <v>87</v>
@@ -39800,7 +39903,7 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B150">
         <v>87</v>
@@ -39835,7 +39938,7 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B151">
         <v>87</v>
@@ -39870,7 +39973,7 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B152">
         <v>87</v>
@@ -39905,7 +40008,7 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B153">
         <v>87</v>
@@ -39940,7 +40043,7 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B154">
         <v>87</v>
@@ -39975,7 +40078,7 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B155">
         <v>87</v>
@@ -40010,7 +40113,7 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B156">
         <v>87</v>
@@ -40045,7 +40148,7 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B157">
         <v>87</v>
@@ -40080,7 +40183,7 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B158">
         <v>87</v>
@@ -40115,7 +40218,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B159">
         <v>87</v>
@@ -40150,7 +40253,7 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B160">
         <v>87</v>
@@ -40185,7 +40288,7 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B161">
         <v>87</v>
@@ -40220,7 +40323,7 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B162">
         <v>87</v>
@@ -40255,7 +40358,7 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B163">
         <v>87</v>
@@ -40290,7 +40393,7 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B164">
         <v>87</v>
@@ -40325,7 +40428,7 @@
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B165">
         <v>87</v>
@@ -40360,7 +40463,7 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B166">
         <v>87</v>
@@ -40395,7 +40498,7 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B167">
         <v>87</v>
@@ -40430,7 +40533,7 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B168">
         <v>87</v>
@@ -40465,7 +40568,7 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B169">
         <v>87</v>
@@ -40500,7 +40603,7 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B170">
         <v>87</v>
@@ -40535,7 +40638,7 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B171">
         <v>87</v>
@@ -40570,7 +40673,7 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B172">
         <v>87</v>
@@ -40605,7 +40708,7 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B173">
         <v>87</v>
@@ -40640,7 +40743,7 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B174">
         <v>87</v>
@@ -40675,7 +40778,7 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B175">
         <v>87</v>
@@ -40710,7 +40813,7 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B176">
         <v>87</v>
@@ -40745,7 +40848,7 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B177">
         <v>86</v>
@@ -40780,7 +40883,7 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B178">
         <v>86</v>
@@ -40815,7 +40918,7 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B179">
         <v>86</v>
@@ -40850,7 +40953,7 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B180">
         <v>86</v>
@@ -40885,7 +40988,7 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B181">
         <v>86</v>
@@ -40920,7 +41023,7 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B182">
         <v>86</v>
@@ -40955,7 +41058,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B183">
         <v>86</v>
@@ -40990,7 +41093,7 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B184">
         <v>86</v>
@@ -41025,7 +41128,7 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B185">
         <v>86</v>
@@ -41060,7 +41163,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B186">
         <v>86</v>
@@ -41095,7 +41198,7 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B187">
         <v>86</v>
@@ -41130,7 +41233,7 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B188">
         <v>86</v>
@@ -41165,7 +41268,7 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B189">
         <v>86</v>
@@ -41200,7 +41303,7 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B190">
         <v>86</v>
@@ -41235,7 +41338,7 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B191">
         <v>86</v>
@@ -41270,7 +41373,7 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B192">
         <v>86</v>
@@ -41305,7 +41408,7 @@
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B193">
         <v>86</v>
@@ -41340,7 +41443,7 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B194">
         <v>86</v>
@@ -41375,7 +41478,7 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B195">
         <v>86</v>
@@ -41410,7 +41513,7 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B196">
         <v>86</v>
@@ -41445,7 +41548,7 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B197">
         <v>86</v>
@@ -41480,7 +41583,7 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B198">
         <v>86</v>
@@ -41515,7 +41618,7 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B199">
         <v>86</v>
@@ -41550,7 +41653,7 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B200">
         <v>86</v>
@@ -41585,7 +41688,7 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B201">
         <v>86</v>
@@ -41620,7 +41723,7 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B202">
         <v>86</v>
@@ -41655,7 +41758,7 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B203">
         <v>86</v>
@@ -41690,7 +41793,7 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B204">
         <v>86</v>
@@ -41725,7 +41828,7 @@
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B205">
         <v>86</v>
@@ -41760,7 +41863,7 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B206">
         <v>86</v>
@@ -41795,7 +41898,7 @@
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B207">
         <v>86</v>
@@ -41830,7 +41933,7 @@
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B208">
         <v>86</v>
@@ -41865,7 +41968,7 @@
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B209">
         <v>86</v>
@@ -41900,7 +42003,7 @@
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B210">
         <v>86</v>
@@ -41935,7 +42038,7 @@
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B211">
         <v>86</v>
@@ -41970,7 +42073,7 @@
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B212">
         <v>86</v>
@@ -42005,7 +42108,7 @@
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B213">
         <v>86</v>
@@ -42040,7 +42143,7 @@
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B214">
         <v>86</v>
@@ -42075,7 +42178,7 @@
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B215">
         <v>86</v>
@@ -42110,7 +42213,7 @@
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B216">
         <v>86</v>
@@ -42145,7 +42248,7 @@
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B217">
         <v>85</v>
@@ -42180,7 +42283,7 @@
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B218">
         <v>85</v>
@@ -42215,7 +42318,7 @@
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B219">
         <v>85</v>
@@ -42250,7 +42353,7 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B220">
         <v>85</v>
@@ -42285,7 +42388,7 @@
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B221">
         <v>85</v>
@@ -42320,7 +42423,7 @@
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B222">
         <v>85</v>
@@ -42355,7 +42458,7 @@
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B223">
         <v>85</v>
@@ -42390,7 +42493,7 @@
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B224">
         <v>85</v>
@@ -42425,7 +42528,7 @@
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B225">
         <v>85</v>
@@ -42460,7 +42563,7 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B226">
         <v>85</v>
@@ -42495,7 +42598,7 @@
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B227">
         <v>85</v>
@@ -42530,7 +42633,7 @@
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B228">
         <v>85</v>
@@ -42565,7 +42668,7 @@
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B229">
         <v>85</v>
@@ -42600,7 +42703,7 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B230">
         <v>85</v>
@@ -42635,7 +42738,7 @@
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B231">
         <v>85</v>
@@ -42670,7 +42773,7 @@
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B232">
         <v>85</v>
@@ -42705,7 +42808,7 @@
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B233">
         <v>85</v>
@@ -42740,7 +42843,7 @@
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B234">
         <v>85</v>
@@ -42775,7 +42878,7 @@
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B235">
         <v>85</v>
@@ -42810,7 +42913,7 @@
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B236">
         <v>85</v>
@@ -42845,7 +42948,7 @@
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B237">
         <v>85</v>
@@ -42880,7 +42983,7 @@
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B238">
         <v>85</v>
@@ -42915,7 +43018,7 @@
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B239">
         <v>85</v>
@@ -42950,7 +43053,7 @@
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B240">
         <v>85</v>
@@ -42985,7 +43088,7 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B241">
         <v>85</v>
@@ -43020,7 +43123,7 @@
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B242">
         <v>85</v>
@@ -43055,7 +43158,7 @@
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B243">
         <v>85</v>
@@ -43090,7 +43193,7 @@
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B244">
         <v>85</v>
@@ -43125,7 +43228,7 @@
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B245">
         <v>85</v>
@@ -43160,7 +43263,7 @@
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B246">
         <v>85</v>
@@ -43195,7 +43298,7 @@
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B247">
         <v>84</v>
@@ -43230,7 +43333,7 @@
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B248">
         <v>84</v>
@@ -43265,7 +43368,7 @@
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B249">
         <v>84</v>
@@ -43300,7 +43403,7 @@
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B250">
         <v>84</v>
@@ -43335,7 +43438,7 @@
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B251">
         <v>84</v>
@@ -43370,7 +43473,7 @@
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B252">
         <v>84</v>
@@ -43405,7 +43508,7 @@
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B253">
         <v>84</v>
@@ -43440,7 +43543,7 @@
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B254">
         <v>84</v>
@@ -43475,7 +43578,7 @@
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B255">
         <v>84</v>
@@ -43510,7 +43613,7 @@
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B256">
         <v>84</v>
@@ -43545,7 +43648,7 @@
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B257">
         <v>84</v>
@@ -43580,7 +43683,7 @@
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B258">
         <v>84</v>
@@ -43615,7 +43718,7 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B259">
         <v>84</v>
@@ -43650,7 +43753,7 @@
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B260">
         <v>84</v>
@@ -43685,7 +43788,7 @@
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B261">
         <v>84</v>
@@ -43720,7 +43823,7 @@
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B262">
         <v>84</v>
@@ -43755,7 +43858,7 @@
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B263">
         <v>84</v>
@@ -43790,7 +43893,7 @@
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B264">
         <v>84</v>
@@ -43825,7 +43928,7 @@
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B265">
         <v>84</v>
@@ -43860,7 +43963,7 @@
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B266">
         <v>84</v>
@@ -43895,7 +43998,7 @@
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B267">
         <v>84</v>
@@ -43930,7 +44033,7 @@
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B268">
         <v>84</v>
@@ -43965,7 +44068,7 @@
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B269">
         <v>84</v>
@@ -44000,7 +44103,7 @@
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B270">
         <v>84</v>
@@ -44035,7 +44138,7 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B271">
         <v>84</v>
@@ -44070,7 +44173,7 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B272">
         <v>84</v>
@@ -44105,7 +44208,7 @@
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B273">
         <v>84</v>
@@ -44140,7 +44243,7 @@
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B274">
         <v>84</v>
@@ -44175,7 +44278,7 @@
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B275">
         <v>84</v>
@@ -44210,7 +44313,7 @@
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B276">
         <v>84</v>
@@ -44245,7 +44348,7 @@
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B277">
         <v>84</v>
@@ -44280,7 +44383,7 @@
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B278">
         <v>84</v>
@@ -44315,7 +44418,7 @@
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B279">
         <v>84</v>
@@ -44350,7 +44453,7 @@
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B280">
         <v>84</v>
@@ -44385,7 +44488,7 @@
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B281">
         <v>84</v>
@@ -44420,7 +44523,7 @@
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B282">
         <v>84</v>
@@ -44455,7 +44558,7 @@
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B283">
         <v>84</v>
@@ -44490,7 +44593,7 @@
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B284">
         <v>84</v>
@@ -44525,7 +44628,7 @@
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B285">
         <v>83</v>
@@ -44560,7 +44663,7 @@
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B286">
         <v>83</v>
@@ -44595,7 +44698,7 @@
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B287">
         <v>83</v>
@@ -44630,7 +44733,7 @@
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B288">
         <v>83</v>
@@ -44665,7 +44768,7 @@
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B289">
         <v>83</v>
@@ -44700,7 +44803,7 @@
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B290">
         <v>83</v>
@@ -44735,7 +44838,7 @@
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B291">
         <v>83</v>
@@ -44770,7 +44873,7 @@
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B292">
         <v>83</v>
@@ -44805,7 +44908,7 @@
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B293">
         <v>83</v>
@@ -44840,7 +44943,7 @@
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B294">
         <v>83</v>
@@ -44875,7 +44978,7 @@
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B295">
         <v>83</v>
@@ -44910,7 +45013,7 @@
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B296">
         <v>83</v>
@@ -44945,7 +45048,7 @@
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B297">
         <v>83</v>
@@ -44980,7 +45083,7 @@
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B298">
         <v>83</v>
@@ -45015,7 +45118,7 @@
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B299">
         <v>83</v>
@@ -45050,7 +45153,7 @@
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B300">
         <v>83</v>
@@ -45085,7 +45188,7 @@
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B301">
         <v>83</v>
@@ -45120,7 +45223,7 @@
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B302">
         <v>83</v>
@@ -45155,7 +45258,7 @@
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B303">
         <v>83</v>
@@ -45190,7 +45293,7 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B304">
         <v>83</v>
@@ -45225,7 +45328,7 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B305">
         <v>83</v>
@@ -45260,7 +45363,7 @@
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B306">
         <v>83</v>
@@ -45295,7 +45398,7 @@
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B307">
         <v>83</v>
@@ -45330,7 +45433,7 @@
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B308">
         <v>83</v>
@@ -45365,7 +45468,7 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B309">
         <v>83</v>
@@ -45400,7 +45503,7 @@
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B310">
         <v>83</v>
@@ -45435,7 +45538,7 @@
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B311">
         <v>83</v>
@@ -45470,7 +45573,7 @@
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B312">
         <v>83</v>
@@ -45505,7 +45608,7 @@
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B313">
         <v>83</v>
@@ -45540,7 +45643,7 @@
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B314">
         <v>83</v>
@@ -45575,7 +45678,7 @@
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B315">
         <v>83</v>
@@ -45610,7 +45713,7 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B316">
         <v>83</v>
@@ -45645,7 +45748,7 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B317">
         <v>83</v>
@@ -45680,7 +45783,7 @@
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B318">
         <v>82</v>
@@ -45715,7 +45818,7 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B319">
         <v>82</v>
@@ -45750,7 +45853,7 @@
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B320">
         <v>82</v>
@@ -45785,7 +45888,7 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B321">
         <v>82</v>
@@ -45820,7 +45923,7 @@
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B322">
         <v>82</v>
@@ -45855,7 +45958,7 @@
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B323">
         <v>82</v>
@@ -45890,7 +45993,7 @@
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B324">
         <v>82</v>
@@ -45925,7 +46028,7 @@
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B325">
         <v>82</v>
@@ -45960,7 +46063,7 @@
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B326">
         <v>82</v>
@@ -45995,7 +46098,7 @@
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B327">
         <v>82</v>
@@ -46030,7 +46133,7 @@
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B328">
         <v>82</v>
@@ -46065,7 +46168,7 @@
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B329">
         <v>82</v>
@@ -46100,7 +46203,7 @@
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B330">
         <v>82</v>
@@ -46135,7 +46238,7 @@
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B331">
         <v>82</v>
@@ -46170,7 +46273,7 @@
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B332">
         <v>82</v>
@@ -46205,7 +46308,7 @@
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B333">
         <v>82</v>
@@ -46240,7 +46343,7 @@
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B334">
         <v>81</v>
@@ -46275,7 +46378,7 @@
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B335">
         <v>81</v>
@@ -46310,7 +46413,7 @@
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B336">
         <v>81</v>
@@ -46345,7 +46448,7 @@
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B337">
         <v>81</v>
@@ -46380,7 +46483,7 @@
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B338">
         <v>81</v>
@@ -46415,7 +46518,7 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B339">
         <v>81</v>
@@ -46450,7 +46553,7 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B340">
         <v>81</v>
@@ -46485,7 +46588,7 @@
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B341">
         <v>81</v>
@@ -46520,7 +46623,7 @@
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B342">
         <v>81</v>
@@ -46555,7 +46658,7 @@
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B343">
         <v>81</v>
@@ -46590,7 +46693,7 @@
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B344">
         <v>81</v>
@@ -46625,7 +46728,7 @@
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B345">
         <v>81</v>
@@ -46660,7 +46763,7 @@
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B346">
         <v>81</v>
@@ -46695,7 +46798,7 @@
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B347">
         <v>81</v>
@@ -46730,7 +46833,7 @@
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B348">
         <v>81</v>
@@ -46765,7 +46868,7 @@
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B349">
         <v>81</v>
@@ -46800,7 +46903,7 @@
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B350">
         <v>81</v>
@@ -46835,7 +46938,7 @@
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B351">
         <v>81</v>
@@ -46870,7 +46973,7 @@
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B352">
         <v>81</v>
@@ -46905,7 +47008,7 @@
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B353">
         <v>81</v>
@@ -46940,7 +47043,7 @@
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B354">
         <v>81</v>
@@ -46975,7 +47078,7 @@
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B355">
         <v>81</v>
@@ -47010,7 +47113,7 @@
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B356">
         <v>81</v>
@@ -47045,7 +47148,7 @@
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B357">
         <v>81</v>
@@ -47080,7 +47183,7 @@
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B358">
         <v>81</v>
@@ -47115,7 +47218,7 @@
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B359">
         <v>81</v>
@@ -47150,7 +47253,7 @@
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B360">
         <v>81</v>
@@ -47185,7 +47288,7 @@
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B361">
         <v>81</v>
@@ -47220,7 +47323,7 @@
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B362">
         <v>81</v>
@@ -47255,7 +47358,7 @@
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B363">
         <v>81</v>
@@ -47290,7 +47393,7 @@
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B364">
         <v>81</v>
@@ -47325,7 +47428,7 @@
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B365">
         <v>80</v>
@@ -47360,7 +47463,7 @@
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B366">
         <v>80</v>
@@ -47395,7 +47498,7 @@
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B367">
         <v>80</v>
@@ -47430,7 +47533,7 @@
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B368">
         <v>80</v>
@@ -47465,7 +47568,7 @@
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B369">
         <v>80</v>
@@ -47500,7 +47603,7 @@
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B370">
         <v>80</v>
@@ -47535,7 +47638,7 @@
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B371">
         <v>80</v>
@@ -47570,7 +47673,7 @@
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B372">
         <v>80</v>
@@ -47605,7 +47708,7 @@
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B373">
         <v>80</v>
@@ -47640,7 +47743,7 @@
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B374">
         <v>80</v>
@@ -47675,7 +47778,7 @@
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B375">
         <v>80</v>
@@ -47710,7 +47813,7 @@
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B376">
         <v>80</v>
@@ -47745,7 +47848,7 @@
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B377">
         <v>80</v>
@@ -47780,7 +47883,7 @@
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B378">
         <v>80</v>
@@ -47815,7 +47918,7 @@
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>3488</v>
+        <v>3497</v>
       </c>
       <c r="B379">
         <v>80</v>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10412" uniqueCount="3747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10452" uniqueCount="3763">
   <si>
     <t>日期</t>
   </si>
@@ -11135,6 +11135,54 @@
   </si>
   <si>
     <t>研究85/技能80/学历100/行业100/企业84</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>2027届管培生秋季校园招聘 — 研发方向</t>
+  </si>
+  <si>
+    <t>2027届应届毕业生，全日制本科及以上学历，医学、材料、机械、生物医学工程等相关专业；公司专注外周及神经血管介入、植入领域医疗器械创新研发；管培生设注册、研发等八大方向，15-18万/年，提供轮岗培养。</t>
+  </si>
+  <si>
+    <t>杭州（余杭）</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/link?url=生物医药校招实习圈-归创通桥管培生秋招</t>
+  </si>
+  <si>
+    <t>智能匹配83分【校园招聘】|强烈推荐|外周/神经血管介入龙头管培生研发方向，方向高度契合，2027届应届可投</t>
+  </si>
+  <si>
+    <t>研究88/技能60/学历100/行业100/企业95</t>
+  </si>
+  <si>
+    <t>归创通桥是国产血管介入（外周+神经介入）细分龙头，管培生研发方向与候选人血管支架研究方向和医疗器械研发目标完全一致；上市公司平台、完善的轮岗培养体系和15-18万年薪为应届硕士提供优质起点，方向+平台双重契合。</t>
+  </si>
+  <si>
+    <t>突出血管支架研究方向与硕士课题，强调材料学、支架结构设计、生物相容性评价与动物实验等核心技能；管培生偏综合，补充沟通协调、项目组织与跨部门协作经历，量化实验/项目成果。</t>
+  </si>
+  <si>
+    <t>江西三鑫医疗科技股份有限公司</t>
+  </si>
+  <si>
+    <t>2027届校园招聘 — 结构研发工程师/材料研发工程师</t>
+  </si>
+  <si>
+    <t>2027届应届毕业生，材料、机械、高分子、生物医学工程等相关专业；专注于医疗器械研发、制造、销售与服务的国家高新技术企业，技术研发类岗位含结构研发工程师、材料研发工程师、工艺工程师、注册工程师等。</t>
+  </si>
+  <si>
+    <t>江西南昌</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/link?url=校友邦实习校招-三鑫医疗2027届校园招聘</t>
+  </si>
+  <si>
+    <t>智能匹配82分【校园招聘】|强烈推荐|上市医疗器械企业2027届校招，材料/结构研发岗，技能方向部分重合</t>
+  </si>
+  <si>
+    <t>研究72/技能75/学历100/行业100/企业92</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -11689,7 +11737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L508"/>
+  <dimension ref="A1:L510"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -31006,6 +31054,82 @@
         <v>79</v>
       </c>
       <c r="L508" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>3707</v>
+      </c>
+      <c r="B509" t="s">
+        <v>829</v>
+      </c>
+      <c r="C509" t="s">
+        <v>3708</v>
+      </c>
+      <c r="D509" t="s">
+        <v>3709</v>
+      </c>
+      <c r="E509" t="s">
+        <v>3710</v>
+      </c>
+      <c r="F509" t="s">
+        <v>3711</v>
+      </c>
+      <c r="G509">
+        <v>8</v>
+      </c>
+      <c r="H509" t="s">
+        <v>3712</v>
+      </c>
+      <c r="I509">
+        <v>83</v>
+      </c>
+      <c r="J509" t="s">
+        <v>3713</v>
+      </c>
+      <c r="K509" t="s">
+        <v>3714</v>
+      </c>
+      <c r="L509" t="s">
+        <v>3715</v>
+      </c>
+    </row>
+    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>3707</v>
+      </c>
+      <c r="B510" t="s">
+        <v>3716</v>
+      </c>
+      <c r="C510" t="s">
+        <v>3717</v>
+      </c>
+      <c r="D510" t="s">
+        <v>3718</v>
+      </c>
+      <c r="E510" t="s">
+        <v>3719</v>
+      </c>
+      <c r="F510" t="s">
+        <v>3720</v>
+      </c>
+      <c r="G510">
+        <v>8</v>
+      </c>
+      <c r="H510" t="s">
+        <v>3721</v>
+      </c>
+      <c r="I510">
+        <v>82</v>
+      </c>
+      <c r="J510" t="s">
+        <v>3722</v>
+      </c>
+      <c r="K510" t="s">
+        <v>79</v>
+      </c>
+      <c r="L510" t="s">
         <v>79</v>
       </c>
     </row>
@@ -31040,7 +31164,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3707</v>
+        <v>3723</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -31049,16 +31173,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3708</v>
+        <v>3724</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3709</v>
+        <v>3725</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3710</v>
+        <v>3726</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3711</v>
+        <v>3727</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -31072,13 +31196,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3712</v>
+        <v>3728</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>3713</v>
+        <v>3729</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>3714</v>
+        <v>3730</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -31121,7 +31245,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>3719</v>
+        <v>3735</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -31131,31 +31255,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>3720</v>
+        <v>3736</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>3721</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3722</v>
+        <v>3738</v>
       </c>
       <c r="B4">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3723</v>
+        <v>3739</v>
       </c>
       <c r="B5" t="s">
-        <v>3724</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3725</v>
+        <v>3741</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -31163,7 +31287,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3726</v>
+        <v>3742</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -31171,7 +31295,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3727</v>
+        <v>3743</v>
       </c>
       <c r="B8">
         <v>269</v>
@@ -31179,15 +31303,15 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3728</v>
+        <v>3744</v>
       </c>
       <c r="B9">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3729</v>
+        <v>3745</v>
       </c>
       <c r="B10">
         <v>20</v>
@@ -31195,15 +31319,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3730</v>
+        <v>3746</v>
       </c>
       <c r="B11" t="s">
-        <v>3676</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>3731</v>
+        <v>3747</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -31213,15 +31337,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>3732</v>
+        <v>3748</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>3733</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3734</v>
+        <v>3750</v>
       </c>
       <c r="B16" s="5">
         <v>9</v>
@@ -31229,7 +31353,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3735</v>
+        <v>3751</v>
       </c>
       <c r="B17" s="5">
         <v>260</v>
@@ -31237,15 +31361,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3736</v>
+        <v>3752</v>
       </c>
       <c r="B18" s="5">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3737</v>
+        <v>3753</v>
       </c>
       <c r="B19" s="5">
         <v>20</v>
@@ -31253,7 +31377,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3738</v>
+        <v>3754</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -31261,7 +31385,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3739</v>
+        <v>3755</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -31269,7 +31393,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3740</v>
+        <v>3756</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -31277,7 +31401,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3741</v>
+        <v>3757</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -31285,7 +31409,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3742</v>
+        <v>3758</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -31293,7 +31417,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3743</v>
+        <v>3759</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -31301,7 +31425,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>3744</v>
+        <v>3760</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -31313,7 +31437,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>3745</v>
+        <v>3761</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -31331,7 +31455,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>3746</v>
+        <v>3762</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -36550,7 +36674,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K408"/>
+  <dimension ref="A1:K410"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -36567,10 +36691,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>3715</v>
+        <v>3731</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>3716</v>
+        <v>3732</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -36597,12 +36721,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>3717</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -36637,7 +36761,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -36672,7 +36796,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -36707,7 +36831,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -36742,7 +36866,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -36777,7 +36901,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -36812,7 +36936,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B8">
         <v>95</v>
@@ -36847,7 +36971,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B9">
         <v>95</v>
@@ -36882,7 +37006,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B10">
         <v>95</v>
@@ -36917,7 +37041,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B11">
         <v>94</v>
@@ -36952,7 +37076,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B12">
         <v>94</v>
@@ -36987,7 +37111,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B13">
         <v>94</v>
@@ -37022,7 +37146,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B14">
         <v>93</v>
@@ -37057,7 +37181,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B15">
         <v>93</v>
@@ -37092,7 +37216,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B16">
         <v>93</v>
@@ -37127,7 +37251,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B17">
         <v>93</v>
@@ -37162,7 +37286,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B18">
         <v>93</v>
@@ -37197,7 +37321,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B19">
         <v>93</v>
@@ -37232,7 +37356,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B20">
         <v>93</v>
@@ -37267,7 +37391,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B21">
         <v>93</v>
@@ -37302,7 +37426,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B22">
         <v>93</v>
@@ -37337,7 +37461,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B23">
         <v>93</v>
@@ -37372,7 +37496,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B24">
         <v>92</v>
@@ -37407,7 +37531,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B25">
         <v>92</v>
@@ -37442,7 +37566,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B26">
         <v>92</v>
@@ -37477,7 +37601,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B27">
         <v>92</v>
@@ -37512,7 +37636,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B28">
         <v>92</v>
@@ -37547,7 +37671,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B29">
         <v>92</v>
@@ -37582,7 +37706,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B30">
         <v>92</v>
@@ -37617,7 +37741,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B31">
         <v>92</v>
@@ -37652,7 +37776,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B32">
         <v>92</v>
@@ -37687,7 +37811,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B33">
         <v>92</v>
@@ -37722,7 +37846,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B34">
         <v>92</v>
@@ -37757,7 +37881,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B35">
         <v>91</v>
@@ -37792,7 +37916,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B36">
         <v>91</v>
@@ -37827,7 +37951,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B37">
         <v>91</v>
@@ -37862,7 +37986,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B38">
         <v>91</v>
@@ -37897,7 +38021,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B39">
         <v>91</v>
@@ -37932,7 +38056,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B40">
         <v>91</v>
@@ -37967,7 +38091,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B41">
         <v>91</v>
@@ -38002,7 +38126,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B42">
         <v>91</v>
@@ -38037,7 +38161,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B43">
         <v>91</v>
@@ -38072,7 +38196,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B44">
         <v>91</v>
@@ -38107,7 +38231,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B45">
         <v>91</v>
@@ -38142,7 +38266,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B46">
         <v>91</v>
@@ -38177,7 +38301,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B47">
         <v>91</v>
@@ -38212,7 +38336,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B48">
         <v>91</v>
@@ -38247,7 +38371,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B49">
         <v>91</v>
@@ -38282,7 +38406,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B50">
         <v>91</v>
@@ -38317,7 +38441,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B51">
         <v>91</v>
@@ -38352,7 +38476,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B52">
         <v>91</v>
@@ -38387,7 +38511,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B53">
         <v>91</v>
@@ -38422,7 +38546,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B54">
         <v>91</v>
@@ -38457,7 +38581,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B55">
         <v>91</v>
@@ -38492,7 +38616,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B56">
         <v>90</v>
@@ -38527,7 +38651,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B57">
         <v>90</v>
@@ -38562,7 +38686,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B58">
         <v>90</v>
@@ -38597,7 +38721,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B59">
         <v>90</v>
@@ -38632,7 +38756,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B60">
         <v>90</v>
@@ -38667,7 +38791,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B61">
         <v>90</v>
@@ -38702,7 +38826,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B62">
         <v>90</v>
@@ -38737,7 +38861,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B63">
         <v>90</v>
@@ -38772,7 +38896,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B64">
         <v>90</v>
@@ -38807,7 +38931,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B65">
         <v>90</v>
@@ -38842,7 +38966,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B66">
         <v>90</v>
@@ -38877,7 +39001,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B67">
         <v>90</v>
@@ -38912,7 +39036,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B68">
         <v>90</v>
@@ -38947,7 +39071,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B69">
         <v>90</v>
@@ -38982,7 +39106,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B70">
         <v>90</v>
@@ -39017,7 +39141,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B71">
         <v>90</v>
@@ -39052,7 +39176,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B72">
         <v>90</v>
@@ -39087,7 +39211,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B73">
         <v>90</v>
@@ -39122,7 +39246,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B74">
         <v>90</v>
@@ -39157,7 +39281,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B75">
         <v>90</v>
@@ -39192,7 +39316,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B76">
         <v>90</v>
@@ -39227,7 +39351,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B77">
         <v>90</v>
@@ -39262,7 +39386,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B78">
         <v>90</v>
@@ -39297,7 +39421,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B79">
         <v>90</v>
@@ -39332,7 +39456,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B80">
         <v>90</v>
@@ -39367,7 +39491,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B81">
         <v>89</v>
@@ -39402,7 +39526,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B82">
         <v>89</v>
@@ -39437,7 +39561,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B83">
         <v>89</v>
@@ -39472,7 +39596,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B84">
         <v>89</v>
@@ -39507,7 +39631,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B85">
         <v>89</v>
@@ -39542,7 +39666,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B86">
         <v>89</v>
@@ -39577,7 +39701,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B87">
         <v>89</v>
@@ -39612,7 +39736,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B88">
         <v>89</v>
@@ -39647,7 +39771,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B89">
         <v>89</v>
@@ -39682,7 +39806,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B90">
         <v>89</v>
@@ -39717,7 +39841,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B91">
         <v>89</v>
@@ -39752,7 +39876,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B92">
         <v>89</v>
@@ -39787,7 +39911,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B93">
         <v>89</v>
@@ -39822,7 +39946,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B94">
         <v>89</v>
@@ -39857,7 +39981,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B95">
         <v>89</v>
@@ -39892,7 +40016,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B96">
         <v>89</v>
@@ -39927,7 +40051,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B97">
         <v>89</v>
@@ -39962,7 +40086,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B98">
         <v>89</v>
@@ -39997,7 +40121,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B99">
         <v>89</v>
@@ -40032,7 +40156,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B100">
         <v>89</v>
@@ -40067,7 +40191,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B101">
         <v>89</v>
@@ -40102,7 +40226,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B102">
         <v>89</v>
@@ -40137,7 +40261,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B103">
         <v>89</v>
@@ -40172,7 +40296,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B104">
         <v>89</v>
@@ -40207,7 +40331,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B105">
         <v>89</v>
@@ -40242,7 +40366,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B106">
         <v>89</v>
@@ -40277,7 +40401,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B107">
         <v>89</v>
@@ -40312,7 +40436,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B108">
         <v>89</v>
@@ -40347,7 +40471,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B109">
         <v>89</v>
@@ -40382,7 +40506,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B110">
         <v>89</v>
@@ -40417,7 +40541,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B111">
         <v>89</v>
@@ -40452,7 +40576,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B112">
         <v>89</v>
@@ -40487,7 +40611,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B113">
         <v>89</v>
@@ -40522,7 +40646,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B114">
         <v>89</v>
@@ -40557,7 +40681,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B115">
         <v>89</v>
@@ -40592,7 +40716,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B116">
         <v>89</v>
@@ -40627,7 +40751,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B117">
         <v>89</v>
@@ -40662,7 +40786,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B118">
         <v>89</v>
@@ -40697,7 +40821,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B119">
         <v>89</v>
@@ -40732,7 +40856,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B120">
         <v>89</v>
@@ -40767,7 +40891,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B121">
         <v>89</v>
@@ -40802,7 +40926,7 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B122">
         <v>89</v>
@@ -40837,7 +40961,7 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B123">
         <v>89</v>
@@ -40872,7 +40996,7 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B124">
         <v>88</v>
@@ -40907,7 +41031,7 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B125">
         <v>88</v>
@@ -40942,7 +41066,7 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B126">
         <v>88</v>
@@ -40977,7 +41101,7 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B127">
         <v>88</v>
@@ -41012,7 +41136,7 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B128">
         <v>88</v>
@@ -41047,7 +41171,7 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B129">
         <v>88</v>
@@ -41082,7 +41206,7 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B130">
         <v>88</v>
@@ -41117,7 +41241,7 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B131">
         <v>88</v>
@@ -41152,7 +41276,7 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B132">
         <v>88</v>
@@ -41187,7 +41311,7 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B133">
         <v>88</v>
@@ -41222,7 +41346,7 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B134">
         <v>88</v>
@@ -41257,7 +41381,7 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B135">
         <v>88</v>
@@ -41292,7 +41416,7 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B136">
         <v>88</v>
@@ -41327,7 +41451,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B137">
         <v>88</v>
@@ -41362,7 +41486,7 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B138">
         <v>88</v>
@@ -41397,7 +41521,7 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B139">
         <v>88</v>
@@ -41432,7 +41556,7 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B140">
         <v>88</v>
@@ -41467,7 +41591,7 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B141">
         <v>88</v>
@@ -41502,7 +41626,7 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B142">
         <v>88</v>
@@ -41537,7 +41661,7 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B143">
         <v>88</v>
@@ -41572,7 +41696,7 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B144">
         <v>88</v>
@@ -41607,7 +41731,7 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B145">
         <v>88</v>
@@ -41642,7 +41766,7 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B146">
         <v>88</v>
@@ -41677,7 +41801,7 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B147">
         <v>88</v>
@@ -41712,7 +41836,7 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B148">
         <v>88</v>
@@ -41747,7 +41871,7 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B149">
         <v>88</v>
@@ -41782,7 +41906,7 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B150">
         <v>88</v>
@@ -41817,7 +41941,7 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B151">
         <v>88</v>
@@ -41852,7 +41976,7 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B152">
         <v>88</v>
@@ -41887,7 +42011,7 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B153">
         <v>88</v>
@@ -41922,7 +42046,7 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B154">
         <v>88</v>
@@ -41957,7 +42081,7 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B155">
         <v>88</v>
@@ -41992,7 +42116,7 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B156">
         <v>88</v>
@@ -42027,7 +42151,7 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B157">
         <v>88</v>
@@ -42062,7 +42186,7 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B158">
         <v>88</v>
@@ -42097,7 +42221,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B159">
         <v>88</v>
@@ -42132,7 +42256,7 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B160">
         <v>88</v>
@@ -42167,7 +42291,7 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B161">
         <v>87</v>
@@ -42202,7 +42326,7 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B162">
         <v>87</v>
@@ -42237,7 +42361,7 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B163">
         <v>87</v>
@@ -42272,7 +42396,7 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B164">
         <v>87</v>
@@ -42307,7 +42431,7 @@
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B165">
         <v>87</v>
@@ -42342,7 +42466,7 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B166">
         <v>87</v>
@@ -42377,7 +42501,7 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B167">
         <v>87</v>
@@ -42412,7 +42536,7 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B168">
         <v>87</v>
@@ -42447,7 +42571,7 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B169">
         <v>87</v>
@@ -42482,7 +42606,7 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B170">
         <v>87</v>
@@ -42517,7 +42641,7 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B171">
         <v>87</v>
@@ -42552,7 +42676,7 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B172">
         <v>87</v>
@@ -42587,7 +42711,7 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B173">
         <v>87</v>
@@ -42622,7 +42746,7 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B174">
         <v>87</v>
@@ -42657,7 +42781,7 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B175">
         <v>87</v>
@@ -42692,7 +42816,7 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B176">
         <v>87</v>
@@ -42727,7 +42851,7 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B177">
         <v>87</v>
@@ -42762,7 +42886,7 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B178">
         <v>87</v>
@@ -42797,7 +42921,7 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B179">
         <v>87</v>
@@ -42832,7 +42956,7 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B180">
         <v>87</v>
@@ -42867,7 +42991,7 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B181">
         <v>87</v>
@@ -42902,7 +43026,7 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B182">
         <v>87</v>
@@ -42937,7 +43061,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B183">
         <v>87</v>
@@ -42972,7 +43096,7 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B184">
         <v>87</v>
@@ -43007,7 +43131,7 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B185">
         <v>87</v>
@@ -43042,7 +43166,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B186">
         <v>87</v>
@@ -43077,7 +43201,7 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B187">
         <v>87</v>
@@ -43112,7 +43236,7 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B188">
         <v>87</v>
@@ -43147,7 +43271,7 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B189">
         <v>87</v>
@@ -43182,7 +43306,7 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B190">
         <v>87</v>
@@ -43217,7 +43341,7 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B191">
         <v>87</v>
@@ -43252,7 +43376,7 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B192">
         <v>87</v>
@@ -43287,7 +43411,7 @@
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B193">
         <v>87</v>
@@ -43322,7 +43446,7 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B194">
         <v>87</v>
@@ -43357,7 +43481,7 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B195">
         <v>86</v>
@@ -43392,7 +43516,7 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B196">
         <v>86</v>
@@ -43427,7 +43551,7 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B197">
         <v>86</v>
@@ -43462,7 +43586,7 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B198">
         <v>86</v>
@@ -43497,7 +43621,7 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B199">
         <v>86</v>
@@ -43532,7 +43656,7 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B200">
         <v>86</v>
@@ -43567,7 +43691,7 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B201">
         <v>86</v>
@@ -43602,7 +43726,7 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B202">
         <v>86</v>
@@ -43637,7 +43761,7 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B203">
         <v>86</v>
@@ -43672,7 +43796,7 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B204">
         <v>86</v>
@@ -43707,7 +43831,7 @@
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B205">
         <v>86</v>
@@ -43742,7 +43866,7 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B206">
         <v>86</v>
@@ -43777,7 +43901,7 @@
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B207">
         <v>86</v>
@@ -43812,7 +43936,7 @@
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B208">
         <v>86</v>
@@ -43847,7 +43971,7 @@
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B209">
         <v>86</v>
@@ -43882,7 +44006,7 @@
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B210">
         <v>86</v>
@@ -43917,7 +44041,7 @@
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B211">
         <v>86</v>
@@ -43952,7 +44076,7 @@
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B212">
         <v>86</v>
@@ -43987,7 +44111,7 @@
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B213">
         <v>86</v>
@@ -44022,7 +44146,7 @@
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B214">
         <v>86</v>
@@ -44057,7 +44181,7 @@
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B215">
         <v>86</v>
@@ -44092,7 +44216,7 @@
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B216">
         <v>86</v>
@@ -44127,7 +44251,7 @@
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B217">
         <v>86</v>
@@ -44162,7 +44286,7 @@
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B218">
         <v>86</v>
@@ -44197,7 +44321,7 @@
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B219">
         <v>86</v>
@@ -44232,7 +44356,7 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B220">
         <v>86</v>
@@ -44267,7 +44391,7 @@
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B221">
         <v>86</v>
@@ -44302,7 +44426,7 @@
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B222">
         <v>86</v>
@@ -44337,7 +44461,7 @@
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B223">
         <v>86</v>
@@ -44372,7 +44496,7 @@
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B224">
         <v>86</v>
@@ -44407,7 +44531,7 @@
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B225">
         <v>86</v>
@@ -44442,7 +44566,7 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B226">
         <v>86</v>
@@ -44477,7 +44601,7 @@
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B227">
         <v>86</v>
@@ -44512,7 +44636,7 @@
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B228">
         <v>86</v>
@@ -44547,7 +44671,7 @@
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B229">
         <v>86</v>
@@ -44582,7 +44706,7 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B230">
         <v>86</v>
@@ -44617,7 +44741,7 @@
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B231">
         <v>86</v>
@@ -44652,7 +44776,7 @@
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B232">
         <v>86</v>
@@ -44687,7 +44811,7 @@
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B233">
         <v>86</v>
@@ -44722,7 +44846,7 @@
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B234">
         <v>86</v>
@@ -44757,7 +44881,7 @@
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B235">
         <v>86</v>
@@ -44792,7 +44916,7 @@
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B236">
         <v>85</v>
@@ -44827,7 +44951,7 @@
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B237">
         <v>85</v>
@@ -44862,7 +44986,7 @@
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B238">
         <v>85</v>
@@ -44897,7 +45021,7 @@
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B239">
         <v>85</v>
@@ -44932,7 +45056,7 @@
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B240">
         <v>85</v>
@@ -44967,7 +45091,7 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B241">
         <v>85</v>
@@ -45002,7 +45126,7 @@
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B242">
         <v>85</v>
@@ -45037,7 +45161,7 @@
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B243">
         <v>85</v>
@@ -45072,7 +45196,7 @@
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B244">
         <v>85</v>
@@ -45107,7 +45231,7 @@
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B245">
         <v>85</v>
@@ -45142,7 +45266,7 @@
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B246">
         <v>85</v>
@@ -45177,7 +45301,7 @@
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B247">
         <v>85</v>
@@ -45212,7 +45336,7 @@
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B248">
         <v>85</v>
@@ -45247,7 +45371,7 @@
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B249">
         <v>85</v>
@@ -45282,7 +45406,7 @@
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B250">
         <v>85</v>
@@ -45317,7 +45441,7 @@
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B251">
         <v>85</v>
@@ -45352,7 +45476,7 @@
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B252">
         <v>85</v>
@@ -45387,7 +45511,7 @@
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B253">
         <v>85</v>
@@ -45422,7 +45546,7 @@
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B254">
         <v>85</v>
@@ -45457,7 +45581,7 @@
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B255">
         <v>85</v>
@@ -45492,7 +45616,7 @@
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B256">
         <v>85</v>
@@ -45527,7 +45651,7 @@
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B257">
         <v>85</v>
@@ -45562,7 +45686,7 @@
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B258">
         <v>85</v>
@@ -45597,7 +45721,7 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B259">
         <v>85</v>
@@ -45632,7 +45756,7 @@
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B260">
         <v>85</v>
@@ -45667,7 +45791,7 @@
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B261">
         <v>85</v>
@@ -45702,7 +45826,7 @@
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B262">
         <v>85</v>
@@ -45737,7 +45861,7 @@
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B263">
         <v>85</v>
@@ -45772,7 +45896,7 @@
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B264">
         <v>85</v>
@@ -45807,7 +45931,7 @@
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B265">
         <v>85</v>
@@ -45842,7 +45966,7 @@
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B266">
         <v>85</v>
@@ -45877,7 +46001,7 @@
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B267">
         <v>85</v>
@@ -45912,7 +46036,7 @@
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B268">
         <v>85</v>
@@ -45947,7 +46071,7 @@
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B269">
         <v>85</v>
@@ -45982,7 +46106,7 @@
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B270">
         <v>85</v>
@@ -46017,7 +46141,7 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B271">
         <v>84</v>
@@ -46052,7 +46176,7 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B272">
         <v>84</v>
@@ -46087,7 +46211,7 @@
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B273">
         <v>84</v>
@@ -46122,7 +46246,7 @@
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B274">
         <v>84</v>
@@ -46157,7 +46281,7 @@
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B275">
         <v>84</v>
@@ -46192,7 +46316,7 @@
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B276">
         <v>84</v>
@@ -46227,7 +46351,7 @@
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B277">
         <v>84</v>
@@ -46262,7 +46386,7 @@
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B278">
         <v>84</v>
@@ -46297,7 +46421,7 @@
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B279">
         <v>84</v>
@@ -46332,7 +46456,7 @@
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B280">
         <v>84</v>
@@ -46367,7 +46491,7 @@
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B281">
         <v>84</v>
@@ -46402,7 +46526,7 @@
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B282">
         <v>84</v>
@@ -46437,7 +46561,7 @@
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B283">
         <v>84</v>
@@ -46472,7 +46596,7 @@
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B284">
         <v>84</v>
@@ -46507,7 +46631,7 @@
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B285">
         <v>84</v>
@@ -46542,7 +46666,7 @@
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B286">
         <v>84</v>
@@ -46577,7 +46701,7 @@
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B287">
         <v>84</v>
@@ -46612,7 +46736,7 @@
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B288">
         <v>84</v>
@@ -46647,7 +46771,7 @@
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B289">
         <v>84</v>
@@ -46682,7 +46806,7 @@
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B290">
         <v>84</v>
@@ -46717,7 +46841,7 @@
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B291">
         <v>84</v>
@@ -46752,7 +46876,7 @@
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B292">
         <v>84</v>
@@ -46787,7 +46911,7 @@
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B293">
         <v>84</v>
@@ -46822,7 +46946,7 @@
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B294">
         <v>84</v>
@@ -46857,7 +46981,7 @@
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B295">
         <v>84</v>
@@ -46892,7 +47016,7 @@
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B296">
         <v>84</v>
@@ -46927,7 +47051,7 @@
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B297">
         <v>84</v>
@@ -46962,7 +47086,7 @@
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B298">
         <v>84</v>
@@ -46997,7 +47121,7 @@
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B299">
         <v>84</v>
@@ -47032,7 +47156,7 @@
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B300">
         <v>84</v>
@@ -47067,7 +47191,7 @@
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B301">
         <v>84</v>
@@ -47102,7 +47226,7 @@
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B302">
         <v>84</v>
@@ -47137,7 +47261,7 @@
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B303">
         <v>84</v>
@@ -47172,7 +47296,7 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B304">
         <v>84</v>
@@ -47207,7 +47331,7 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B305">
         <v>84</v>
@@ -47242,7 +47366,7 @@
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B306">
         <v>84</v>
@@ -47277,7 +47401,7 @@
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B307">
         <v>84</v>
@@ -47312,7 +47436,7 @@
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B308">
         <v>84</v>
@@ -47347,7 +47471,7 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B309">
         <v>84</v>
@@ -47382,7 +47506,7 @@
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B310">
         <v>83</v>
@@ -47417,7 +47541,7 @@
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B311">
         <v>83</v>
@@ -47452,7 +47576,7 @@
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B312">
         <v>83</v>
@@ -47487,7 +47611,7 @@
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B313">
         <v>83</v>
@@ -47522,7 +47646,7 @@
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B314">
         <v>83</v>
@@ -47557,7 +47681,7 @@
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B315">
         <v>83</v>
@@ -47592,7 +47716,7 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B316">
         <v>83</v>
@@ -47627,7 +47751,7 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B317">
         <v>83</v>
@@ -47662,7 +47786,7 @@
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B318">
         <v>83</v>
@@ -47697,7 +47821,7 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B319">
         <v>83</v>
@@ -47732,7 +47856,7 @@
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B320">
         <v>83</v>
@@ -47767,7 +47891,7 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B321">
         <v>83</v>
@@ -47802,7 +47926,7 @@
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B322">
         <v>83</v>
@@ -47837,7 +47961,7 @@
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B323">
         <v>83</v>
@@ -47872,7 +47996,7 @@
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B324">
         <v>83</v>
@@ -47907,7 +48031,7 @@
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B325">
         <v>83</v>
@@ -47942,7 +48066,7 @@
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B326">
         <v>83</v>
@@ -47977,7 +48101,7 @@
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B327">
         <v>83</v>
@@ -48012,7 +48136,7 @@
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B328">
         <v>83</v>
@@ -48047,7 +48171,7 @@
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B329">
         <v>83</v>
@@ -48082,7 +48206,7 @@
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B330">
         <v>83</v>
@@ -48117,7 +48241,7 @@
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B331">
         <v>83</v>
@@ -48152,7 +48276,7 @@
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B332">
         <v>83</v>
@@ -48187,7 +48311,7 @@
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B333">
         <v>83</v>
@@ -48222,7 +48346,7 @@
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B334">
         <v>83</v>
@@ -48257,7 +48381,7 @@
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B335">
         <v>83</v>
@@ -48292,7 +48416,7 @@
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B336">
         <v>83</v>
@@ -48327,7 +48451,7 @@
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B337">
         <v>83</v>
@@ -48362,7 +48486,7 @@
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B338">
         <v>83</v>
@@ -48397,7 +48521,7 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B339">
         <v>83</v>
@@ -48432,7 +48556,7 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B340">
         <v>83</v>
@@ -48467,7 +48591,7 @@
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B341">
         <v>83</v>
@@ -48502,7 +48626,7 @@
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B342">
         <v>83</v>
@@ -48537,7 +48661,7 @@
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B343">
         <v>83</v>
@@ -48572,42 +48696,42 @@
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B344">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C344" t="s">
-        <v>159</v>
+        <v>3707</v>
       </c>
       <c r="D344" t="s">
-        <v>227</v>
+        <v>829</v>
       </c>
       <c r="E344" t="s">
-        <v>228</v>
+        <v>3708</v>
       </c>
       <c r="F344" t="s">
-        <v>230</v>
+        <v>3710</v>
       </c>
       <c r="G344" t="s">
-        <v>231</v>
+        <v>3711</v>
       </c>
       <c r="H344" t="s">
-        <v>233</v>
+        <v>3713</v>
       </c>
       <c r="I344" t="s">
-        <v>234</v>
+        <v>3714</v>
       </c>
       <c r="J344" t="s">
-        <v>235</v>
+        <v>3715</v>
       </c>
       <c r="K344" t="s">
-        <v>229</v>
+        <v>3709</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B345">
         <v>82</v>
@@ -48616,138 +48740,138 @@
         <v>159</v>
       </c>
       <c r="D345" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="E345" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="F345" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="G345" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c r="H345" t="s">
-        <v>270</v>
+        <v>233</v>
       </c>
       <c r="I345" t="s">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="J345" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="K345" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B346">
         <v>82</v>
       </c>
       <c r="C346" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D346" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="E346" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="F346" t="s">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="G346" t="s">
-        <v>342</v>
+        <v>58</v>
       </c>
       <c r="H346" t="s">
-        <v>344</v>
+        <v>270</v>
       </c>
       <c r="I346" t="s">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="J346" t="s">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="K346" t="s">
-        <v>340</v>
+        <v>268</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B347">
         <v>82</v>
       </c>
       <c r="C347" t="s">
-        <v>591</v>
+        <v>284</v>
       </c>
       <c r="D347" t="s">
-        <v>601</v>
+        <v>338</v>
       </c>
       <c r="E347" t="s">
-        <v>602</v>
+        <v>339</v>
       </c>
       <c r="F347" t="s">
-        <v>75</v>
+        <v>341</v>
       </c>
       <c r="G347" t="s">
-        <v>604</v>
+        <v>342</v>
       </c>
       <c r="H347" t="s">
-        <v>606</v>
+        <v>344</v>
       </c>
       <c r="I347" t="s">
-        <v>607</v>
+        <v>345</v>
       </c>
       <c r="J347" t="s">
-        <v>608</v>
+        <v>346</v>
       </c>
       <c r="K347" t="s">
-        <v>603</v>
+        <v>340</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B348">
         <v>82</v>
       </c>
       <c r="C348" t="s">
-        <v>934</v>
+        <v>591</v>
       </c>
       <c r="D348" t="s">
-        <v>13</v>
+        <v>601</v>
       </c>
       <c r="E348" t="s">
-        <v>1009</v>
+        <v>602</v>
       </c>
       <c r="F348" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G348" t="s">
-        <v>1011</v>
+        <v>604</v>
       </c>
       <c r="H348" t="s">
-        <v>1013</v>
+        <v>606</v>
       </c>
       <c r="I348" t="s">
-        <v>1014</v>
+        <v>607</v>
       </c>
       <c r="J348" t="s">
-        <v>1015</v>
+        <v>608</v>
       </c>
       <c r="K348" t="s">
-        <v>1010</v>
+        <v>603</v>
       </c>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B349">
         <v>82</v>
@@ -48756,173 +48880,173 @@
         <v>934</v>
       </c>
       <c r="D349" t="s">
-        <v>1023</v>
+        <v>13</v>
       </c>
       <c r="E349" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="F349" t="s">
-        <v>1026</v>
+        <v>16</v>
       </c>
       <c r="G349" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="H349" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="I349" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="J349" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="K349" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B350">
         <v>82</v>
       </c>
       <c r="C350" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D350" t="s">
-        <v>1112</v>
+        <v>1023</v>
       </c>
       <c r="E350" t="s">
-        <v>1113</v>
+        <v>1024</v>
       </c>
       <c r="F350" t="s">
-        <v>25</v>
+        <v>1026</v>
       </c>
       <c r="G350" t="s">
-        <v>1115</v>
+        <v>1027</v>
       </c>
       <c r="H350" t="s">
-        <v>1117</v>
+        <v>1029</v>
       </c>
       <c r="I350" t="s">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="J350" t="s">
-        <v>1119</v>
+        <v>1031</v>
       </c>
       <c r="K350" t="s">
-        <v>1114</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B351">
         <v>82</v>
       </c>
       <c r="C351" t="s">
-        <v>1210</v>
+        <v>1087</v>
       </c>
       <c r="D351" t="s">
-        <v>1211</v>
+        <v>1112</v>
       </c>
       <c r="E351" t="s">
-        <v>89</v>
+        <v>1113</v>
       </c>
       <c r="F351" t="s">
-        <v>1213</v>
+        <v>25</v>
       </c>
       <c r="G351" t="s">
-        <v>1214</v>
+        <v>1115</v>
       </c>
       <c r="H351" t="s">
-        <v>1216</v>
+        <v>1117</v>
       </c>
       <c r="I351" t="s">
-        <v>1217</v>
+        <v>1118</v>
       </c>
       <c r="J351" t="s">
-        <v>1218</v>
+        <v>1119</v>
       </c>
       <c r="K351" t="s">
-        <v>1212</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B352">
         <v>82</v>
       </c>
       <c r="C352" t="s">
-        <v>1368</v>
+        <v>1210</v>
       </c>
       <c r="D352" t="s">
-        <v>1369</v>
+        <v>1211</v>
       </c>
       <c r="E352" t="s">
-        <v>1370</v>
+        <v>89</v>
       </c>
       <c r="F352" t="s">
-        <v>1372</v>
+        <v>1213</v>
       </c>
       <c r="G352" t="s">
-        <v>1373</v>
+        <v>1214</v>
       </c>
       <c r="H352" t="s">
-        <v>1375</v>
+        <v>1216</v>
       </c>
       <c r="I352" t="s">
-        <v>1376</v>
+        <v>1217</v>
       </c>
       <c r="J352" t="s">
-        <v>1377</v>
+        <v>1218</v>
       </c>
       <c r="K352" t="s">
-        <v>1371</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B353">
         <v>82</v>
       </c>
       <c r="C353" t="s">
-        <v>1534</v>
+        <v>1368</v>
       </c>
       <c r="D353" t="s">
-        <v>1608</v>
+        <v>1369</v>
       </c>
       <c r="E353" t="s">
-        <v>1609</v>
+        <v>1370</v>
       </c>
       <c r="F353" t="s">
-        <v>1559</v>
+        <v>1372</v>
       </c>
       <c r="G353" t="s">
-        <v>1611</v>
+        <v>1373</v>
       </c>
       <c r="H353" t="s">
-        <v>1613</v>
+        <v>1375</v>
       </c>
       <c r="I353" t="s">
-        <v>1614</v>
+        <v>1376</v>
       </c>
       <c r="J353" t="s">
-        <v>1615</v>
+        <v>1377</v>
       </c>
       <c r="K353" t="s">
-        <v>1610</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B354">
         <v>82</v>
@@ -48931,558 +49055,558 @@
         <v>1534</v>
       </c>
       <c r="D354" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="E354" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="F354" t="s">
-        <v>1619</v>
+        <v>1559</v>
       </c>
       <c r="G354" t="s">
-        <v>1620</v>
+        <v>1611</v>
       </c>
       <c r="H354" t="s">
-        <v>1622</v>
+        <v>1613</v>
       </c>
       <c r="I354" t="s">
-        <v>1623</v>
+        <v>1614</v>
       </c>
       <c r="J354" t="s">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="K354" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B355">
         <v>82</v>
       </c>
       <c r="C355" t="s">
-        <v>1884</v>
+        <v>1534</v>
       </c>
       <c r="D355" t="s">
-        <v>1979</v>
+        <v>1616</v>
       </c>
       <c r="E355" t="s">
-        <v>1980</v>
+        <v>1617</v>
       </c>
       <c r="F355" t="s">
-        <v>1982</v>
+        <v>1619</v>
       </c>
       <c r="G355" t="s">
-        <v>1983</v>
+        <v>1620</v>
       </c>
       <c r="H355" t="s">
-        <v>1985</v>
+        <v>1622</v>
       </c>
       <c r="I355" t="s">
-        <v>1986</v>
+        <v>1623</v>
       </c>
       <c r="J355" t="s">
-        <v>1987</v>
+        <v>1624</v>
       </c>
       <c r="K355" t="s">
-        <v>1981</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B356">
         <v>82</v>
       </c>
       <c r="C356" t="s">
-        <v>2258</v>
+        <v>1884</v>
       </c>
       <c r="D356" t="s">
-        <v>2283</v>
+        <v>1979</v>
       </c>
       <c r="E356" t="s">
-        <v>2284</v>
+        <v>1980</v>
       </c>
       <c r="F356" t="s">
-        <v>2286</v>
+        <v>1982</v>
       </c>
       <c r="G356" t="s">
-        <v>2287</v>
+        <v>1983</v>
       </c>
       <c r="H356" t="s">
-        <v>2289</v>
+        <v>1985</v>
       </c>
       <c r="I356" t="s">
-        <v>2290</v>
+        <v>1986</v>
       </c>
       <c r="J356" t="s">
-        <v>2291</v>
+        <v>1987</v>
       </c>
       <c r="K356" t="s">
-        <v>2285</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B357">
         <v>82</v>
       </c>
       <c r="C357" t="s">
-        <v>2675</v>
+        <v>2258</v>
       </c>
       <c r="D357" t="s">
-        <v>2676</v>
+        <v>2283</v>
       </c>
       <c r="E357" t="s">
-        <v>2677</v>
+        <v>2284</v>
       </c>
       <c r="F357" t="s">
-        <v>66</v>
+        <v>2286</v>
       </c>
       <c r="G357" t="s">
-        <v>2679</v>
+        <v>2287</v>
       </c>
       <c r="H357" t="s">
-        <v>2681</v>
+        <v>2289</v>
       </c>
       <c r="I357" t="s">
-        <v>2682</v>
+        <v>2290</v>
       </c>
       <c r="J357" t="s">
-        <v>2683</v>
+        <v>2291</v>
       </c>
       <c r="K357" t="s">
-        <v>2678</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B358">
         <v>82</v>
       </c>
       <c r="C358" t="s">
-        <v>2871</v>
+        <v>2675</v>
       </c>
       <c r="D358" t="s">
-        <v>2904</v>
+        <v>2676</v>
       </c>
       <c r="E358" t="s">
-        <v>2905</v>
+        <v>2677</v>
       </c>
       <c r="F358" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G358" t="s">
-        <v>2907</v>
+        <v>2679</v>
       </c>
       <c r="H358" t="s">
-        <v>2909</v>
+        <v>2681</v>
       </c>
       <c r="I358" t="s">
-        <v>2910</v>
+        <v>2682</v>
       </c>
       <c r="J358" t="s">
-        <v>2911</v>
+        <v>2683</v>
       </c>
       <c r="K358" t="s">
-        <v>2906</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B359">
         <v>82</v>
       </c>
       <c r="C359" t="s">
-        <v>2985</v>
+        <v>2871</v>
       </c>
       <c r="D359" t="s">
-        <v>3062</v>
+        <v>2904</v>
       </c>
       <c r="E359" t="s">
-        <v>3063</v>
+        <v>2905</v>
       </c>
       <c r="F359" t="s">
-        <v>3065</v>
+        <v>75</v>
       </c>
       <c r="G359" t="s">
-        <v>3066</v>
+        <v>2907</v>
       </c>
       <c r="H359" t="s">
-        <v>3068</v>
+        <v>2909</v>
       </c>
       <c r="I359" t="s">
-        <v>3069</v>
+        <v>2910</v>
       </c>
       <c r="J359" t="s">
-        <v>3070</v>
+        <v>2911</v>
       </c>
       <c r="K359" t="s">
-        <v>3064</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B360">
         <v>82</v>
       </c>
       <c r="C360" t="s">
-        <v>3486</v>
+        <v>2985</v>
       </c>
       <c r="D360" t="s">
-        <v>1048</v>
+        <v>3062</v>
       </c>
       <c r="E360" t="s">
-        <v>3591</v>
+        <v>3063</v>
       </c>
       <c r="F360" t="s">
-        <v>3587</v>
+        <v>3065</v>
       </c>
       <c r="G360" t="s">
-        <v>3593</v>
+        <v>3066</v>
       </c>
       <c r="H360" t="s">
-        <v>3595</v>
+        <v>3068</v>
       </c>
       <c r="I360" t="s">
-        <v>79</v>
+        <v>3069</v>
       </c>
       <c r="J360" t="s">
-        <v>79</v>
+        <v>3070</v>
       </c>
       <c r="K360" t="s">
-        <v>3592</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B361">
         <v>82</v>
       </c>
       <c r="C361" t="s">
-        <v>3628</v>
+        <v>3486</v>
       </c>
       <c r="D361" t="s">
-        <v>3637</v>
+        <v>1048</v>
       </c>
       <c r="E361" t="s">
-        <v>3638</v>
+        <v>3591</v>
       </c>
       <c r="F361" t="s">
-        <v>16</v>
+        <v>3587</v>
       </c>
       <c r="G361" t="s">
-        <v>3640</v>
+        <v>3593</v>
       </c>
       <c r="H361" t="s">
-        <v>3642</v>
+        <v>3595</v>
       </c>
       <c r="I361" t="s">
-        <v>3643</v>
+        <v>79</v>
       </c>
       <c r="J361" t="s">
-        <v>3644</v>
+        <v>79</v>
       </c>
       <c r="K361" t="s">
-        <v>3639</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B362">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C362" t="s">
-        <v>12</v>
+        <v>3628</v>
       </c>
       <c r="D362" t="s">
-        <v>80</v>
+        <v>3637</v>
       </c>
       <c r="E362" t="s">
-        <v>81</v>
+        <v>3638</v>
       </c>
       <c r="F362" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G362" t="s">
-        <v>83</v>
+        <v>3640</v>
       </c>
       <c r="H362" t="s">
-        <v>85</v>
+        <v>3642</v>
       </c>
       <c r="I362" t="s">
-        <v>86</v>
+        <v>3643</v>
       </c>
       <c r="J362" t="s">
-        <v>87</v>
+        <v>3644</v>
       </c>
       <c r="K362" t="s">
-        <v>82</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
+        <v>3734</v>
+      </c>
+      <c r="B363">
+        <v>82</v>
+      </c>
+      <c r="C363" t="s">
+        <v>3707</v>
+      </c>
+      <c r="D363" t="s">
+        <v>3716</v>
+      </c>
+      <c r="E363" t="s">
+        <v>3717</v>
+      </c>
+      <c r="F363" t="s">
+        <v>3719</v>
+      </c>
+      <c r="G363" t="s">
+        <v>3720</v>
+      </c>
+      <c r="H363" t="s">
+        <v>3722</v>
+      </c>
+      <c r="I363" t="s">
+        <v>79</v>
+      </c>
+      <c r="J363" t="s">
+        <v>79</v>
+      </c>
+      <c r="K363" t="s">
         <v>3718</v>
-      </c>
-      <c r="B363">
-        <v>81</v>
-      </c>
-      <c r="C363" t="s">
-        <v>284</v>
-      </c>
-      <c r="D363" t="s">
-        <v>377</v>
-      </c>
-      <c r="E363" t="s">
-        <v>378</v>
-      </c>
-      <c r="F363" t="s">
-        <v>380</v>
-      </c>
-      <c r="G363" t="s">
-        <v>381</v>
-      </c>
-      <c r="H363" t="s">
-        <v>383</v>
-      </c>
-      <c r="I363" t="s">
-        <v>384</v>
-      </c>
-      <c r="J363" t="s">
-        <v>385</v>
-      </c>
-      <c r="K363" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B364">
         <v>81</v>
       </c>
       <c r="C364" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D364" t="s">
-        <v>499</v>
+        <v>80</v>
       </c>
       <c r="E364" t="s">
-        <v>500</v>
+        <v>81</v>
       </c>
       <c r="F364" t="s">
-        <v>502</v>
+        <v>25</v>
       </c>
       <c r="G364" t="s">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="H364" t="s">
-        <v>505</v>
+        <v>85</v>
       </c>
       <c r="I364" t="s">
-        <v>506</v>
+        <v>86</v>
       </c>
       <c r="J364" t="s">
-        <v>507</v>
+        <v>87</v>
       </c>
       <c r="K364" t="s">
-        <v>501</v>
+        <v>82</v>
       </c>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B365">
         <v>81</v>
       </c>
       <c r="C365" t="s">
-        <v>591</v>
+        <v>284</v>
       </c>
       <c r="D365" t="s">
-        <v>616</v>
+        <v>377</v>
       </c>
       <c r="E365" t="s">
-        <v>610</v>
+        <v>378</v>
       </c>
       <c r="F365" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G365" t="s">
-        <v>618</v>
+        <v>381</v>
       </c>
       <c r="H365" t="s">
-        <v>620</v>
+        <v>383</v>
       </c>
       <c r="I365" t="s">
-        <v>621</v>
+        <v>384</v>
       </c>
       <c r="J365" t="s">
-        <v>622</v>
+        <v>385</v>
       </c>
       <c r="K365" t="s">
-        <v>617</v>
+        <v>379</v>
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B366">
         <v>81</v>
       </c>
       <c r="C366" t="s">
-        <v>845</v>
+        <v>473</v>
       </c>
       <c r="D366" t="s">
-        <v>888</v>
+        <v>499</v>
       </c>
       <c r="E366" t="s">
-        <v>889</v>
+        <v>500</v>
       </c>
       <c r="F366" t="s">
-        <v>25</v>
+        <v>502</v>
       </c>
       <c r="G366" t="s">
-        <v>891</v>
+        <v>503</v>
       </c>
       <c r="H366" t="s">
-        <v>893</v>
+        <v>505</v>
       </c>
       <c r="I366" t="s">
-        <v>894</v>
+        <v>506</v>
       </c>
       <c r="J366" t="s">
-        <v>895</v>
+        <v>507</v>
       </c>
       <c r="K366" t="s">
-        <v>890</v>
+        <v>501</v>
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B367">
         <v>81</v>
       </c>
       <c r="C367" t="s">
-        <v>1087</v>
+        <v>591</v>
       </c>
       <c r="D367" t="s">
-        <v>1120</v>
+        <v>616</v>
       </c>
       <c r="E367" t="s">
-        <v>1121</v>
+        <v>610</v>
       </c>
       <c r="F367" t="s">
-        <v>1123</v>
+        <v>16</v>
       </c>
       <c r="G367" t="s">
-        <v>1124</v>
+        <v>618</v>
       </c>
       <c r="H367" t="s">
-        <v>1126</v>
+        <v>620</v>
       </c>
       <c r="I367" t="s">
-        <v>1127</v>
+        <v>621</v>
       </c>
       <c r="J367" t="s">
-        <v>1128</v>
+        <v>622</v>
       </c>
       <c r="K367" t="s">
-        <v>1122</v>
+        <v>617</v>
       </c>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B368">
         <v>81</v>
       </c>
       <c r="C368" t="s">
-        <v>1394</v>
+        <v>845</v>
       </c>
       <c r="D368" t="s">
-        <v>1412</v>
+        <v>888</v>
       </c>
       <c r="E368" t="s">
-        <v>1413</v>
+        <v>889</v>
       </c>
       <c r="F368" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G368" t="s">
-        <v>1415</v>
+        <v>891</v>
       </c>
       <c r="H368" t="s">
-        <v>1417</v>
+        <v>893</v>
       </c>
       <c r="I368" t="s">
-        <v>1418</v>
+        <v>894</v>
       </c>
       <c r="J368" t="s">
-        <v>1419</v>
+        <v>895</v>
       </c>
       <c r="K368" t="s">
-        <v>1414</v>
+        <v>890</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B369">
         <v>81</v>
       </c>
       <c r="C369" t="s">
-        <v>1394</v>
+        <v>1087</v>
       </c>
       <c r="D369" t="s">
-        <v>1420</v>
+        <v>1120</v>
       </c>
       <c r="E369" t="s">
-        <v>1421</v>
+        <v>1121</v>
       </c>
       <c r="F369" t="s">
-        <v>16</v>
+        <v>1123</v>
       </c>
       <c r="G369" t="s">
-        <v>1423</v>
+        <v>1124</v>
       </c>
       <c r="H369" t="s">
-        <v>1425</v>
+        <v>1126</v>
       </c>
       <c r="I369" t="s">
-        <v>1426</v>
+        <v>1127</v>
       </c>
       <c r="J369" t="s">
-        <v>1427</v>
+        <v>1128</v>
       </c>
       <c r="K369" t="s">
-        <v>1422</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B370">
         <v>81</v>
@@ -49491,313 +49615,313 @@
         <v>1394</v>
       </c>
       <c r="D370" t="s">
-        <v>1467</v>
+        <v>1412</v>
       </c>
       <c r="E370" t="s">
-        <v>1468</v>
+        <v>1413</v>
       </c>
       <c r="F370" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G370" t="s">
-        <v>1470</v>
+        <v>1415</v>
       </c>
       <c r="H370" t="s">
-        <v>1472</v>
+        <v>1417</v>
       </c>
       <c r="I370" t="s">
-        <v>1473</v>
+        <v>1418</v>
       </c>
       <c r="J370" t="s">
-        <v>1474</v>
+        <v>1419</v>
       </c>
       <c r="K370" t="s">
-        <v>1469</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B371">
         <v>81</v>
       </c>
       <c r="C371" t="s">
-        <v>1534</v>
+        <v>1394</v>
       </c>
       <c r="D371" t="s">
-        <v>271</v>
+        <v>1420</v>
       </c>
       <c r="E371" t="s">
-        <v>1600</v>
+        <v>1421</v>
       </c>
       <c r="F371" t="s">
-        <v>1602</v>
+        <v>16</v>
       </c>
       <c r="G371" t="s">
-        <v>1603</v>
+        <v>1423</v>
       </c>
       <c r="H371" t="s">
-        <v>1605</v>
+        <v>1425</v>
       </c>
       <c r="I371" t="s">
-        <v>1606</v>
+        <v>1426</v>
       </c>
       <c r="J371" t="s">
-        <v>1607</v>
+        <v>1427</v>
       </c>
       <c r="K371" t="s">
-        <v>1601</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B372">
         <v>81</v>
       </c>
       <c r="C372" t="s">
-        <v>1664</v>
+        <v>1394</v>
       </c>
       <c r="D372" t="s">
-        <v>1708</v>
+        <v>1467</v>
       </c>
       <c r="E372" t="s">
-        <v>1709</v>
+        <v>1468</v>
       </c>
       <c r="F372" t="s">
-        <v>1711</v>
+        <v>16</v>
       </c>
       <c r="G372" t="s">
-        <v>1034</v>
+        <v>1470</v>
       </c>
       <c r="H372" t="s">
-        <v>1713</v>
+        <v>1472</v>
       </c>
       <c r="I372" t="s">
-        <v>1714</v>
+        <v>1473</v>
       </c>
       <c r="J372" t="s">
-        <v>1715</v>
+        <v>1474</v>
       </c>
       <c r="K372" t="s">
-        <v>1710</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B373">
         <v>81</v>
       </c>
       <c r="C373" t="s">
-        <v>1727</v>
+        <v>1534</v>
       </c>
       <c r="D373" t="s">
-        <v>1773</v>
+        <v>271</v>
       </c>
       <c r="E373" t="s">
-        <v>1774</v>
+        <v>1600</v>
       </c>
       <c r="F373" t="s">
-        <v>16</v>
+        <v>1602</v>
       </c>
       <c r="G373" t="s">
-        <v>1776</v>
+        <v>1603</v>
       </c>
       <c r="H373" t="s">
-        <v>1778</v>
+        <v>1605</v>
       </c>
       <c r="I373" t="s">
-        <v>79</v>
+        <v>1606</v>
       </c>
       <c r="J373" t="s">
-        <v>79</v>
+        <v>1607</v>
       </c>
       <c r="K373" t="s">
-        <v>1775</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B374">
         <v>81</v>
       </c>
       <c r="C374" t="s">
-        <v>1727</v>
+        <v>1664</v>
       </c>
       <c r="D374" t="s">
-        <v>964</v>
+        <v>1708</v>
       </c>
       <c r="E374" t="s">
-        <v>362</v>
+        <v>1709</v>
       </c>
       <c r="F374" t="s">
-        <v>356</v>
+        <v>1711</v>
       </c>
       <c r="G374" t="s">
-        <v>1792</v>
+        <v>1034</v>
       </c>
       <c r="H374" t="s">
-        <v>1794</v>
+        <v>1713</v>
       </c>
       <c r="I374" t="s">
-        <v>79</v>
+        <v>1714</v>
       </c>
       <c r="J374" t="s">
-        <v>79</v>
+        <v>1715</v>
       </c>
       <c r="K374" t="s">
-        <v>1791</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B375">
         <v>81</v>
       </c>
       <c r="C375" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D375" t="s">
-        <v>1963</v>
+        <v>1773</v>
       </c>
       <c r="E375" t="s">
-        <v>1964</v>
+        <v>1774</v>
       </c>
       <c r="F375" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G375" t="s">
-        <v>1034</v>
+        <v>1776</v>
       </c>
       <c r="H375" t="s">
-        <v>1967</v>
+        <v>1778</v>
       </c>
       <c r="I375" t="s">
-        <v>1968</v>
+        <v>79</v>
       </c>
       <c r="J375" t="s">
-        <v>1969</v>
+        <v>79</v>
       </c>
       <c r="K375" t="s">
-        <v>1965</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B376">
         <v>81</v>
       </c>
       <c r="C376" t="s">
-        <v>1884</v>
+        <v>1727</v>
       </c>
       <c r="D376" t="s">
-        <v>1979</v>
+        <v>964</v>
       </c>
       <c r="E376" t="s">
-        <v>1988</v>
+        <v>362</v>
       </c>
       <c r="F376" t="s">
-        <v>1982</v>
+        <v>356</v>
       </c>
       <c r="G376" t="s">
-        <v>1983</v>
+        <v>1792</v>
       </c>
       <c r="H376" t="s">
-        <v>1991</v>
+        <v>1794</v>
       </c>
       <c r="I376" t="s">
-        <v>1992</v>
+        <v>79</v>
       </c>
       <c r="J376" t="s">
-        <v>1993</v>
+        <v>79</v>
       </c>
       <c r="K376" t="s">
-        <v>1989</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B377">
         <v>81</v>
       </c>
       <c r="C377" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D377" t="s">
-        <v>2114</v>
+        <v>1963</v>
       </c>
       <c r="E377" t="s">
-        <v>830</v>
+        <v>1964</v>
       </c>
       <c r="F377" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G377" t="s">
-        <v>2116</v>
+        <v>1034</v>
       </c>
       <c r="H377" t="s">
-        <v>2118</v>
+        <v>1967</v>
       </c>
       <c r="I377" t="s">
-        <v>2119</v>
+        <v>1968</v>
       </c>
       <c r="J377" t="s">
-        <v>2120</v>
+        <v>1969</v>
       </c>
       <c r="K377" t="s">
-        <v>2115</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B378">
         <v>81</v>
       </c>
       <c r="C378" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D378" t="s">
-        <v>2126</v>
+        <v>1979</v>
       </c>
       <c r="E378" t="s">
-        <v>2127</v>
+        <v>1988</v>
       </c>
       <c r="F378" t="s">
-        <v>16</v>
+        <v>1982</v>
       </c>
       <c r="G378" t="s">
-        <v>2129</v>
+        <v>1983</v>
       </c>
       <c r="H378" t="s">
-        <v>2118</v>
+        <v>1991</v>
       </c>
       <c r="I378" t="s">
-        <v>2131</v>
+        <v>1992</v>
       </c>
       <c r="J378" t="s">
-        <v>2132</v>
+        <v>1993</v>
       </c>
       <c r="K378" t="s">
-        <v>2128</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B379">
         <v>81</v>
@@ -49806,33 +49930,33 @@
         <v>2098</v>
       </c>
       <c r="D379" t="s">
-        <v>2148</v>
+        <v>2114</v>
       </c>
       <c r="E379" t="s">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="F379" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G379" t="s">
-        <v>2150</v>
+        <v>2116</v>
       </c>
       <c r="H379" t="s">
-        <v>2152</v>
+        <v>2118</v>
       </c>
       <c r="I379" t="s">
-        <v>2153</v>
+        <v>2119</v>
       </c>
       <c r="J379" t="s">
-        <v>2154</v>
+        <v>2120</v>
       </c>
       <c r="K379" t="s">
-        <v>2149</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B380">
         <v>81</v>
@@ -49841,33 +49965,33 @@
         <v>2098</v>
       </c>
       <c r="D380" t="s">
-        <v>2184</v>
+        <v>2126</v>
       </c>
       <c r="E380" t="s">
-        <v>2177</v>
+        <v>2127</v>
       </c>
       <c r="F380" t="s">
-        <v>2042</v>
+        <v>16</v>
       </c>
       <c r="G380" t="s">
-        <v>2186</v>
+        <v>2129</v>
       </c>
       <c r="H380" t="s">
-        <v>2188</v>
+        <v>2118</v>
       </c>
       <c r="I380" t="s">
-        <v>2189</v>
+        <v>2131</v>
       </c>
       <c r="J380" t="s">
-        <v>2190</v>
+        <v>2132</v>
       </c>
       <c r="K380" t="s">
-        <v>2185</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B381">
         <v>81</v>
@@ -49876,593 +50000,593 @@
         <v>2098</v>
       </c>
       <c r="D381" t="s">
-        <v>2211</v>
+        <v>2148</v>
       </c>
       <c r="E381" t="s">
         <v>110</v>
       </c>
       <c r="F381" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G381" t="s">
-        <v>2220</v>
+        <v>2150</v>
       </c>
       <c r="H381" t="s">
-        <v>2222</v>
+        <v>2152</v>
       </c>
       <c r="I381" t="s">
-        <v>2223</v>
+        <v>2153</v>
       </c>
       <c r="J381" t="s">
-        <v>2224</v>
+        <v>2154</v>
       </c>
       <c r="K381" t="s">
-        <v>2219</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B382">
         <v>81</v>
       </c>
       <c r="C382" t="s">
-        <v>2258</v>
+        <v>2098</v>
       </c>
       <c r="D382" t="s">
-        <v>2274</v>
+        <v>2184</v>
       </c>
       <c r="E382" t="s">
-        <v>2275</v>
+        <v>2177</v>
       </c>
       <c r="F382" t="s">
-        <v>2277</v>
+        <v>2042</v>
       </c>
       <c r="G382" t="s">
-        <v>2278</v>
+        <v>2186</v>
       </c>
       <c r="H382" t="s">
-        <v>2280</v>
+        <v>2188</v>
       </c>
       <c r="I382" t="s">
-        <v>2281</v>
+        <v>2189</v>
       </c>
       <c r="J382" t="s">
-        <v>2282</v>
+        <v>2190</v>
       </c>
       <c r="K382" t="s">
-        <v>2276</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B383">
         <v>81</v>
       </c>
       <c r="C383" t="s">
-        <v>2377</v>
+        <v>2098</v>
       </c>
       <c r="D383" t="s">
-        <v>2400</v>
+        <v>2211</v>
       </c>
       <c r="E383" t="s">
-        <v>2401</v>
+        <v>110</v>
       </c>
       <c r="F383" t="s">
         <v>16</v>
       </c>
       <c r="G383" t="s">
-        <v>2395</v>
+        <v>2220</v>
       </c>
       <c r="H383" t="s">
-        <v>2404</v>
+        <v>2222</v>
       </c>
       <c r="I383" t="s">
-        <v>2405</v>
+        <v>2223</v>
       </c>
       <c r="J383" t="s">
-        <v>2406</v>
+        <v>2224</v>
       </c>
       <c r="K383" t="s">
-        <v>2402</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B384">
         <v>81</v>
       </c>
       <c r="C384" t="s">
-        <v>2692</v>
+        <v>2258</v>
       </c>
       <c r="D384" t="s">
-        <v>2719</v>
+        <v>2274</v>
       </c>
       <c r="E384" t="s">
-        <v>2720</v>
+        <v>2275</v>
       </c>
       <c r="F384" t="s">
-        <v>66</v>
+        <v>2277</v>
       </c>
       <c r="G384" t="s">
-        <v>2722</v>
+        <v>2278</v>
       </c>
       <c r="H384" t="s">
-        <v>505</v>
+        <v>2280</v>
       </c>
       <c r="I384" t="s">
-        <v>79</v>
+        <v>2281</v>
       </c>
       <c r="J384" t="s">
-        <v>79</v>
+        <v>2282</v>
       </c>
       <c r="K384" t="s">
-        <v>2721</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B385">
         <v>81</v>
       </c>
       <c r="C385" t="s">
-        <v>2760</v>
+        <v>2377</v>
       </c>
       <c r="D385" t="s">
-        <v>2831</v>
+        <v>2400</v>
       </c>
       <c r="E385" t="s">
-        <v>2177</v>
+        <v>2401</v>
       </c>
       <c r="F385" t="s">
-        <v>2833</v>
+        <v>16</v>
       </c>
       <c r="G385" t="s">
-        <v>2834</v>
+        <v>2395</v>
       </c>
       <c r="H385" t="s">
-        <v>2836</v>
+        <v>2404</v>
       </c>
       <c r="I385" t="s">
-        <v>2837</v>
+        <v>2405</v>
       </c>
       <c r="J385" t="s">
-        <v>2838</v>
+        <v>2406</v>
       </c>
       <c r="K385" t="s">
-        <v>2832</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B386">
         <v>81</v>
       </c>
       <c r="C386" t="s">
-        <v>2871</v>
+        <v>2692</v>
       </c>
       <c r="D386" t="s">
-        <v>2936</v>
+        <v>2719</v>
       </c>
       <c r="E386" t="s">
-        <v>2937</v>
+        <v>2720</v>
       </c>
       <c r="F386" t="s">
-        <v>2939</v>
+        <v>66</v>
       </c>
       <c r="G386" t="s">
-        <v>2940</v>
+        <v>2722</v>
       </c>
       <c r="H386" t="s">
-        <v>2942</v>
+        <v>505</v>
       </c>
       <c r="I386" t="s">
-        <v>2943</v>
+        <v>79</v>
       </c>
       <c r="J386" t="s">
-        <v>2944</v>
+        <v>79</v>
       </c>
       <c r="K386" t="s">
-        <v>2938</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B387">
         <v>81</v>
       </c>
       <c r="C387" t="s">
-        <v>2985</v>
+        <v>2760</v>
       </c>
       <c r="D387" t="s">
-        <v>3071</v>
+        <v>2831</v>
       </c>
       <c r="E387" t="s">
-        <v>3072</v>
+        <v>2177</v>
       </c>
       <c r="F387" t="s">
-        <v>3074</v>
+        <v>2833</v>
       </c>
       <c r="G387" t="s">
-        <v>3012</v>
+        <v>2834</v>
       </c>
       <c r="H387" t="s">
-        <v>3076</v>
+        <v>2836</v>
       </c>
       <c r="I387" t="s">
-        <v>3077</v>
+        <v>2837</v>
       </c>
       <c r="J387" t="s">
-        <v>3078</v>
+        <v>2838</v>
       </c>
       <c r="K387" t="s">
-        <v>3073</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B388">
         <v>81</v>
       </c>
       <c r="C388" t="s">
-        <v>3243</v>
+        <v>2871</v>
       </c>
       <c r="D388" t="s">
-        <v>3303</v>
+        <v>2936</v>
       </c>
       <c r="E388" t="s">
-        <v>3304</v>
+        <v>2937</v>
       </c>
       <c r="F388" t="s">
-        <v>66</v>
+        <v>2939</v>
       </c>
       <c r="G388" t="s">
-        <v>3306</v>
+        <v>2940</v>
       </c>
       <c r="H388" t="s">
-        <v>3308</v>
+        <v>2942</v>
       </c>
       <c r="I388" t="s">
-        <v>3309</v>
+        <v>2943</v>
       </c>
       <c r="J388" t="s">
-        <v>3310</v>
+        <v>2944</v>
       </c>
       <c r="K388" t="s">
-        <v>3305</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B389">
         <v>81</v>
       </c>
       <c r="C389" t="s">
-        <v>3311</v>
+        <v>2985</v>
       </c>
       <c r="D389" t="s">
-        <v>1048</v>
+        <v>3071</v>
       </c>
       <c r="E389" t="s">
-        <v>3312</v>
+        <v>3072</v>
       </c>
       <c r="F389" t="s">
-        <v>3298</v>
+        <v>3074</v>
       </c>
       <c r="G389" t="s">
-        <v>3314</v>
+        <v>3012</v>
       </c>
       <c r="H389" t="s">
-        <v>3316</v>
+        <v>3076</v>
       </c>
       <c r="I389" t="s">
-        <v>79</v>
+        <v>3077</v>
       </c>
       <c r="J389" t="s">
-        <v>79</v>
+        <v>3078</v>
       </c>
       <c r="K389" t="s">
-        <v>3313</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B390">
         <v>81</v>
       </c>
       <c r="C390" t="s">
-        <v>3321</v>
+        <v>3243</v>
       </c>
       <c r="D390" t="s">
-        <v>3355</v>
+        <v>3303</v>
       </c>
       <c r="E390" t="s">
-        <v>610</v>
+        <v>3304</v>
       </c>
       <c r="F390" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G390" t="s">
-        <v>1312</v>
+        <v>3306</v>
       </c>
       <c r="H390" t="s">
-        <v>3358</v>
+        <v>3308</v>
       </c>
       <c r="I390" t="s">
-        <v>3359</v>
+        <v>3309</v>
       </c>
       <c r="J390" t="s">
-        <v>3360</v>
+        <v>3310</v>
       </c>
       <c r="K390" t="s">
-        <v>3356</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B391">
         <v>81</v>
       </c>
       <c r="C391" t="s">
-        <v>3369</v>
+        <v>3311</v>
       </c>
       <c r="D391" t="s">
-        <v>3453</v>
+        <v>1048</v>
       </c>
       <c r="E391" t="s">
-        <v>1130</v>
+        <v>3312</v>
       </c>
       <c r="F391" t="s">
-        <v>75</v>
+        <v>3298</v>
       </c>
       <c r="G391" t="s">
-        <v>3455</v>
+        <v>3314</v>
       </c>
       <c r="H391" t="s">
-        <v>3457</v>
+        <v>3316</v>
       </c>
       <c r="I391" t="s">
-        <v>3458</v>
+        <v>79</v>
       </c>
       <c r="J391" t="s">
-        <v>3459</v>
+        <v>79</v>
       </c>
       <c r="K391" t="s">
-        <v>3454</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B392">
         <v>81</v>
       </c>
       <c r="C392" t="s">
-        <v>3460</v>
+        <v>3321</v>
       </c>
       <c r="D392" t="s">
-        <v>3461</v>
+        <v>3355</v>
       </c>
       <c r="E392" t="s">
-        <v>3462</v>
+        <v>610</v>
       </c>
       <c r="F392" t="s">
         <v>25</v>
       </c>
       <c r="G392" t="s">
-        <v>3464</v>
+        <v>1312</v>
       </c>
       <c r="H392" t="s">
-        <v>3466</v>
+        <v>3358</v>
       </c>
       <c r="I392" t="s">
-        <v>79</v>
+        <v>3359</v>
       </c>
       <c r="J392" t="s">
-        <v>79</v>
+        <v>3360</v>
       </c>
       <c r="K392" t="s">
-        <v>3463</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B393">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C393" t="s">
-        <v>934</v>
+        <v>3369</v>
       </c>
       <c r="D393" t="s">
-        <v>1039</v>
+        <v>3453</v>
       </c>
       <c r="E393" t="s">
-        <v>1040</v>
+        <v>1130</v>
       </c>
       <c r="F393" t="s">
-        <v>1042</v>
+        <v>75</v>
       </c>
       <c r="G393" t="s">
-        <v>1043</v>
+        <v>3455</v>
       </c>
       <c r="H393" t="s">
-        <v>1045</v>
+        <v>3457</v>
       </c>
       <c r="I393" t="s">
-        <v>1046</v>
+        <v>3458</v>
       </c>
       <c r="J393" t="s">
-        <v>1047</v>
+        <v>3459</v>
       </c>
       <c r="K393" t="s">
-        <v>1041</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B394">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C394" t="s">
-        <v>1884</v>
+        <v>3460</v>
       </c>
       <c r="D394" t="s">
-        <v>1947</v>
+        <v>3461</v>
       </c>
       <c r="E394" t="s">
-        <v>1948</v>
+        <v>3462</v>
       </c>
       <c r="F394" t="s">
-        <v>1950</v>
+        <v>25</v>
       </c>
       <c r="G394" t="s">
-        <v>1034</v>
+        <v>3464</v>
       </c>
       <c r="H394" t="s">
-        <v>1952</v>
+        <v>3466</v>
       </c>
       <c r="I394" t="s">
-        <v>1953</v>
+        <v>79</v>
       </c>
       <c r="J394" t="s">
-        <v>1954</v>
+        <v>79</v>
       </c>
       <c r="K394" t="s">
-        <v>1949</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B395">
         <v>80</v>
       </c>
       <c r="C395" t="s">
-        <v>1884</v>
+        <v>934</v>
       </c>
       <c r="D395" t="s">
-        <v>1970</v>
+        <v>1039</v>
       </c>
       <c r="E395" t="s">
-        <v>1971</v>
+        <v>1040</v>
       </c>
       <c r="F395" t="s">
-        <v>1973</v>
+        <v>1042</v>
       </c>
       <c r="G395" t="s">
-        <v>1974</v>
+        <v>1043</v>
       </c>
       <c r="H395" t="s">
-        <v>1976</v>
+        <v>1045</v>
       </c>
       <c r="I395" t="s">
-        <v>1977</v>
+        <v>1046</v>
       </c>
       <c r="J395" t="s">
-        <v>1978</v>
+        <v>1047</v>
       </c>
       <c r="K395" t="s">
-        <v>1972</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B396">
         <v>80</v>
       </c>
       <c r="C396" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D396" t="s">
-        <v>2107</v>
+        <v>1947</v>
       </c>
       <c r="E396" t="s">
-        <v>830</v>
+        <v>1948</v>
       </c>
       <c r="F396" t="s">
-        <v>66</v>
+        <v>1950</v>
       </c>
       <c r="G396" t="s">
-        <v>2109</v>
+        <v>1034</v>
       </c>
       <c r="H396" t="s">
-        <v>2111</v>
+        <v>1952</v>
       </c>
       <c r="I396" t="s">
-        <v>2112</v>
+        <v>1953</v>
       </c>
       <c r="J396" t="s">
-        <v>2113</v>
+        <v>1954</v>
       </c>
       <c r="K396" t="s">
-        <v>2108</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B397">
         <v>80</v>
       </c>
       <c r="C397" t="s">
-        <v>2098</v>
+        <v>1884</v>
       </c>
       <c r="D397" t="s">
-        <v>2133</v>
+        <v>1970</v>
       </c>
       <c r="E397" t="s">
-        <v>110</v>
+        <v>1971</v>
       </c>
       <c r="F397" t="s">
-        <v>16</v>
+        <v>1973</v>
       </c>
       <c r="G397" t="s">
-        <v>2135</v>
+        <v>1974</v>
       </c>
       <c r="H397" t="s">
-        <v>2137</v>
+        <v>1976</v>
       </c>
       <c r="I397" t="s">
-        <v>2138</v>
+        <v>1977</v>
       </c>
       <c r="J397" t="s">
-        <v>2139</v>
+        <v>1978</v>
       </c>
       <c r="K397" t="s">
-        <v>2134</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B398">
         <v>80</v>
@@ -50471,33 +50595,33 @@
         <v>2098</v>
       </c>
       <c r="D398" t="s">
-        <v>2140</v>
+        <v>2107</v>
       </c>
       <c r="E398" t="s">
-        <v>2141</v>
+        <v>830</v>
       </c>
       <c r="F398" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G398" t="s">
-        <v>2143</v>
+        <v>2109</v>
       </c>
       <c r="H398" t="s">
-        <v>2145</v>
+        <v>2111</v>
       </c>
       <c r="I398" t="s">
-        <v>2146</v>
+        <v>2112</v>
       </c>
       <c r="J398" t="s">
-        <v>2147</v>
+        <v>2113</v>
       </c>
       <c r="K398" t="s">
-        <v>2142</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B399">
         <v>80</v>
@@ -50506,33 +50630,33 @@
         <v>2098</v>
       </c>
       <c r="D399" t="s">
-        <v>2155</v>
+        <v>2133</v>
       </c>
       <c r="E399" t="s">
         <v>110</v>
       </c>
       <c r="F399" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G399" t="s">
-        <v>2157</v>
+        <v>2135</v>
       </c>
       <c r="H399" t="s">
-        <v>2159</v>
+        <v>2137</v>
       </c>
       <c r="I399" t="s">
-        <v>2160</v>
+        <v>2138</v>
       </c>
       <c r="J399" t="s">
-        <v>2161</v>
+        <v>2139</v>
       </c>
       <c r="K399" t="s">
-        <v>2156</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B400">
         <v>80</v>
@@ -50541,33 +50665,33 @@
         <v>2098</v>
       </c>
       <c r="D400" t="s">
-        <v>2162</v>
+        <v>2140</v>
       </c>
       <c r="E400" t="s">
-        <v>110</v>
+        <v>2141</v>
       </c>
       <c r="F400" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G400" t="s">
-        <v>2171</v>
+        <v>2143</v>
       </c>
       <c r="H400" t="s">
-        <v>2173</v>
+        <v>2145</v>
       </c>
       <c r="I400" t="s">
-        <v>2174</v>
+        <v>2146</v>
       </c>
       <c r="J400" t="s">
-        <v>2175</v>
+        <v>2147</v>
       </c>
       <c r="K400" t="s">
-        <v>2170</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B401">
         <v>80</v>
@@ -50576,33 +50700,33 @@
         <v>2098</v>
       </c>
       <c r="D401" t="s">
-        <v>2203</v>
+        <v>2155</v>
       </c>
       <c r="E401" t="s">
-        <v>2204</v>
+        <v>110</v>
       </c>
       <c r="F401" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="G401" t="s">
-        <v>2206</v>
+        <v>2157</v>
       </c>
       <c r="H401" t="s">
-        <v>2208</v>
+        <v>2159</v>
       </c>
       <c r="I401" t="s">
-        <v>2209</v>
+        <v>2160</v>
       </c>
       <c r="J401" t="s">
-        <v>2210</v>
+        <v>2161</v>
       </c>
       <c r="K401" t="s">
-        <v>2205</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B402">
         <v>80</v>
@@ -50611,237 +50735,307 @@
         <v>2098</v>
       </c>
       <c r="D402" t="s">
-        <v>2225</v>
+        <v>2162</v>
       </c>
       <c r="E402" t="s">
-        <v>2226</v>
+        <v>110</v>
       </c>
       <c r="F402" t="s">
         <v>16</v>
       </c>
       <c r="G402" t="s">
-        <v>112</v>
+        <v>2171</v>
       </c>
       <c r="H402" t="s">
-        <v>2229</v>
+        <v>2173</v>
       </c>
       <c r="I402" t="s">
-        <v>2230</v>
+        <v>2174</v>
       </c>
       <c r="J402" t="s">
-        <v>2231</v>
+        <v>2175</v>
       </c>
       <c r="K402" t="s">
-        <v>2227</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B403">
         <v>80</v>
       </c>
       <c r="C403" t="s">
-        <v>2258</v>
+        <v>2098</v>
       </c>
       <c r="D403" t="s">
-        <v>2292</v>
+        <v>2203</v>
       </c>
       <c r="E403" t="s">
-        <v>2293</v>
+        <v>2204</v>
       </c>
       <c r="F403" t="s">
-        <v>747</v>
+        <v>106</v>
       </c>
       <c r="G403" t="s">
-        <v>2295</v>
+        <v>2206</v>
       </c>
       <c r="H403" t="s">
-        <v>2297</v>
+        <v>2208</v>
       </c>
       <c r="I403" t="s">
-        <v>2298</v>
+        <v>2209</v>
       </c>
       <c r="J403" t="s">
-        <v>2299</v>
+        <v>2210</v>
       </c>
       <c r="K403" t="s">
-        <v>2294</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B404">
         <v>80</v>
       </c>
       <c r="C404" t="s">
-        <v>2377</v>
+        <v>2098</v>
       </c>
       <c r="D404" t="s">
-        <v>2392</v>
+        <v>2225</v>
       </c>
       <c r="E404" t="s">
-        <v>2393</v>
+        <v>2226</v>
       </c>
       <c r="F404" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G404" t="s">
-        <v>2395</v>
+        <v>112</v>
       </c>
       <c r="H404" t="s">
-        <v>2397</v>
+        <v>2229</v>
       </c>
       <c r="I404" t="s">
-        <v>2398</v>
+        <v>2230</v>
       </c>
       <c r="J404" t="s">
-        <v>2399</v>
+        <v>2231</v>
       </c>
       <c r="K404" t="s">
-        <v>2394</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B405">
         <v>80</v>
       </c>
       <c r="C405" t="s">
-        <v>2377</v>
+        <v>2258</v>
       </c>
       <c r="D405" t="s">
-        <v>2414</v>
+        <v>2292</v>
       </c>
       <c r="E405" t="s">
-        <v>2415</v>
+        <v>2293</v>
       </c>
       <c r="F405" t="s">
-        <v>124</v>
+        <v>747</v>
       </c>
       <c r="G405" t="s">
-        <v>2417</v>
+        <v>2295</v>
       </c>
       <c r="H405" t="s">
-        <v>2419</v>
+        <v>2297</v>
       </c>
       <c r="I405" t="s">
-        <v>2420</v>
+        <v>2298</v>
       </c>
       <c r="J405" t="s">
-        <v>2421</v>
+        <v>2299</v>
       </c>
       <c r="K405" t="s">
-        <v>2416</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B406">
         <v>80</v>
       </c>
       <c r="C406" t="s">
-        <v>2760</v>
+        <v>2377</v>
       </c>
       <c r="D406" t="s">
-        <v>1681</v>
+        <v>2392</v>
       </c>
       <c r="E406" t="s">
-        <v>2864</v>
+        <v>2393</v>
       </c>
       <c r="F406" t="s">
-        <v>1684</v>
+        <v>66</v>
       </c>
       <c r="G406" t="s">
-        <v>2866</v>
+        <v>2395</v>
       </c>
       <c r="H406" t="s">
-        <v>2868</v>
+        <v>2397</v>
       </c>
       <c r="I406" t="s">
-        <v>2869</v>
+        <v>2398</v>
       </c>
       <c r="J406" t="s">
-        <v>2870</v>
+        <v>2399</v>
       </c>
       <c r="K406" t="s">
-        <v>2865</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B407">
         <v>80</v>
       </c>
       <c r="C407" t="s">
-        <v>3311</v>
+        <v>2377</v>
       </c>
       <c r="D407" t="s">
-        <v>1048</v>
+        <v>2414</v>
       </c>
       <c r="E407" t="s">
-        <v>3317</v>
+        <v>2415</v>
       </c>
       <c r="F407" t="s">
-        <v>3298</v>
+        <v>124</v>
       </c>
       <c r="G407" t="s">
-        <v>3314</v>
+        <v>2417</v>
       </c>
       <c r="H407" t="s">
-        <v>3320</v>
+        <v>2419</v>
       </c>
       <c r="I407" t="s">
-        <v>79</v>
+        <v>2420</v>
       </c>
       <c r="J407" t="s">
-        <v>79</v>
+        <v>2421</v>
       </c>
       <c r="K407" t="s">
-        <v>3318</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>3718</v>
+        <v>3734</v>
       </c>
       <c r="B408">
         <v>80</v>
       </c>
       <c r="C408" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D408" t="s">
+        <v>1681</v>
+      </c>
+      <c r="E408" t="s">
+        <v>2864</v>
+      </c>
+      <c r="F408" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G408" t="s">
+        <v>2866</v>
+      </c>
+      <c r="H408" t="s">
+        <v>2868</v>
+      </c>
+      <c r="I408" t="s">
+        <v>2869</v>
+      </c>
+      <c r="J408" t="s">
+        <v>2870</v>
+      </c>
+      <c r="K408" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>3734</v>
+      </c>
+      <c r="B409">
+        <v>80</v>
+      </c>
+      <c r="C409" t="s">
+        <v>3311</v>
+      </c>
+      <c r="D409" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E409" t="s">
+        <v>3317</v>
+      </c>
+      <c r="F409" t="s">
+        <v>3298</v>
+      </c>
+      <c r="G409" t="s">
+        <v>3314</v>
+      </c>
+      <c r="H409" t="s">
+        <v>3320</v>
+      </c>
+      <c r="I409" t="s">
+        <v>79</v>
+      </c>
+      <c r="J409" t="s">
+        <v>79</v>
+      </c>
+      <c r="K409" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>3734</v>
+      </c>
+      <c r="B410">
+        <v>80</v>
+      </c>
+      <c r="C410" t="s">
         <v>3676</v>
       </c>
-      <c r="D408" t="s">
+      <c r="D410" t="s">
         <v>3689</v>
       </c>
-      <c r="E408" t="s">
+      <c r="E410" t="s">
         <v>3690</v>
       </c>
-      <c r="F408" t="s">
+      <c r="F410" t="s">
         <v>280</v>
       </c>
-      <c r="G408" t="s">
+      <c r="G410" t="s">
         <v>3692</v>
       </c>
-      <c r="H408" t="s">
+      <c r="H410" t="s">
         <v>3694</v>
       </c>
-      <c r="I408" t="s">
+      <c r="I410" t="s">
         <v>79</v>
       </c>
-      <c r="J408" t="s">
+      <c r="J410" t="s">
         <v>79</v>
       </c>
-      <c r="K408" t="s">
+      <c r="K410" t="s">
         <v>3691</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6349" uniqueCount="3044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6349" uniqueCount="3045">
   <si>
     <t>日期</t>
   </si>
@@ -9077,6 +9077,9 @@
   </si>
   <si>
     <t>数据更新日期</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
   </si>
   <si>
     <t>岗位总数</t>
@@ -32423,12 +32426,12 @@
         <v>3020</v>
       </c>
       <c r="B2" t="s">
-        <v>1119</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="B3">
         <v>444</v>
@@ -32436,7 +32439,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="B4">
         <v>112</v>
@@ -32444,7 +32447,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="B5">
         <v>444</v>
@@ -32452,7 +32455,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -32460,7 +32463,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -32468,7 +32471,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -32476,7 +32479,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="B9">
         <v>120</v>
@@ -32484,7 +32487,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="B10">
         <v>206</v>
@@ -32492,7 +32495,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3029</v>
+        <v>3030</v>
       </c>
       <c r="B11">
         <v>89</v>
@@ -32500,7 +32503,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="B12">
         <v>17</v>
@@ -32508,7 +32511,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -32516,48 +32519,48 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="B14" t="s">
-        <v>3033</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="B15" t="s">
-        <v>3035</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="B16" t="s">
-        <v>3037</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="18" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>3038</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="B19" t="s">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="C19" t="s">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="D19" t="s">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="E19" t="s">
-        <v>3043</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="2516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5173" uniqueCount="2510">
   <si>
     <t>日期</t>
   </si>
@@ -6031,24 +6031,6 @@
     <t>突出植入器械/生物材料研究背景；补充动物实验与生物相容性评价能力；强调产学研转化兴趣。</t>
   </si>
   <si>
-    <t>机械工程师（医疗器械方向）</t>
-  </si>
-  <si>
-    <t>负责产品结构设计，熟悉高分子材料/金属材料，有医疗背景优先。乐普为心血管支架龙头。</t>
-  </si>
-  <si>
-    <t>https://www.liepin.com/job/1983994883.shtml</t>
-  </si>
-  <si>
-    <t>技能70/公司100/方向75</t>
-  </si>
-  <si>
-    <t>乐普为心血管支架国产龙头（目标公司），岗位做产品结构设计并涉及高分子/金属材料，材料与结构设计技能对口，平台价值高。</t>
-  </si>
-  <si>
-    <t>突出材料学与结构设计项目；补充高分子/金属材料性能测试经验；强调医疗器械研发流程理解。</t>
-  </si>
-  <si>
     <t>导管研发工程师-电生理</t>
   </si>
   <si>
@@ -7531,19 +7513,19 @@
     <t>岗位族分布</t>
   </si>
   <si>
-    <t>{"研发":338,"工艺制造":9,"其他":6,"质量":3,"临床医学":1,"注册法规":3}</t>
+    <t>{"研发":337,"工艺制造":9,"其他":6,"质量":3,"临床医学":1,"注册法规":3}</t>
   </si>
   <si>
     <t>城市分布</t>
   </si>
   <si>
-    <t>{"上海":96,"深圳":66,"北京":48,"苏州":48,"杭州":23,"天津":8,"东莞":12,"未知":30,"无锡":4,"珠海":5,"广州":2,"厦门":6,"武汉":1,"南京":3,"常州":2,"嘉兴":1,"宁波":1,"成都":2,"佛山":1,"西安":1}</t>
+    <t>{"上海":96,"深圳":66,"北京":47,"苏州":48,"杭州":23,"天津":8,"东莞":12,"未知":30,"无锡":4,"珠海":5,"广州":2,"厦门":6,"武汉":1,"南京":3,"常州":2,"嘉兴":1,"宁波":1,"成都":2,"佛山":1,"西安":1}</t>
   </si>
   <si>
     <t>状态分布</t>
   </si>
   <si>
-    <t>{"unknown":330,"active":30}</t>
+    <t>{"unknown":329,"active":30}</t>
   </si>
   <si>
     <t>Top 20（分数降序）</t>
@@ -7959,7 +7941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P361"/>
+  <dimension ref="A1:P360"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -22131,10 +22113,10 @@
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>16</v>
+        <v>880</v>
       </c>
       <c r="B284" t="s">
-        <v>1081</v>
+        <v>881</v>
       </c>
       <c r="C284" t="s">
         <v>2005</v>
@@ -22143,7 +22125,7 @@
         <v>2006</v>
       </c>
       <c r="E284" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F284" s="4" t="s">
         <v>2007</v>
@@ -22152,19 +22134,19 @@
         <v>8</v>
       </c>
       <c r="H284" t="s">
-        <v>1923</v>
+        <v>2008</v>
       </c>
       <c r="I284">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J284" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="K284" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="L284" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="M284" t="s">
         <v>26</v>
@@ -22176,45 +22158,45 @@
         <v>28</v>
       </c>
       <c r="P284" t="s">
-        <v>29</v>
+        <v>889</v>
       </c>
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>880</v>
+        <v>2012</v>
       </c>
       <c r="B285" t="s">
-        <v>881</v>
+        <v>2013</v>
       </c>
       <c r="C285" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="E285" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="G285">
         <v>8</v>
       </c>
       <c r="H285" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="I285">
         <v>80</v>
       </c>
       <c r="J285" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="K285" t="s">
-        <v>2016</v>
+        <v>28</v>
       </c>
       <c r="L285" t="s">
-        <v>2017</v>
+        <v>28</v>
       </c>
       <c r="M285" t="s">
         <v>26</v>
@@ -22226,39 +22208,39 @@
         <v>28</v>
       </c>
       <c r="P285" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>2018</v>
+        <v>1316</v>
       </c>
       <c r="B286" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C286" t="s">
         <v>2019</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D286" s="3" t="s">
         <v>2020</v>
       </c>
-      <c r="D286" s="3" t="s">
+      <c r="E286" t="s">
+        <v>28</v>
+      </c>
+      <c r="F286" s="4" t="s">
         <v>2021</v>
-      </c>
-      <c r="E286" t="s">
-        <v>28</v>
-      </c>
-      <c r="F286" s="4" t="s">
-        <v>2022</v>
       </c>
       <c r="G286">
         <v>8</v>
       </c>
       <c r="H286" t="s">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="I286">
         <v>80</v>
       </c>
       <c r="J286" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="K286" t="s">
         <v>28</v>
@@ -22281,19 +22263,19 @@
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1316</v>
+        <v>243</v>
       </c>
       <c r="B287" t="s">
-        <v>1196</v>
+        <v>2023</v>
       </c>
       <c r="C287" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D287" s="3" t="s">
         <v>2025</v>
       </c>
-      <c r="D287" s="3" t="s">
+      <c r="E287" t="s">
         <v>2026</v>
-      </c>
-      <c r="E287" t="s">
-        <v>28</v>
       </c>
       <c r="F287" s="4" t="s">
         <v>2027</v>
@@ -22302,13 +22284,13 @@
         <v>8</v>
       </c>
       <c r="H287" t="s">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="I287">
         <v>80</v>
       </c>
       <c r="J287" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="K287" t="s">
         <v>28</v>
@@ -22331,19 +22313,19 @@
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="C288" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="E288" t="s">
-        <v>2032</v>
+        <v>28</v>
       </c>
       <c r="F288" s="4" t="s">
         <v>2033</v>
@@ -22361,16 +22343,16 @@
         <v>2035</v>
       </c>
       <c r="K288" t="s">
-        <v>28</v>
+        <v>2036</v>
       </c>
       <c r="L288" t="s">
-        <v>28</v>
+        <v>2037</v>
       </c>
       <c r="M288" t="s">
         <v>26</v>
       </c>
       <c r="N288" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O288" t="s">
         <v>28</v>
@@ -22381,46 +22363,46 @@
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>287</v>
+        <v>1571</v>
       </c>
       <c r="B289" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="C289" t="s">
-        <v>2037</v>
+        <v>1274</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="E289" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="G289">
         <v>8</v>
       </c>
       <c r="H289" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="I289">
         <v>80</v>
       </c>
       <c r="J289" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="K289" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="L289" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="M289" t="s">
         <v>26</v>
       </c>
       <c r="N289" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O289" t="s">
         <v>28</v>
@@ -22434,25 +22416,25 @@
         <v>1571</v>
       </c>
       <c r="B290" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="C290" t="s">
-        <v>1274</v>
+        <v>404</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="E290" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="G290">
         <v>8</v>
       </c>
       <c r="H290" t="s">
-        <v>2047</v>
+        <v>2041</v>
       </c>
       <c r="I290">
         <v>80</v>
@@ -22484,16 +22466,16 @@
         <v>1571</v>
       </c>
       <c r="B291" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C291" t="s">
         <v>2051</v>
-      </c>
-      <c r="C291" t="s">
-        <v>404</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>2052</v>
       </c>
       <c r="E291" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="F291" s="4" t="s">
         <v>2053</v>
@@ -22502,7 +22484,7 @@
         <v>8</v>
       </c>
       <c r="H291" t="s">
-        <v>2047</v>
+        <v>2041</v>
       </c>
       <c r="I291">
         <v>80</v>
@@ -22534,16 +22516,16 @@
         <v>1571</v>
       </c>
       <c r="B292" t="s">
-        <v>1130</v>
+        <v>2057</v>
       </c>
       <c r="C292" t="s">
-        <v>2057</v>
+        <v>404</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>2058</v>
       </c>
       <c r="E292" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>2059</v>
@@ -22552,7 +22534,7 @@
         <v>8</v>
       </c>
       <c r="H292" t="s">
-        <v>2047</v>
+        <v>2041</v>
       </c>
       <c r="I292">
         <v>80</v>
@@ -22587,34 +22569,34 @@
         <v>2063</v>
       </c>
       <c r="C293" t="s">
-        <v>404</v>
+        <v>2064</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="E293" t="s">
-        <v>34</v>
+        <v>620</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="G293">
         <v>8</v>
       </c>
       <c r="H293" t="s">
-        <v>2047</v>
+        <v>2017</v>
       </c>
       <c r="I293">
         <v>80</v>
       </c>
       <c r="J293" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="K293" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="L293" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="M293" t="s">
         <v>26</v>
@@ -22631,31 +22613,31 @@
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1571</v>
+        <v>880</v>
       </c>
       <c r="B294" t="s">
-        <v>2069</v>
+        <v>881</v>
       </c>
       <c r="C294" t="s">
         <v>2070</v>
       </c>
       <c r="D294" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E294" t="s">
+        <v>34</v>
+      </c>
+      <c r="F294" s="4" t="s">
         <v>2071</v>
-      </c>
-      <c r="E294" t="s">
-        <v>620</v>
-      </c>
-      <c r="F294" s="4" t="s">
-        <v>2072</v>
       </c>
       <c r="G294">
         <v>8</v>
       </c>
       <c r="H294" t="s">
-        <v>2023</v>
+        <v>2072</v>
       </c>
       <c r="I294">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J294" t="s">
         <v>2073</v>
@@ -22676,101 +22658,101 @@
         <v>28</v>
       </c>
       <c r="P294" t="s">
-        <v>29</v>
+        <v>889</v>
       </c>
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>880</v>
+        <v>2076</v>
       </c>
       <c r="B295" t="s">
-        <v>881</v>
+        <v>920</v>
       </c>
       <c r="C295" t="s">
-        <v>2076</v>
+        <v>332</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>1658</v>
+        <v>2077</v>
       </c>
       <c r="E295" t="s">
-        <v>34</v>
+        <v>923</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="G295">
         <v>8</v>
       </c>
       <c r="H295" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="I295">
         <v>79</v>
       </c>
       <c r="J295" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="K295" t="s">
-        <v>2080</v>
+        <v>28</v>
       </c>
       <c r="L295" t="s">
-        <v>2081</v>
+        <v>28</v>
       </c>
       <c r="M295" t="s">
         <v>26</v>
       </c>
       <c r="N295" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O295" t="s">
         <v>28</v>
       </c>
       <c r="P295" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
+        <v>287</v>
+      </c>
+      <c r="B296" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C296" t="s">
         <v>2082</v>
-      </c>
-      <c r="B296" t="s">
-        <v>920</v>
-      </c>
-      <c r="C296" t="s">
-        <v>332</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>2083</v>
       </c>
       <c r="E296" t="s">
-        <v>923</v>
+        <v>2084</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="G296">
         <v>8</v>
       </c>
       <c r="H296" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="I296">
         <v>79</v>
       </c>
       <c r="J296" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="K296" t="s">
-        <v>28</v>
+        <v>2088</v>
       </c>
       <c r="L296" t="s">
-        <v>28</v>
+        <v>2089</v>
       </c>
       <c r="M296" t="s">
         <v>26</v>
       </c>
       <c r="N296" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O296" t="s">
         <v>28</v>
@@ -22784,37 +22766,37 @@
         <v>287</v>
       </c>
       <c r="B297" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="C297" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="E297" t="s">
-        <v>2090</v>
+        <v>28</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="G297">
         <v>8</v>
       </c>
       <c r="H297" t="s">
-        <v>2092</v>
+        <v>2086</v>
       </c>
       <c r="I297">
         <v>79</v>
       </c>
       <c r="J297" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="K297" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="L297" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="M297" t="s">
         <v>26</v>
@@ -22831,19 +22813,19 @@
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>287</v>
+        <v>1571</v>
       </c>
       <c r="B298" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="C298" t="s">
-        <v>2097</v>
+        <v>1274</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>2098</v>
       </c>
       <c r="E298" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="F298" s="4" t="s">
         <v>2099</v>
@@ -22852,19 +22834,19 @@
         <v>8</v>
       </c>
       <c r="H298" t="s">
-        <v>2092</v>
+        <v>2100</v>
       </c>
       <c r="I298">
         <v>79</v>
       </c>
       <c r="J298" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="K298" t="s">
-        <v>2101</v>
+        <v>28</v>
       </c>
       <c r="L298" t="s">
-        <v>2102</v>
+        <v>28</v>
       </c>
       <c r="M298" t="s">
         <v>26</v>
@@ -22881,40 +22863,40 @@
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1571</v>
+        <v>638</v>
       </c>
       <c r="B299" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C299" t="s">
+        <v>679</v>
+      </c>
+      <c r="D299" s="3" t="s">
         <v>2103</v>
       </c>
-      <c r="C299" t="s">
-        <v>1274</v>
-      </c>
-      <c r="D299" s="3" t="s">
+      <c r="E299" t="s">
+        <v>67</v>
+      </c>
+      <c r="F299" s="4" t="s">
         <v>2104</v>
-      </c>
-      <c r="E299" t="s">
-        <v>77</v>
-      </c>
-      <c r="F299" s="4" t="s">
-        <v>2105</v>
       </c>
       <c r="G299">
         <v>8</v>
       </c>
       <c r="H299" t="s">
-        <v>2106</v>
+        <v>2100</v>
       </c>
       <c r="I299">
         <v>79</v>
       </c>
       <c r="J299" t="s">
-        <v>2107</v>
+        <v>1903</v>
       </c>
       <c r="K299" t="s">
-        <v>28</v>
+        <v>2105</v>
       </c>
       <c r="L299" t="s">
-        <v>28</v>
+        <v>2106</v>
       </c>
       <c r="M299" t="s">
         <v>26</v>
@@ -22931,13 +22913,13 @@
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>638</v>
+        <v>1240</v>
       </c>
       <c r="B300" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C300" t="s">
         <v>2108</v>
-      </c>
-      <c r="C300" t="s">
-        <v>679</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>2109</v>
@@ -22952,25 +22934,25 @@
         <v>8</v>
       </c>
       <c r="H300" t="s">
-        <v>2106</v>
+        <v>2111</v>
       </c>
       <c r="I300">
         <v>79</v>
       </c>
       <c r="J300" t="s">
-        <v>1903</v>
+        <v>2112</v>
       </c>
       <c r="K300" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="L300" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="M300" t="s">
         <v>26</v>
       </c>
       <c r="N300" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O300" t="s">
         <v>28</v>
@@ -22981,46 +22963,46 @@
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1240</v>
+        <v>2115</v>
       </c>
       <c r="B301" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="C301" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="E301" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="G301">
         <v>8</v>
       </c>
       <c r="H301" t="s">
-        <v>2117</v>
+        <v>2100</v>
       </c>
       <c r="I301">
         <v>79</v>
       </c>
       <c r="J301" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="K301" t="s">
-        <v>2119</v>
+        <v>28</v>
       </c>
       <c r="L301" t="s">
-        <v>2120</v>
+        <v>28</v>
       </c>
       <c r="M301" t="s">
         <v>26</v>
       </c>
       <c r="N301" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O301" t="s">
         <v>28</v>
@@ -23031,28 +23013,28 @@
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B302" t="s">
         <v>2121</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C302" t="s">
         <v>2122</v>
       </c>
-      <c r="C302" t="s">
+      <c r="D302" s="3" t="s">
         <v>2123</v>
       </c>
-      <c r="D302" s="3" t="s">
+      <c r="E302" t="s">
+        <v>77</v>
+      </c>
+      <c r="F302" s="4" t="s">
         <v>2124</v>
-      </c>
-      <c r="E302" t="s">
-        <v>20</v>
-      </c>
-      <c r="F302" s="4" t="s">
-        <v>2125</v>
       </c>
       <c r="G302">
         <v>8</v>
       </c>
       <c r="H302" t="s">
-        <v>2106</v>
+        <v>2125</v>
       </c>
       <c r="I302">
         <v>79</v>
@@ -23061,10 +23043,10 @@
         <v>2126</v>
       </c>
       <c r="K302" t="s">
-        <v>28</v>
+        <v>2127</v>
       </c>
       <c r="L302" t="s">
-        <v>28</v>
+        <v>2128</v>
       </c>
       <c r="M302" t="s">
         <v>26</v>
@@ -23081,46 +23063,46 @@
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="B303" t="s">
-        <v>2127</v>
+        <v>221</v>
       </c>
       <c r="C303" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="E303" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="G303">
         <v>8</v>
       </c>
       <c r="H303" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="I303">
         <v>79</v>
       </c>
       <c r="J303" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="K303" t="s">
-        <v>2133</v>
+        <v>28</v>
       </c>
       <c r="L303" t="s">
-        <v>2134</v>
+        <v>28</v>
       </c>
       <c r="M303" t="s">
         <v>26</v>
       </c>
       <c r="N303" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O303" t="s">
         <v>28</v>
@@ -23131,34 +23113,34 @@
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>1073</v>
+        <v>206</v>
       </c>
       <c r="B304" t="s">
-        <v>221</v>
+        <v>480</v>
       </c>
       <c r="C304" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D304" s="3" t="s">
         <v>2135</v>
       </c>
-      <c r="D304" s="3" t="s">
+      <c r="E304" t="s">
+        <v>20</v>
+      </c>
+      <c r="F304" s="4" t="s">
         <v>2136</v>
-      </c>
-      <c r="E304" t="s">
-        <v>34</v>
-      </c>
-      <c r="F304" s="4" t="s">
-        <v>2137</v>
       </c>
       <c r="G304">
         <v>8</v>
       </c>
       <c r="H304" t="s">
-        <v>2138</v>
+        <v>2100</v>
       </c>
       <c r="I304">
         <v>79</v>
       </c>
       <c r="J304" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="K304" t="s">
         <v>28</v>
@@ -23170,7 +23152,7 @@
         <v>26</v>
       </c>
       <c r="N304" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O304" t="s">
         <v>28</v>
@@ -23181,28 +23163,28 @@
     </row>
     <row r="305" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>206</v>
+        <v>16</v>
       </c>
       <c r="B305" t="s">
-        <v>480</v>
+        <v>2138</v>
       </c>
       <c r="C305" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D305" s="3" t="s">
         <v>2140</v>
       </c>
-      <c r="D305" s="3" t="s">
+      <c r="E305" t="s">
+        <v>620</v>
+      </c>
+      <c r="F305" s="4" t="s">
         <v>2141</v>
-      </c>
-      <c r="E305" t="s">
-        <v>20</v>
-      </c>
-      <c r="F305" s="4" t="s">
-        <v>2142</v>
       </c>
       <c r="G305">
         <v>8</v>
       </c>
       <c r="H305" t="s">
-        <v>2106</v>
+        <v>2142</v>
       </c>
       <c r="I305">
         <v>79</v>
@@ -23231,7 +23213,7 @@
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>16</v>
+        <v>1350</v>
       </c>
       <c r="B306" t="s">
         <v>2144</v>
@@ -23243,7 +23225,7 @@
         <v>2146</v>
       </c>
       <c r="E306" t="s">
-        <v>620</v>
+        <v>67</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>2147</v>
@@ -23255,19 +23237,19 @@
         <v>2148</v>
       </c>
       <c r="I306">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J306" t="s">
         <v>2149</v>
       </c>
       <c r="K306" t="s">
-        <v>28</v>
+        <v>2150</v>
       </c>
       <c r="L306" t="s">
-        <v>28</v>
+        <v>2151</v>
       </c>
       <c r="M306" t="s">
-        <v>26</v>
+        <v>2152</v>
       </c>
       <c r="N306" t="s">
         <v>27</v>
@@ -23281,43 +23263,43 @@
     </row>
     <row r="307" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1350</v>
+        <v>1240</v>
       </c>
       <c r="B307" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="C307" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="E307" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="G307">
         <v>8</v>
       </c>
       <c r="H307" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="I307">
         <v>78</v>
       </c>
       <c r="J307" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="K307" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="L307" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="M307" t="s">
-        <v>2158</v>
+        <v>563</v>
       </c>
       <c r="N307" t="s">
         <v>27</v>
@@ -23334,40 +23316,40 @@
         <v>1240</v>
       </c>
       <c r="B308" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="C308" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="E308" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="G308">
         <v>8</v>
       </c>
       <c r="H308" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I308">
         <v>78</v>
       </c>
       <c r="J308" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="K308" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="L308" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="M308" t="s">
-        <v>563</v>
+        <v>26</v>
       </c>
       <c r="N308" t="s">
         <v>27</v>
@@ -23381,43 +23363,43 @@
     </row>
     <row r="309" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1240</v>
+        <v>1300</v>
       </c>
       <c r="B309" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="C309" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="E309" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="G309">
         <v>8</v>
       </c>
       <c r="H309" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I309">
         <v>78</v>
       </c>
       <c r="J309" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="K309" t="s">
-        <v>2173</v>
+        <v>28</v>
       </c>
       <c r="L309" t="s">
-        <v>2174</v>
+        <v>28</v>
       </c>
       <c r="M309" t="s">
-        <v>26</v>
+        <v>2175</v>
       </c>
       <c r="N309" t="s">
         <v>27</v>
@@ -23431,34 +23413,34 @@
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1300</v>
+        <v>206</v>
       </c>
       <c r="B310" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="C310" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="E310" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="G310">
         <v>8</v>
       </c>
       <c r="H310" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="I310">
         <v>78</v>
       </c>
       <c r="J310" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="K310" t="s">
         <v>28</v>
@@ -23467,7 +23449,7 @@
         <v>28</v>
       </c>
       <c r="M310" t="s">
-        <v>2181</v>
+        <v>26</v>
       </c>
       <c r="N310" t="s">
         <v>27</v>
@@ -23487,28 +23469,28 @@
         <v>2182</v>
       </c>
       <c r="C311" t="s">
+        <v>679</v>
+      </c>
+      <c r="D311" s="3" t="s">
         <v>2183</v>
       </c>
-      <c r="D311" s="3" t="s">
+      <c r="E311" t="s">
+        <v>97</v>
+      </c>
+      <c r="F311" s="4" t="s">
         <v>2184</v>
-      </c>
-      <c r="E311" t="s">
-        <v>20</v>
-      </c>
-      <c r="F311" s="4" t="s">
-        <v>2185</v>
       </c>
       <c r="G311">
         <v>8</v>
       </c>
       <c r="H311" t="s">
-        <v>2186</v>
+        <v>2165</v>
       </c>
       <c r="I311">
         <v>78</v>
       </c>
       <c r="J311" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="K311" t="s">
         <v>28</v>
@@ -23531,34 +23513,34 @@
     </row>
     <row r="312" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>206</v>
+        <v>16</v>
       </c>
       <c r="B312" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C312" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D312" s="3" t="s">
         <v>2188</v>
       </c>
-      <c r="C312" t="s">
-        <v>679</v>
-      </c>
-      <c r="D312" s="3" t="s">
+      <c r="E312" t="s">
+        <v>20</v>
+      </c>
+      <c r="F312" s="4" t="s">
         <v>2189</v>
-      </c>
-      <c r="E312" t="s">
-        <v>97</v>
-      </c>
-      <c r="F312" s="4" t="s">
-        <v>2190</v>
       </c>
       <c r="G312">
         <v>8</v>
       </c>
       <c r="H312" t="s">
-        <v>2171</v>
+        <v>2180</v>
       </c>
       <c r="I312">
         <v>78</v>
       </c>
       <c r="J312" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K312" t="s">
         <v>28</v>
@@ -23584,31 +23566,31 @@
         <v>16</v>
       </c>
       <c r="B313" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C313" t="s">
         <v>2192</v>
       </c>
-      <c r="C313" t="s">
+      <c r="D313" s="3" t="s">
         <v>2193</v>
       </c>
-      <c r="D313" s="3" t="s">
+      <c r="E313" t="s">
+        <v>67</v>
+      </c>
+      <c r="F313" s="4" t="s">
         <v>2194</v>
-      </c>
-      <c r="E313" t="s">
-        <v>20</v>
-      </c>
-      <c r="F313" s="4" t="s">
-        <v>2195</v>
       </c>
       <c r="G313">
         <v>8</v>
       </c>
       <c r="H313" t="s">
-        <v>2186</v>
+        <v>2180</v>
       </c>
       <c r="I313">
         <v>78</v>
       </c>
       <c r="J313" t="s">
-        <v>2196</v>
+        <v>2181</v>
       </c>
       <c r="K313" t="s">
         <v>28</v>
@@ -23631,40 +23613,40 @@
     </row>
     <row r="314" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>16</v>
+        <v>880</v>
       </c>
       <c r="B314" t="s">
+        <v>881</v>
+      </c>
+      <c r="C314" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E314" t="s">
+        <v>34</v>
+      </c>
+      <c r="F314" s="4" t="s">
         <v>2197</v>
-      </c>
-      <c r="C314" t="s">
-        <v>2198</v>
-      </c>
-      <c r="D314" s="3" t="s">
-        <v>2199</v>
-      </c>
-      <c r="E314" t="s">
-        <v>67</v>
-      </c>
-      <c r="F314" s="4" t="s">
-        <v>2200</v>
       </c>
       <c r="G314">
         <v>8</v>
       </c>
       <c r="H314" t="s">
-        <v>2186</v>
+        <v>2198</v>
       </c>
       <c r="I314">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J314" t="s">
-        <v>2187</v>
+        <v>2199</v>
       </c>
       <c r="K314" t="s">
-        <v>28</v>
+        <v>2200</v>
       </c>
       <c r="L314" t="s">
-        <v>28</v>
+        <v>2201</v>
       </c>
       <c r="M314" t="s">
         <v>26</v>
@@ -23676,45 +23658,45 @@
         <v>28</v>
       </c>
       <c r="P314" t="s">
-        <v>29</v>
+        <v>889</v>
       </c>
     </row>
     <row r="315" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>880</v>
+        <v>1316</v>
       </c>
       <c r="B315" t="s">
-        <v>881</v>
+        <v>2202</v>
       </c>
       <c r="C315" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="E315" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="G315">
         <v>8</v>
       </c>
       <c r="H315" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="I315">
         <v>77</v>
       </c>
       <c r="J315" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="K315" t="s">
-        <v>2206</v>
+        <v>28</v>
       </c>
       <c r="L315" t="s">
-        <v>2207</v>
+        <v>28</v>
       </c>
       <c r="M315" t="s">
         <v>26</v>
@@ -23726,51 +23708,51 @@
         <v>28</v>
       </c>
       <c r="P315" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1316</v>
+        <v>1350</v>
       </c>
       <c r="B316" t="s">
+        <v>920</v>
+      </c>
+      <c r="C316" t="s">
         <v>2208</v>
       </c>
-      <c r="C316" t="s">
+      <c r="D316" s="3" t="s">
         <v>2209</v>
       </c>
-      <c r="D316" s="3" t="s">
+      <c r="E316" t="s">
+        <v>923</v>
+      </c>
+      <c r="F316" s="4" t="s">
         <v>2210</v>
-      </c>
-      <c r="E316" t="s">
-        <v>67</v>
-      </c>
-      <c r="F316" s="4" t="s">
-        <v>2211</v>
       </c>
       <c r="G316">
         <v>8</v>
       </c>
       <c r="H316" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="I316">
         <v>77</v>
       </c>
       <c r="J316" t="s">
+        <v>2212</v>
+      </c>
+      <c r="K316" t="s">
         <v>2213</v>
       </c>
-      <c r="K316" t="s">
-        <v>28</v>
-      </c>
       <c r="L316" t="s">
-        <v>28</v>
+        <v>2214</v>
       </c>
       <c r="M316" t="s">
         <v>26</v>
       </c>
       <c r="N316" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O316" t="s">
         <v>28</v>
@@ -23781,46 +23763,46 @@
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>1350</v>
+        <v>120</v>
       </c>
       <c r="B317" t="s">
-        <v>920</v>
+        <v>2215</v>
       </c>
       <c r="C317" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="E317" t="s">
-        <v>923</v>
+        <v>67</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="G317">
         <v>8</v>
       </c>
       <c r="H317" t="s">
-        <v>2217</v>
+        <v>2206</v>
       </c>
       <c r="I317">
         <v>77</v>
       </c>
       <c r="J317" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="K317" t="s">
-        <v>2219</v>
+        <v>28</v>
       </c>
       <c r="L317" t="s">
-        <v>2220</v>
+        <v>28</v>
       </c>
       <c r="M317" t="s">
         <v>26</v>
       </c>
       <c r="N317" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O317" t="s">
         <v>28</v>
@@ -23831,34 +23813,34 @@
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>120</v>
+        <v>1571</v>
       </c>
       <c r="B318" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C318" t="s">
+        <v>404</v>
+      </c>
+      <c r="D318" s="3" t="s">
         <v>2221</v>
       </c>
-      <c r="C318" t="s">
+      <c r="E318" t="s">
+        <v>28</v>
+      </c>
+      <c r="F318" s="4" t="s">
         <v>2222</v>
-      </c>
-      <c r="D318" s="3" t="s">
-        <v>2223</v>
-      </c>
-      <c r="E318" t="s">
-        <v>67</v>
-      </c>
-      <c r="F318" s="4" t="s">
-        <v>2224</v>
       </c>
       <c r="G318">
         <v>8</v>
       </c>
       <c r="H318" t="s">
-        <v>2212</v>
+        <v>2223</v>
       </c>
       <c r="I318">
         <v>77</v>
       </c>
       <c r="J318" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="K318" t="s">
         <v>28</v>
@@ -23884,16 +23866,16 @@
         <v>1571</v>
       </c>
       <c r="B319" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C319" t="s">
         <v>2226</v>
-      </c>
-      <c r="C319" t="s">
-        <v>404</v>
       </c>
       <c r="D319" s="3" t="s">
         <v>2227</v>
       </c>
       <c r="E319" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>2228</v>
@@ -23931,34 +23913,34 @@
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1571</v>
+        <v>446</v>
       </c>
       <c r="B320" t="s">
         <v>2231</v>
       </c>
       <c r="C320" t="s">
+        <v>404</v>
+      </c>
+      <c r="D320" s="3" t="s">
         <v>2232</v>
-      </c>
-      <c r="D320" s="3" t="s">
-        <v>2233</v>
       </c>
       <c r="E320" t="s">
         <v>20</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="G320">
         <v>8</v>
       </c>
       <c r="H320" t="s">
-        <v>2235</v>
+        <v>2206</v>
       </c>
       <c r="I320">
         <v>77</v>
       </c>
       <c r="J320" t="s">
-        <v>2236</v>
+        <v>2181</v>
       </c>
       <c r="K320" t="s">
         <v>28</v>
@@ -23981,34 +23963,34 @@
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>446</v>
+        <v>858</v>
       </c>
       <c r="B321" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C321" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="E321" t="s">
+        <v>67</v>
+      </c>
+      <c r="F321" s="4" t="s">
         <v>2237</v>
-      </c>
-      <c r="C321" t="s">
-        <v>404</v>
-      </c>
-      <c r="D321" s="3" t="s">
-        <v>2238</v>
-      </c>
-      <c r="E321" t="s">
-        <v>20</v>
-      </c>
-      <c r="F321" s="4" t="s">
-        <v>2239</v>
       </c>
       <c r="G321">
         <v>8</v>
       </c>
       <c r="H321" t="s">
-        <v>2212</v>
+        <v>2238</v>
       </c>
       <c r="I321">
         <v>77</v>
       </c>
       <c r="J321" t="s">
-        <v>2187</v>
+        <v>2239</v>
       </c>
       <c r="K321" t="s">
         <v>28</v>
@@ -24020,7 +24002,7 @@
         <v>26</v>
       </c>
       <c r="N321" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O321" t="s">
         <v>28</v>
@@ -24031,7 +24013,7 @@
     </row>
     <row r="322" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>858</v>
+        <v>30</v>
       </c>
       <c r="B322" t="s">
         <v>2240</v>
@@ -24043,7 +24025,7 @@
         <v>2242</v>
       </c>
       <c r="E322" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>2243</v>
@@ -24052,13 +24034,13 @@
         <v>8</v>
       </c>
       <c r="H322" t="s">
-        <v>2244</v>
+        <v>2206</v>
       </c>
       <c r="I322">
         <v>77</v>
       </c>
       <c r="J322" t="s">
-        <v>2245</v>
+        <v>1648</v>
       </c>
       <c r="K322" t="s">
         <v>28</v>
@@ -24070,7 +24052,7 @@
         <v>26</v>
       </c>
       <c r="N322" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O322" t="s">
         <v>28</v>
@@ -24081,34 +24063,34 @@
     </row>
     <row r="323" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="B323" t="s">
+        <v>488</v>
+      </c>
+      <c r="C323" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E323" t="s">
+        <v>34</v>
+      </c>
+      <c r="F323" s="4" t="s">
         <v>2246</v>
-      </c>
-      <c r="C323" t="s">
-        <v>2247</v>
-      </c>
-      <c r="D323" s="3" t="s">
-        <v>2248</v>
-      </c>
-      <c r="E323" t="s">
-        <v>20</v>
-      </c>
-      <c r="F323" s="4" t="s">
-        <v>2249</v>
       </c>
       <c r="G323">
         <v>8</v>
       </c>
       <c r="H323" t="s">
-        <v>2212</v>
+        <v>2206</v>
       </c>
       <c r="I323">
         <v>77</v>
       </c>
       <c r="J323" t="s">
-        <v>1648</v>
+        <v>2247</v>
       </c>
       <c r="K323" t="s">
         <v>28</v>
@@ -24134,31 +24116,31 @@
         <v>206</v>
       </c>
       <c r="B324" t="s">
-        <v>488</v>
+        <v>655</v>
       </c>
       <c r="C324" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E324" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F324" s="4" t="s">
         <v>2250</v>
-      </c>
-      <c r="D324" s="3" t="s">
-        <v>2251</v>
-      </c>
-      <c r="E324" t="s">
-        <v>34</v>
-      </c>
-      <c r="F324" s="4" t="s">
-        <v>2252</v>
       </c>
       <c r="G324">
         <v>8</v>
       </c>
       <c r="H324" t="s">
-        <v>2212</v>
+        <v>2223</v>
       </c>
       <c r="I324">
         <v>77</v>
       </c>
       <c r="J324" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="K324" t="s">
         <v>28</v>
@@ -24181,40 +24163,40 @@
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>206</v>
+        <v>880</v>
       </c>
       <c r="B325" t="s">
-        <v>655</v>
+        <v>2252</v>
       </c>
       <c r="C325" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D325" s="3" t="s">
         <v>2254</v>
       </c>
-      <c r="D325" s="3" t="s">
+      <c r="E325" t="s">
+        <v>20</v>
+      </c>
+      <c r="F325" s="4" t="s">
         <v>2255</v>
-      </c>
-      <c r="E325" t="s">
-        <v>2032</v>
-      </c>
-      <c r="F325" s="4" t="s">
-        <v>2256</v>
       </c>
       <c r="G325">
         <v>8</v>
       </c>
       <c r="H325" t="s">
-        <v>2229</v>
+        <v>2256</v>
       </c>
       <c r="I325">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J325" t="s">
         <v>2257</v>
       </c>
       <c r="K325" t="s">
-        <v>28</v>
+        <v>2258</v>
       </c>
       <c r="L325" t="s">
-        <v>28</v>
+        <v>2259</v>
       </c>
       <c r="M325" t="s">
         <v>26</v>
@@ -24226,7 +24208,7 @@
         <v>28</v>
       </c>
       <c r="P325" t="s">
-        <v>29</v>
+        <v>889</v>
       </c>
     </row>
     <row r="326" spans="1:16" x14ac:dyDescent="0.25">
@@ -24234,16 +24216,16 @@
         <v>880</v>
       </c>
       <c r="B326" t="s">
-        <v>2258</v>
+        <v>881</v>
       </c>
       <c r="C326" t="s">
-        <v>2259</v>
+        <v>305</v>
       </c>
       <c r="D326" s="3" t="s">
         <v>2260</v>
       </c>
       <c r="E326" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>2261</v>
@@ -24252,19 +24234,19 @@
         <v>8</v>
       </c>
       <c r="H326" t="s">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="I326">
         <v>76</v>
       </c>
       <c r="J326" t="s">
+        <v>2262</v>
+      </c>
+      <c r="K326" t="s">
         <v>2263</v>
       </c>
-      <c r="K326" t="s">
+      <c r="L326" t="s">
         <v>2264</v>
-      </c>
-      <c r="L326" t="s">
-        <v>2265</v>
       </c>
       <c r="M326" t="s">
         <v>26</v>
@@ -24287,34 +24269,34 @@
         <v>881</v>
       </c>
       <c r="C327" t="s">
-        <v>305</v>
+        <v>2265</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>2266</v>
+        <v>2196</v>
       </c>
       <c r="E327" t="s">
         <v>34</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="G327">
         <v>8</v>
       </c>
       <c r="H327" t="s">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="I327">
         <v>76</v>
       </c>
       <c r="J327" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K327" t="s">
         <v>2268</v>
       </c>
-      <c r="K327" t="s">
+      <c r="L327" t="s">
         <v>2269</v>
-      </c>
-      <c r="L327" t="s">
-        <v>2270</v>
       </c>
       <c r="M327" t="s">
         <v>26</v>
@@ -24331,40 +24313,40 @@
     </row>
     <row r="328" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>880</v>
+        <v>844</v>
       </c>
       <c r="B328" t="s">
-        <v>881</v>
+        <v>2270</v>
       </c>
       <c r="C328" t="s">
         <v>2271</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>2202</v>
+        <v>2272</v>
       </c>
       <c r="E328" t="s">
-        <v>34</v>
-      </c>
-      <c r="F328" s="4" t="s">
-        <v>2272</v>
+        <v>2273</v>
+      </c>
+      <c r="F328" t="s">
+        <v>2274</v>
       </c>
       <c r="G328">
         <v>8</v>
       </c>
       <c r="H328" t="s">
-        <v>2262</v>
+        <v>2275</v>
       </c>
       <c r="I328">
         <v>76</v>
       </c>
       <c r="J328" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
       <c r="K328" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="L328" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="M328" t="s">
         <v>26</v>
@@ -24376,45 +24358,45 @@
         <v>28</v>
       </c>
       <c r="P328" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
     </row>
     <row r="329" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>844</v>
+        <v>137</v>
       </c>
       <c r="B329" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
       <c r="C329" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="E329" t="s">
-        <v>2279</v>
-      </c>
-      <c r="F329" t="s">
-        <v>2280</v>
+        <v>20</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>2282</v>
       </c>
       <c r="G329">
         <v>8</v>
       </c>
       <c r="H329" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="I329">
         <v>76</v>
       </c>
       <c r="J329" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="K329" t="s">
-        <v>2283</v>
+        <v>28</v>
       </c>
       <c r="L329" t="s">
-        <v>2284</v>
+        <v>28</v>
       </c>
       <c r="M329" t="s">
         <v>26</v>
@@ -24431,7 +24413,7 @@
     </row>
     <row r="330" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="B330" t="s">
         <v>2285</v>
@@ -24443,7 +24425,7 @@
         <v>2287</v>
       </c>
       <c r="E330" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>2288</v>
@@ -24481,7 +24463,7 @@
     </row>
     <row r="331" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="B331" t="s">
         <v>2291</v>
@@ -24493,7 +24475,7 @@
         <v>2293</v>
       </c>
       <c r="E331" t="s">
-        <v>114</v>
+        <v>620</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>2294</v>
@@ -24508,7 +24490,7 @@
         <v>76</v>
       </c>
       <c r="J331" t="s">
-        <v>2296</v>
+        <v>2185</v>
       </c>
       <c r="K331" t="s">
         <v>28</v>
@@ -24531,34 +24513,34 @@
     </row>
     <row r="332" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>206</v>
+        <v>16</v>
       </c>
       <c r="B332" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C332" t="s">
+        <v>679</v>
+      </c>
+      <c r="D332" s="3" t="s">
         <v>2297</v>
       </c>
-      <c r="C332" t="s">
+      <c r="E332" t="s">
+        <v>805</v>
+      </c>
+      <c r="F332" s="4" t="s">
         <v>2298</v>
-      </c>
-      <c r="D332" s="3" t="s">
-        <v>2299</v>
-      </c>
-      <c r="E332" t="s">
-        <v>620</v>
-      </c>
-      <c r="F332" s="4" t="s">
-        <v>2300</v>
       </c>
       <c r="G332">
         <v>8</v>
       </c>
       <c r="H332" t="s">
-        <v>2301</v>
+        <v>2295</v>
       </c>
       <c r="I332">
         <v>76</v>
       </c>
       <c r="J332" t="s">
-        <v>2191</v>
+        <v>2299</v>
       </c>
       <c r="K332" t="s">
         <v>28</v>
@@ -24581,52 +24563,52 @@
     </row>
     <row r="333" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>16</v>
+        <v>880</v>
       </c>
       <c r="B333" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C333" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E333" t="s">
+        <v>67</v>
+      </c>
+      <c r="F333" s="4" t="s">
         <v>2302</v>
-      </c>
-      <c r="C333" t="s">
-        <v>679</v>
-      </c>
-      <c r="D333" s="3" t="s">
-        <v>2303</v>
-      </c>
-      <c r="E333" t="s">
-        <v>805</v>
-      </c>
-      <c r="F333" s="4" t="s">
-        <v>2304</v>
       </c>
       <c r="G333">
         <v>8</v>
       </c>
       <c r="H333" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="I333">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J333" t="s">
+        <v>2304</v>
+      </c>
+      <c r="K333" t="s">
         <v>2305</v>
       </c>
-      <c r="K333" t="s">
-        <v>28</v>
-      </c>
       <c r="L333" t="s">
-        <v>28</v>
+        <v>2306</v>
       </c>
       <c r="M333" t="s">
-        <v>26</v>
+        <v>1417</v>
       </c>
       <c r="N333" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O333" t="s">
-        <v>28</v>
+        <v>2307</v>
       </c>
       <c r="P333" t="s">
-        <v>29</v>
+        <v>889</v>
       </c>
     </row>
     <row r="334" spans="1:16" x14ac:dyDescent="0.25">
@@ -24634,46 +24616,46 @@
         <v>880</v>
       </c>
       <c r="B334" t="s">
-        <v>2306</v>
+        <v>881</v>
       </c>
       <c r="C334" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>28</v>
+        <v>2309</v>
       </c>
       <c r="E334" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F334" s="4" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="G334">
         <v>8</v>
       </c>
       <c r="H334" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="I334">
         <v>75</v>
       </c>
       <c r="J334" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="K334" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="L334" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="M334" t="s">
-        <v>1417</v>
+        <v>26</v>
       </c>
       <c r="N334" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O334" t="s">
-        <v>2313</v>
+        <v>28</v>
       </c>
       <c r="P334" t="s">
         <v>889</v>
@@ -24681,28 +24663,28 @@
     </row>
     <row r="335" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>880</v>
+        <v>2315</v>
       </c>
       <c r="B335" t="s">
-        <v>881</v>
+        <v>2300</v>
       </c>
       <c r="C335" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>2315</v>
+        <v>28</v>
       </c>
       <c r="E335" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="G335">
         <v>8</v>
       </c>
       <c r="H335" t="s">
-        <v>2317</v>
+        <v>2303</v>
       </c>
       <c r="I335">
         <v>75</v>
@@ -24717,13 +24699,13 @@
         <v>2320</v>
       </c>
       <c r="M335" t="s">
-        <v>26</v>
+        <v>1417</v>
       </c>
       <c r="N335" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O335" t="s">
-        <v>28</v>
+        <v>2307</v>
       </c>
       <c r="P335" t="s">
         <v>889</v>
@@ -24731,57 +24713,57 @@
     </row>
     <row r="336" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>243</v>
+      </c>
+      <c r="B336" t="s">
         <v>2321</v>
-      </c>
-      <c r="B336" t="s">
-        <v>2306</v>
       </c>
       <c r="C336" t="s">
         <v>2322</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>28</v>
+        <v>2323</v>
       </c>
       <c r="E336" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F336" s="4" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G336">
         <v>8</v>
       </c>
       <c r="H336" t="s">
-        <v>2309</v>
+        <v>2325</v>
       </c>
       <c r="I336">
         <v>75</v>
       </c>
       <c r="J336" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="K336" t="s">
-        <v>2325</v>
+        <v>28</v>
       </c>
       <c r="L336" t="s">
-        <v>2326</v>
+        <v>28</v>
       </c>
       <c r="M336" t="s">
-        <v>1417</v>
+        <v>26</v>
       </c>
       <c r="N336" t="s">
         <v>83</v>
       </c>
       <c r="O336" t="s">
-        <v>2313</v>
+        <v>28</v>
       </c>
       <c r="P336" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
     </row>
     <row r="337" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>243</v>
+        <v>1300</v>
       </c>
       <c r="B337" t="s">
         <v>2327</v>
@@ -24808,7 +24790,7 @@
         <v>75</v>
       </c>
       <c r="J337" t="s">
-        <v>2332</v>
+        <v>1769</v>
       </c>
       <c r="K337" t="s">
         <v>28</v>
@@ -24820,7 +24802,7 @@
         <v>26</v>
       </c>
       <c r="N337" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O337" t="s">
         <v>28</v>
@@ -24831,34 +24813,34 @@
     </row>
     <row r="338" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>1300</v>
+        <v>206</v>
       </c>
       <c r="B338" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C338" t="s">
         <v>2333</v>
       </c>
-      <c r="C338" t="s">
+      <c r="D338" s="3" t="s">
         <v>2334</v>
       </c>
-      <c r="D338" s="3" t="s">
+      <c r="E338" t="s">
+        <v>413</v>
+      </c>
+      <c r="F338" s="4" t="s">
         <v>2335</v>
-      </c>
-      <c r="E338" t="s">
-        <v>34</v>
-      </c>
-      <c r="F338" s="4" t="s">
-        <v>2336</v>
       </c>
       <c r="G338">
         <v>8</v>
       </c>
       <c r="H338" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="I338">
         <v>75</v>
       </c>
       <c r="J338" t="s">
-        <v>1769</v>
+        <v>2337</v>
       </c>
       <c r="K338" t="s">
         <v>28</v>
@@ -24884,31 +24866,31 @@
         <v>206</v>
       </c>
       <c r="B339" t="s">
+        <v>763</v>
+      </c>
+      <c r="C339" t="s">
         <v>2338</v>
       </c>
-      <c r="C339" t="s">
+      <c r="D339" s="3" t="s">
         <v>2339</v>
       </c>
-      <c r="D339" s="3" t="s">
+      <c r="E339" t="s">
+        <v>77</v>
+      </c>
+      <c r="F339" s="4" t="s">
         <v>2340</v>
       </c>
-      <c r="E339" t="s">
-        <v>413</v>
-      </c>
-      <c r="F339" s="4" t="s">
+      <c r="G339">
+        <v>7</v>
+      </c>
+      <c r="H339" t="s">
         <v>2341</v>
       </c>
-      <c r="G339">
-        <v>8</v>
-      </c>
-      <c r="H339" t="s">
+      <c r="I339">
+        <v>74</v>
+      </c>
+      <c r="J339" t="s">
         <v>2342</v>
-      </c>
-      <c r="I339">
-        <v>75</v>
-      </c>
-      <c r="J339" t="s">
-        <v>2343</v>
       </c>
       <c r="K339" t="s">
         <v>28</v>
@@ -24931,40 +24913,40 @@
     </row>
     <row r="340" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>206</v>
+        <v>880</v>
       </c>
       <c r="B340" t="s">
-        <v>763</v>
+        <v>881</v>
       </c>
       <c r="C340" t="s">
+        <v>2343</v>
+      </c>
+      <c r="D340" s="3" t="s">
         <v>2344</v>
       </c>
-      <c r="D340" s="3" t="s">
+      <c r="E340" t="s">
+        <v>34</v>
+      </c>
+      <c r="F340" s="4" t="s">
         <v>2345</v>
-      </c>
-      <c r="E340" t="s">
-        <v>77</v>
-      </c>
-      <c r="F340" s="4" t="s">
-        <v>2346</v>
       </c>
       <c r="G340">
         <v>7</v>
       </c>
       <c r="H340" t="s">
+        <v>2346</v>
+      </c>
+      <c r="I340">
+        <v>73</v>
+      </c>
+      <c r="J340" t="s">
         <v>2347</v>
       </c>
-      <c r="I340">
-        <v>74</v>
-      </c>
-      <c r="J340" t="s">
+      <c r="K340" t="s">
         <v>2348</v>
       </c>
-      <c r="K340" t="s">
-        <v>28</v>
-      </c>
       <c r="L340" t="s">
-        <v>28</v>
+        <v>2349</v>
       </c>
       <c r="M340" t="s">
         <v>26</v>
@@ -24976,7 +24958,7 @@
         <v>28</v>
       </c>
       <c r="P340" t="s">
-        <v>29</v>
+        <v>889</v>
       </c>
     </row>
     <row r="341" spans="1:16" x14ac:dyDescent="0.25">
@@ -24984,40 +24966,40 @@
         <v>880</v>
       </c>
       <c r="B341" t="s">
-        <v>881</v>
+        <v>2350</v>
       </c>
       <c r="C341" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="E341" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="F341" s="4" t="s">
-        <v>2351</v>
+        <v>658</v>
       </c>
       <c r="G341">
         <v>7</v>
       </c>
       <c r="H341" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="I341">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J341" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="K341" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="L341" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="M341" t="s">
-        <v>26</v>
+        <v>2152</v>
       </c>
       <c r="N341" t="s">
         <v>27</v>
@@ -25034,7 +25016,7 @@
         <v>880</v>
       </c>
       <c r="B342" t="s">
-        <v>2356</v>
+        <v>881</v>
       </c>
       <c r="C342" t="s">
         <v>2357</v>
@@ -25043,31 +25025,31 @@
         <v>2358</v>
       </c>
       <c r="E342" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F342" s="4" t="s">
-        <v>658</v>
+        <v>2359</v>
       </c>
       <c r="G342">
         <v>7</v>
       </c>
       <c r="H342" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="I342">
         <v>72</v>
       </c>
       <c r="J342" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="K342" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="L342" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="M342" t="s">
-        <v>2158</v>
+        <v>26</v>
       </c>
       <c r="N342" t="s">
         <v>27</v>
@@ -25084,40 +25066,40 @@
         <v>880</v>
       </c>
       <c r="B343" t="s">
-        <v>881</v>
+        <v>1793</v>
       </c>
       <c r="C343" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>2364</v>
+        <v>28</v>
       </c>
       <c r="E343" t="s">
         <v>34</v>
       </c>
       <c r="F343" s="4" t="s">
-        <v>2365</v>
+        <v>1795</v>
       </c>
       <c r="G343">
         <v>7</v>
       </c>
       <c r="H343" t="s">
+        <v>2365</v>
+      </c>
+      <c r="I343">
+        <v>71</v>
+      </c>
+      <c r="J343" t="s">
         <v>2366</v>
       </c>
-      <c r="I343">
-        <v>72</v>
-      </c>
-      <c r="J343" t="s">
+      <c r="K343" t="s">
         <v>2367</v>
       </c>
-      <c r="K343" t="s">
+      <c r="L343" t="s">
         <v>2368</v>
       </c>
-      <c r="L343" t="s">
-        <v>2369</v>
-      </c>
       <c r="M343" t="s">
-        <v>26</v>
+        <v>563</v>
       </c>
       <c r="N343" t="s">
         <v>27</v>
@@ -25134,40 +25116,40 @@
         <v>880</v>
       </c>
       <c r="B344" t="s">
-        <v>1793</v>
+        <v>881</v>
       </c>
       <c r="C344" t="s">
+        <v>2369</v>
+      </c>
+      <c r="D344" s="3" t="s">
         <v>2370</v>
-      </c>
-      <c r="D344" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="E344" t="s">
         <v>34</v>
       </c>
       <c r="F344" s="4" t="s">
-        <v>1795</v>
+        <v>2371</v>
       </c>
       <c r="G344">
         <v>7</v>
       </c>
       <c r="H344" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="I344">
         <v>71</v>
       </c>
       <c r="J344" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="K344" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="L344" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="M344" t="s">
-        <v>563</v>
+        <v>26</v>
       </c>
       <c r="N344" t="s">
         <v>27</v>
@@ -25187,22 +25169,22 @@
         <v>881</v>
       </c>
       <c r="C345" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="E345" t="s">
         <v>34</v>
       </c>
       <c r="F345" s="4" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="G345">
         <v>7</v>
       </c>
       <c r="H345" t="s">
-        <v>2378</v>
+        <v>2372</v>
       </c>
       <c r="I345">
         <v>71</v>
@@ -25252,7 +25234,7 @@
         <v>7</v>
       </c>
       <c r="H346" t="s">
-        <v>2378</v>
+        <v>2372</v>
       </c>
       <c r="I346">
         <v>71</v>
@@ -25281,84 +25263,84 @@
     </row>
     <row r="347" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>880</v>
+        <v>2388</v>
       </c>
       <c r="B347" t="s">
-        <v>881</v>
+        <v>2389</v>
       </c>
       <c r="C347" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="E347" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="F347" s="4" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="G347">
         <v>7</v>
       </c>
       <c r="H347" t="s">
-        <v>2378</v>
+        <v>2393</v>
       </c>
       <c r="I347">
         <v>71</v>
       </c>
       <c r="J347" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="K347" t="s">
-        <v>2392</v>
+        <v>28</v>
       </c>
       <c r="L347" t="s">
-        <v>2393</v>
+        <v>28</v>
       </c>
       <c r="M347" t="s">
         <v>26</v>
       </c>
       <c r="N347" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O347" t="s">
         <v>28</v>
       </c>
       <c r="P347" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="B348" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="C348" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="E348" t="s">
-        <v>67</v>
+        <v>1021</v>
       </c>
       <c r="F348" s="4" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="G348">
         <v>7</v>
       </c>
       <c r="H348" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="I348">
         <v>71</v>
       </c>
       <c r="J348" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="K348" t="s">
         <v>28</v>
@@ -25370,7 +25352,7 @@
         <v>26</v>
       </c>
       <c r="N348" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O348" t="s">
         <v>28</v>
@@ -25381,43 +25363,43 @@
     </row>
     <row r="349" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>2401</v>
+        <v>880</v>
       </c>
       <c r="B349" t="s">
+        <v>881</v>
+      </c>
+      <c r="C349" t="s">
         <v>2402</v>
       </c>
-      <c r="C349" t="s">
+      <c r="D349" s="3" t="s">
         <v>2403</v>
       </c>
-      <c r="D349" s="3" t="s">
+      <c r="E349" t="s">
+        <v>34</v>
+      </c>
+      <c r="F349" s="4" t="s">
         <v>2404</v>
-      </c>
-      <c r="E349" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F349" s="4" t="s">
-        <v>2405</v>
       </c>
       <c r="G349">
         <v>7</v>
       </c>
       <c r="H349" t="s">
+        <v>2405</v>
+      </c>
+      <c r="I349">
+        <v>70</v>
+      </c>
+      <c r="J349" t="s">
         <v>2406</v>
       </c>
-      <c r="I349">
-        <v>71</v>
-      </c>
-      <c r="J349" t="s">
+      <c r="K349" t="s">
         <v>2407</v>
       </c>
-      <c r="K349" t="s">
-        <v>28</v>
-      </c>
       <c r="L349" t="s">
-        <v>28</v>
+        <v>2408</v>
       </c>
       <c r="M349" t="s">
-        <v>26</v>
+        <v>2152</v>
       </c>
       <c r="N349" t="s">
         <v>27</v>
@@ -25426,48 +25408,48 @@
         <v>28</v>
       </c>
       <c r="P349" t="s">
-        <v>29</v>
+        <v>889</v>
       </c>
     </row>
     <row r="350" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>880</v>
+        <v>1571</v>
       </c>
       <c r="B350" t="s">
-        <v>881</v>
+        <v>2409</v>
       </c>
       <c r="C350" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="E350" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F350" s="4" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="G350">
         <v>7</v>
       </c>
       <c r="H350" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="I350">
         <v>70</v>
       </c>
       <c r="J350" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="K350" t="s">
-        <v>2413</v>
+        <v>28</v>
       </c>
       <c r="L350" t="s">
-        <v>2414</v>
+        <v>28</v>
       </c>
       <c r="M350" t="s">
-        <v>2158</v>
+        <v>26</v>
       </c>
       <c r="N350" t="s">
         <v>27</v>
@@ -25476,15 +25458,15 @@
         <v>28</v>
       </c>
       <c r="P350" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
     </row>
     <row r="351" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1571</v>
+        <v>2415</v>
       </c>
       <c r="B351" t="s">
-        <v>2415</v>
+        <v>28</v>
       </c>
       <c r="C351" t="s">
         <v>2416</v>
@@ -25493,7 +25475,7 @@
         <v>2417</v>
       </c>
       <c r="E351" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="F351" s="4" t="s">
         <v>2418</v>
@@ -25505,16 +25487,16 @@
         <v>2419</v>
       </c>
       <c r="I351">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J351" t="s">
         <v>2420</v>
       </c>
       <c r="K351" t="s">
-        <v>28</v>
+        <v>2421</v>
       </c>
       <c r="L351" t="s">
-        <v>28</v>
+        <v>2422</v>
       </c>
       <c r="M351" t="s">
         <v>26</v>
@@ -25526,33 +25508,33 @@
         <v>28</v>
       </c>
       <c r="P351" t="s">
-        <v>29</v>
+        <v>889</v>
       </c>
     </row>
     <row r="352" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>2421</v>
+        <v>880</v>
       </c>
       <c r="B352" t="s">
-        <v>28</v>
+        <v>881</v>
       </c>
       <c r="C352" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="E352" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F352" s="4" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="G352">
         <v>7</v>
       </c>
       <c r="H352" t="s">
-        <v>2425</v>
+        <v>2419</v>
       </c>
       <c r="I352">
         <v>69</v>
@@ -25584,7 +25566,7 @@
         <v>880</v>
       </c>
       <c r="B353" t="s">
-        <v>881</v>
+        <v>2252</v>
       </c>
       <c r="C353" t="s">
         <v>2429</v>
@@ -25593,7 +25575,7 @@
         <v>2430</v>
       </c>
       <c r="E353" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F353" s="4" t="s">
         <v>2431</v>
@@ -25602,19 +25584,19 @@
         <v>7</v>
       </c>
       <c r="H353" t="s">
-        <v>2425</v>
+        <v>2432</v>
       </c>
       <c r="I353">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J353" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="K353" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="L353" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="M353" t="s">
         <v>26</v>
@@ -25631,49 +25613,49 @@
     </row>
     <row r="354" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>880</v>
+        <v>2315</v>
       </c>
       <c r="B354" t="s">
-        <v>2258</v>
+        <v>2436</v>
       </c>
       <c r="C354" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>2436</v>
+        <v>28</v>
       </c>
       <c r="E354" t="s">
         <v>20</v>
       </c>
       <c r="F354" s="4" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="G354">
         <v>7</v>
       </c>
       <c r="H354" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="I354">
         <v>68</v>
       </c>
       <c r="J354" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="K354" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="L354" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="M354" t="s">
-        <v>26</v>
+        <v>1417</v>
       </c>
       <c r="N354" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O354" t="s">
-        <v>28</v>
+        <v>2443</v>
       </c>
       <c r="P354" t="s">
         <v>889</v>
@@ -25681,69 +25663,69 @@
     </row>
     <row r="355" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>2321</v>
+        <v>1203</v>
       </c>
       <c r="B355" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="C355" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>28</v>
+        <v>2446</v>
       </c>
       <c r="E355" t="s">
         <v>20</v>
       </c>
       <c r="F355" s="4" t="s">
-        <v>2444</v>
+        <v>2447</v>
       </c>
       <c r="G355">
         <v>7</v>
       </c>
       <c r="H355" t="s">
-        <v>2445</v>
+        <v>2448</v>
       </c>
       <c r="I355">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J355" t="s">
-        <v>2446</v>
+        <v>2449</v>
       </c>
       <c r="K355" t="s">
-        <v>2447</v>
+        <v>2450</v>
       </c>
       <c r="L355" t="s">
-        <v>2448</v>
+        <v>2451</v>
       </c>
       <c r="M355" t="s">
-        <v>1417</v>
+        <v>26</v>
       </c>
       <c r="N355" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O355" t="s">
-        <v>2449</v>
+        <v>28</v>
       </c>
       <c r="P355" t="s">
-        <v>889</v>
+        <v>29</v>
       </c>
     </row>
     <row r="356" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1203</v>
+        <v>2315</v>
       </c>
       <c r="B356" t="s">
-        <v>2450</v>
+        <v>161</v>
       </c>
       <c r="C356" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>2452</v>
+        <v>28</v>
       </c>
       <c r="E356" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="F356" s="4" t="s">
         <v>2453</v>
@@ -25755,7 +25737,7 @@
         <v>2454</v>
       </c>
       <c r="I356">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J356" t="s">
         <v>2455</v>
@@ -25767,63 +25749,63 @@
         <v>2457</v>
       </c>
       <c r="M356" t="s">
-        <v>26</v>
+        <v>1417</v>
       </c>
       <c r="N356" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O356" t="s">
-        <v>28</v>
+        <v>2458</v>
       </c>
       <c r="P356" t="s">
-        <v>29</v>
+        <v>889</v>
       </c>
     </row>
     <row r="357" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>2321</v>
+        <v>2415</v>
       </c>
       <c r="B357" t="s">
-        <v>161</v>
+        <v>1371</v>
       </c>
       <c r="C357" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>28</v>
+        <v>2460</v>
       </c>
       <c r="E357" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="F357" s="4" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="G357">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H357" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="I357">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J357" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="K357" t="s">
-        <v>2462</v>
+        <v>28</v>
       </c>
       <c r="L357" t="s">
-        <v>2463</v>
+        <v>28</v>
       </c>
       <c r="M357" t="s">
-        <v>1417</v>
+        <v>2464</v>
       </c>
       <c r="N357" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O357" t="s">
-        <v>2464</v>
+        <v>28</v>
       </c>
       <c r="P357" t="s">
         <v>889</v>
@@ -25831,10 +25813,10 @@
     </row>
     <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>2421</v>
+        <v>880</v>
       </c>
       <c r="B358" t="s">
-        <v>1371</v>
+        <v>2350</v>
       </c>
       <c r="C358" t="s">
         <v>2465</v>
@@ -25843,22 +25825,22 @@
         <v>2466</v>
       </c>
       <c r="E358" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="F358" s="4" t="s">
-        <v>2467</v>
+        <v>658</v>
       </c>
       <c r="G358">
         <v>6</v>
       </c>
       <c r="H358" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
       <c r="I358">
         <v>64</v>
       </c>
       <c r="J358" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="K358" t="s">
         <v>28</v>
@@ -25867,7 +25849,7 @@
         <v>28</v>
       </c>
       <c r="M358" t="s">
-        <v>2470</v>
+        <v>2464</v>
       </c>
       <c r="N358" t="s">
         <v>27</v>
@@ -25884,31 +25866,31 @@
         <v>880</v>
       </c>
       <c r="B359" t="s">
-        <v>2356</v>
+        <v>1371</v>
       </c>
       <c r="C359" t="s">
-        <v>2471</v>
+        <v>2459</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>2472</v>
+        <v>2460</v>
       </c>
       <c r="E359" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="F359" s="4" t="s">
-        <v>658</v>
+        <v>2468</v>
       </c>
       <c r="G359">
         <v>6</v>
       </c>
       <c r="H359" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
       <c r="I359">
         <v>64</v>
       </c>
       <c r="J359" t="s">
-        <v>2473</v>
+        <v>2469</v>
       </c>
       <c r="K359" t="s">
         <v>28</v>
@@ -25917,7 +25899,7 @@
         <v>28</v>
       </c>
       <c r="M359" t="s">
-        <v>2470</v>
+        <v>2464</v>
       </c>
       <c r="N359" t="s">
         <v>27</v>
@@ -25931,31 +25913,31 @@
     </row>
     <row r="360" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>880</v>
+        <v>2415</v>
       </c>
       <c r="B360" t="s">
-        <v>1371</v>
+        <v>2470</v>
       </c>
       <c r="C360" t="s">
-        <v>2465</v>
+        <v>2471</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>2466</v>
+        <v>2472</v>
       </c>
       <c r="E360" t="s">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="F360" s="4" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G360">
+        <v>3</v>
+      </c>
+      <c r="H360" t="s">
         <v>2474</v>
       </c>
-      <c r="G360">
-        <v>6</v>
-      </c>
-      <c r="H360" t="s">
-        <v>2468</v>
-      </c>
       <c r="I360">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="J360" t="s">
         <v>2475</v>
@@ -25967,7 +25949,7 @@
         <v>28</v>
       </c>
       <c r="M360" t="s">
-        <v>2470</v>
+        <v>26</v>
       </c>
       <c r="N360" t="s">
         <v>27</v>
@@ -25976,56 +25958,6 @@
         <v>28</v>
       </c>
       <c r="P360" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A361" t="s">
-        <v>2421</v>
-      </c>
-      <c r="B361" t="s">
-        <v>2476</v>
-      </c>
-      <c r="C361" t="s">
-        <v>2477</v>
-      </c>
-      <c r="D361" s="3" t="s">
-        <v>2478</v>
-      </c>
-      <c r="E361" t="s">
-        <v>413</v>
-      </c>
-      <c r="F361" s="4" t="s">
-        <v>2479</v>
-      </c>
-      <c r="G361">
-        <v>3</v>
-      </c>
-      <c r="H361" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I361">
-        <v>30</v>
-      </c>
-      <c r="J361" t="s">
-        <v>2481</v>
-      </c>
-      <c r="K361" t="s">
-        <v>28</v>
-      </c>
-      <c r="L361" t="s">
-        <v>28</v>
-      </c>
-      <c r="M361" t="s">
-        <v>26</v>
-      </c>
-      <c r="N361" t="s">
-        <v>27</v>
-      </c>
-      <c r="O361" t="s">
-        <v>28</v>
-      </c>
-      <c r="P361" t="s">
         <v>889</v>
       </c>
     </row>
@@ -26357,7 +26289,7 @@
     <hyperlink ref="F325" r:id="rId323"/>
     <hyperlink ref="F326" r:id="rId324"/>
     <hyperlink ref="F327" r:id="rId325"/>
-    <hyperlink ref="F328" r:id="rId326"/>
+    <hyperlink ref="F329" r:id="rId326"/>
     <hyperlink ref="F330" r:id="rId327"/>
     <hyperlink ref="F331" r:id="rId328"/>
     <hyperlink ref="F332" r:id="rId329"/>
@@ -26389,7 +26321,6 @@
     <hyperlink ref="F358" r:id="rId355"/>
     <hyperlink ref="F359" r:id="rId356"/>
     <hyperlink ref="F360" r:id="rId357"/>
-    <hyperlink ref="F361" r:id="rId358"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -26491,7 +26422,7 @@
         <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>2482</v>
+        <v>2476</v>
       </c>
       <c r="I2">
         <v>87</v>
@@ -26541,7 +26472,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -26550,16 +26481,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2484</v>
+        <v>2478</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2485</v>
+        <v>2479</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2486</v>
+        <v>2480</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2487</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -26573,10 +26504,10 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>2488</v>
+        <v>2482</v>
       </c>
       <c r="E2" t="s">
-        <v>2489</v>
+        <v>2483</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -26603,31 +26534,31 @@
   <sheetData>
     <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>2490</v>
+        <v>2484</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2491</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2492</v>
+        <v>2486</v>
       </c>
       <c r="B2" t="s">
-        <v>2421</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2493</v>
+        <v>2487</v>
       </c>
       <c r="B3">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2494</v>
+        <v>2488</v>
       </c>
       <c r="B4">
         <v>101</v>
@@ -26635,15 +26566,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2495</v>
+        <v>2489</v>
       </c>
       <c r="B5">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2496</v>
+        <v>2490</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -26651,7 +26582,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2497</v>
+        <v>2491</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -26659,7 +26590,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -26667,7 +26598,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2499</v>
+        <v>2493</v>
       </c>
       <c r="B9">
         <v>117</v>
@@ -26675,15 +26606,15 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2500</v>
+        <v>2494</v>
       </c>
       <c r="B10">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2501</v>
+        <v>2495</v>
       </c>
       <c r="B11">
         <v>57</v>
@@ -26691,7 +26622,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2502</v>
+        <v>2496</v>
       </c>
       <c r="B12">
         <v>9</v>
@@ -26699,7 +26630,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2503</v>
+        <v>2497</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -26707,48 +26638,48 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2504</v>
+        <v>2498</v>
       </c>
       <c r="B14" t="s">
-        <v>2505</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2506</v>
+        <v>2500</v>
       </c>
       <c r="B15" t="s">
-        <v>2507</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2508</v>
+        <v>2502</v>
       </c>
       <c r="B16" t="s">
-        <v>2509</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="18" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>2510</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2511</v>
+        <v>2505</v>
       </c>
       <c r="B19" t="s">
-        <v>2512</v>
+        <v>2506</v>
       </c>
       <c r="C19" t="s">
-        <v>2513</v>
+        <v>2507</v>
       </c>
       <c r="D19" t="s">
-        <v>2514</v>
+        <v>2508</v>
       </c>
       <c r="E19" t="s">
-        <v>2515</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
